--- a/data/HD_data.xlsx
+++ b/data/HD_data.xlsx
@@ -4719,7 +4719,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-06 05:35:20</t>
+          <t>2026-09-06 05:42:21</t>
         </is>
       </c>
     </row>

--- a/data/HD_data.xlsx
+++ b/data/HD_data.xlsx
@@ -4474,7 +4474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4595,25 +4595,45 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>book_value</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>price_to_book</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>earnings_growth</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>shares_outstanding</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -4649,7 +4669,7 @@
         <v>2259444</v>
       </c>
       <c r="I2" t="n">
-        <v>4231874</v>
+        <v>4200590</v>
       </c>
       <c r="J2" t="n">
         <v>320308248576</v>
@@ -4673,7 +4693,7 @@
         <v>0.955</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -4697,29 +4717,41 @@
       <c r="W2" t="n">
         <v>1.078</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X2" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>19.282282</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>997689626</v>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Home Improvement Retail</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>https://www.homedepot.com</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>The Home Depot, Inc. operates as a home improvement retailer in the United States and internationally. It sells various building materials, home improvement products, lawn and garden products, and décor products, as well as facilities maintenance, repair, and operations products. The company also offers installation services for flooring, water heaters, baths, garage doors, cabinets, cabinet makeovers, countertops, sheds, furnaces and central air systems, windows, and window coverings. In addition, it provides tool and equipment rental services. The company serves consumers, such as do-it-yourself homeowners and do-it-for-me customers; and professional renovators/remodelers, general contractors, homebuilders, maintenance professionals, handymen, property managers, building service contractors and specialty tradespeople, such as electricians, landscapers, insulation installers, plumbers, painters, pool contractors, roofers, and wallboard and ceiling installers. It sells its products through websites and its mobile applications, including homedepot.com; homedepot.ca and homedepot.com.mx; blinds.com, justblinds.com, and americanblinds.com for custom window coverings; constructionresourcesusa.com or design-oriented surfaces, appliances, and architectural specialty products; thecompanystore.com, an online site for textiles and décor products; hdsupply.com for maintenance, repair, and operations products and related services; and srsdistribution.com, heritagelandscapesupplygroup.com, heritagepoolsupplygroup.com, and gms.com for roofing and building materials, landscape, and pool products; and The Home Depot stores. The Home Depot, Inc. was incorporated in 1978 and is headquartered in Atlanta, Georgia.</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>2026-09-06 05:42:21</t>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>2026-09-06 16:10:24</t>
         </is>
       </c>
     </row>

--- a/data/HD_data.xlsx
+++ b/data/HD_data.xlsx
@@ -4751,7 +4751,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:10:24</t>
+          <t>2026-09-06 16:24:59</t>
         </is>
       </c>
     </row>

--- a/data/HD_data.xlsx
+++ b/data/HD_data.xlsx
@@ -4751,7 +4751,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:24:59</t>
+          <t>2026-09-06 16:34:54</t>
         </is>
       </c>
     </row>

--- a/data/HD_data.xlsx
+++ b/data/HD_data.xlsx
@@ -4751,7 +4751,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:34:54</t>
+          <t>2026-09-06 16:49:28</t>
         </is>
       </c>
     </row>

--- a/data/HD_data.xlsx
+++ b/data/HD_data.xlsx
@@ -4695,15 +4695,11 @@
       <c r="Q2" t="n">
         <v>2.9</v>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="R2" t="n">
+        <v>0.08409999999999999</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.12858</v>
       </c>
       <c r="T2" t="n">
         <v>1.0429599</v>
@@ -4751,7 +4747,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:49:28</t>
+          <t>2026-09-06 16:59:59</t>
         </is>
       </c>
     </row>

--- a/data/HD_data.xlsx
+++ b/data/HD_data.xlsx
@@ -4474,7 +4474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4615,25 +4615,40 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
+          <t>total_revenue</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -4725,29 +4740,38 @@
       <c r="AA2" t="n">
         <v>997689626</v>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB2" t="n">
+        <v>169176006656</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>381411262464</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>24647999488</v>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Home Improvement Retail</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>https://www.homedepot.com</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>The Home Depot, Inc. operates as a home improvement retailer in the United States and internationally. It sells various building materials, home improvement products, lawn and garden products, and décor products, as well as facilities maintenance, repair, and operations products. The company also offers installation services for flooring, water heaters, baths, garage doors, cabinets, cabinet makeovers, countertops, sheds, furnaces and central air systems, windows, and window coverings. In addition, it provides tool and equipment rental services. The company serves consumers, such as do-it-yourself homeowners and do-it-for-me customers; and professional renovators/remodelers, general contractors, homebuilders, maintenance professionals, handymen, property managers, building service contractors and specialty tradespeople, such as electricians, landscapers, insulation installers, plumbers, painters, pool contractors, roofers, and wallboard and ceiling installers. It sells its products through websites and its mobile applications, including homedepot.com; homedepot.ca and homedepot.com.mx; blinds.com, justblinds.com, and americanblinds.com for custom window coverings; constructionresourcesusa.com or design-oriented surfaces, appliances, and architectural specialty products; thecompanystore.com, an online site for textiles and décor products; hdsupply.com for maintenance, repair, and operations products and related services; and srsdistribution.com, heritagelandscapesupplygroup.com, heritagepoolsupplygroup.com, and gms.com for roofing and building materials, landscape, and pool products; and The Home Depot stores. The Home Depot, Inc. was incorporated in 1978 and is headquartered in Atlanta, Georgia.</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>2026-09-06 16:59:59</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2026-09-06 22:21:04</t>
         </is>
       </c>
     </row>

--- a/data/HD_data.xlsx
+++ b/data/HD_data.xlsx
@@ -4771,7 +4771,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:21:04</t>
+          <t>2026-09-06 22:41:58</t>
         </is>
       </c>
     </row>

--- a/data/HD_data.xlsx
+++ b/data/HD_data.xlsx
@@ -4771,7 +4771,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:41:58</t>
+          <t>2026-09-06 22:59:53</t>
         </is>
       </c>
     </row>

--- a/data/HD_data.xlsx
+++ b/data/HD_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -433,22 +433,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Open</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Close</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -469,25 +469,17 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46239</v>
-      </c>
-      <c r="B2" t="n">
-        <v>347.5984599855233</v>
-      </c>
-      <c r="C2" t="n">
-        <v>351.9563298372728</v>
-      </c>
-      <c r="D2" t="n">
-        <v>345.6031541488199</v>
-      </c>
-      <c r="E2" t="n">
-        <v>350.5566711425781</v>
-      </c>
+        <v>45904</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>3140400</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -495,22 +487,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46240</v>
+        <v>45905</v>
       </c>
       <c r="B3" t="n">
-        <v>350.9140306560572</v>
+        <v>407.4126281738281</v>
       </c>
       <c r="C3" t="n">
-        <v>350.9636527717977</v>
+        <v>408.8226790956362</v>
       </c>
       <c r="D3" t="n">
-        <v>344.967859180145</v>
+        <v>402.6183719436316</v>
       </c>
       <c r="E3" t="n">
-        <v>346.963134765625</v>
+        <v>405.117604329066</v>
       </c>
       <c r="F3" t="n">
-        <v>2622400</v>
+        <v>5855600</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +513,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46241</v>
+        <v>45908</v>
       </c>
       <c r="B4" t="n">
-        <v>348.9386046403958</v>
+        <v>408.3753051757812</v>
       </c>
       <c r="C4" t="n">
-        <v>354.219664160909</v>
+        <v>408.9976648300841</v>
       </c>
       <c r="D4" t="n">
-        <v>346.1888486641563</v>
+        <v>404.3006909076745</v>
       </c>
       <c r="E4" t="n">
-        <v>353.0185241699219</v>
+        <v>406.974958857154</v>
       </c>
       <c r="F4" t="n">
-        <v>3584800</v>
+        <v>3742600</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +539,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46244</v>
+        <v>45909</v>
       </c>
       <c r="B5" t="n">
-        <v>349.524279261052</v>
+        <v>403.9019775390625</v>
       </c>
       <c r="C5" t="n">
-        <v>351.4103740800161</v>
+        <v>407.1889007063392</v>
       </c>
       <c r="D5" t="n">
-        <v>344.5211400290252</v>
+        <v>401.3833069272346</v>
       </c>
       <c r="E5" t="n">
-        <v>348.2139282226562</v>
+        <v>406.605418128494</v>
       </c>
       <c r="F5" t="n">
-        <v>3124800</v>
+        <v>3516000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +565,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46245</v>
+        <v>45910</v>
       </c>
       <c r="B6" t="n">
-        <v>349.7128894956296</v>
+        <v>401.85009765625</v>
       </c>
       <c r="C6" t="n">
-        <v>355.7384623950411</v>
+        <v>405.9344163339586</v>
       </c>
       <c r="D6" t="n">
-        <v>348.0352499864083</v>
+        <v>400.4011104850302</v>
       </c>
       <c r="E6" t="n">
-        <v>351.8868713378906</v>
+        <v>404.0770121335462</v>
       </c>
       <c r="F6" t="n">
-        <v>2549700</v>
+        <v>2897800</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +591,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46246</v>
+        <v>45911</v>
       </c>
       <c r="B7" t="n">
-        <v>349.4250091127092</v>
+        <v>411.7594604492188</v>
       </c>
       <c r="C7" t="n">
-        <v>351.2813246265272</v>
+        <v>413.5098784241463</v>
       </c>
       <c r="D7" t="n">
-        <v>340.5206262766717</v>
+        <v>402.8419797879972</v>
       </c>
       <c r="E7" t="n">
-        <v>340.9176940917969</v>
+        <v>404.2520601457455</v>
       </c>
       <c r="F7" t="n">
-        <v>3965800</v>
+        <v>5316400</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +617,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46247</v>
+        <v>45912</v>
       </c>
       <c r="B8" t="n">
-        <v>344.4615642861647</v>
+        <v>411.0495910644531</v>
       </c>
       <c r="C8" t="n">
-        <v>345.206077753642</v>
+        <v>411.8470163012535</v>
       </c>
       <c r="D8" t="n">
-        <v>338.0190507751135</v>
+        <v>407.3445165905575</v>
       </c>
       <c r="E8" t="n">
-        <v>339.2003479003906</v>
+        <v>408.6962221082555</v>
       </c>
       <c r="F8" t="n">
-        <v>2439900</v>
+        <v>5004200</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +643,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46248</v>
+        <v>45915</v>
       </c>
       <c r="B9" t="n">
-        <v>338.3168506868042</v>
+        <v>411.0690307617188</v>
       </c>
       <c r="C9" t="n">
-        <v>338.3168506868042</v>
+        <v>411.6427792599144</v>
       </c>
       <c r="D9" t="n">
-        <v>333.5519765191293</v>
+        <v>406.245631927433</v>
       </c>
       <c r="E9" t="n">
-        <v>336.381103515625</v>
+        <v>410.8356495901566</v>
       </c>
       <c r="F9" t="n">
-        <v>3073100</v>
+        <v>4884700</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +669,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46251</v>
+        <v>45916</v>
       </c>
       <c r="B10" t="n">
-        <v>332.2614710050206</v>
+        <v>409.84375</v>
       </c>
       <c r="C10" t="n">
-        <v>336.9568803095206</v>
+        <v>412.8389171851107</v>
       </c>
       <c r="D10" t="n">
-        <v>330.4548079641576</v>
+        <v>408.5211874475655</v>
       </c>
       <c r="E10" t="n">
-        <v>335.4082946777344</v>
+        <v>412.0803987002532</v>
       </c>
       <c r="F10" t="n">
-        <v>5580000</v>
+        <v>3726700</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +695,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46252</v>
+        <v>45917</v>
       </c>
       <c r="B11" t="n">
-        <v>334.3163510292147</v>
+        <v>405.5162658691406</v>
       </c>
       <c r="C11" t="n">
-        <v>342.0195939717831</v>
+        <v>414.9977612941385</v>
       </c>
       <c r="D11" t="n">
-        <v>328.2709048600699</v>
+        <v>404.3590348225837</v>
       </c>
       <c r="E11" t="n">
-        <v>335.0211486816406</v>
+        <v>412.7513785983885</v>
       </c>
       <c r="F11" t="n">
-        <v>6603400</v>
+        <v>4771700</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +721,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46253</v>
+        <v>45918</v>
       </c>
       <c r="B12" t="n">
-        <v>338.9224047058033</v>
+        <v>405.9830627441406</v>
       </c>
       <c r="C12" t="n">
-        <v>347.8366934263856</v>
+        <v>409.7853891317768</v>
       </c>
       <c r="D12" t="n">
-        <v>338.9224047058033</v>
+        <v>404.4076508642465</v>
       </c>
       <c r="E12" t="n">
-        <v>341.7813110351562</v>
+        <v>406.0511124651653</v>
       </c>
       <c r="F12" t="n">
-        <v>4971000</v>
+        <v>3677200</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +747,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46254</v>
+        <v>45919</v>
       </c>
       <c r="B13" t="n">
-        <v>333.542054389882</v>
+        <v>404.2423400878906</v>
       </c>
       <c r="C13" t="n">
-        <v>336.4009911317456</v>
+        <v>407.0527371169607</v>
       </c>
       <c r="D13" t="n">
-        <v>329.1643112906949</v>
+        <v>403.6685916242002</v>
       </c>
       <c r="E13" t="n">
-        <v>332.0430908203125</v>
+        <v>405.8760675448892</v>
       </c>
       <c r="F13" t="n">
-        <v>4027700</v>
+        <v>6718400</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +773,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46255</v>
+        <v>45922</v>
       </c>
       <c r="B14" t="n">
-        <v>334.0582233645888</v>
+        <v>400.6539611816406</v>
       </c>
       <c r="C14" t="n">
-        <v>336.1031512946537</v>
+        <v>403.4546538139739</v>
       </c>
       <c r="D14" t="n">
-        <v>330.5639843459303</v>
+        <v>399.8079247983643</v>
       </c>
       <c r="E14" t="n">
-        <v>333.1548767089844</v>
+        <v>402.7058397960551</v>
       </c>
       <c r="F14" t="n">
-        <v>3422800</v>
+        <v>2656300</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +799,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46258</v>
+        <v>45923</v>
       </c>
       <c r="B15" t="n">
-        <v>333.4229292601251</v>
+        <v>399.593994140625</v>
       </c>
       <c r="C15" t="n">
-        <v>339.7165463845368</v>
+        <v>402.3363415649943</v>
       </c>
       <c r="D15" t="n">
-        <v>332.7081950914107</v>
+        <v>396.2389914749436</v>
       </c>
       <c r="E15" t="n">
-        <v>334.9615783691406</v>
+        <v>400.6539731783087</v>
       </c>
       <c r="F15" t="n">
-        <v>3298600</v>
+        <v>2597000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +825,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46259</v>
+        <v>45924</v>
       </c>
       <c r="B16" t="n">
-        <v>336.8873851133212</v>
+        <v>398.4853820800781</v>
       </c>
       <c r="C16" t="n">
-        <v>337.0065024243307</v>
+        <v>399.3411526132105</v>
       </c>
       <c r="D16" t="n">
-        <v>331.2588801078031</v>
+        <v>393.856487333743</v>
       </c>
       <c r="E16" t="n">
-        <v>335.4082946777344</v>
+        <v>395.5874669386123</v>
       </c>
       <c r="F16" t="n">
-        <v>2528100</v>
+        <v>3220700</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +851,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46260</v>
+        <v>45925</v>
       </c>
       <c r="B17" t="n">
-        <v>336.9469338983794</v>
+        <v>396.2292785644531</v>
       </c>
       <c r="C17" t="n">
-        <v>336.9568704387829</v>
+        <v>399.5453447284057</v>
       </c>
       <c r="D17" t="n">
-        <v>332.0629425240725</v>
+        <v>394.4399240629465</v>
       </c>
       <c r="E17" t="n">
-        <v>332.4004516601562</v>
+        <v>395.4512918948509</v>
       </c>
       <c r="F17" t="n">
-        <v>4258100</v>
+        <v>2554300</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +877,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46261</v>
+        <v>45926</v>
       </c>
       <c r="B18" t="n">
-        <v>328.1517689125653</v>
+        <v>398.7965698242188</v>
       </c>
       <c r="C18" t="n">
-        <v>329.5812372185705</v>
+        <v>400.08022560159</v>
       </c>
       <c r="D18" t="n">
-        <v>325.4814448058147</v>
+        <v>394.6636101400317</v>
       </c>
       <c r="E18" t="n">
-        <v>326.2060852050781</v>
+        <v>396.9197270195646</v>
       </c>
       <c r="F18" t="n">
-        <v>3618000</v>
+        <v>2316600</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +903,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46262</v>
+        <v>45929</v>
       </c>
       <c r="B19" t="n">
-        <v>328.0822659405567</v>
+        <v>395.59716796875</v>
       </c>
       <c r="C19" t="n">
-        <v>329.1841313242223</v>
+        <v>399.6329053199512</v>
       </c>
       <c r="D19" t="n">
-        <v>325.1042120893565</v>
+        <v>392.7284254984301</v>
       </c>
       <c r="E19" t="n">
-        <v>327.7745361328125</v>
+        <v>398.7576665785797</v>
       </c>
       <c r="F19" t="n">
-        <v>3136100</v>
+        <v>3008400</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +929,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46265</v>
+        <v>45930</v>
       </c>
       <c r="B20" t="n">
-        <v>325.838797551875</v>
+        <v>394.0315246582031</v>
       </c>
       <c r="C20" t="n">
-        <v>326.8414187355763</v>
+        <v>395.7916769160157</v>
       </c>
       <c r="D20" t="n">
-        <v>323.3670224847805</v>
+        <v>392.3686244480866</v>
       </c>
       <c r="E20" t="n">
-        <v>325.4317932128906</v>
+        <v>395.4318710489828</v>
       </c>
       <c r="F20" t="n">
-        <v>3858700</v>
+        <v>3211600</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +955,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46266</v>
+        <v>45931</v>
       </c>
       <c r="B21" t="n">
-        <v>323.6251283531417</v>
+        <v>386.0865173339844</v>
       </c>
       <c r="C21" t="n">
-        <v>324.439106732169</v>
+        <v>393.9731927384614</v>
       </c>
       <c r="D21" t="n">
-        <v>316.4678503051231</v>
+        <v>384.4236170674206</v>
       </c>
       <c r="E21" t="n">
-        <v>317.4307556152344</v>
+        <v>393.2535809799684</v>
       </c>
       <c r="F21" t="n">
-        <v>3291000</v>
+        <v>3787800</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +981,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46267</v>
+        <v>45932</v>
       </c>
       <c r="B22" t="n">
-        <v>319.1481100391916</v>
+        <v>384.1318969726562</v>
       </c>
       <c r="C22" t="n">
-        <v>319.813222073911</v>
+        <v>386.4366252014962</v>
       </c>
       <c r="D22" t="n">
-        <v>315.3858267914646</v>
+        <v>382.9454931559638</v>
       </c>
       <c r="E22" t="n">
-        <v>316.1799926757812</v>
+        <v>384.6083934501511</v>
       </c>
       <c r="F22" t="n">
-        <v>3499300</v>
+        <v>2964700</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,25 +1007,25 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46268</v>
+        <v>45933</v>
       </c>
       <c r="B23" t="n">
-        <v>318.2099914550781</v>
+        <v>384.1805114746094</v>
       </c>
       <c r="C23" t="n">
-        <v>320.4400024414062</v>
+        <v>386.3782832385467</v>
       </c>
       <c r="D23" t="n">
-        <v>315.2099914550781</v>
+        <v>381.8174379292481</v>
       </c>
       <c r="E23" t="n">
-        <v>318.0700073242188</v>
+        <v>383.2761296995442</v>
       </c>
       <c r="F23" t="n">
-        <v>3377700</v>
+        <v>2951300</v>
       </c>
       <c r="G23" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1041,27 +1033,6007 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B24" t="n">
+        <v>378.6082458496094</v>
+      </c>
+      <c r="C24" t="n">
+        <v>383.6358825136301</v>
+      </c>
+      <c r="D24" t="n">
+        <v>375.0976757198047</v>
+      </c>
+      <c r="E24" t="n">
+        <v>383.6358825136301</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3653700</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B25" t="n">
+        <v>376.1576538085938</v>
+      </c>
+      <c r="C25" t="n">
+        <v>379.0166916502498</v>
+      </c>
+      <c r="D25" t="n">
+        <v>374.8934663230858</v>
+      </c>
+      <c r="E25" t="n">
+        <v>378.7249652081036</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2505700</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B26" t="n">
+        <v>373.2208251953125</v>
+      </c>
+      <c r="C26" t="n">
+        <v>375.8172795135579</v>
+      </c>
+      <c r="D26" t="n">
+        <v>372.4331341390219</v>
+      </c>
+      <c r="E26" t="n">
+        <v>375.8172795135579</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2517600</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B27" t="n">
+        <v>367.2888488769531</v>
+      </c>
+      <c r="C27" t="n">
+        <v>373.7751480356932</v>
+      </c>
+      <c r="D27" t="n">
+        <v>367.0651721318674</v>
+      </c>
+      <c r="E27" t="n">
+        <v>372.3553630865562</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3321400</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B28" t="n">
+        <v>365.4022521972656</v>
+      </c>
+      <c r="C28" t="n">
+        <v>369.7880611814068</v>
+      </c>
+      <c r="D28" t="n">
+        <v>364.4589637589981</v>
+      </c>
+      <c r="E28" t="n">
+        <v>369.7880611814068</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2992400</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B29" t="n">
+        <v>368.9225463867188</v>
+      </c>
+      <c r="C29" t="n">
+        <v>371.7815842680138</v>
+      </c>
+      <c r="D29" t="n">
+        <v>366.8025884053155</v>
+      </c>
+      <c r="E29" t="n">
+        <v>368.6308199405279</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2925900</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B30" t="n">
+        <v>377.0426025390625</v>
+      </c>
+      <c r="C30" t="n">
+        <v>378.1803950347029</v>
+      </c>
+      <c r="D30" t="n">
+        <v>367.6000139768833</v>
+      </c>
+      <c r="E30" t="n">
+        <v>368.4363162416045</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4399900</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B31" t="n">
+        <v>377.6066589355469</v>
+      </c>
+      <c r="C31" t="n">
+        <v>383.509505336445</v>
+      </c>
+      <c r="D31" t="n">
+        <v>376.0799174593716</v>
+      </c>
+      <c r="E31" t="n">
+        <v>378.5110703746846</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3690100</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B32" t="n">
+        <v>376.7217407226562</v>
+      </c>
+      <c r="C32" t="n">
+        <v>379.259850089759</v>
+      </c>
+      <c r="D32" t="n">
+        <v>373.3959105177652</v>
+      </c>
+      <c r="E32" t="n">
+        <v>378.9292168586321</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2783700</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B33" t="n">
+        <v>381.1075134277344</v>
+      </c>
+      <c r="C33" t="n">
+        <v>382.2841830931986</v>
+      </c>
+      <c r="D33" t="n">
+        <v>376.5369638928536</v>
+      </c>
+      <c r="E33" t="n">
+        <v>377.8011514993366</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2657700</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B34" t="n">
+        <v>378.180419921875</v>
+      </c>
+      <c r="C34" t="n">
+        <v>382.3522567670641</v>
+      </c>
+      <c r="D34" t="n">
+        <v>377.4024332180988</v>
+      </c>
+      <c r="E34" t="n">
+        <v>380.6310112651639</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2761100</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B35" t="n">
+        <v>380.1350402832031</v>
+      </c>
+      <c r="C35" t="n">
+        <v>382.7898697855445</v>
+      </c>
+      <c r="D35" t="n">
+        <v>375.2338280008644</v>
+      </c>
+      <c r="E35" t="n">
+        <v>376.8870237514197</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2306900</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B36" t="n">
+        <v>378.2582092285156</v>
+      </c>
+      <c r="C36" t="n">
+        <v>382.225837605147</v>
+      </c>
+      <c r="D36" t="n">
+        <v>377.4802521906377</v>
+      </c>
+      <c r="E36" t="n">
+        <v>380.4754194313423</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2857000</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B37" t="n">
+        <v>374.4266662597656</v>
+      </c>
+      <c r="C37" t="n">
+        <v>378.0150498065191</v>
+      </c>
+      <c r="D37" t="n">
+        <v>370.7993759625135</v>
+      </c>
+      <c r="E37" t="n">
+        <v>376.468840342194</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2767300</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B38" t="n">
+        <v>376.03125</v>
+      </c>
+      <c r="C38" t="n">
+        <v>378.9681015073717</v>
+      </c>
+      <c r="D38" t="n">
+        <v>375.0490844721456</v>
+      </c>
+      <c r="E38" t="n">
+        <v>378.9681015073717</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2426800</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B39" t="n">
+        <v>374.6600952148438</v>
+      </c>
+      <c r="C39" t="n">
+        <v>378.5694080170153</v>
+      </c>
+      <c r="D39" t="n">
+        <v>372.3553670460668</v>
+      </c>
+      <c r="E39" t="n">
+        <v>377.0231983553949</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3065800</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B40" t="n">
+        <v>375.1268920898438</v>
+      </c>
+      <c r="C40" t="n">
+        <v>379.2695861239365</v>
+      </c>
+      <c r="D40" t="n">
+        <v>372.2872924475712</v>
+      </c>
+      <c r="E40" t="n">
+        <v>373.8335318063046</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2372800</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B41" t="n">
+        <v>367.6292114257812</v>
+      </c>
+      <c r="C41" t="n">
+        <v>374.3975325355203</v>
+      </c>
+      <c r="D41" t="n">
+        <v>364.8674253963886</v>
+      </c>
+      <c r="E41" t="n">
+        <v>372.4526102885826</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3852300</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B42" t="n">
+        <v>369.0975952148438</v>
+      </c>
+      <c r="C42" t="n">
+        <v>374.1057935751742</v>
+      </c>
+      <c r="D42" t="n">
+        <v>365.7523266876615</v>
+      </c>
+      <c r="E42" t="n">
+        <v>367.3082703686788</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2384300</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B43" t="n">
+        <v>369.1365356445312</v>
+      </c>
+      <c r="C43" t="n">
+        <v>370.4493641725706</v>
+      </c>
+      <c r="D43" t="n">
+        <v>364.6826764994138</v>
+      </c>
+      <c r="E43" t="n">
+        <v>366.5789579935506</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2643500</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B44" t="n">
+        <v>367.9306640625</v>
+      </c>
+      <c r="C44" t="n">
+        <v>368.0570887541689</v>
+      </c>
+      <c r="D44" t="n">
+        <v>363.3892576559226</v>
+      </c>
+      <c r="E44" t="n">
+        <v>366.6275697464224</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2897600</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B45" t="n">
+        <v>372.5303955078125</v>
+      </c>
+      <c r="C45" t="n">
+        <v>373.1138781194984</v>
+      </c>
+      <c r="D45" t="n">
+        <v>366.3747296312804</v>
+      </c>
+      <c r="E45" t="n">
+        <v>366.9582122429663</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2590000</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B46" t="n">
+        <v>363.5448608398438</v>
+      </c>
+      <c r="C46" t="n">
+        <v>372.8610549707219</v>
+      </c>
+      <c r="D46" t="n">
+        <v>360.3260169130116</v>
+      </c>
+      <c r="E46" t="n">
+        <v>372.2483997179557</v>
+      </c>
+      <c r="F46" t="n">
+        <v>4763000</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B47" t="n">
+        <v>358.90625</v>
+      </c>
+      <c r="C47" t="n">
+        <v>362.3973820280062</v>
+      </c>
+      <c r="D47" t="n">
+        <v>357.4280900328899</v>
+      </c>
+      <c r="E47" t="n">
+        <v>361.5805182090473</v>
+      </c>
+      <c r="F47" t="n">
+        <v>3622100</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B48" t="n">
+        <v>360.8900451660156</v>
+      </c>
+      <c r="C48" t="n">
+        <v>363.3601048105454</v>
+      </c>
+      <c r="D48" t="n">
+        <v>357.4475540431628</v>
+      </c>
+      <c r="E48" t="n">
+        <v>358.8284322647385</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2766400</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B49" t="n">
+        <v>360.2287902832031</v>
+      </c>
+      <c r="C49" t="n">
+        <v>360.452467039932</v>
+      </c>
+      <c r="D49" t="n">
+        <v>353.4410301931099</v>
+      </c>
+      <c r="E49" t="n">
+        <v>359.6064305558101</v>
+      </c>
+      <c r="F49" t="n">
+        <v>3257900</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B50" t="n">
+        <v>363.933837890625</v>
+      </c>
+      <c r="C50" t="n">
+        <v>365.6453789483504</v>
+      </c>
+      <c r="D50" t="n">
+        <v>360.6955554382075</v>
+      </c>
+      <c r="E50" t="n">
+        <v>361.7458003836202</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2407300</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B51" t="n">
+        <v>360.9094543457031</v>
+      </c>
+      <c r="C51" t="n">
+        <v>363.2725274444605</v>
+      </c>
+      <c r="D51" t="n">
+        <v>358.8478417816602</v>
+      </c>
+      <c r="E51" t="n">
+        <v>361.8138359498466</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3375800</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B52" t="n">
+        <v>357.9337768554688</v>
+      </c>
+      <c r="C52" t="n">
+        <v>363.2336722315698</v>
+      </c>
+      <c r="D52" t="n">
+        <v>356.5236963397476</v>
+      </c>
+      <c r="E52" t="n">
+        <v>361.4249087666506</v>
+      </c>
+      <c r="F52" t="n">
+        <v>3034800</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B53" t="n">
+        <v>352.3810119628906</v>
+      </c>
+      <c r="C53" t="n">
+        <v>357.2141451188847</v>
+      </c>
+      <c r="D53" t="n">
+        <v>349.8915137655536</v>
+      </c>
+      <c r="E53" t="n">
+        <v>355.8332668898346</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3413300</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B54" t="n">
+        <v>348.1702270507812</v>
+      </c>
+      <c r="C54" t="n">
+        <v>353.7618780642933</v>
+      </c>
+      <c r="D54" t="n">
+        <v>346.2933843548503</v>
+      </c>
+      <c r="E54" t="n">
+        <v>351.1848622282798</v>
+      </c>
+      <c r="F54" t="n">
+        <v>5127200</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B55" t="n">
+        <v>327.2137145996094</v>
+      </c>
+      <c r="C55" t="n">
+        <v>339.1944125402241</v>
+      </c>
+      <c r="D55" t="n">
+        <v>326.7566567053178</v>
+      </c>
+      <c r="E55" t="n">
+        <v>330.6173283766702</v>
+      </c>
+      <c r="F55" t="n">
+        <v>10168500</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B56" t="n">
+        <v>325.2882385253906</v>
+      </c>
+      <c r="C56" t="n">
+        <v>332.3385815128617</v>
+      </c>
+      <c r="D56" t="n">
+        <v>322.2444305286613</v>
+      </c>
+      <c r="E56" t="n">
+        <v>331.5800630406063</v>
+      </c>
+      <c r="F56" t="n">
+        <v>7595000</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B57" t="n">
+        <v>323.2266540527344</v>
+      </c>
+      <c r="C57" t="n">
+        <v>329.567090307595</v>
+      </c>
+      <c r="D57" t="n">
+        <v>322.9835387560075</v>
+      </c>
+      <c r="E57" t="n">
+        <v>327.0970305832446</v>
+      </c>
+      <c r="F57" t="n">
+        <v>4025300</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B58" t="n">
+        <v>333.8653869628906</v>
+      </c>
+      <c r="C58" t="n">
+        <v>337.3662532252054</v>
+      </c>
+      <c r="D58" t="n">
+        <v>323.8295802366419</v>
+      </c>
+      <c r="E58" t="n">
+        <v>325.356351446162</v>
+      </c>
+      <c r="F58" t="n">
+        <v>7441300</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B59" t="n">
+        <v>327.3109436035156</v>
+      </c>
+      <c r="C59" t="n">
+        <v>334.2445959868845</v>
+      </c>
+      <c r="D59" t="n">
+        <v>327.2817709576355</v>
+      </c>
+      <c r="E59" t="n">
+        <v>332.7761999080408</v>
+      </c>
+      <c r="F59" t="n">
+        <v>6132900</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B60" t="n">
+        <v>341.4019470214844</v>
+      </c>
+      <c r="C60" t="n">
+        <v>343.2787899402826</v>
+      </c>
+      <c r="D60" t="n">
+        <v>329.5184704432642</v>
+      </c>
+      <c r="E60" t="n">
+        <v>329.6643336820279</v>
+      </c>
+      <c r="F60" t="n">
+        <v>6316600</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B61" t="n">
+        <v>345.6807556152344</v>
+      </c>
+      <c r="C61" t="n">
+        <v>347.4895190539308</v>
+      </c>
+      <c r="D61" t="n">
+        <v>339.3889309798961</v>
+      </c>
+      <c r="E61" t="n">
+        <v>340.6142414881474</v>
+      </c>
+      <c r="F61" t="n">
+        <v>4517300</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B62" t="n">
+        <v>347.0908203125</v>
+      </c>
+      <c r="C62" t="n">
+        <v>347.975733775784</v>
+      </c>
+      <c r="D62" t="n">
+        <v>343.7649903745483</v>
+      </c>
+      <c r="E62" t="n">
+        <v>345.1556025907452</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2119600</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B63" t="n">
+        <v>347.4895324707031</v>
+      </c>
+      <c r="C63" t="n">
+        <v>352.3129611811121</v>
+      </c>
+      <c r="D63" t="n">
+        <v>343.1620981246396</v>
+      </c>
+      <c r="E63" t="n">
+        <v>344.2998610600955</v>
+      </c>
+      <c r="F63" t="n">
+        <v>5107100</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B64" t="n">
+        <v>344.2803955078125</v>
+      </c>
+      <c r="C64" t="n">
+        <v>347.654836647816</v>
+      </c>
+      <c r="D64" t="n">
+        <v>341.6255660714526</v>
+      </c>
+      <c r="E64" t="n">
+        <v>347.0032746652403</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3965300</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B65" t="n">
+        <v>348.0535583496094</v>
+      </c>
+      <c r="C65" t="n">
+        <v>350.5430564092279</v>
+      </c>
+      <c r="D65" t="n">
+        <v>344.0081165834399</v>
+      </c>
+      <c r="E65" t="n">
+        <v>344.7374624136521</v>
+      </c>
+      <c r="F65" t="n">
+        <v>4166700</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B66" t="n">
+        <v>343.7079467773438</v>
+      </c>
+      <c r="C66" t="n">
+        <v>349.9132235394517</v>
+      </c>
+      <c r="D66" t="n">
+        <v>342.5627951482988</v>
+      </c>
+      <c r="E66" t="n">
+        <v>348.7191463158849</v>
+      </c>
+      <c r="F66" t="n">
+        <v>4022800</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B67" t="n">
+        <v>347.0747985839844</v>
+      </c>
+      <c r="C67" t="n">
+        <v>348.0633464265518</v>
+      </c>
+      <c r="D67" t="n">
+        <v>342.1027577808173</v>
+      </c>
+      <c r="E67" t="n">
+        <v>343.1989538716508</v>
+      </c>
+      <c r="F67" t="n">
+        <v>5959200</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B68" t="n">
+        <v>342.4747009277344</v>
+      </c>
+      <c r="C68" t="n">
+        <v>344.6083705337733</v>
+      </c>
+      <c r="D68" t="n">
+        <v>338.3541683639427</v>
+      </c>
+      <c r="E68" t="n">
+        <v>344.471360951741</v>
+      </c>
+      <c r="F68" t="n">
+        <v>7273000</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B69" t="n">
+        <v>337.9332580566406</v>
+      </c>
+      <c r="C69" t="n">
+        <v>349.0910404146574</v>
+      </c>
+      <c r="D69" t="n">
+        <v>337.6298477160418</v>
+      </c>
+      <c r="E69" t="n">
+        <v>340.3703677160696</v>
+      </c>
+      <c r="F69" t="n">
+        <v>5063100</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B70" t="n">
+        <v>343.6687316894531</v>
+      </c>
+      <c r="C70" t="n">
+        <v>344.5398042643482</v>
+      </c>
+      <c r="D70" t="n">
+        <v>336.6902345489607</v>
+      </c>
+      <c r="E70" t="n">
+        <v>336.7881155909637</v>
+      </c>
+      <c r="F70" t="n">
+        <v>6316100</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B71" t="n">
+        <v>349.8642272949219</v>
+      </c>
+      <c r="C71" t="n">
+        <v>355.0124656886035</v>
+      </c>
+      <c r="D71" t="n">
+        <v>346.4190354810299</v>
+      </c>
+      <c r="E71" t="n">
+        <v>348.4352595936447</v>
+      </c>
+      <c r="F71" t="n">
+        <v>6609800</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B72" t="n">
+        <v>352.0077209472656</v>
+      </c>
+      <c r="C72" t="n">
+        <v>353.0941498724499</v>
+      </c>
+      <c r="D72" t="n">
+        <v>348.4842120764174</v>
+      </c>
+      <c r="E72" t="n">
+        <v>351.6260236653551</v>
+      </c>
+      <c r="F72" t="n">
+        <v>3861200</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B73" t="n">
+        <v>349.4042358398438</v>
+      </c>
+      <c r="C73" t="n">
+        <v>354.9635630414982</v>
+      </c>
+      <c r="D73" t="n">
+        <v>348.0633520332391</v>
+      </c>
+      <c r="E73" t="n">
+        <v>351.753261637015</v>
+      </c>
+      <c r="F73" t="n">
+        <v>4387400</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B74" t="n">
+        <v>345.185791015625</v>
+      </c>
+      <c r="C74" t="n">
+        <v>351.1170178905755</v>
+      </c>
+      <c r="D74" t="n">
+        <v>344.334282682454</v>
+      </c>
+      <c r="E74" t="n">
+        <v>349.3161201800424</v>
+      </c>
+      <c r="F74" t="n">
+        <v>3497200</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B75" t="n">
+        <v>349.1693115234375</v>
+      </c>
+      <c r="C75" t="n">
+        <v>349.9033745469626</v>
+      </c>
+      <c r="D75" t="n">
+        <v>343.5219307486607</v>
+      </c>
+      <c r="E75" t="n">
+        <v>344.4908843816016</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3875200</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B76" t="n">
+        <v>347.4467468261719</v>
+      </c>
+      <c r="C76" t="n">
+        <v>358.5164162998122</v>
+      </c>
+      <c r="D76" t="n">
+        <v>347.0258911387745</v>
+      </c>
+      <c r="E76" t="n">
+        <v>355.8150843258923</v>
+      </c>
+      <c r="F76" t="n">
+        <v>4805200</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B77" t="n">
+        <v>337.6690063476562</v>
+      </c>
+      <c r="C77" t="n">
+        <v>346.5854112795514</v>
+      </c>
+      <c r="D77" t="n">
+        <v>337.5907194306183</v>
+      </c>
+      <c r="E77" t="n">
+        <v>346.5854112795514</v>
+      </c>
+      <c r="F77" t="n">
+        <v>12825600</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B78" t="n">
+        <v>339.0295104980469</v>
+      </c>
+      <c r="C78" t="n">
+        <v>340.5074039236039</v>
+      </c>
+      <c r="D78" t="n">
+        <v>336.3966684056612</v>
+      </c>
+      <c r="E78" t="n">
+        <v>337.9724428869297</v>
+      </c>
+      <c r="F78" t="n">
+        <v>3523700</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B79" t="n">
+        <v>337.6396484375</v>
+      </c>
+      <c r="C79" t="n">
+        <v>340.1158866476816</v>
+      </c>
+      <c r="D79" t="n">
+        <v>334.6740348508469</v>
+      </c>
+      <c r="E79" t="n">
+        <v>336.6902590123812</v>
+      </c>
+      <c r="F79" t="n">
+        <v>3873400</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B80" t="n">
+        <v>339.9592895507812</v>
+      </c>
+      <c r="C80" t="n">
+        <v>340.8597534033964</v>
+      </c>
+      <c r="D80" t="n">
+        <v>336.592384505686</v>
+      </c>
+      <c r="E80" t="n">
+        <v>337.0230372348798</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1368600</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B81" t="n">
+        <v>342.3474426269531</v>
+      </c>
+      <c r="C81" t="n">
+        <v>342.6116945815832</v>
+      </c>
+      <c r="D81" t="n">
+        <v>339.2056610232721</v>
+      </c>
+      <c r="E81" t="n">
+        <v>339.6167196193633</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1786900</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B82" t="n">
+        <v>340.0669555664062</v>
+      </c>
+      <c r="C82" t="n">
+        <v>342.8759654029374</v>
+      </c>
+      <c r="D82" t="n">
+        <v>337.4243166284915</v>
+      </c>
+      <c r="E82" t="n">
+        <v>342.5627579984686</v>
+      </c>
+      <c r="F82" t="n">
+        <v>3790000</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B83" t="n">
+        <v>338.9903564453125</v>
+      </c>
+      <c r="C83" t="n">
+        <v>339.6069742481806</v>
+      </c>
+      <c r="D83" t="n">
+        <v>336.4162369795515</v>
+      </c>
+      <c r="E83" t="n">
+        <v>338.6771490106644</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2392600</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B84" t="n">
+        <v>336.7881469726562</v>
+      </c>
+      <c r="C84" t="n">
+        <v>339.342672153089</v>
+      </c>
+      <c r="D84" t="n">
+        <v>336.6609045931061</v>
+      </c>
+      <c r="E84" t="n">
+        <v>338.1583920810744</v>
+      </c>
+      <c r="F84" t="n">
+        <v>2317500</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B85" t="n">
+        <v>338.4715881347656</v>
+      </c>
+      <c r="C85" t="n">
+        <v>341.0848358843269</v>
+      </c>
+      <c r="D85" t="n">
+        <v>333.6757154817447</v>
+      </c>
+      <c r="E85" t="n">
+        <v>336.1323595285862</v>
+      </c>
+      <c r="F85" t="n">
+        <v>3763000</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B86" t="n">
+        <v>336.7783508300781</v>
+      </c>
+      <c r="C86" t="n">
+        <v>339.9690879170088</v>
+      </c>
+      <c r="D86" t="n">
+        <v>333.9987022113515</v>
+      </c>
+      <c r="E86" t="n">
+        <v>335.4179027837736</v>
+      </c>
+      <c r="F86" t="n">
+        <v>4725300</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B87" t="n">
+        <v>341.8678588867188</v>
+      </c>
+      <c r="C87" t="n">
+        <v>343.2283069014873</v>
+      </c>
+      <c r="D87" t="n">
+        <v>330.5339084400161</v>
+      </c>
+      <c r="E87" t="n">
+        <v>334.2433821573216</v>
+      </c>
+      <c r="F87" t="n">
+        <v>4680300</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B88" t="n">
+        <v>341.6427307128906</v>
+      </c>
+      <c r="C88" t="n">
+        <v>350.8821400825564</v>
+      </c>
+      <c r="D88" t="n">
+        <v>341.6133693854721</v>
+      </c>
+      <c r="E88" t="n">
+        <v>345.83178268285</v>
+      </c>
+      <c r="F88" t="n">
+        <v>4442700</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B89" t="n">
+        <v>351.9196166992188</v>
+      </c>
+      <c r="C89" t="n">
+        <v>355.5214122846852</v>
+      </c>
+      <c r="D89" t="n">
+        <v>336.7881384925595</v>
+      </c>
+      <c r="E89" t="n">
+        <v>337.9724185347548</v>
+      </c>
+      <c r="F89" t="n">
+        <v>5196500</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B90" t="n">
+        <v>366.67919921875</v>
+      </c>
+      <c r="C90" t="n">
+        <v>367.5111134698199</v>
+      </c>
+      <c r="D90" t="n">
+        <v>353.632434855731</v>
+      </c>
+      <c r="E90" t="n">
+        <v>355.7759014105663</v>
+      </c>
+      <c r="F90" t="n">
+        <v>7093500</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B91" t="n">
+        <v>366.9728088378906</v>
+      </c>
+      <c r="C91" t="n">
+        <v>368.4213707017282</v>
+      </c>
+      <c r="D91" t="n">
+        <v>361.4037146771692</v>
+      </c>
+      <c r="E91" t="n">
+        <v>366.6791955603369</v>
+      </c>
+      <c r="F91" t="n">
+        <v>5859800</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B92" t="n">
+        <v>371.6708374023438</v>
+      </c>
+      <c r="C92" t="n">
+        <v>372.1014901649237</v>
+      </c>
+      <c r="D92" t="n">
+        <v>362.9403965662702</v>
+      </c>
+      <c r="E92" t="n">
+        <v>367.8830764002425</v>
+      </c>
+      <c r="F92" t="n">
+        <v>4785800</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B93" t="n">
+        <v>367.9613647460938</v>
+      </c>
+      <c r="C93" t="n">
+        <v>372.0133774109565</v>
+      </c>
+      <c r="D93" t="n">
+        <v>366.023427464314</v>
+      </c>
+      <c r="E93" t="n">
+        <v>368.6856307593888</v>
+      </c>
+      <c r="F93" t="n">
+        <v>4959900</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B94" t="n">
+        <v>371.1031494140625</v>
+      </c>
+      <c r="C94" t="n">
+        <v>372.1014644570138</v>
+      </c>
+      <c r="D94" t="n">
+        <v>366.5030087993679</v>
+      </c>
+      <c r="E94" t="n">
+        <v>368.0298576269892</v>
+      </c>
+      <c r="F94" t="n">
+        <v>2990100</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B95" t="n">
+        <v>372.0917053222656</v>
+      </c>
+      <c r="C95" t="n">
+        <v>374.6364335107019</v>
+      </c>
+      <c r="D95" t="n">
+        <v>369.4882246061678</v>
+      </c>
+      <c r="E95" t="n">
+        <v>371.1912414425437</v>
+      </c>
+      <c r="F95" t="n">
+        <v>3709000</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B96" t="n">
+        <v>367.1391906738281</v>
+      </c>
+      <c r="C96" t="n">
+        <v>369.3218156656606</v>
+      </c>
+      <c r="D96" t="n">
+        <v>363.4101525923161</v>
+      </c>
+      <c r="E96" t="n">
+        <v>364.330180714857</v>
+      </c>
+      <c r="F96" t="n">
+        <v>5353700</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B97" t="n">
+        <v>376.4667358398438</v>
+      </c>
+      <c r="C97" t="n">
+        <v>377.719535714972</v>
+      </c>
+      <c r="D97" t="n">
+        <v>366.7183560089877</v>
+      </c>
+      <c r="E97" t="n">
+        <v>367.8145521660867</v>
+      </c>
+      <c r="F97" t="n">
+        <v>5169800</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B98" t="n">
+        <v>372.9334106445312</v>
+      </c>
+      <c r="C98" t="n">
+        <v>382.3000628313615</v>
+      </c>
+      <c r="D98" t="n">
+        <v>372.4440352517285</v>
+      </c>
+      <c r="E98" t="n">
+        <v>378.2382530449191</v>
+      </c>
+      <c r="F98" t="n">
+        <v>4828100</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B99" t="n">
+        <v>375.6151733398438</v>
+      </c>
+      <c r="C99" t="n">
+        <v>376.2024297773683</v>
+      </c>
+      <c r="D99" t="n">
+        <v>371.1520722052226</v>
+      </c>
+      <c r="E99" t="n">
+        <v>373.3934198383746</v>
+      </c>
+      <c r="F99" t="n">
+        <v>3138300</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B100" t="n">
+        <v>378.3165588378906</v>
+      </c>
+      <c r="C100" t="n">
+        <v>379.1876614177048</v>
+      </c>
+      <c r="D100" t="n">
+        <v>373.8338931586024</v>
+      </c>
+      <c r="E100" t="n">
+        <v>376.8190712559752</v>
+      </c>
+      <c r="F100" t="n">
+        <v>3984800</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B101" t="n">
+        <v>372.2776489257812</v>
+      </c>
+      <c r="C101" t="n">
+        <v>378.2871933198306</v>
+      </c>
+      <c r="D101" t="n">
+        <v>370.2320632887583</v>
+      </c>
+      <c r="E101" t="n">
+        <v>376.7701414908988</v>
+      </c>
+      <c r="F101" t="n">
+        <v>3466100</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B102" t="n">
+        <v>367.3251647949219</v>
+      </c>
+      <c r="C102" t="n">
+        <v>372.9040563253842</v>
+      </c>
+      <c r="D102" t="n">
+        <v>365.7102319421367</v>
+      </c>
+      <c r="E102" t="n">
+        <v>372.1308348268722</v>
+      </c>
+      <c r="F102" t="n">
+        <v>3371500</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B103" t="n">
+        <v>363.9093322753906</v>
+      </c>
+      <c r="C103" t="n">
+        <v>369.0771353006065</v>
+      </c>
+      <c r="D103" t="n">
+        <v>362.284602364362</v>
+      </c>
+      <c r="E103" t="n">
+        <v>366.9336686607455</v>
+      </c>
+      <c r="F103" t="n">
+        <v>4744500</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B104" t="n">
+        <v>366.6302490234375</v>
+      </c>
+      <c r="C104" t="n">
+        <v>367.1489857391411</v>
+      </c>
+      <c r="D104" t="n">
+        <v>360.7185859823057</v>
+      </c>
+      <c r="E104" t="n">
+        <v>364.4965795036834</v>
+      </c>
+      <c r="F104" t="n">
+        <v>3755600</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B105" t="n">
+        <v>370.0852355957031</v>
+      </c>
+      <c r="C105" t="n">
+        <v>371.5827230758924</v>
+      </c>
+      <c r="D105" t="n">
+        <v>360.4151732293658</v>
+      </c>
+      <c r="E105" t="n">
+        <v>366.2876778370263</v>
+      </c>
+      <c r="F105" t="n">
+        <v>4757200</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B106" t="n">
+        <v>373.0019226074219</v>
+      </c>
+      <c r="C106" t="n">
+        <v>383.4549736116182</v>
+      </c>
+      <c r="D106" t="n">
+        <v>368.9890384961104</v>
+      </c>
+      <c r="E106" t="n">
+        <v>369.2728845813793</v>
+      </c>
+      <c r="F106" t="n">
+        <v>5684400</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B107" t="n">
+        <v>378.9722900390625</v>
+      </c>
+      <c r="C107" t="n">
+        <v>382.2315167883015</v>
+      </c>
+      <c r="D107" t="n">
+        <v>376.192611714533</v>
+      </c>
+      <c r="E107" t="n">
+        <v>376.4177351325982</v>
+      </c>
+      <c r="F107" t="n">
+        <v>5574700</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B108" t="n">
+        <v>374.2449035644531</v>
+      </c>
+      <c r="C108" t="n">
+        <v>378.7765241230696</v>
+      </c>
+      <c r="D108" t="n">
+        <v>372.7376191102791</v>
+      </c>
+      <c r="E108" t="n">
+        <v>378.4633167278202</v>
+      </c>
+      <c r="F108" t="n">
+        <v>3759700</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B109" t="n">
+        <v>376.9658508300781</v>
+      </c>
+      <c r="C109" t="n">
+        <v>378.1599279570784</v>
+      </c>
+      <c r="D109" t="n">
+        <v>371.0444206547449</v>
+      </c>
+      <c r="E109" t="n">
+        <v>373.2368128082787</v>
+      </c>
+      <c r="F109" t="n">
+        <v>4685400</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B110" t="n">
+        <v>372.904052734375</v>
+      </c>
+      <c r="C110" t="n">
+        <v>377.5824803376956</v>
+      </c>
+      <c r="D110" t="n">
+        <v>370.163562457197</v>
+      </c>
+      <c r="E110" t="n">
+        <v>376.1926410669886</v>
+      </c>
+      <c r="F110" t="n">
+        <v>3639300</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B111" t="n">
+        <v>381.3995971679688</v>
+      </c>
+      <c r="C111" t="n">
+        <v>383.4158213872818</v>
+      </c>
+      <c r="D111" t="n">
+        <v>373.8240756812119</v>
+      </c>
+      <c r="E111" t="n">
+        <v>375.6543348626084</v>
+      </c>
+      <c r="F111" t="n">
+        <v>3160800</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B112" t="n">
+        <v>382.3783569335938</v>
+      </c>
+      <c r="C112" t="n">
+        <v>383.1026528395359</v>
+      </c>
+      <c r="D112" t="n">
+        <v>373.9610940454729</v>
+      </c>
+      <c r="E112" t="n">
+        <v>376.8190595355247</v>
+      </c>
+      <c r="F112" t="n">
+        <v>3229900</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B113" t="n">
+        <v>381.9281311035156</v>
+      </c>
+      <c r="C113" t="n">
+        <v>389.1806779778082</v>
+      </c>
+      <c r="D113" t="n">
+        <v>380.7340539554721</v>
+      </c>
+      <c r="E113" t="n">
+        <v>385.187358063094</v>
+      </c>
+      <c r="F113" t="n">
+        <v>3702200</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B114" t="n">
+        <v>382.7405090332031</v>
+      </c>
+      <c r="C114" t="n">
+        <v>385.6278359965556</v>
+      </c>
+      <c r="D114" t="n">
+        <v>378.8744610861731</v>
+      </c>
+      <c r="E114" t="n">
+        <v>381.908594703622</v>
+      </c>
+      <c r="F114" t="n">
+        <v>2875900</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B115" t="n">
+        <v>374.9007263183594</v>
+      </c>
+      <c r="C115" t="n">
+        <v>385.6278270527202</v>
+      </c>
+      <c r="D115" t="n">
+        <v>372.4146908465991</v>
+      </c>
+      <c r="E115" t="n">
+        <v>383.895448836351</v>
+      </c>
+      <c r="F115" t="n">
+        <v>3485300</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B116" t="n">
+        <v>375.3704833984375</v>
+      </c>
+      <c r="C116" t="n">
+        <v>376.9364905994225</v>
+      </c>
+      <c r="D116" t="n">
+        <v>371.4750744620919</v>
+      </c>
+      <c r="E116" t="n">
+        <v>374.6168560607417</v>
+      </c>
+      <c r="F116" t="n">
+        <v>2982600</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B117" t="n">
+        <v>370.5354614257812</v>
+      </c>
+      <c r="C117" t="n">
+        <v>375.5858190931522</v>
+      </c>
+      <c r="D117" t="n">
+        <v>369.3707754637165</v>
+      </c>
+      <c r="E117" t="n">
+        <v>375.5858190931522</v>
+      </c>
+      <c r="F117" t="n">
+        <v>2930900</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B118" t="n">
+        <v>374.1274719238281</v>
+      </c>
+      <c r="C118" t="n">
+        <v>376.6428685046932</v>
+      </c>
+      <c r="D118" t="n">
+        <v>367.9613541837774</v>
+      </c>
+      <c r="E118" t="n">
+        <v>369.4294802998945</v>
+      </c>
+      <c r="F118" t="n">
+        <v>3984100</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B119" t="n">
+        <v>368.9792785644531</v>
+      </c>
+      <c r="C119" t="n">
+        <v>375.9773711355021</v>
+      </c>
+      <c r="D119" t="n">
+        <v>361.726731079823</v>
+      </c>
+      <c r="E119" t="n">
+        <v>372.8942820194261</v>
+      </c>
+      <c r="F119" t="n">
+        <v>5495700</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B120" t="n">
+        <v>376.3101196289062</v>
+      </c>
+      <c r="C120" t="n">
+        <v>385.9703852790173</v>
+      </c>
+      <c r="D120" t="n">
+        <v>374.0883361890514</v>
+      </c>
+      <c r="E120" t="n">
+        <v>380.8417107584177</v>
+      </c>
+      <c r="F120" t="n">
+        <v>5675800</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B121" t="n">
+        <v>367.5894165039062</v>
+      </c>
+      <c r="C121" t="n">
+        <v>373.3346784735209</v>
+      </c>
+      <c r="D121" t="n">
+        <v>363.4786515163307</v>
+      </c>
+      <c r="E121" t="n">
+        <v>372.9725454847734</v>
+      </c>
+      <c r="F121" t="n">
+        <v>5036900</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B122" t="n">
+        <v>367.11962890625</v>
+      </c>
+      <c r="C122" t="n">
+        <v>373.3738607688525</v>
+      </c>
+      <c r="D122" t="n">
+        <v>366.9728222621029</v>
+      </c>
+      <c r="E122" t="n">
+        <v>370.3592916198801</v>
+      </c>
+      <c r="F122" t="n">
+        <v>2889400</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B123" t="n">
+        <v>372.6300048828125</v>
+      </c>
+      <c r="C123" t="n">
+        <v>374.0687697501482</v>
+      </c>
+      <c r="D123" t="n">
+        <v>364.4280684193005</v>
+      </c>
+      <c r="E123" t="n">
+        <v>365.915758878878</v>
+      </c>
+      <c r="F123" t="n">
+        <v>4819500</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B124" t="n">
+        <v>362.9305419921875</v>
+      </c>
+      <c r="C124" t="n">
+        <v>367.139158023408</v>
+      </c>
+      <c r="D124" t="n">
+        <v>361.159005627823</v>
+      </c>
+      <c r="E124" t="n">
+        <v>367.0315097843729</v>
+      </c>
+      <c r="F124" t="n">
+        <v>4537600</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B125" t="n">
+        <v>359.1232604980469</v>
+      </c>
+      <c r="C125" t="n">
+        <v>360.9437226682394</v>
+      </c>
+      <c r="D125" t="n">
+        <v>352.4677370657963</v>
+      </c>
+      <c r="E125" t="n">
+        <v>356.0010430233106</v>
+      </c>
+      <c r="F125" t="n">
+        <v>3964700</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B126" t="n">
+        <v>361.2666931152344</v>
+      </c>
+      <c r="C126" t="n">
+        <v>361.716939988571</v>
+      </c>
+      <c r="D126" t="n">
+        <v>353.8282109374275</v>
+      </c>
+      <c r="E126" t="n">
+        <v>358.4185545746917</v>
+      </c>
+      <c r="F126" t="n">
+        <v>4324400</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B127" t="n">
+        <v>353.9945678710938</v>
+      </c>
+      <c r="C127" t="n">
+        <v>359.1819648229422</v>
+      </c>
+      <c r="D127" t="n">
+        <v>351.5672851014027</v>
+      </c>
+      <c r="E127" t="n">
+        <v>358.3402236370215</v>
+      </c>
+      <c r="F127" t="n">
+        <v>4752200</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B128" t="n">
+        <v>350.3145141601562</v>
+      </c>
+      <c r="C128" t="n">
+        <v>351.8120017521521</v>
+      </c>
+      <c r="D128" t="n">
+        <v>345.7143732597218</v>
+      </c>
+      <c r="E128" t="n">
+        <v>349.9425840615119</v>
+      </c>
+      <c r="F128" t="n">
+        <v>4167400</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B129" t="n">
+        <v>346.047119140625</v>
+      </c>
+      <c r="C129" t="n">
+        <v>348.9148517222478</v>
+      </c>
+      <c r="D129" t="n">
+        <v>338.2954297848507</v>
+      </c>
+      <c r="E129" t="n">
+        <v>348.0437790706712</v>
+      </c>
+      <c r="F129" t="n">
+        <v>4224500</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B130" t="n">
+        <v>349.5608520507812</v>
+      </c>
+      <c r="C130" t="n">
+        <v>353.9554635770335</v>
+      </c>
+      <c r="D130" t="n">
+        <v>343.5611046994417</v>
+      </c>
+      <c r="E130" t="n">
+        <v>345.5382004871225</v>
+      </c>
+      <c r="F130" t="n">
+        <v>3986000</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B131" t="n">
+        <v>343.3849182128906</v>
+      </c>
+      <c r="C131" t="n">
+        <v>348.7484832111462</v>
+      </c>
+      <c r="D131" t="n">
+        <v>341.6916686197754</v>
+      </c>
+      <c r="E131" t="n">
+        <v>347.906742012967</v>
+      </c>
+      <c r="F131" t="n">
+        <v>3197100</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B132" t="n">
+        <v>333.94580078125</v>
+      </c>
+      <c r="C132" t="n">
+        <v>343.5425880232349</v>
+      </c>
+      <c r="D132" t="n">
+        <v>333.719202328884</v>
+      </c>
+      <c r="E132" t="n">
+        <v>340.9512591186561</v>
+      </c>
+      <c r="F132" t="n">
+        <v>3893600</v>
+      </c>
+      <c r="G132" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B133" t="n">
+        <v>334.0443115234375</v>
+      </c>
+      <c r="C133" t="n">
+        <v>338.3697677547303</v>
+      </c>
+      <c r="D133" t="n">
+        <v>333.0590172641502</v>
+      </c>
+      <c r="E133" t="n">
+        <v>336.6651978613972</v>
+      </c>
+      <c r="F133" t="n">
+        <v>2531900</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B134" t="n">
+        <v>337.5421142578125</v>
+      </c>
+      <c r="C134" t="n">
+        <v>340.1630007521627</v>
+      </c>
+      <c r="D134" t="n">
+        <v>335.6405034404279</v>
+      </c>
+      <c r="E134" t="n">
+        <v>337.4041886890553</v>
+      </c>
+      <c r="F134" t="n">
+        <v>3194400</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B135" t="n">
+        <v>336.4090270996094</v>
+      </c>
+      <c r="C135" t="n">
+        <v>341.6803576413574</v>
+      </c>
+      <c r="D135" t="n">
+        <v>335.9262425125186</v>
+      </c>
+      <c r="E135" t="n">
+        <v>339.81816704201</v>
+      </c>
+      <c r="F135" t="n">
+        <v>3075900</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B136" t="n">
+        <v>326.0634460449219</v>
+      </c>
+      <c r="C136" t="n">
+        <v>334.8030019580219</v>
+      </c>
+      <c r="D136" t="n">
+        <v>325.2850851722408</v>
+      </c>
+      <c r="E136" t="n">
+        <v>333.6206668009991</v>
+      </c>
+      <c r="F136" t="n">
+        <v>3592200</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B137" t="n">
+        <v>323.3834533691406</v>
+      </c>
+      <c r="C137" t="n">
+        <v>325.3737672197113</v>
+      </c>
+      <c r="D137" t="n">
+        <v>319.8561127917808</v>
+      </c>
+      <c r="E137" t="n">
+        <v>324.1224241388957</v>
+      </c>
+      <c r="F137" t="n">
+        <v>3845400</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B138" t="n">
+        <v>316.0331726074219</v>
+      </c>
+      <c r="C138" t="n">
+        <v>325.3737741611631</v>
+      </c>
+      <c r="D138" t="n">
+        <v>315.5503879828975</v>
+      </c>
+      <c r="E138" t="n">
+        <v>322.930233272276</v>
+      </c>
+      <c r="F138" t="n">
+        <v>9672200</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B139" t="n">
+        <v>326.0339050292969</v>
+      </c>
+      <c r="C139" t="n">
+        <v>329.7977367855016</v>
+      </c>
+      <c r="D139" t="n">
+        <v>323.3834607358939</v>
+      </c>
+      <c r="E139" t="n">
+        <v>327.1078722975504</v>
+      </c>
+      <c r="F139" t="n">
+        <v>5806300</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B140" t="n">
+        <v>326.0437316894531</v>
+      </c>
+      <c r="C140" t="n">
+        <v>327.6300410369481</v>
+      </c>
+      <c r="D140" t="n">
+        <v>318.2697454376269</v>
+      </c>
+      <c r="E140" t="n">
+        <v>321.1073977566388</v>
+      </c>
+      <c r="F140" t="n">
+        <v>4566400</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B141" t="n">
+        <v>327.6202392578125</v>
+      </c>
+      <c r="C141" t="n">
+        <v>332.2314096741407</v>
+      </c>
+      <c r="D141" t="n">
+        <v>322.1813951135094</v>
+      </c>
+      <c r="E141" t="n">
+        <v>330.0736126071158</v>
+      </c>
+      <c r="F141" t="n">
+        <v>4397800</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B142" t="n">
+        <v>323.6001892089844</v>
+      </c>
+      <c r="C142" t="n">
+        <v>329.2065159991698</v>
+      </c>
+      <c r="D142" t="n">
+        <v>321.7872513641968</v>
+      </c>
+      <c r="E142" t="n">
+        <v>326.5659345775528</v>
+      </c>
+      <c r="F142" t="n">
+        <v>3448400</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B143" t="n">
+        <v>316.919921875</v>
+      </c>
+      <c r="C143" t="n">
+        <v>322.7233200333912</v>
+      </c>
+      <c r="D143" t="n">
+        <v>316.0233004076466</v>
+      </c>
+      <c r="E143" t="n">
+        <v>322.6838998401017</v>
+      </c>
+      <c r="F143" t="n">
+        <v>3977400</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B144" t="n">
+        <v>318.7427062988281</v>
+      </c>
+      <c r="C144" t="n">
+        <v>323.1666680872671</v>
+      </c>
+      <c r="D144" t="n">
+        <v>317.8362223118503</v>
+      </c>
+      <c r="E144" t="n">
+        <v>320.9300608492875</v>
+      </c>
+      <c r="F144" t="n">
+        <v>4066000</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B145" t="n">
+        <v>324.053466796875</v>
+      </c>
+      <c r="C145" t="n">
+        <v>326.5659553121756</v>
+      </c>
+      <c r="D145" t="n">
+        <v>318.6540430408731</v>
+      </c>
+      <c r="E145" t="n">
+        <v>323.6593250096307</v>
+      </c>
+      <c r="F145" t="n">
+        <v>5749100</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B146" t="n">
+        <v>324.7135925292969</v>
+      </c>
+      <c r="C146" t="n">
+        <v>328.1916802636729</v>
+      </c>
+      <c r="D146" t="n">
+        <v>322.98932747548</v>
+      </c>
+      <c r="E146" t="n">
+        <v>324.5263842036645</v>
+      </c>
+      <c r="F146" t="n">
+        <v>3386200</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B147" t="n">
+        <v>316.9002075195312</v>
+      </c>
+      <c r="C147" t="n">
+        <v>321.5015150184395</v>
+      </c>
+      <c r="D147" t="n">
+        <v>313.9738822734865</v>
+      </c>
+      <c r="E147" t="n">
+        <v>318.841238474905</v>
+      </c>
+      <c r="F147" t="n">
+        <v>3732300</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B148" t="n">
+        <v>321.8463745117188</v>
+      </c>
+      <c r="C148" t="n">
+        <v>321.875932137731</v>
+      </c>
+      <c r="D148" t="n">
+        <v>314.2300688775543</v>
+      </c>
+      <c r="E148" t="n">
+        <v>314.9985972226668</v>
+      </c>
+      <c r="F148" t="n">
+        <v>2448300</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B149" t="n">
+        <v>314.082275390625</v>
+      </c>
+      <c r="C149" t="n">
+        <v>319.6097924401727</v>
+      </c>
+      <c r="D149" t="n">
+        <v>310.673165290877</v>
+      </c>
+      <c r="E149" t="n">
+        <v>318.2500813990391</v>
+      </c>
+      <c r="F149" t="n">
+        <v>4661600</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B150" t="n">
+        <v>331.2165222167969</v>
+      </c>
+      <c r="C150" t="n">
+        <v>333.7979883682909</v>
+      </c>
+      <c r="D150" t="n">
+        <v>327.3640180499997</v>
+      </c>
+      <c r="E150" t="n">
+        <v>328.3591748751156</v>
+      </c>
+      <c r="F150" t="n">
+        <v>4610600</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B151" t="n">
+        <v>334.5862426757812</v>
+      </c>
+      <c r="C151" t="n">
+        <v>335.5617045306175</v>
+      </c>
+      <c r="D151" t="n">
+        <v>323.6199418005998</v>
+      </c>
+      <c r="E151" t="n">
+        <v>326.388616523007</v>
+      </c>
+      <c r="F151" t="n">
+        <v>3002000</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B152" t="n">
+        <v>332.3792114257812</v>
+      </c>
+      <c r="C152" t="n">
+        <v>336.2120210994593</v>
+      </c>
+      <c r="D152" t="n">
+        <v>330.8717121868362</v>
+      </c>
+      <c r="E152" t="n">
+        <v>336.0248127567512</v>
+      </c>
+      <c r="F152" t="n">
+        <v>3208300</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B153" t="n">
+        <v>336.1430358886719</v>
+      </c>
+      <c r="C153" t="n">
+        <v>336.4189171136328</v>
+      </c>
+      <c r="D153" t="n">
+        <v>327.0487578932272</v>
+      </c>
+      <c r="E153" t="n">
+        <v>330.6056862577288</v>
+      </c>
+      <c r="F153" t="n">
+        <v>3741200</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B154" t="n">
+        <v>337.6701965332031</v>
+      </c>
+      <c r="C154" t="n">
+        <v>337.7194792888092</v>
+      </c>
+      <c r="D154" t="n">
+        <v>333.3644653118732</v>
+      </c>
+      <c r="E154" t="n">
+        <v>335.9853517224209</v>
+      </c>
+      <c r="F154" t="n">
+        <v>2882500</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B155" t="n">
+        <v>333.9261169433594</v>
+      </c>
+      <c r="C155" t="n">
+        <v>337.236691577658</v>
+      </c>
+      <c r="D155" t="n">
+        <v>331.6697844276179</v>
+      </c>
+      <c r="E155" t="n">
+        <v>336.8228847827696</v>
+      </c>
+      <c r="F155" t="n">
+        <v>3365200</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B156" t="n">
+        <v>332.1919860839844</v>
+      </c>
+      <c r="C156" t="n">
+        <v>336.9509746615948</v>
+      </c>
+      <c r="D156" t="n">
+        <v>331.7387590995254</v>
+      </c>
+      <c r="E156" t="n">
+        <v>334.9902184465357</v>
+      </c>
+      <c r="F156" t="n">
+        <v>2856700</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B157" t="n">
+        <v>344.2618103027344</v>
+      </c>
+      <c r="C157" t="n">
+        <v>346.8432764669682</v>
+      </c>
+      <c r="D157" t="n">
+        <v>337.7982823274818</v>
+      </c>
+      <c r="E157" t="n">
+        <v>337.7982823274818</v>
+      </c>
+      <c r="F157" t="n">
+        <v>4930400</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B158" t="n">
+        <v>345.8284606933594</v>
+      </c>
+      <c r="C158" t="n">
+        <v>346.0058365319325</v>
+      </c>
+      <c r="D158" t="n">
+        <v>338.5668460102951</v>
+      </c>
+      <c r="E158" t="n">
+        <v>343.2174366312315</v>
+      </c>
+      <c r="F158" t="n">
+        <v>3260900</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B159" t="n">
+        <v>338.8624267578125</v>
+      </c>
+      <c r="C159" t="n">
+        <v>348.350785549426</v>
+      </c>
+      <c r="D159" t="n">
+        <v>337.9263851511736</v>
+      </c>
+      <c r="E159" t="n">
+        <v>347.7399078982703</v>
+      </c>
+      <c r="F159" t="n">
+        <v>3081000</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B160" t="n">
+        <v>334.5074462890625</v>
+      </c>
+      <c r="C160" t="n">
+        <v>340.163026480594</v>
+      </c>
+      <c r="D160" t="n">
+        <v>332.9506943790196</v>
+      </c>
+      <c r="E160" t="n">
+        <v>338.8920183636698</v>
+      </c>
+      <c r="F160" t="n">
+        <v>2855800</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B161" t="n">
+        <v>335.1577453613281</v>
+      </c>
+      <c r="C161" t="n">
+        <v>335.81787576814</v>
+      </c>
+      <c r="D161" t="n">
+        <v>331.9259809451064</v>
+      </c>
+      <c r="E161" t="n">
+        <v>334.5074474516935</v>
+      </c>
+      <c r="F161" t="n">
+        <v>2712400</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B162" t="n">
+        <v>330.9505310058594</v>
+      </c>
+      <c r="C162" t="n">
+        <v>335.2660949665313</v>
+      </c>
+      <c r="D162" t="n">
+        <v>329.758303202367</v>
+      </c>
+      <c r="E162" t="n">
+        <v>332.9112571246521</v>
+      </c>
+      <c r="F162" t="n">
+        <v>3255900</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B163" t="n">
+        <v>327.4132995605469</v>
+      </c>
+      <c r="C163" t="n">
+        <v>332.4186116830558</v>
+      </c>
+      <c r="D163" t="n">
+        <v>327.2556789255299</v>
+      </c>
+      <c r="E163" t="n">
+        <v>329.5612640898174</v>
+      </c>
+      <c r="F163" t="n">
+        <v>3282900</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B164" t="n">
+        <v>324.220947265625</v>
+      </c>
+      <c r="C164" t="n">
+        <v>330.9899144482985</v>
+      </c>
+      <c r="D164" t="n">
+        <v>322.5459348903251</v>
+      </c>
+      <c r="E164" t="n">
+        <v>329.5316980954363</v>
+      </c>
+      <c r="F164" t="n">
+        <v>4279300</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B165" t="n">
+        <v>318.0628662109375</v>
+      </c>
+      <c r="C165" t="n">
+        <v>321.0483068839262</v>
+      </c>
+      <c r="D165" t="n">
+        <v>314.3581498388285</v>
+      </c>
+      <c r="E165" t="n">
+        <v>320.8709611177203</v>
+      </c>
+      <c r="F165" t="n">
+        <v>4150000</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B166" t="n">
+        <v>323.9647521972656</v>
+      </c>
+      <c r="C166" t="n">
+        <v>325.2653478832921</v>
+      </c>
+      <c r="D166" t="n">
+        <v>317.501224026995</v>
+      </c>
+      <c r="E166" t="n">
+        <v>317.501224026995</v>
+      </c>
+      <c r="F166" t="n">
+        <v>4317900</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B167" t="n">
+        <v>319.1171264648438</v>
+      </c>
+      <c r="C167" t="n">
+        <v>325.6594650583568</v>
+      </c>
+      <c r="D167" t="n">
+        <v>318.6047541787617</v>
+      </c>
+      <c r="E167" t="n">
+        <v>325.245658285994</v>
+      </c>
+      <c r="F167" t="n">
+        <v>3865300</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B168" t="n">
+        <v>307.82568359375</v>
+      </c>
+      <c r="C168" t="n">
+        <v>317.3436008490747</v>
+      </c>
+      <c r="D168" t="n">
+        <v>307.6680328846103</v>
+      </c>
+      <c r="E168" t="n">
+        <v>317.3436008490747</v>
+      </c>
+      <c r="F168" t="n">
+        <v>6396100</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B169" t="n">
+        <v>310.7815551757812</v>
+      </c>
+      <c r="C169" t="n">
+        <v>312.959047256485</v>
+      </c>
+      <c r="D169" t="n">
+        <v>305.8353583254913</v>
+      </c>
+      <c r="E169" t="n">
+        <v>308.8011039225745</v>
+      </c>
+      <c r="F169" t="n">
+        <v>6391400</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B170" t="n">
+        <v>318.2993469238281</v>
+      </c>
+      <c r="C170" t="n">
+        <v>320.457144085882</v>
+      </c>
+      <c r="D170" t="n">
+        <v>314.6537756503886</v>
+      </c>
+      <c r="E170" t="n">
+        <v>317.225379625856</v>
+      </c>
+      <c r="F170" t="n">
+        <v>5455900</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B171" t="n">
+        <v>317.8953857421875</v>
+      </c>
+      <c r="C171" t="n">
+        <v>322.6740393180987</v>
+      </c>
+      <c r="D171" t="n">
+        <v>317.688452277705</v>
+      </c>
+      <c r="E171" t="n">
+        <v>320.2305285570251</v>
+      </c>
+      <c r="F171" t="n">
+        <v>4411700</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B172" t="n">
+        <v>312.7817077636719</v>
+      </c>
+      <c r="C172" t="n">
+        <v>319.2353738179666</v>
+      </c>
+      <c r="D172" t="n">
+        <v>312.1412423722705</v>
+      </c>
+      <c r="E172" t="n">
+        <v>317.9347780414561</v>
+      </c>
+      <c r="F172" t="n">
+        <v>4995500</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B173" t="n">
+        <v>306.8206481933594</v>
+      </c>
+      <c r="C173" t="n">
+        <v>312.4565329608662</v>
+      </c>
+      <c r="D173" t="n">
+        <v>305.1554983709962</v>
+      </c>
+      <c r="E173" t="n">
+        <v>311.8456552875821</v>
+      </c>
+      <c r="F173" t="n">
+        <v>4335700</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B174" t="n">
+        <v>305.8944702148438</v>
+      </c>
+      <c r="C174" t="n">
+        <v>310.150948950067</v>
+      </c>
+      <c r="D174" t="n">
+        <v>304.5643168514869</v>
+      </c>
+      <c r="E174" t="n">
+        <v>308.6237547613812</v>
+      </c>
+      <c r="F174" t="n">
+        <v>4225700</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B175" t="n">
+        <v>298.1007995605469</v>
+      </c>
+      <c r="C175" t="n">
+        <v>303.1652270544281</v>
+      </c>
+      <c r="D175" t="n">
+        <v>294.8690352302997</v>
+      </c>
+      <c r="E175" t="n">
+        <v>303.0863866663159</v>
+      </c>
+      <c r="F175" t="n">
+        <v>6307800</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B176" t="n">
+        <v>299.8743286132812</v>
+      </c>
+      <c r="C176" t="n">
+        <v>301.4803631461129</v>
+      </c>
+      <c r="D176" t="n">
+        <v>296.9874235077401</v>
+      </c>
+      <c r="E176" t="n">
+        <v>300.5738791526044</v>
+      </c>
+      <c r="F176" t="n">
+        <v>5072600</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B177" t="n">
+        <v>293.1349182128906</v>
+      </c>
+      <c r="C177" t="n">
+        <v>298.4751965058313</v>
+      </c>
+      <c r="D177" t="n">
+        <v>292.5141779899232</v>
+      </c>
+      <c r="E177" t="n">
+        <v>295.8937302385283</v>
+      </c>
+      <c r="F177" t="n">
+        <v>6121500</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B178" t="n">
+        <v>295.4010925292969</v>
+      </c>
+      <c r="C178" t="n">
+        <v>299.3127122467453</v>
+      </c>
+      <c r="D178" t="n">
+        <v>292.9279941234309</v>
+      </c>
+      <c r="E178" t="n">
+        <v>294.8493301065311</v>
+      </c>
+      <c r="F178" t="n">
+        <v>6366100</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B179" t="n">
+        <v>297.9924011230469</v>
+      </c>
+      <c r="C179" t="n">
+        <v>298.7313718247998</v>
+      </c>
+      <c r="D179" t="n">
+        <v>284.84857918279</v>
+      </c>
+      <c r="E179" t="n">
+        <v>287.5778334831647</v>
+      </c>
+      <c r="F179" t="n">
+        <v>8692500</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B180" t="n">
+        <v>306.0126953125</v>
+      </c>
+      <c r="C180" t="n">
+        <v>306.4363947204983</v>
+      </c>
+      <c r="D180" t="n">
+        <v>292.307277842878</v>
+      </c>
+      <c r="E180" t="n">
+        <v>296.6327042526405</v>
+      </c>
+      <c r="F180" t="n">
+        <v>5810900</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B181" t="n">
+        <v>309.1656494140625</v>
+      </c>
+      <c r="C181" t="n">
+        <v>309.3725528012548</v>
+      </c>
+      <c r="D181" t="n">
+        <v>299.9038888531578</v>
+      </c>
+      <c r="E181" t="n">
+        <v>301.8547523557064</v>
+      </c>
+      <c r="F181" t="n">
+        <v>4516600</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B182" t="n">
+        <v>308.4660949707031</v>
+      </c>
+      <c r="C182" t="n">
+        <v>310.3282855694948</v>
+      </c>
+      <c r="D182" t="n">
+        <v>306.8797555054846</v>
+      </c>
+      <c r="E182" t="n">
+        <v>309.8750586089163</v>
+      </c>
+      <c r="F182" t="n">
+        <v>2963800</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B183" t="n">
+        <v>305.9732971191406</v>
+      </c>
+      <c r="C183" t="n">
+        <v>312.1313864292915</v>
+      </c>
+      <c r="D183" t="n">
+        <v>304.416515303009</v>
+      </c>
+      <c r="E183" t="n">
+        <v>310.4268164834753</v>
+      </c>
+      <c r="F183" t="n">
+        <v>6978200</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B184" t="n">
+        <v>313.1758117675781</v>
+      </c>
+      <c r="C184" t="n">
+        <v>316.2794829226862</v>
+      </c>
+      <c r="D184" t="n">
+        <v>309.8849322824949</v>
+      </c>
+      <c r="E184" t="n">
+        <v>310.1213933019174</v>
+      </c>
+      <c r="F184" t="n">
+        <v>5990100</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B185" t="n">
+        <v>316.4863586425781</v>
+      </c>
+      <c r="C185" t="n">
+        <v>317.1465190224739</v>
+      </c>
+      <c r="D185" t="n">
+        <v>310.5253404383965</v>
+      </c>
+      <c r="E185" t="n">
+        <v>312.7816726974261</v>
+      </c>
+      <c r="F185" t="n">
+        <v>6818900</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B186" t="n">
+        <v>312.4762573242188</v>
+      </c>
+      <c r="C186" t="n">
+        <v>317.3633087672889</v>
+      </c>
+      <c r="D186" t="n">
+        <v>312.3383016854047</v>
+      </c>
+      <c r="E186" t="n">
+        <v>315.7671367684214</v>
+      </c>
+      <c r="F186" t="n">
+        <v>6963300</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B187" t="n">
+        <v>306.12109375</v>
+      </c>
+      <c r="C187" t="n">
+        <v>311.2446362258477</v>
+      </c>
+      <c r="D187" t="n">
+        <v>303.1652107990409</v>
+      </c>
+      <c r="E187" t="n">
+        <v>310.4958029229232</v>
+      </c>
+      <c r="F187" t="n">
+        <v>4544200</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B188" t="n">
+        <v>306.9388732910156</v>
+      </c>
+      <c r="C188" t="n">
+        <v>307.6088962755514</v>
+      </c>
+      <c r="D188" t="n">
+        <v>304.0322731114999</v>
+      </c>
+      <c r="E188" t="n">
+        <v>305.4215416998635</v>
+      </c>
+      <c r="F188" t="n">
+        <v>4310000</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B189" t="n">
+        <v>308.3675842285156</v>
+      </c>
+      <c r="C189" t="n">
+        <v>308.9094841116081</v>
+      </c>
+      <c r="D189" t="n">
+        <v>302.6036060746125</v>
+      </c>
+      <c r="E189" t="n">
+        <v>303.411554685127</v>
+      </c>
+      <c r="F189" t="n">
+        <v>4328300</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B190" t="n">
+        <v>307.6826171875</v>
+      </c>
+      <c r="C190" t="n">
+        <v>318.403599213189</v>
+      </c>
+      <c r="D190" t="n">
+        <v>305.8560507855353</v>
+      </c>
+      <c r="E190" t="n">
+        <v>315.5049467263879</v>
+      </c>
+      <c r="F190" t="n">
+        <v>4558600</v>
+      </c>
+      <c r="G190" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B191" t="n">
+        <v>308.5065307617188</v>
+      </c>
+      <c r="C191" t="n">
+        <v>311.7525986238699</v>
+      </c>
+      <c r="D191" t="n">
+        <v>306.3722648476684</v>
+      </c>
+      <c r="E191" t="n">
+        <v>308.5561528759146</v>
+      </c>
+      <c r="F191" t="n">
+        <v>3946300</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B192" t="n">
+        <v>307.4443664550781</v>
+      </c>
+      <c r="C192" t="n">
+        <v>311.4746638676563</v>
+      </c>
+      <c r="D192" t="n">
+        <v>304.8236946299612</v>
+      </c>
+      <c r="E192" t="n">
+        <v>306.6204514929628</v>
+      </c>
+      <c r="F192" t="n">
+        <v>4381800</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B193" t="n">
+        <v>318.9793395996094</v>
+      </c>
+      <c r="C193" t="n">
+        <v>320.5279554969379</v>
+      </c>
+      <c r="D193" t="n">
+        <v>308.000249988811</v>
+      </c>
+      <c r="E193" t="n">
+        <v>309.0723663566284</v>
+      </c>
+      <c r="F193" t="n">
+        <v>4875300</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B194" t="n">
+        <v>316.5870056152344</v>
+      </c>
+      <c r="C194" t="n">
+        <v>321.6298303667879</v>
+      </c>
+      <c r="D194" t="n">
+        <v>316.4678580086006</v>
+      </c>
+      <c r="E194" t="n">
+        <v>320.9051596578416</v>
+      </c>
+      <c r="F194" t="n">
+        <v>4823800</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B195" t="n">
+        <v>323.6251220703125</v>
+      </c>
+      <c r="C195" t="n">
+        <v>324.6376494749074</v>
+      </c>
+      <c r="D195" t="n">
+        <v>316.2196730066971</v>
+      </c>
+      <c r="E195" t="n">
+        <v>319.9323340788724</v>
+      </c>
+      <c r="F195" t="n">
+        <v>4656600</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B196" t="n">
+        <v>325.9877319335938</v>
+      </c>
+      <c r="C196" t="n">
+        <v>328.598467157331</v>
+      </c>
+      <c r="D196" t="n">
+        <v>322.9104034108394</v>
+      </c>
+      <c r="E196" t="n">
+        <v>326.0969127055492</v>
+      </c>
+      <c r="F196" t="n">
+        <v>3649000</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B197" t="n">
+        <v>327.4072570800781</v>
+      </c>
+      <c r="C197" t="n">
+        <v>335.5274102103883</v>
+      </c>
+      <c r="D197" t="n">
+        <v>327.1293065910854</v>
+      </c>
+      <c r="E197" t="n">
+        <v>331.3184370072605</v>
+      </c>
+      <c r="F197" t="n">
+        <v>4695000</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B198" t="n">
+        <v>334.6240539550781</v>
+      </c>
+      <c r="C198" t="n">
+        <v>335.7954145326594</v>
+      </c>
+      <c r="D198" t="n">
+        <v>327.337752500619</v>
+      </c>
+      <c r="E198" t="n">
+        <v>329.4819549089526</v>
+      </c>
+      <c r="F198" t="n">
+        <v>5131500</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B199" t="n">
+        <v>325.0843811035156</v>
+      </c>
+      <c r="C199" t="n">
+        <v>338.6543633465824</v>
+      </c>
+      <c r="D199" t="n">
+        <v>323.7839666314997</v>
+      </c>
+      <c r="E199" t="n">
+        <v>333.5519799826949</v>
+      </c>
+      <c r="F199" t="n">
+        <v>6085400</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B200" t="n">
+        <v>331.8346252441406</v>
+      </c>
+      <c r="C200" t="n">
+        <v>335.5472561594589</v>
+      </c>
+      <c r="D200" t="n">
+        <v>328.4793462633244</v>
+      </c>
+      <c r="E200" t="n">
+        <v>329.2735121638814</v>
+      </c>
+      <c r="F200" t="n">
+        <v>10604400</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B201" t="n">
+        <v>324.2306518554688</v>
+      </c>
+      <c r="C201" t="n">
+        <v>329.30328611244</v>
+      </c>
+      <c r="D201" t="n">
+        <v>323.9527013683971</v>
+      </c>
+      <c r="E201" t="n">
+        <v>327.585930781475</v>
+      </c>
+      <c r="F201" t="n">
+        <v>4713600</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B202" t="n">
+        <v>322.0765380859375</v>
+      </c>
+      <c r="C202" t="n">
+        <v>326.6130837898613</v>
+      </c>
+      <c r="D202" t="n">
+        <v>319.3466553723836</v>
+      </c>
+      <c r="E202" t="n">
+        <v>321.5007640397083</v>
+      </c>
+      <c r="F202" t="n">
+        <v>4788000</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B203" t="n">
+        <v>340.3518371582031</v>
+      </c>
+      <c r="C203" t="n">
+        <v>340.4511116799111</v>
+      </c>
+      <c r="D203" t="n">
+        <v>325.3126710965327</v>
+      </c>
+      <c r="E203" t="n">
+        <v>326.7123600579221</v>
+      </c>
+      <c r="F203" t="n">
+        <v>6385000</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B204" t="n">
+        <v>342.4761962890625</v>
+      </c>
+      <c r="C204" t="n">
+        <v>346.0895828723475</v>
+      </c>
+      <c r="D204" t="n">
+        <v>339.3194664460809</v>
+      </c>
+      <c r="E204" t="n">
+        <v>339.7463135650192</v>
+      </c>
+      <c r="F204" t="n">
+        <v>6974100</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B205" t="n">
+        <v>346.3079528808594</v>
+      </c>
+      <c r="C205" t="n">
+        <v>347.9359702501276</v>
+      </c>
+      <c r="D205" t="n">
+        <v>343.3199926808538</v>
+      </c>
+      <c r="E205" t="n">
+        <v>345.3549840981078</v>
+      </c>
+      <c r="F205" t="n">
+        <v>7771700</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B206" t="n">
+        <v>348.2437133789062</v>
+      </c>
+      <c r="C206" t="n">
+        <v>348.779771593463</v>
+      </c>
+      <c r="D206" t="n">
+        <v>343.0122759730193</v>
+      </c>
+      <c r="E206" t="n">
+        <v>346.307966117321</v>
+      </c>
+      <c r="F206" t="n">
+        <v>5786500</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B207" t="n">
+        <v>350.1000061035156</v>
+      </c>
+      <c r="C207" t="n">
+        <v>350.9140147662578</v>
+      </c>
+      <c r="D207" t="n">
+        <v>344.7593579765289</v>
+      </c>
+      <c r="E207" t="n">
+        <v>348.1245733949154</v>
+      </c>
+      <c r="F207" t="n">
+        <v>4579000</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B208" t="n">
+        <v>348.2734985351562</v>
+      </c>
+      <c r="C208" t="n">
+        <v>354.507557275585</v>
+      </c>
+      <c r="D208" t="n">
+        <v>348.2734985351562</v>
+      </c>
+      <c r="E208" t="n">
+        <v>351.3905430525372</v>
+      </c>
+      <c r="F208" t="n">
+        <v>4041300</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B209" t="n">
+        <v>355.2818298339844</v>
+      </c>
+      <c r="C209" t="n">
+        <v>355.5697168646199</v>
+      </c>
+      <c r="D209" t="n">
+        <v>345.1068121812833</v>
+      </c>
+      <c r="E209" t="n">
+        <v>350.2588479333682</v>
+      </c>
+      <c r="F209" t="n">
+        <v>3110500</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B210" t="n">
+        <v>348.0848693847656</v>
+      </c>
+      <c r="C210" t="n">
+        <v>356.2248957008094</v>
+      </c>
+      <c r="D210" t="n">
+        <v>343.2703427329958</v>
+      </c>
+      <c r="E210" t="n">
+        <v>355.2024317145021</v>
+      </c>
+      <c r="F210" t="n">
+        <v>4460800</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B211" t="n">
+        <v>342.6846618652344</v>
+      </c>
+      <c r="C211" t="n">
+        <v>352.8199940223038</v>
+      </c>
+      <c r="D211" t="n">
+        <v>341.9600214541982</v>
+      </c>
+      <c r="E211" t="n">
+        <v>352.4626117928308</v>
+      </c>
+      <c r="F211" t="n">
+        <v>3592800</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B212" t="n">
+        <v>333.75048828125</v>
+      </c>
+      <c r="C212" t="n">
+        <v>335.5174656966423</v>
+      </c>
+      <c r="D212" t="n">
+        <v>328.241100746865</v>
+      </c>
+      <c r="E212" t="n">
+        <v>335.5174656966423</v>
+      </c>
+      <c r="F212" t="n">
+        <v>4192300</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B213" t="n">
+        <v>336.2520751953125</v>
+      </c>
+      <c r="C213" t="n">
+        <v>338.2374444527704</v>
+      </c>
+      <c r="D213" t="n">
+        <v>333.1548737064404</v>
+      </c>
+      <c r="E213" t="n">
+        <v>335.2891698936722</v>
+      </c>
+      <c r="F213" t="n">
+        <v>2780800</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B214" t="n">
+        <v>340.7886352539062</v>
+      </c>
+      <c r="C214" t="n">
+        <v>341.8805944502874</v>
+      </c>
+      <c r="D214" t="n">
+        <v>335.4281440922459</v>
+      </c>
+      <c r="E214" t="n">
+        <v>337.0660677396515</v>
+      </c>
+      <c r="F214" t="n">
+        <v>2748000</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B215" t="n">
+        <v>334.6439208984375</v>
+      </c>
+      <c r="C215" t="n">
+        <v>342.5853984087983</v>
+      </c>
+      <c r="D215" t="n">
+        <v>332.9762178919015</v>
+      </c>
+      <c r="E215" t="n">
+        <v>341.4835329455154</v>
+      </c>
+      <c r="F215" t="n">
+        <v>3650400</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B216" t="n">
+        <v>335.2693176269531</v>
+      </c>
+      <c r="C216" t="n">
+        <v>339.2499929294707</v>
+      </c>
+      <c r="D216" t="n">
+        <v>334.1078935040618</v>
+      </c>
+      <c r="E216" t="n">
+        <v>337.0362951640151</v>
+      </c>
+      <c r="F216" t="n">
+        <v>2807300</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B217" t="n">
+        <v>338.9422607421875</v>
+      </c>
+      <c r="C217" t="n">
+        <v>343.7170716460562</v>
+      </c>
+      <c r="D217" t="n">
+        <v>334.7928460359882</v>
+      </c>
+      <c r="E217" t="n">
+        <v>336.5101711499915</v>
+      </c>
+      <c r="F217" t="n">
+        <v>3953100</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B218" t="n">
+        <v>345.4740905761719</v>
+      </c>
+      <c r="C218" t="n">
+        <v>348.2436891486228</v>
+      </c>
+      <c r="D218" t="n">
+        <v>338.148103527179</v>
+      </c>
+      <c r="E218" t="n">
+        <v>339.0514198724459</v>
+      </c>
+      <c r="F218" t="n">
+        <v>3810300</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B219" t="n">
+        <v>336.3910522460938</v>
+      </c>
+      <c r="C219" t="n">
+        <v>351.3905334952897</v>
+      </c>
+      <c r="D219" t="n">
+        <v>335.6167594084301</v>
+      </c>
+      <c r="E219" t="n">
+        <v>346.3774576909258</v>
+      </c>
+      <c r="F219" t="n">
+        <v>4434000</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B220" t="n">
+        <v>330.6036987304688</v>
+      </c>
+      <c r="C220" t="n">
+        <v>337.7113243396537</v>
+      </c>
+      <c r="D220" t="n">
+        <v>328.985617931225</v>
+      </c>
+      <c r="E220" t="n">
+        <v>337.4829959680537</v>
+      </c>
+      <c r="F220" t="n">
+        <v>4125300</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B221" t="n">
+        <v>329.1742248535156</v>
+      </c>
+      <c r="C221" t="n">
+        <v>330.5639772575944</v>
+      </c>
+      <c r="D221" t="n">
+        <v>324.6078695592594</v>
+      </c>
+      <c r="E221" t="n">
+        <v>328.8764012920007</v>
+      </c>
+      <c r="F221" t="n">
+        <v>3112600</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B222" t="n">
+        <v>329.0253295898438</v>
+      </c>
+      <c r="C222" t="n">
+        <v>334.097933459434</v>
+      </c>
+      <c r="D222" t="n">
+        <v>328.2907223705125</v>
+      </c>
+      <c r="E222" t="n">
+        <v>331.0901002710247</v>
+      </c>
+      <c r="F222" t="n">
+        <v>2907700</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B223" t="n">
+        <v>322.3346252441406</v>
+      </c>
+      <c r="C223" t="n">
+        <v>325.8288946116248</v>
+      </c>
+      <c r="D223" t="n">
+        <v>320.6867650845805</v>
+      </c>
+      <c r="E223" t="n">
+        <v>322.9203055541834</v>
+      </c>
+      <c r="F223" t="n">
+        <v>4523100</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B224" t="n">
+        <v>330.5441589355469</v>
+      </c>
+      <c r="C224" t="n">
+        <v>331.0206281983068</v>
+      </c>
+      <c r="D224" t="n">
+        <v>320.8654832094117</v>
+      </c>
+      <c r="E224" t="n">
+        <v>322.6920194034342</v>
+      </c>
+      <c r="F224" t="n">
+        <v>3874500</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B225" t="n">
+        <v>333.6313781738281</v>
+      </c>
+      <c r="C225" t="n">
+        <v>339.3889672822994</v>
+      </c>
+      <c r="D225" t="n">
+        <v>332.8968012318786</v>
+      </c>
+      <c r="E225" t="n">
+        <v>336.9072556737336</v>
+      </c>
+      <c r="F225" t="n">
+        <v>3622400</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B226" t="n">
+        <v>341.9500732421875</v>
+      </c>
+      <c r="C226" t="n">
+        <v>346.8737804890717</v>
+      </c>
+      <c r="D226" t="n">
+        <v>340.0937578445657</v>
+      </c>
+      <c r="E226" t="n">
+        <v>340.133473711892</v>
+      </c>
+      <c r="F226" t="n">
+        <v>4308000</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B227" t="n">
+        <v>335.7954406738281</v>
+      </c>
+      <c r="C227" t="n">
+        <v>342.7442335347337</v>
+      </c>
+      <c r="D227" t="n">
+        <v>334.495026147691</v>
+      </c>
+      <c r="E227" t="n">
+        <v>337.8900211320969</v>
+      </c>
+      <c r="F227" t="n">
+        <v>4028500</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B228" t="n">
+        <v>330.9114379882812</v>
+      </c>
+      <c r="C228" t="n">
+        <v>333.2343164610006</v>
+      </c>
+      <c r="D228" t="n">
+        <v>327.8341094785939</v>
+      </c>
+      <c r="E228" t="n">
+        <v>332.5394250801792</v>
+      </c>
+      <c r="F228" t="n">
+        <v>6275400</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B229" t="n">
+        <v>329.5315856933594</v>
+      </c>
+      <c r="C229" t="n">
+        <v>331.5566708480175</v>
+      </c>
+      <c r="D229" t="n">
+        <v>326.3946985853459</v>
+      </c>
+      <c r="E229" t="n">
+        <v>330.0080852280822</v>
+      </c>
+      <c r="F229" t="n">
+        <v>4961900</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B230" t="n">
+        <v>337.5326232910156</v>
+      </c>
+      <c r="C230" t="n">
+        <v>341.126167165973</v>
+      </c>
+      <c r="D230" t="n">
+        <v>331.2787221229386</v>
+      </c>
+      <c r="E230" t="n">
+        <v>337.3142314565633</v>
+      </c>
+      <c r="F230" t="n">
+        <v>2908100</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B231" t="n">
+        <v>345.6925048828125</v>
+      </c>
+      <c r="C231" t="n">
+        <v>348.2933339094608</v>
+      </c>
+      <c r="D231" t="n">
+        <v>336.8675537894677</v>
+      </c>
+      <c r="E231" t="n">
+        <v>337.741121159039</v>
+      </c>
+      <c r="F231" t="n">
+        <v>4275000</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B232" t="n">
+        <v>350.5566711425781</v>
+      </c>
+      <c r="C232" t="n">
+        <v>351.9563298372728</v>
+      </c>
+      <c r="D232" t="n">
+        <v>345.6031541488199</v>
+      </c>
+      <c r="E232" t="n">
+        <v>347.5984599855233</v>
+      </c>
+      <c r="F232" t="n">
+        <v>3140400</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B233" t="n">
+        <v>346.963134765625</v>
+      </c>
+      <c r="C233" t="n">
+        <v>350.9636527717977</v>
+      </c>
+      <c r="D233" t="n">
+        <v>344.967859180145</v>
+      </c>
+      <c r="E233" t="n">
+        <v>350.9140306560572</v>
+      </c>
+      <c r="F233" t="n">
+        <v>2622400</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B234" t="n">
+        <v>353.0185241699219</v>
+      </c>
+      <c r="C234" t="n">
+        <v>354.219664160909</v>
+      </c>
+      <c r="D234" t="n">
+        <v>346.1888486641563</v>
+      </c>
+      <c r="E234" t="n">
+        <v>348.9386046403958</v>
+      </c>
+      <c r="F234" t="n">
+        <v>3584800</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B235" t="n">
+        <v>348.2139282226562</v>
+      </c>
+      <c r="C235" t="n">
+        <v>351.4103740800161</v>
+      </c>
+      <c r="D235" t="n">
+        <v>344.5211400290252</v>
+      </c>
+      <c r="E235" t="n">
+        <v>349.524279261052</v>
+      </c>
+      <c r="F235" t="n">
+        <v>3124800</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B236" t="n">
+        <v>351.8868713378906</v>
+      </c>
+      <c r="C236" t="n">
+        <v>355.7384623950411</v>
+      </c>
+      <c r="D236" t="n">
+        <v>348.0352499864083</v>
+      </c>
+      <c r="E236" t="n">
+        <v>349.7128894956296</v>
+      </c>
+      <c r="F236" t="n">
+        <v>2549700</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B237" t="n">
+        <v>340.9176940917969</v>
+      </c>
+      <c r="C237" t="n">
+        <v>351.2813246265272</v>
+      </c>
+      <c r="D237" t="n">
+        <v>340.5206262766717</v>
+      </c>
+      <c r="E237" t="n">
+        <v>349.4250091127092</v>
+      </c>
+      <c r="F237" t="n">
+        <v>3965800</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B238" t="n">
+        <v>339.2003479003906</v>
+      </c>
+      <c r="C238" t="n">
+        <v>345.206077753642</v>
+      </c>
+      <c r="D238" t="n">
+        <v>338.0190507751135</v>
+      </c>
+      <c r="E238" t="n">
+        <v>344.4615642861647</v>
+      </c>
+      <c r="F238" t="n">
+        <v>2439900</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B239" t="n">
+        <v>336.381103515625</v>
+      </c>
+      <c r="C239" t="n">
+        <v>338.3168506868042</v>
+      </c>
+      <c r="D239" t="n">
+        <v>333.5519765191293</v>
+      </c>
+      <c r="E239" t="n">
+        <v>338.3168506868042</v>
+      </c>
+      <c r="F239" t="n">
+        <v>3073100</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B240" t="n">
+        <v>335.4082946777344</v>
+      </c>
+      <c r="C240" t="n">
+        <v>336.9568803095206</v>
+      </c>
+      <c r="D240" t="n">
+        <v>330.4548079641576</v>
+      </c>
+      <c r="E240" t="n">
+        <v>332.2614710050206</v>
+      </c>
+      <c r="F240" t="n">
+        <v>5580000</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B241" t="n">
+        <v>335.0211486816406</v>
+      </c>
+      <c r="C241" t="n">
+        <v>342.0195939717831</v>
+      </c>
+      <c r="D241" t="n">
+        <v>328.2709048600699</v>
+      </c>
+      <c r="E241" t="n">
+        <v>334.3163510292147</v>
+      </c>
+      <c r="F241" t="n">
+        <v>6603400</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B242" t="n">
+        <v>341.7813110351562</v>
+      </c>
+      <c r="C242" t="n">
+        <v>347.8366934263856</v>
+      </c>
+      <c r="D242" t="n">
+        <v>338.9224047058033</v>
+      </c>
+      <c r="E242" t="n">
+        <v>338.9224047058033</v>
+      </c>
+      <c r="F242" t="n">
+        <v>4971000</v>
+      </c>
+      <c r="G242" t="n">
+        <v>0</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B243" t="n">
+        <v>332.0430908203125</v>
+      </c>
+      <c r="C243" t="n">
+        <v>336.4009911317456</v>
+      </c>
+      <c r="D243" t="n">
+        <v>329.1643112906949</v>
+      </c>
+      <c r="E243" t="n">
+        <v>333.542054389882</v>
+      </c>
+      <c r="F243" t="n">
+        <v>4027700</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B244" t="n">
+        <v>333.1548767089844</v>
+      </c>
+      <c r="C244" t="n">
+        <v>336.1031512946537</v>
+      </c>
+      <c r="D244" t="n">
+        <v>330.5639843459303</v>
+      </c>
+      <c r="E244" t="n">
+        <v>334.0582233645888</v>
+      </c>
+      <c r="F244" t="n">
+        <v>3422800</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B245" t="n">
+        <v>334.9615783691406</v>
+      </c>
+      <c r="C245" t="n">
+        <v>339.7165463845368</v>
+      </c>
+      <c r="D245" t="n">
+        <v>332.7081950914107</v>
+      </c>
+      <c r="E245" t="n">
+        <v>333.4229292601251</v>
+      </c>
+      <c r="F245" t="n">
+        <v>3298600</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B246" t="n">
+        <v>335.4082946777344</v>
+      </c>
+      <c r="C246" t="n">
+        <v>337.0065024243307</v>
+      </c>
+      <c r="D246" t="n">
+        <v>331.2588801078031</v>
+      </c>
+      <c r="E246" t="n">
+        <v>336.8873851133212</v>
+      </c>
+      <c r="F246" t="n">
+        <v>2528100</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B247" t="n">
+        <v>332.4004516601562</v>
+      </c>
+      <c r="C247" t="n">
+        <v>336.9568704387829</v>
+      </c>
+      <c r="D247" t="n">
+        <v>332.0629425240725</v>
+      </c>
+      <c r="E247" t="n">
+        <v>336.9469338983794</v>
+      </c>
+      <c r="F247" t="n">
+        <v>4258100</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B248" t="n">
+        <v>326.2060852050781</v>
+      </c>
+      <c r="C248" t="n">
+        <v>329.5812372185705</v>
+      </c>
+      <c r="D248" t="n">
+        <v>325.4814448058147</v>
+      </c>
+      <c r="E248" t="n">
+        <v>328.1517689125653</v>
+      </c>
+      <c r="F248" t="n">
+        <v>3618000</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B249" t="n">
+        <v>327.7745361328125</v>
+      </c>
+      <c r="C249" t="n">
+        <v>329.1841313242223</v>
+      </c>
+      <c r="D249" t="n">
+        <v>325.1042120893565</v>
+      </c>
+      <c r="E249" t="n">
+        <v>328.0822659405567</v>
+      </c>
+      <c r="F249" t="n">
+        <v>3136100</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B250" t="n">
+        <v>325.4317932128906</v>
+      </c>
+      <c r="C250" t="n">
+        <v>326.8414187355763</v>
+      </c>
+      <c r="D250" t="n">
+        <v>323.3670224847805</v>
+      </c>
+      <c r="E250" t="n">
+        <v>325.838797551875</v>
+      </c>
+      <c r="F250" t="n">
+        <v>3858700</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B251" t="n">
+        <v>317.4307556152344</v>
+      </c>
+      <c r="C251" t="n">
+        <v>324.439106732169</v>
+      </c>
+      <c r="D251" t="n">
+        <v>316.4678503051231</v>
+      </c>
+      <c r="E251" t="n">
+        <v>323.6251283531417</v>
+      </c>
+      <c r="F251" t="n">
+        <v>3291000</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B252" t="n">
+        <v>316.1799926757812</v>
+      </c>
+      <c r="C252" t="n">
+        <v>319.813222073911</v>
+      </c>
+      <c r="D252" t="n">
+        <v>315.3858267914646</v>
+      </c>
+      <c r="E252" t="n">
+        <v>319.1481100391916</v>
+      </c>
+      <c r="F252" t="n">
+        <v>3499300</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B253" t="n">
+        <v>318.0700073242188</v>
+      </c>
+      <c r="C253" t="n">
+        <v>320.4400024414062</v>
+      </c>
+      <c r="D253" t="n">
+        <v>315.2099914550781</v>
+      </c>
+      <c r="E253" t="n">
+        <v>318.2099914550781</v>
+      </c>
+      <c r="F253" t="n">
+        <v>3377700</v>
+      </c>
+      <c r="G253" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H253" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="n">
         <v>46269</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B254" t="n">
+        <v>321.0499877929688</v>
+      </c>
+      <c r="C254" t="n">
+        <v>321.7999877929688</v>
+      </c>
+      <c r="D254" t="n">
+        <v>316.1000061035156</v>
+      </c>
+      <c r="E254" t="n">
         <v>316.7000122070312</v>
       </c>
-      <c r="C24" t="n">
-        <v>321.7999877929688</v>
-      </c>
-      <c r="D24" t="n">
-        <v>316.1000061035156</v>
-      </c>
-      <c r="E24" t="n">
-        <v>321.0499877929688</v>
-      </c>
-      <c r="F24" t="n">
+      <c r="F254" t="n">
         <v>2261000</v>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="G254" t="n">
+        <v>0</v>
+      </c>
+      <c r="H254" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4771,7 +10743,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:59:53</t>
+          <t>2026-09-07 03:08:44</t>
         </is>
       </c>
     </row>

--- a/data/HD_data.xlsx
+++ b/data/HD_data.xlsx
@@ -516,16 +516,16 @@
         <v>45908</v>
       </c>
       <c r="B4" t="n">
-        <v>408.3753051757812</v>
+        <v>408.3753356933594</v>
       </c>
       <c r="C4" t="n">
-        <v>408.9976648300841</v>
+        <v>408.9976953941706</v>
       </c>
       <c r="D4" t="n">
-        <v>404.3006909076745</v>
+        <v>404.3007211207598</v>
       </c>
       <c r="E4" t="n">
-        <v>406.974958857154</v>
+        <v>406.9749892700853</v>
       </c>
       <c r="F4" t="n">
         <v>3742600</v>
@@ -542,16 +542,16 @@
         <v>45909</v>
       </c>
       <c r="B5" t="n">
-        <v>403.9019775390625</v>
+        <v>403.9020080566406</v>
       </c>
       <c r="C5" t="n">
-        <v>407.1889007063392</v>
+        <v>407.1889314722671</v>
       </c>
       <c r="D5" t="n">
-        <v>401.3833069272346</v>
+        <v>401.3833372545098</v>
       </c>
       <c r="E5" t="n">
-        <v>406.605418128494</v>
+        <v>406.6054488503357</v>
       </c>
       <c r="F5" t="n">
         <v>3516000</v>
@@ -594,16 +594,16 @@
         <v>45911</v>
       </c>
       <c r="B7" t="n">
-        <v>411.7594604492188</v>
+        <v>411.7594909667969</v>
       </c>
       <c r="C7" t="n">
-        <v>413.5098784241463</v>
+        <v>413.5099090714568</v>
       </c>
       <c r="D7" t="n">
-        <v>402.8419797879972</v>
+        <v>402.8420096446557</v>
       </c>
       <c r="E7" t="n">
-        <v>404.2520601457455</v>
+        <v>404.2520901069122</v>
       </c>
       <c r="F7" t="n">
         <v>5316400</v>
@@ -698,16 +698,16 @@
         <v>45917</v>
       </c>
       <c r="B11" t="n">
-        <v>405.5162658691406</v>
+        <v>405.5162353515625</v>
       </c>
       <c r="C11" t="n">
-        <v>414.9977612941385</v>
+        <v>414.9977300630199</v>
       </c>
       <c r="D11" t="n">
-        <v>404.3590348225837</v>
+        <v>404.3590043920943</v>
       </c>
       <c r="E11" t="n">
-        <v>412.7513785983885</v>
+        <v>412.7513475363239</v>
       </c>
       <c r="F11" t="n">
         <v>4771700</v>
@@ -724,16 +724,16 @@
         <v>45918</v>
       </c>
       <c r="B12" t="n">
-        <v>405.9830627441406</v>
+        <v>405.9830932617188</v>
       </c>
       <c r="C12" t="n">
-        <v>409.7853891317768</v>
+        <v>409.7854199351742</v>
       </c>
       <c r="D12" t="n">
-        <v>404.4076508642465</v>
+        <v>404.4076812634016</v>
       </c>
       <c r="E12" t="n">
-        <v>406.0511124651653</v>
+        <v>406.0511429878587</v>
       </c>
       <c r="F12" t="n">
         <v>3677200</v>
@@ -802,16 +802,16 @@
         <v>45923</v>
       </c>
       <c r="B15" t="n">
-        <v>399.593994140625</v>
+        <v>399.5940246582031</v>
       </c>
       <c r="C15" t="n">
-        <v>402.3363415649943</v>
+        <v>402.3363722920096</v>
       </c>
       <c r="D15" t="n">
-        <v>396.2389914749436</v>
+        <v>396.2390217362953</v>
       </c>
       <c r="E15" t="n">
-        <v>400.6539731783087</v>
+        <v>400.654003776839</v>
       </c>
       <c r="F15" t="n">
         <v>2597000</v>
@@ -854,16 +854,16 @@
         <v>45925</v>
       </c>
       <c r="B17" t="n">
-        <v>396.2292785644531</v>
+        <v>396.2293090820312</v>
       </c>
       <c r="C17" t="n">
-        <v>399.5453447284057</v>
+        <v>399.5453755013872</v>
       </c>
       <c r="D17" t="n">
-        <v>394.4399240629465</v>
+        <v>394.4399544427085</v>
       </c>
       <c r="E17" t="n">
-        <v>395.4512918948509</v>
+        <v>395.4513223525085</v>
       </c>
       <c r="F17" t="n">
         <v>2554300</v>
@@ -880,16 +880,16 @@
         <v>45926</v>
       </c>
       <c r="B18" t="n">
-        <v>398.7965698242188</v>
+        <v>398.7966003417969</v>
       </c>
       <c r="C18" t="n">
-        <v>400.08022560159</v>
+        <v>400.0802562173988</v>
       </c>
       <c r="D18" t="n">
-        <v>394.6636101400317</v>
+        <v>394.6636403413385</v>
       </c>
       <c r="E18" t="n">
-        <v>396.9197270195646</v>
+        <v>396.9197573935189</v>
       </c>
       <c r="F18" t="n">
         <v>2316600</v>
@@ -906,16 +906,16 @@
         <v>45929</v>
       </c>
       <c r="B19" t="n">
-        <v>395.59716796875</v>
+        <v>395.5971984863281</v>
       </c>
       <c r="C19" t="n">
-        <v>399.6329053199512</v>
+        <v>399.6329361488585</v>
       </c>
       <c r="D19" t="n">
-        <v>392.7284254984301</v>
+        <v>392.7284557947046</v>
       </c>
       <c r="E19" t="n">
-        <v>398.7576665785797</v>
+        <v>398.7576973399684</v>
       </c>
       <c r="F19" t="n">
         <v>3008400</v>
@@ -932,16 +932,16 @@
         <v>45930</v>
       </c>
       <c r="B20" t="n">
-        <v>394.0315246582031</v>
+        <v>394.031494140625</v>
       </c>
       <c r="C20" t="n">
-        <v>395.7916769160157</v>
+        <v>395.7916462621145</v>
       </c>
       <c r="D20" t="n">
-        <v>392.3686244480866</v>
+        <v>392.3685940592994</v>
       </c>
       <c r="E20" t="n">
-        <v>395.4318710489828</v>
+        <v>395.4318404229484</v>
       </c>
       <c r="F20" t="n">
         <v>3211600</v>
@@ -1010,16 +1010,16 @@
         <v>45933</v>
       </c>
       <c r="B23" t="n">
-        <v>384.1805114746094</v>
+        <v>384.1804809570312</v>
       </c>
       <c r="C23" t="n">
-        <v>386.3782832385467</v>
+        <v>386.3782525463874</v>
       </c>
       <c r="D23" t="n">
-        <v>381.8174379292481</v>
+        <v>381.817407599382</v>
       </c>
       <c r="E23" t="n">
-        <v>383.2761296995442</v>
+        <v>383.2760992538061</v>
       </c>
       <c r="F23" t="n">
         <v>2951300</v>
@@ -1062,16 +1062,16 @@
         <v>45937</v>
       </c>
       <c r="B25" t="n">
-        <v>376.1576538085938</v>
+        <v>376.1576843261719</v>
       </c>
       <c r="C25" t="n">
-        <v>379.0166916502498</v>
+        <v>379.016722399781</v>
       </c>
       <c r="D25" t="n">
-        <v>374.8934663230858</v>
+        <v>374.8934967381007</v>
       </c>
       <c r="E25" t="n">
-        <v>378.7249652081036</v>
+        <v>378.7249959339671</v>
       </c>
       <c r="F25" t="n">
         <v>2505700</v>
@@ -1088,16 +1088,16 @@
         <v>45938</v>
       </c>
       <c r="B26" t="n">
-        <v>373.2208251953125</v>
+        <v>373.2208557128906</v>
       </c>
       <c r="C26" t="n">
-        <v>375.8172795135579</v>
+        <v>375.8173102434433</v>
       </c>
       <c r="D26" t="n">
-        <v>372.4331341390219</v>
+        <v>372.4331645921919</v>
       </c>
       <c r="E26" t="n">
-        <v>375.8172795135579</v>
+        <v>375.8173102434433</v>
       </c>
       <c r="F26" t="n">
         <v>2517600</v>
@@ -1114,16 +1114,16 @@
         <v>45939</v>
       </c>
       <c r="B27" t="n">
-        <v>367.2888488769531</v>
+        <v>367.288818359375</v>
       </c>
       <c r="C27" t="n">
-        <v>373.7751480356932</v>
+        <v>373.7751169791765</v>
       </c>
       <c r="D27" t="n">
-        <v>367.0651721318674</v>
+        <v>367.0651416328743</v>
       </c>
       <c r="E27" t="n">
-        <v>372.3553630865562</v>
+        <v>372.3553321480077</v>
       </c>
       <c r="F27" t="n">
         <v>3321400</v>
@@ -1192,16 +1192,16 @@
         <v>45944</v>
       </c>
       <c r="B30" t="n">
-        <v>377.0426025390625</v>
+        <v>377.0426330566406</v>
       </c>
       <c r="C30" t="n">
-        <v>378.1803950347029</v>
+        <v>378.1804256443732</v>
       </c>
       <c r="D30" t="n">
-        <v>367.6000139768833</v>
+        <v>367.6000437301846</v>
       </c>
       <c r="E30" t="n">
-        <v>368.4363162416045</v>
+        <v>368.4363460625955</v>
       </c>
       <c r="F30" t="n">
         <v>4399900</v>
@@ -1270,16 +1270,16 @@
         <v>45947</v>
       </c>
       <c r="B33" t="n">
-        <v>381.1075134277344</v>
+        <v>381.1075439453125</v>
       </c>
       <c r="C33" t="n">
-        <v>382.2841830931986</v>
+        <v>382.2842137049998</v>
       </c>
       <c r="D33" t="n">
-        <v>376.5369638928536</v>
+        <v>376.5369940444402</v>
       </c>
       <c r="E33" t="n">
-        <v>377.8011514993366</v>
+        <v>377.8011817521544</v>
       </c>
       <c r="F33" t="n">
         <v>2657700</v>
@@ -1348,16 +1348,16 @@
         <v>45952</v>
       </c>
       <c r="B36" t="n">
-        <v>378.2582092285156</v>
+        <v>378.2581787109375</v>
       </c>
       <c r="C36" t="n">
-        <v>382.225837605147</v>
+        <v>382.2258067674637</v>
       </c>
       <c r="D36" t="n">
-        <v>377.4802521906377</v>
+        <v>377.4802217358246</v>
       </c>
       <c r="E36" t="n">
-        <v>380.4754194313423</v>
+        <v>380.4753887348813</v>
       </c>
       <c r="F36" t="n">
         <v>2857000</v>
@@ -1452,16 +1452,16 @@
         <v>45958</v>
       </c>
       <c r="B40" t="n">
-        <v>375.1268920898438</v>
+        <v>375.1268615722656</v>
       </c>
       <c r="C40" t="n">
-        <v>379.2695861239365</v>
+        <v>379.2695552693392</v>
       </c>
       <c r="D40" t="n">
-        <v>372.2872924475712</v>
+        <v>372.2872621610022</v>
       </c>
       <c r="E40" t="n">
-        <v>373.8335318063046</v>
+        <v>373.8335013939448</v>
       </c>
       <c r="F40" t="n">
         <v>2372800</v>
@@ -1504,16 +1504,16 @@
         <v>45960</v>
       </c>
       <c r="B42" t="n">
-        <v>369.0975952148438</v>
+        <v>369.0976257324219</v>
       </c>
       <c r="C42" t="n">
-        <v>374.1057935751742</v>
+        <v>374.1058245068382</v>
       </c>
       <c r="D42" t="n">
-        <v>365.7523266876615</v>
+        <v>365.7523569286475</v>
       </c>
       <c r="E42" t="n">
-        <v>367.3082703686788</v>
+        <v>367.3083007383128</v>
       </c>
       <c r="F42" t="n">
         <v>2384300</v>
@@ -1582,16 +1582,16 @@
         <v>45965</v>
       </c>
       <c r="B45" t="n">
-        <v>372.5303955078125</v>
+        <v>372.5303649902344</v>
       </c>
       <c r="C45" t="n">
-        <v>373.1138781194984</v>
+        <v>373.1138475541215</v>
       </c>
       <c r="D45" t="n">
-        <v>366.3747296312804</v>
+        <v>366.3746996179726</v>
       </c>
       <c r="E45" t="n">
-        <v>366.9582122429663</v>
+        <v>366.9581821818597</v>
       </c>
       <c r="F45" t="n">
         <v>2590000</v>
@@ -1634,16 +1634,16 @@
         <v>45967</v>
       </c>
       <c r="B47" t="n">
-        <v>358.90625</v>
+        <v>358.9062194824219</v>
       </c>
       <c r="C47" t="n">
-        <v>362.3973820280062</v>
+        <v>362.3973512135793</v>
       </c>
       <c r="D47" t="n">
-        <v>357.4280900328899</v>
+        <v>357.4280596409988</v>
       </c>
       <c r="E47" t="n">
-        <v>361.5805182090473</v>
+        <v>361.5804874640777</v>
       </c>
       <c r="F47" t="n">
         <v>3622100</v>
@@ -1660,16 +1660,16 @@
         <v>45968</v>
       </c>
       <c r="B48" t="n">
-        <v>360.8900451660156</v>
+        <v>360.8900146484375</v>
       </c>
       <c r="C48" t="n">
-        <v>363.3601048105454</v>
+        <v>363.3600740840942</v>
       </c>
       <c r="D48" t="n">
-        <v>357.4475540431628</v>
+        <v>357.4475238166886</v>
       </c>
       <c r="E48" t="n">
-        <v>358.8284322647385</v>
+        <v>358.8284019214945</v>
       </c>
       <c r="F48" t="n">
         <v>2766400</v>
@@ -1686,16 +1686,16 @@
         <v>45971</v>
       </c>
       <c r="B49" t="n">
-        <v>360.2287902832031</v>
+        <v>360.228759765625</v>
       </c>
       <c r="C49" t="n">
-        <v>360.452467039932</v>
+        <v>360.4524365034046</v>
       </c>
       <c r="D49" t="n">
-        <v>353.4410301931099</v>
+        <v>353.4410002505718</v>
       </c>
       <c r="E49" t="n">
-        <v>359.6064305558101</v>
+        <v>359.6064000909565</v>
       </c>
       <c r="F49" t="n">
         <v>3257900</v>
@@ -1712,16 +1712,16 @@
         <v>45972</v>
       </c>
       <c r="B50" t="n">
-        <v>363.933837890625</v>
+        <v>363.9338684082031</v>
       </c>
       <c r="C50" t="n">
-        <v>365.6453789483504</v>
+        <v>365.6454096094494</v>
       </c>
       <c r="D50" t="n">
-        <v>360.6955554382075</v>
+        <v>360.6955856842403</v>
       </c>
       <c r="E50" t="n">
-        <v>361.7458003836202</v>
+        <v>361.745830717721</v>
       </c>
       <c r="F50" t="n">
         <v>2407300</v>
@@ -1738,16 +1738,16 @@
         <v>45973</v>
       </c>
       <c r="B51" t="n">
-        <v>360.9094543457031</v>
+        <v>360.9094848632812</v>
       </c>
       <c r="C51" t="n">
-        <v>363.2725274444605</v>
+        <v>363.272558161854</v>
       </c>
       <c r="D51" t="n">
-        <v>358.8478417816602</v>
+        <v>358.8478721249137</v>
       </c>
       <c r="E51" t="n">
-        <v>361.8138359498466</v>
+        <v>361.8138665438969</v>
       </c>
       <c r="F51" t="n">
         <v>3375800</v>
@@ -1816,16 +1816,16 @@
         <v>45978</v>
       </c>
       <c r="B54" t="n">
-        <v>348.1702270507812</v>
+        <v>348.1702575683594</v>
       </c>
       <c r="C54" t="n">
-        <v>353.7618780642933</v>
+        <v>353.7619090719871</v>
       </c>
       <c r="D54" t="n">
-        <v>346.2933843548503</v>
+        <v>346.2934147079206</v>
       </c>
       <c r="E54" t="n">
-        <v>351.1848622282798</v>
+        <v>351.1848930100947</v>
       </c>
       <c r="F54" t="n">
         <v>5127200</v>
@@ -1842,16 +1842,16 @@
         <v>45979</v>
       </c>
       <c r="B55" t="n">
-        <v>327.2137145996094</v>
+        <v>327.2137451171875</v>
       </c>
       <c r="C55" t="n">
-        <v>339.1944125402241</v>
+        <v>339.1944441751817</v>
       </c>
       <c r="D55" t="n">
-        <v>326.7566567053178</v>
+        <v>326.7566871802684</v>
       </c>
       <c r="E55" t="n">
-        <v>330.6173283766702</v>
+        <v>330.6173592116862</v>
       </c>
       <c r="F55" t="n">
         <v>10168500</v>
@@ -1920,16 +1920,16 @@
         <v>45982</v>
       </c>
       <c r="B58" t="n">
-        <v>333.8653869628906</v>
+        <v>333.8653564453125</v>
       </c>
       <c r="C58" t="n">
-        <v>337.3662532252054</v>
+        <v>337.3662223876241</v>
       </c>
       <c r="D58" t="n">
-        <v>323.8295802366419</v>
+        <v>323.8295506364051</v>
       </c>
       <c r="E58" t="n">
-        <v>325.356351446162</v>
+        <v>325.3563217063679</v>
       </c>
       <c r="F58" t="n">
         <v>7441300</v>
@@ -1998,16 +1998,16 @@
         <v>45987</v>
       </c>
       <c r="B61" t="n">
-        <v>345.6807556152344</v>
+        <v>345.6807861328125</v>
       </c>
       <c r="C61" t="n">
-        <v>347.4895190539308</v>
+        <v>347.4895497311912</v>
       </c>
       <c r="D61" t="n">
-        <v>339.3889309798961</v>
+        <v>339.388960942016</v>
       </c>
       <c r="E61" t="n">
-        <v>340.6142414881474</v>
+        <v>340.6142715584407</v>
       </c>
       <c r="F61" t="n">
         <v>4517300</v>
@@ -2024,16 +2024,16 @@
         <v>45989</v>
       </c>
       <c r="B62" t="n">
-        <v>347.0908203125</v>
+        <v>347.0908508300781</v>
       </c>
       <c r="C62" t="n">
-        <v>347.975733775784</v>
+        <v>347.9757643711671</v>
       </c>
       <c r="D62" t="n">
-        <v>343.7649903745483</v>
+        <v>343.7650205997065</v>
       </c>
       <c r="E62" t="n">
-        <v>345.1556025907452</v>
+        <v>345.1556329381714</v>
       </c>
       <c r="F62" t="n">
         <v>2119600</v>
@@ -2050,16 +2050,16 @@
         <v>45992</v>
       </c>
       <c r="B63" t="n">
-        <v>347.4895324707031</v>
+        <v>347.489501953125</v>
       </c>
       <c r="C63" t="n">
-        <v>352.3129611811121</v>
+        <v>352.312930239926</v>
       </c>
       <c r="D63" t="n">
-        <v>343.1620981246396</v>
+        <v>343.1620679871098</v>
       </c>
       <c r="E63" t="n">
-        <v>344.2998610600955</v>
+        <v>344.299830822644</v>
       </c>
       <c r="F63" t="n">
         <v>5107100</v>
@@ -2076,16 +2076,16 @@
         <v>45993</v>
       </c>
       <c r="B64" t="n">
-        <v>344.2803955078125</v>
+        <v>344.2804260253906</v>
       </c>
       <c r="C64" t="n">
-        <v>347.654836647816</v>
+        <v>347.6548674645102</v>
       </c>
       <c r="D64" t="n">
-        <v>341.6255660714526</v>
+        <v>341.6255963537023</v>
       </c>
       <c r="E64" t="n">
-        <v>347.0032746652403</v>
+        <v>347.0033054241789</v>
       </c>
       <c r="F64" t="n">
         <v>3965300</v>
@@ -10743,7 +10743,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-07 03:08:44</t>
+          <t>2026-09-08 08:52:35</t>
         </is>
       </c>
     </row>

--- a/data/HD_data.xlsx
+++ b/data/HD_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H254"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -433,22 +433,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Close</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Open</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -469,17 +469,25 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+        <v>45909</v>
+      </c>
+      <c r="B2" t="n">
+        <v>406.6054488503357</v>
+      </c>
+      <c r="C2" t="n">
+        <v>407.1889314722671</v>
+      </c>
+      <c r="D2" t="n">
+        <v>401.3833372545098</v>
+      </c>
+      <c r="E2" t="n">
+        <v>403.9020080566406</v>
+      </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>3516000</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -487,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45905</v>
+        <v>45910</v>
       </c>
       <c r="B3" t="n">
-        <v>407.4126281738281</v>
+        <v>404.0770121335462</v>
       </c>
       <c r="C3" t="n">
-        <v>408.8226790956362</v>
+        <v>405.9344163339586</v>
       </c>
       <c r="D3" t="n">
-        <v>402.6183719436316</v>
+        <v>400.4011104850302</v>
       </c>
       <c r="E3" t="n">
-        <v>405.117604329066</v>
+        <v>401.85009765625</v>
       </c>
       <c r="F3" t="n">
-        <v>5855600</v>
+        <v>2897800</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -513,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45908</v>
+        <v>45911</v>
       </c>
       <c r="B4" t="n">
-        <v>408.3753356933594</v>
+        <v>404.2521200680789</v>
       </c>
       <c r="C4" t="n">
-        <v>408.9976953941706</v>
+        <v>413.5099397187673</v>
       </c>
       <c r="D4" t="n">
-        <v>404.3007211207598</v>
+        <v>402.8420395013142</v>
       </c>
       <c r="E4" t="n">
-        <v>406.9749892700853</v>
+        <v>411.759521484375</v>
       </c>
       <c r="F4" t="n">
-        <v>3742600</v>
+        <v>5316400</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -539,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45909</v>
+        <v>45912</v>
       </c>
       <c r="B5" t="n">
-        <v>403.9020080566406</v>
+        <v>408.6962221082555</v>
       </c>
       <c r="C5" t="n">
-        <v>407.1889314722671</v>
+        <v>411.8470163012535</v>
       </c>
       <c r="D5" t="n">
-        <v>401.3833372545098</v>
+        <v>407.3445165905575</v>
       </c>
       <c r="E5" t="n">
-        <v>406.6054488503357</v>
+        <v>411.0495910644531</v>
       </c>
       <c r="F5" t="n">
-        <v>3516000</v>
+        <v>5004200</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -565,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45910</v>
+        <v>45915</v>
       </c>
       <c r="B6" t="n">
-        <v>401.85009765625</v>
+        <v>410.8356495901566</v>
       </c>
       <c r="C6" t="n">
-        <v>405.9344163339586</v>
+        <v>411.6427792599144</v>
       </c>
       <c r="D6" t="n">
-        <v>400.4011104850302</v>
+        <v>406.245631927433</v>
       </c>
       <c r="E6" t="n">
-        <v>404.0770121335462</v>
+        <v>411.0690307617188</v>
       </c>
       <c r="F6" t="n">
-        <v>2897800</v>
+        <v>4884700</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -591,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45911</v>
+        <v>45916</v>
       </c>
       <c r="B7" t="n">
-        <v>411.7594909667969</v>
+        <v>412.0803987002532</v>
       </c>
       <c r="C7" t="n">
-        <v>413.5099090714568</v>
+        <v>412.8389171851107</v>
       </c>
       <c r="D7" t="n">
-        <v>402.8420096446557</v>
+        <v>408.5211874475655</v>
       </c>
       <c r="E7" t="n">
-        <v>404.2520901069122</v>
+        <v>409.84375</v>
       </c>
       <c r="F7" t="n">
-        <v>5316400</v>
+        <v>3726700</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -617,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45912</v>
+        <v>45917</v>
       </c>
       <c r="B8" t="n">
-        <v>411.0495910644531</v>
+        <v>412.7514096604531</v>
       </c>
       <c r="C8" t="n">
-        <v>411.8470163012535</v>
+        <v>414.9977925252571</v>
       </c>
       <c r="D8" t="n">
-        <v>407.3445165905575</v>
+        <v>404.3590652530731</v>
       </c>
       <c r="E8" t="n">
-        <v>408.6962221082555</v>
+        <v>405.5162963867188</v>
       </c>
       <c r="F8" t="n">
-        <v>5004200</v>
+        <v>4771700</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -643,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45915</v>
+        <v>45918</v>
       </c>
       <c r="B9" t="n">
-        <v>411.0690307617188</v>
+        <v>406.0511124651653</v>
       </c>
       <c r="C9" t="n">
-        <v>411.6427792599144</v>
+        <v>409.7853891317768</v>
       </c>
       <c r="D9" t="n">
-        <v>406.245631927433</v>
+        <v>404.4076508642465</v>
       </c>
       <c r="E9" t="n">
-        <v>410.8356495901566</v>
+        <v>405.9830627441406</v>
       </c>
       <c r="F9" t="n">
-        <v>4884700</v>
+        <v>3677200</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -669,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45916</v>
+        <v>45919</v>
       </c>
       <c r="B10" t="n">
-        <v>409.84375</v>
+        <v>405.8760981858028</v>
       </c>
       <c r="C10" t="n">
-        <v>412.8389171851107</v>
+        <v>407.0527678467049</v>
       </c>
       <c r="D10" t="n">
-        <v>408.5211874475655</v>
+        <v>403.6686220984643</v>
       </c>
       <c r="E10" t="n">
-        <v>412.0803987002532</v>
+        <v>404.2423706054688</v>
       </c>
       <c r="F10" t="n">
-        <v>3726700</v>
+        <v>6718400</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -695,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45917</v>
+        <v>45922</v>
       </c>
       <c r="B11" t="n">
-        <v>405.5162353515625</v>
+        <v>402.7058704699236</v>
       </c>
       <c r="C11" t="n">
-        <v>414.9977300630199</v>
+        <v>403.4546845448791</v>
       </c>
       <c r="D11" t="n">
-        <v>404.3590043920943</v>
+        <v>399.8079552515003</v>
       </c>
       <c r="E11" t="n">
-        <v>412.7513475363239</v>
+        <v>400.6539916992188</v>
       </c>
       <c r="F11" t="n">
-        <v>4771700</v>
+        <v>2656300</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -721,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45918</v>
+        <v>45923</v>
       </c>
       <c r="B12" t="n">
-        <v>405.9830932617188</v>
+        <v>400.654003776839</v>
       </c>
       <c r="C12" t="n">
-        <v>409.7854199351742</v>
+        <v>402.3363722920096</v>
       </c>
       <c r="D12" t="n">
-        <v>404.4076812634016</v>
+        <v>396.2390217362953</v>
       </c>
       <c r="E12" t="n">
-        <v>406.0511429878587</v>
+        <v>399.5940246582031</v>
       </c>
       <c r="F12" t="n">
-        <v>3677200</v>
+        <v>2597000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -747,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45919</v>
+        <v>45924</v>
       </c>
       <c r="B13" t="n">
-        <v>404.2423400878906</v>
+        <v>395.5874669386123</v>
       </c>
       <c r="C13" t="n">
-        <v>407.0527371169607</v>
+        <v>399.3411526132105</v>
       </c>
       <c r="D13" t="n">
-        <v>403.6685916242002</v>
+        <v>393.856487333743</v>
       </c>
       <c r="E13" t="n">
-        <v>405.8760675448892</v>
+        <v>398.4853820800781</v>
       </c>
       <c r="F13" t="n">
-        <v>6718400</v>
+        <v>3220700</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -773,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45922</v>
+        <v>45925</v>
       </c>
       <c r="B14" t="n">
-        <v>400.6539611816406</v>
+        <v>395.4512918948509</v>
       </c>
       <c r="C14" t="n">
-        <v>403.4546538139739</v>
+        <v>399.5453447284057</v>
       </c>
       <c r="D14" t="n">
-        <v>399.8079247983643</v>
+        <v>394.4399240629465</v>
       </c>
       <c r="E14" t="n">
-        <v>402.7058397960551</v>
+        <v>396.2292785644531</v>
       </c>
       <c r="F14" t="n">
-        <v>2656300</v>
+        <v>2554300</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -799,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45923</v>
+        <v>45926</v>
       </c>
       <c r="B15" t="n">
-        <v>399.5940246582031</v>
+        <v>396.9197270195646</v>
       </c>
       <c r="C15" t="n">
-        <v>402.3363722920096</v>
+        <v>400.08022560159</v>
       </c>
       <c r="D15" t="n">
-        <v>396.2390217362953</v>
+        <v>394.6636101400317</v>
       </c>
       <c r="E15" t="n">
-        <v>400.654003776839</v>
+        <v>398.7965698242188</v>
       </c>
       <c r="F15" t="n">
-        <v>2597000</v>
+        <v>2316600</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -825,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45924</v>
+        <v>45929</v>
       </c>
       <c r="B16" t="n">
-        <v>398.4853820800781</v>
+        <v>398.7576665785797</v>
       </c>
       <c r="C16" t="n">
-        <v>399.3411526132105</v>
+        <v>399.6329053199512</v>
       </c>
       <c r="D16" t="n">
-        <v>393.856487333743</v>
+        <v>392.7284254984301</v>
       </c>
       <c r="E16" t="n">
-        <v>395.5874669386123</v>
+        <v>395.59716796875</v>
       </c>
       <c r="F16" t="n">
-        <v>3220700</v>
+        <v>3008400</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -851,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45925</v>
+        <v>45930</v>
       </c>
       <c r="B17" t="n">
-        <v>396.2293090820312</v>
+        <v>395.4318710489828</v>
       </c>
       <c r="C17" t="n">
-        <v>399.5453755013872</v>
+        <v>395.7916769160157</v>
       </c>
       <c r="D17" t="n">
-        <v>394.4399544427085</v>
+        <v>392.3686244480866</v>
       </c>
       <c r="E17" t="n">
-        <v>395.4513223525085</v>
+        <v>394.0315246582031</v>
       </c>
       <c r="F17" t="n">
-        <v>2554300</v>
+        <v>3211600</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -877,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45926</v>
+        <v>45931</v>
       </c>
       <c r="B18" t="n">
-        <v>398.7966003417969</v>
+        <v>393.2535809799684</v>
       </c>
       <c r="C18" t="n">
-        <v>400.0802562173988</v>
+        <v>393.9731927384614</v>
       </c>
       <c r="D18" t="n">
-        <v>394.6636403413385</v>
+        <v>384.4236170674206</v>
       </c>
       <c r="E18" t="n">
-        <v>396.9197573935189</v>
+        <v>386.0865173339844</v>
       </c>
       <c r="F18" t="n">
-        <v>2316600</v>
+        <v>3787800</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -903,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45929</v>
+        <v>45932</v>
       </c>
       <c r="B19" t="n">
-        <v>395.5971984863281</v>
+        <v>384.6083628947175</v>
       </c>
       <c r="C19" t="n">
-        <v>399.6329361488585</v>
+        <v>386.4365945008176</v>
       </c>
       <c r="D19" t="n">
-        <v>392.7284557947046</v>
+        <v>382.9454627326402</v>
       </c>
       <c r="E19" t="n">
-        <v>398.7576973399684</v>
+        <v>384.1318664550781</v>
       </c>
       <c r="F19" t="n">
-        <v>3008400</v>
+        <v>2964700</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -929,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45930</v>
+        <v>45933</v>
       </c>
       <c r="B20" t="n">
-        <v>394.031494140625</v>
+        <v>383.2760992538061</v>
       </c>
       <c r="C20" t="n">
-        <v>395.7916462621145</v>
+        <v>386.3782525463874</v>
       </c>
       <c r="D20" t="n">
-        <v>392.3685940592994</v>
+        <v>381.817407599382</v>
       </c>
       <c r="E20" t="n">
-        <v>395.4318404229484</v>
+        <v>384.1804809570312</v>
       </c>
       <c r="F20" t="n">
-        <v>3211600</v>
+        <v>2951300</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -955,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45931</v>
+        <v>45936</v>
       </c>
       <c r="B21" t="n">
-        <v>386.0865173339844</v>
+        <v>383.6359134364591</v>
       </c>
       <c r="C21" t="n">
-        <v>393.9731927384614</v>
+        <v>383.6359134364591</v>
       </c>
       <c r="D21" t="n">
-        <v>384.4236170674206</v>
+        <v>375.0977059544146</v>
       </c>
       <c r="E21" t="n">
-        <v>393.2535809799684</v>
+        <v>378.6082763671875</v>
       </c>
       <c r="F21" t="n">
-        <v>3787800</v>
+        <v>3653700</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -981,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45932</v>
+        <v>45937</v>
       </c>
       <c r="B22" t="n">
-        <v>384.1318969726562</v>
+        <v>378.7249959339671</v>
       </c>
       <c r="C22" t="n">
-        <v>386.4366252014962</v>
+        <v>379.016722399781</v>
       </c>
       <c r="D22" t="n">
-        <v>382.9454931559638</v>
+        <v>374.8934967381007</v>
       </c>
       <c r="E22" t="n">
-        <v>384.6083934501511</v>
+        <v>376.1576843261719</v>
       </c>
       <c r="F22" t="n">
-        <v>2964700</v>
+        <v>2505700</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1007,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45933</v>
+        <v>45938</v>
       </c>
       <c r="B23" t="n">
-        <v>384.1804809570312</v>
+        <v>375.8172795135579</v>
       </c>
       <c r="C23" t="n">
-        <v>386.3782525463874</v>
+        <v>375.8172795135579</v>
       </c>
       <c r="D23" t="n">
-        <v>381.817407599382</v>
+        <v>372.4331341390219</v>
       </c>
       <c r="E23" t="n">
-        <v>383.2760992538061</v>
+        <v>373.2208251953125</v>
       </c>
       <c r="F23" t="n">
-        <v>2951300</v>
+        <v>2517600</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1033,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45936</v>
+        <v>45939</v>
       </c>
       <c r="B24" t="n">
-        <v>378.6082458496094</v>
+        <v>372.3553321480077</v>
       </c>
       <c r="C24" t="n">
-        <v>383.6358825136301</v>
+        <v>373.7751169791765</v>
       </c>
       <c r="D24" t="n">
-        <v>375.0976757198047</v>
+        <v>367.0651416328743</v>
       </c>
       <c r="E24" t="n">
-        <v>383.6358825136301</v>
+        <v>367.288818359375</v>
       </c>
       <c r="F24" t="n">
-        <v>3653700</v>
+        <v>3321400</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1059,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45937</v>
+        <v>45940</v>
       </c>
       <c r="B25" t="n">
-        <v>376.1576843261719</v>
+        <v>369.7880611814068</v>
       </c>
       <c r="C25" t="n">
-        <v>379.016722399781</v>
+        <v>369.7880611814068</v>
       </c>
       <c r="D25" t="n">
-        <v>374.8934967381007</v>
+        <v>364.4589637589981</v>
       </c>
       <c r="E25" t="n">
-        <v>378.7249959339671</v>
+        <v>365.4022521972656</v>
       </c>
       <c r="F25" t="n">
-        <v>2505700</v>
+        <v>2992400</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1085,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45938</v>
+        <v>45943</v>
       </c>
       <c r="B26" t="n">
-        <v>373.2208557128906</v>
+        <v>368.6308504339742</v>
       </c>
       <c r="C26" t="n">
-        <v>375.8173102434433</v>
+        <v>371.7816150220939</v>
       </c>
       <c r="D26" t="n">
-        <v>372.4331645921919</v>
+        <v>366.8026187475289</v>
       </c>
       <c r="E26" t="n">
-        <v>375.8173102434433</v>
+        <v>368.9225769042969</v>
       </c>
       <c r="F26" t="n">
-        <v>2517600</v>
+        <v>2925900</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1111,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45939</v>
+        <v>45944</v>
       </c>
       <c r="B27" t="n">
-        <v>367.288818359375</v>
+        <v>368.4363162416045</v>
       </c>
       <c r="C27" t="n">
-        <v>373.7751169791765</v>
+        <v>378.1803950347029</v>
       </c>
       <c r="D27" t="n">
-        <v>367.0651416328743</v>
+        <v>367.6000139768833</v>
       </c>
       <c r="E27" t="n">
-        <v>372.3553321480077</v>
+        <v>377.0426025390625</v>
       </c>
       <c r="F27" t="n">
-        <v>3321400</v>
+        <v>4399900</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1137,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45940</v>
+        <v>45945</v>
       </c>
       <c r="B28" t="n">
-        <v>365.4022521972656</v>
+        <v>378.5110397840133</v>
       </c>
       <c r="C28" t="n">
-        <v>369.7880611814068</v>
+        <v>383.5094743418081</v>
       </c>
       <c r="D28" t="n">
-        <v>364.4589637589981</v>
+        <v>376.0798870651823</v>
       </c>
       <c r="E28" t="n">
-        <v>369.7880611814068</v>
+        <v>377.6066284179688</v>
       </c>
       <c r="F28" t="n">
-        <v>2992400</v>
+        <v>3690100</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1163,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45943</v>
+        <v>45946</v>
       </c>
       <c r="B29" t="n">
-        <v>368.9225463867188</v>
+        <v>378.9292168586321</v>
       </c>
       <c r="C29" t="n">
-        <v>371.7815842680138</v>
+        <v>379.259850089759</v>
       </c>
       <c r="D29" t="n">
-        <v>366.8025884053155</v>
+        <v>373.3959105177652</v>
       </c>
       <c r="E29" t="n">
-        <v>368.6308199405279</v>
+        <v>376.7217407226562</v>
       </c>
       <c r="F29" t="n">
-        <v>2925900</v>
+        <v>2783700</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1189,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45944</v>
+        <v>45947</v>
       </c>
       <c r="B30" t="n">
-        <v>377.0426330566406</v>
+        <v>377.8011514993366</v>
       </c>
       <c r="C30" t="n">
-        <v>378.1804256443732</v>
+        <v>382.2841830931986</v>
       </c>
       <c r="D30" t="n">
-        <v>367.6000437301846</v>
+        <v>376.5369638928536</v>
       </c>
       <c r="E30" t="n">
-        <v>368.4363460625955</v>
+        <v>381.1075134277344</v>
       </c>
       <c r="F30" t="n">
-        <v>4399900</v>
+        <v>2657700</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1215,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45945</v>
+        <v>45950</v>
       </c>
       <c r="B31" t="n">
-        <v>377.6066589355469</v>
+        <v>380.6310112651639</v>
       </c>
       <c r="C31" t="n">
-        <v>383.509505336445</v>
+        <v>382.3522567670641</v>
       </c>
       <c r="D31" t="n">
-        <v>376.0799174593716</v>
+        <v>377.4024332180988</v>
       </c>
       <c r="E31" t="n">
-        <v>378.5110703746846</v>
+        <v>378.180419921875</v>
       </c>
       <c r="F31" t="n">
-        <v>3690100</v>
+        <v>2761100</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1241,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45946</v>
+        <v>45951</v>
       </c>
       <c r="B32" t="n">
-        <v>376.7217407226562</v>
+        <v>376.8870540082442</v>
       </c>
       <c r="C32" t="n">
-        <v>379.259850089759</v>
+        <v>382.7899005162546</v>
       </c>
       <c r="D32" t="n">
-        <v>373.3959105177652</v>
+        <v>375.2338581249689</v>
       </c>
       <c r="E32" t="n">
-        <v>378.9292168586321</v>
+        <v>380.1350708007812</v>
       </c>
       <c r="F32" t="n">
-        <v>2783700</v>
+        <v>2306900</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1267,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45947</v>
+        <v>45952</v>
       </c>
       <c r="B33" t="n">
-        <v>381.1075439453125</v>
+        <v>380.4754194313423</v>
       </c>
       <c r="C33" t="n">
-        <v>382.2842137049998</v>
+        <v>382.225837605147</v>
       </c>
       <c r="D33" t="n">
-        <v>376.5369940444402</v>
+        <v>377.4802521906377</v>
       </c>
       <c r="E33" t="n">
-        <v>377.8011817521544</v>
+        <v>378.2582092285156</v>
       </c>
       <c r="F33" t="n">
-        <v>2657700</v>
+        <v>2857000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1293,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45950</v>
+        <v>45953</v>
       </c>
       <c r="B34" t="n">
-        <v>378.180419921875</v>
+        <v>376.4688710262192</v>
       </c>
       <c r="C34" t="n">
-        <v>382.3522567670641</v>
+        <v>378.0150806165678</v>
       </c>
       <c r="D34" t="n">
-        <v>377.4024332180988</v>
+        <v>370.79940618445</v>
       </c>
       <c r="E34" t="n">
-        <v>380.6310112651639</v>
+        <v>374.4266967773438</v>
       </c>
       <c r="F34" t="n">
-        <v>2761100</v>
+        <v>2767300</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1319,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45951</v>
+        <v>45954</v>
       </c>
       <c r="B35" t="n">
-        <v>380.1350402832031</v>
+        <v>378.968132263296</v>
       </c>
       <c r="C35" t="n">
-        <v>382.7898697855445</v>
+        <v>378.968132263296</v>
       </c>
       <c r="D35" t="n">
-        <v>375.2338280008644</v>
+        <v>375.0491149100141</v>
       </c>
       <c r="E35" t="n">
-        <v>376.8870237514197</v>
+        <v>376.0312805175781</v>
       </c>
       <c r="F35" t="n">
-        <v>2306900</v>
+        <v>2426800</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1345,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45952</v>
+        <v>45957</v>
       </c>
       <c r="B36" t="n">
-        <v>378.2581787109375</v>
+        <v>377.0231983553949</v>
       </c>
       <c r="C36" t="n">
-        <v>382.2258067674637</v>
+        <v>378.5694080170153</v>
       </c>
       <c r="D36" t="n">
-        <v>377.4802217358246</v>
+        <v>372.3553670460668</v>
       </c>
       <c r="E36" t="n">
-        <v>380.4753887348813</v>
+        <v>374.6600952148438</v>
       </c>
       <c r="F36" t="n">
-        <v>2857000</v>
+        <v>3065800</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1371,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45953</v>
+        <v>45958</v>
       </c>
       <c r="B37" t="n">
-        <v>374.4266662597656</v>
+        <v>373.8335013939448</v>
       </c>
       <c r="C37" t="n">
-        <v>378.0150498065191</v>
+        <v>379.2695552693392</v>
       </c>
       <c r="D37" t="n">
-        <v>370.7993759625135</v>
+        <v>372.2872621610022</v>
       </c>
       <c r="E37" t="n">
-        <v>376.468840342194</v>
+        <v>375.1268615722656</v>
       </c>
       <c r="F37" t="n">
-        <v>2767300</v>
+        <v>2372800</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1397,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45954</v>
+        <v>45959</v>
       </c>
       <c r="B38" t="n">
-        <v>376.03125</v>
+        <v>372.4526102885826</v>
       </c>
       <c r="C38" t="n">
-        <v>378.9681015073717</v>
+        <v>374.3975325355203</v>
       </c>
       <c r="D38" t="n">
-        <v>375.0490844721456</v>
+        <v>364.8674253963886</v>
       </c>
       <c r="E38" t="n">
-        <v>378.9681015073717</v>
+        <v>367.6292114257812</v>
       </c>
       <c r="F38" t="n">
-        <v>2426800</v>
+        <v>3852300</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1423,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45957</v>
+        <v>45960</v>
       </c>
       <c r="B39" t="n">
-        <v>374.6600952148438</v>
+        <v>367.3082703686788</v>
       </c>
       <c r="C39" t="n">
-        <v>378.5694080170153</v>
+        <v>374.1057935751742</v>
       </c>
       <c r="D39" t="n">
-        <v>372.3553670460668</v>
+        <v>365.7523266876615</v>
       </c>
       <c r="E39" t="n">
-        <v>377.0231983553949</v>
+        <v>369.0975952148438</v>
       </c>
       <c r="F39" t="n">
-        <v>3065800</v>
+        <v>2384300</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1449,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45958</v>
+        <v>45961</v>
       </c>
       <c r="B40" t="n">
-        <v>375.1268615722656</v>
+        <v>366.5789579935506</v>
       </c>
       <c r="C40" t="n">
-        <v>379.2695552693392</v>
+        <v>370.4493641725706</v>
       </c>
       <c r="D40" t="n">
-        <v>372.2872621610022</v>
+        <v>364.6826764994138</v>
       </c>
       <c r="E40" t="n">
-        <v>373.8335013939448</v>
+        <v>369.1365356445312</v>
       </c>
       <c r="F40" t="n">
-        <v>2372800</v>
+        <v>2643500</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1475,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45959</v>
+        <v>45964</v>
       </c>
       <c r="B41" t="n">
-        <v>367.6292114257812</v>
+        <v>366.6275697464224</v>
       </c>
       <c r="C41" t="n">
-        <v>374.3975325355203</v>
+        <v>368.0570887541689</v>
       </c>
       <c r="D41" t="n">
-        <v>364.8674253963886</v>
+        <v>363.3892576559226</v>
       </c>
       <c r="E41" t="n">
-        <v>372.4526102885826</v>
+        <v>367.9306640625</v>
       </c>
       <c r="F41" t="n">
-        <v>3852300</v>
+        <v>2897600</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1501,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45960</v>
+        <v>45965</v>
       </c>
       <c r="B42" t="n">
-        <v>369.0976257324219</v>
+        <v>366.9581821818597</v>
       </c>
       <c r="C42" t="n">
-        <v>374.1058245068382</v>
+        <v>373.1138475541215</v>
       </c>
       <c r="D42" t="n">
-        <v>365.7523569286475</v>
+        <v>366.3746996179726</v>
       </c>
       <c r="E42" t="n">
-        <v>367.3083007383128</v>
+        <v>372.5303649902344</v>
       </c>
       <c r="F42" t="n">
-        <v>2384300</v>
+        <v>2590000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1527,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45961</v>
+        <v>45966</v>
       </c>
       <c r="B43" t="n">
-        <v>369.1365356445312</v>
+        <v>372.2483997179557</v>
       </c>
       <c r="C43" t="n">
-        <v>370.4493641725706</v>
+        <v>372.8610549707219</v>
       </c>
       <c r="D43" t="n">
-        <v>364.6826764994138</v>
+        <v>360.3260169130116</v>
       </c>
       <c r="E43" t="n">
-        <v>366.5789579935506</v>
+        <v>363.5448608398438</v>
       </c>
       <c r="F43" t="n">
-        <v>2643500</v>
+        <v>4763000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1553,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45964</v>
+        <v>45967</v>
       </c>
       <c r="B44" t="n">
-        <v>367.9306640625</v>
+        <v>361.5805182090473</v>
       </c>
       <c r="C44" t="n">
-        <v>368.0570887541689</v>
+        <v>362.3973820280062</v>
       </c>
       <c r="D44" t="n">
-        <v>363.3892576559226</v>
+        <v>357.4280900328899</v>
       </c>
       <c r="E44" t="n">
-        <v>366.6275697464224</v>
+        <v>358.90625</v>
       </c>
       <c r="F44" t="n">
-        <v>2897600</v>
+        <v>3622100</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1579,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45965</v>
+        <v>45968</v>
       </c>
       <c r="B45" t="n">
-        <v>372.5303649902344</v>
+        <v>358.8284019214945</v>
       </c>
       <c r="C45" t="n">
-        <v>373.1138475541215</v>
+        <v>363.3600740840942</v>
       </c>
       <c r="D45" t="n">
-        <v>366.3746996179726</v>
+        <v>357.4475238166886</v>
       </c>
       <c r="E45" t="n">
-        <v>366.9581821818597</v>
+        <v>360.8900146484375</v>
       </c>
       <c r="F45" t="n">
-        <v>2590000</v>
+        <v>2766400</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1605,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45966</v>
+        <v>45971</v>
       </c>
       <c r="B46" t="n">
-        <v>363.5448608398438</v>
+        <v>359.6064000909565</v>
       </c>
       <c r="C46" t="n">
-        <v>372.8610549707219</v>
+        <v>360.4524365034046</v>
       </c>
       <c r="D46" t="n">
-        <v>360.3260169130116</v>
+        <v>353.4410002505718</v>
       </c>
       <c r="E46" t="n">
-        <v>372.2483997179557</v>
+        <v>360.228759765625</v>
       </c>
       <c r="F46" t="n">
-        <v>4763000</v>
+        <v>3257900</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1631,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45967</v>
+        <v>45972</v>
       </c>
       <c r="B47" t="n">
-        <v>358.9062194824219</v>
+        <v>361.7458003836202</v>
       </c>
       <c r="C47" t="n">
-        <v>362.3973512135793</v>
+        <v>365.6453789483504</v>
       </c>
       <c r="D47" t="n">
-        <v>357.4280596409988</v>
+        <v>360.6955554382075</v>
       </c>
       <c r="E47" t="n">
-        <v>361.5804874640777</v>
+        <v>363.933837890625</v>
       </c>
       <c r="F47" t="n">
-        <v>3622100</v>
+        <v>2407300</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1657,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45968</v>
+        <v>45973</v>
       </c>
       <c r="B48" t="n">
-        <v>360.8900146484375</v>
+        <v>361.8138971379473</v>
       </c>
       <c r="C48" t="n">
-        <v>363.3600740840942</v>
+        <v>363.2725888792476</v>
       </c>
       <c r="D48" t="n">
-        <v>357.4475238166886</v>
+        <v>358.8479024681671</v>
       </c>
       <c r="E48" t="n">
-        <v>358.8284019214945</v>
+        <v>360.9095153808594</v>
       </c>
       <c r="F48" t="n">
-        <v>2766400</v>
+        <v>3375800</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1683,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45971</v>
+        <v>45974</v>
       </c>
       <c r="B49" t="n">
-        <v>360.228759765625</v>
+        <v>361.4249087666506</v>
       </c>
       <c r="C49" t="n">
-        <v>360.4524365034046</v>
+        <v>363.2336722315698</v>
       </c>
       <c r="D49" t="n">
-        <v>353.4410002505718</v>
+        <v>356.5236963397476</v>
       </c>
       <c r="E49" t="n">
-        <v>359.6064000909565</v>
+        <v>357.9337768554688</v>
       </c>
       <c r="F49" t="n">
-        <v>3257900</v>
+        <v>3034800</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1709,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45972</v>
+        <v>45975</v>
       </c>
       <c r="B50" t="n">
-        <v>363.9338684082031</v>
+        <v>355.8332668898346</v>
       </c>
       <c r="C50" t="n">
-        <v>365.6454096094494</v>
+        <v>357.2141451188847</v>
       </c>
       <c r="D50" t="n">
-        <v>360.6955856842403</v>
+        <v>349.8915137655536</v>
       </c>
       <c r="E50" t="n">
-        <v>361.745830717721</v>
+        <v>352.3810119628906</v>
       </c>
       <c r="F50" t="n">
-        <v>2407300</v>
+        <v>3413300</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1735,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45973</v>
+        <v>45978</v>
       </c>
       <c r="B51" t="n">
-        <v>360.9094848632812</v>
+        <v>351.1848930100947</v>
       </c>
       <c r="C51" t="n">
-        <v>363.272558161854</v>
+        <v>353.7619090719871</v>
       </c>
       <c r="D51" t="n">
-        <v>358.8478721249137</v>
+        <v>346.2934147079206</v>
       </c>
       <c r="E51" t="n">
-        <v>361.8138665438969</v>
+        <v>348.1702575683594</v>
       </c>
       <c r="F51" t="n">
-        <v>3375800</v>
+        <v>5127200</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1761,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45974</v>
+        <v>45979</v>
       </c>
       <c r="B52" t="n">
-        <v>357.9337768554688</v>
+        <v>330.6173592116862</v>
       </c>
       <c r="C52" t="n">
-        <v>363.2336722315698</v>
+        <v>339.1944441751817</v>
       </c>
       <c r="D52" t="n">
-        <v>356.5236963397476</v>
+        <v>326.7566871802684</v>
       </c>
       <c r="E52" t="n">
-        <v>361.4249087666506</v>
+        <v>327.2137451171875</v>
       </c>
       <c r="F52" t="n">
-        <v>3034800</v>
+        <v>10168500</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1787,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45975</v>
+        <v>45980</v>
       </c>
       <c r="B53" t="n">
-        <v>352.3810119628906</v>
+        <v>331.5800630406063</v>
       </c>
       <c r="C53" t="n">
-        <v>357.2141451188847</v>
+        <v>332.3385815128617</v>
       </c>
       <c r="D53" t="n">
-        <v>349.8915137655536</v>
+        <v>322.2444305286613</v>
       </c>
       <c r="E53" t="n">
-        <v>355.8332668898346</v>
+        <v>325.2882385253906</v>
       </c>
       <c r="F53" t="n">
-        <v>3413300</v>
+        <v>7595000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1813,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45978</v>
+        <v>45981</v>
       </c>
       <c r="B54" t="n">
-        <v>348.1702575683594</v>
+        <v>327.0970305832446</v>
       </c>
       <c r="C54" t="n">
-        <v>353.7619090719871</v>
+        <v>329.567090307595</v>
       </c>
       <c r="D54" t="n">
-        <v>346.2934147079206</v>
+        <v>322.9835387560075</v>
       </c>
       <c r="E54" t="n">
-        <v>351.1848930100947</v>
+        <v>323.2266540527344</v>
       </c>
       <c r="F54" t="n">
-        <v>5127200</v>
+        <v>4025300</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1839,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45979</v>
+        <v>45982</v>
       </c>
       <c r="B55" t="n">
-        <v>327.2137451171875</v>
+        <v>325.356351446162</v>
       </c>
       <c r="C55" t="n">
-        <v>339.1944441751817</v>
+        <v>337.3662532252054</v>
       </c>
       <c r="D55" t="n">
-        <v>326.7566871802684</v>
+        <v>323.8295802366419</v>
       </c>
       <c r="E55" t="n">
-        <v>330.6173592116862</v>
+        <v>333.8653869628906</v>
       </c>
       <c r="F55" t="n">
-        <v>10168500</v>
+        <v>7441300</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1865,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45980</v>
+        <v>45985</v>
       </c>
       <c r="B56" t="n">
-        <v>325.2882385253906</v>
+        <v>332.7761999080408</v>
       </c>
       <c r="C56" t="n">
-        <v>332.3385815128617</v>
+        <v>334.2445959868845</v>
       </c>
       <c r="D56" t="n">
-        <v>322.2444305286613</v>
+        <v>327.2817709576355</v>
       </c>
       <c r="E56" t="n">
-        <v>331.5800630406063</v>
+        <v>327.3109436035156</v>
       </c>
       <c r="F56" t="n">
-        <v>7595000</v>
+        <v>6132900</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1891,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45981</v>
+        <v>45986</v>
       </c>
       <c r="B57" t="n">
-        <v>323.2266540527344</v>
+        <v>329.6643336820279</v>
       </c>
       <c r="C57" t="n">
-        <v>329.567090307595</v>
+        <v>343.2787899402826</v>
       </c>
       <c r="D57" t="n">
-        <v>322.9835387560075</v>
+        <v>329.5184704432642</v>
       </c>
       <c r="E57" t="n">
-        <v>327.0970305832446</v>
+        <v>341.4019470214844</v>
       </c>
       <c r="F57" t="n">
-        <v>4025300</v>
+        <v>6316600</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1917,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45982</v>
+        <v>45987</v>
       </c>
       <c r="B58" t="n">
-        <v>333.8653564453125</v>
+        <v>340.6142414881474</v>
       </c>
       <c r="C58" t="n">
-        <v>337.3662223876241</v>
+        <v>347.4895190539308</v>
       </c>
       <c r="D58" t="n">
-        <v>323.8295506364051</v>
+        <v>339.3889309798961</v>
       </c>
       <c r="E58" t="n">
-        <v>325.3563217063679</v>
+        <v>345.6807556152344</v>
       </c>
       <c r="F58" t="n">
-        <v>7441300</v>
+        <v>4517300</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1943,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45985</v>
+        <v>45989</v>
       </c>
       <c r="B59" t="n">
-        <v>327.3109436035156</v>
+        <v>345.1556025907452</v>
       </c>
       <c r="C59" t="n">
-        <v>334.2445959868845</v>
+        <v>347.975733775784</v>
       </c>
       <c r="D59" t="n">
-        <v>327.2817709576355</v>
+        <v>343.7649903745483</v>
       </c>
       <c r="E59" t="n">
-        <v>332.7761999080408</v>
+        <v>347.0908203125</v>
       </c>
       <c r="F59" t="n">
-        <v>6132900</v>
+        <v>2119600</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1969,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45986</v>
+        <v>45992</v>
       </c>
       <c r="B60" t="n">
-        <v>341.4019470214844</v>
+        <v>344.299830822644</v>
       </c>
       <c r="C60" t="n">
-        <v>343.2787899402826</v>
+        <v>352.312930239926</v>
       </c>
       <c r="D60" t="n">
-        <v>329.5184704432642</v>
+        <v>343.1620679871098</v>
       </c>
       <c r="E60" t="n">
-        <v>329.6643336820279</v>
+        <v>347.489501953125</v>
       </c>
       <c r="F60" t="n">
-        <v>6316600</v>
+        <v>5107100</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -1995,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45987</v>
+        <v>45993</v>
       </c>
       <c r="B61" t="n">
-        <v>345.6807861328125</v>
+        <v>347.0033054241789</v>
       </c>
       <c r="C61" t="n">
-        <v>347.4895497311912</v>
+        <v>347.6548674645102</v>
       </c>
       <c r="D61" t="n">
-        <v>339.388960942016</v>
+        <v>341.6255963537023</v>
       </c>
       <c r="E61" t="n">
-        <v>340.6142715584407</v>
+        <v>344.2804260253906</v>
       </c>
       <c r="F61" t="n">
-        <v>4517300</v>
+        <v>3965300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2021,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45989</v>
+        <v>45994</v>
       </c>
       <c r="B62" t="n">
-        <v>347.0908508300781</v>
+        <v>344.7374926404726</v>
       </c>
       <c r="C62" t="n">
-        <v>347.9757643711671</v>
+        <v>350.5430871450869</v>
       </c>
       <c r="D62" t="n">
-        <v>343.7650205997065</v>
+        <v>344.0081467463108</v>
       </c>
       <c r="E62" t="n">
-        <v>345.1556329381714</v>
+        <v>348.0535888671875</v>
       </c>
       <c r="F62" t="n">
-        <v>2119600</v>
+        <v>4166700</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2047,25 +2055,25 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45992</v>
+        <v>45995</v>
       </c>
       <c r="B63" t="n">
-        <v>347.489501953125</v>
+        <v>348.7191463158849</v>
       </c>
       <c r="C63" t="n">
-        <v>352.312930239926</v>
+        <v>349.9132235394517</v>
       </c>
       <c r="D63" t="n">
-        <v>343.1620679871098</v>
+        <v>342.5627951482988</v>
       </c>
       <c r="E63" t="n">
-        <v>344.299830822644</v>
+        <v>343.7079467773438</v>
       </c>
       <c r="F63" t="n">
-        <v>5107100</v>
+        <v>4022800</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2073,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45993</v>
+        <v>45996</v>
       </c>
       <c r="B64" t="n">
-        <v>344.2804260253906</v>
+        <v>343.1989538716508</v>
       </c>
       <c r="C64" t="n">
-        <v>347.6548674645102</v>
+        <v>348.0633464265518</v>
       </c>
       <c r="D64" t="n">
-        <v>341.6255963537023</v>
+        <v>342.1027577808173</v>
       </c>
       <c r="E64" t="n">
-        <v>347.0033054241789</v>
+        <v>347.0747985839844</v>
       </c>
       <c r="F64" t="n">
-        <v>3965300</v>
+        <v>5959200</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2099,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45994</v>
+        <v>45999</v>
       </c>
       <c r="B65" t="n">
-        <v>348.0535583496094</v>
+        <v>344.471360951741</v>
       </c>
       <c r="C65" t="n">
-        <v>350.5430564092279</v>
+        <v>344.6083705337733</v>
       </c>
       <c r="D65" t="n">
-        <v>344.0081165834399</v>
+        <v>338.3541683639427</v>
       </c>
       <c r="E65" t="n">
-        <v>344.7374624136521</v>
+        <v>342.4747009277344</v>
       </c>
       <c r="F65" t="n">
-        <v>4166700</v>
+        <v>7273000</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2125,25 +2133,25 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="B66" t="n">
-        <v>343.7079467773438</v>
+        <v>340.3703677160696</v>
       </c>
       <c r="C66" t="n">
-        <v>349.9132235394517</v>
+        <v>349.0910404146574</v>
       </c>
       <c r="D66" t="n">
-        <v>342.5627951482988</v>
+        <v>337.6298477160418</v>
       </c>
       <c r="E66" t="n">
-        <v>348.7191463158849</v>
+        <v>337.9332580566406</v>
       </c>
       <c r="F66" t="n">
-        <v>4022800</v>
+        <v>5063100</v>
       </c>
       <c r="G66" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2151,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45996</v>
+        <v>46001</v>
       </c>
       <c r="B67" t="n">
-        <v>347.0747985839844</v>
+        <v>336.7881155909637</v>
       </c>
       <c r="C67" t="n">
-        <v>348.0633464265518</v>
+        <v>344.5398042643482</v>
       </c>
       <c r="D67" t="n">
-        <v>342.1027577808173</v>
+        <v>336.6902345489607</v>
       </c>
       <c r="E67" t="n">
-        <v>343.1989538716508</v>
+        <v>343.6687316894531</v>
       </c>
       <c r="F67" t="n">
-        <v>5959200</v>
+        <v>6316100</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2177,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>45999</v>
+        <v>46002</v>
       </c>
       <c r="B68" t="n">
-        <v>342.4747009277344</v>
+        <v>348.4352595936447</v>
       </c>
       <c r="C68" t="n">
-        <v>344.6083705337733</v>
+        <v>355.0124656886035</v>
       </c>
       <c r="D68" t="n">
-        <v>338.3541683639427</v>
+        <v>346.4190354810299</v>
       </c>
       <c r="E68" t="n">
-        <v>344.471360951741</v>
+        <v>349.8642272949219</v>
       </c>
       <c r="F68" t="n">
-        <v>7273000</v>
+        <v>6609800</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2203,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="B69" t="n">
-        <v>337.9332580566406</v>
+        <v>351.6260236653551</v>
       </c>
       <c r="C69" t="n">
-        <v>349.0910404146574</v>
+        <v>353.0941498724499</v>
       </c>
       <c r="D69" t="n">
-        <v>337.6298477160418</v>
+        <v>348.4842120764174</v>
       </c>
       <c r="E69" t="n">
-        <v>340.3703677160696</v>
+        <v>352.0077209472656</v>
       </c>
       <c r="F69" t="n">
-        <v>5063100</v>
+        <v>3861200</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2229,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46001</v>
+        <v>46006</v>
       </c>
       <c r="B70" t="n">
-        <v>343.6687316894531</v>
+        <v>351.7532309142689</v>
       </c>
       <c r="C70" t="n">
-        <v>344.5398042643482</v>
+        <v>354.9635320383587</v>
       </c>
       <c r="D70" t="n">
-        <v>336.6902345489607</v>
+        <v>348.0633216327761</v>
       </c>
       <c r="E70" t="n">
-        <v>336.7881155909637</v>
+        <v>349.4042053222656</v>
       </c>
       <c r="F70" t="n">
-        <v>6316100</v>
+        <v>4387400</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2255,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="B71" t="n">
-        <v>349.8642272949219</v>
+        <v>349.3161510627795</v>
       </c>
       <c r="C71" t="n">
-        <v>355.0124656886035</v>
+        <v>351.1170489325283</v>
       </c>
       <c r="D71" t="n">
-        <v>346.4190354810299</v>
+        <v>344.3343131247511</v>
       </c>
       <c r="E71" t="n">
-        <v>348.4352595936447</v>
+        <v>345.1858215332031</v>
       </c>
       <c r="F71" t="n">
-        <v>6609800</v>
+        <v>3497200</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2281,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="B72" t="n">
-        <v>352.0077209472656</v>
+        <v>344.4908843816016</v>
       </c>
       <c r="C72" t="n">
-        <v>353.0941498724499</v>
+        <v>349.9033745469626</v>
       </c>
       <c r="D72" t="n">
-        <v>348.4842120764174</v>
+        <v>343.5219307486607</v>
       </c>
       <c r="E72" t="n">
-        <v>351.6260236653551</v>
+        <v>349.1693115234375</v>
       </c>
       <c r="F72" t="n">
-        <v>3861200</v>
+        <v>3875200</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2307,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46006</v>
+        <v>46009</v>
       </c>
       <c r="B73" t="n">
-        <v>349.4042358398438</v>
+        <v>355.8150530732911</v>
       </c>
       <c r="C73" t="n">
-        <v>354.9635630414982</v>
+        <v>358.5163848099426</v>
       </c>
       <c r="D73" t="n">
-        <v>348.0633520332391</v>
+        <v>347.0258606581617</v>
       </c>
       <c r="E73" t="n">
-        <v>351.753261637015</v>
+        <v>347.4467163085938</v>
       </c>
       <c r="F73" t="n">
-        <v>4387400</v>
+        <v>4805200</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2333,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46007</v>
+        <v>46010</v>
       </c>
       <c r="B74" t="n">
-        <v>345.185791015625</v>
+        <v>346.5854112795514</v>
       </c>
       <c r="C74" t="n">
-        <v>351.1170178905755</v>
+        <v>346.5854112795514</v>
       </c>
       <c r="D74" t="n">
-        <v>344.334282682454</v>
+        <v>337.5907194306183</v>
       </c>
       <c r="E74" t="n">
-        <v>349.3161201800424</v>
+        <v>337.6690063476562</v>
       </c>
       <c r="F74" t="n">
-        <v>3497200</v>
+        <v>12825600</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2359,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46008</v>
+        <v>46013</v>
       </c>
       <c r="B75" t="n">
-        <v>349.1693115234375</v>
+        <v>337.9724428869297</v>
       </c>
       <c r="C75" t="n">
-        <v>349.9033745469626</v>
+        <v>340.5074039236039</v>
       </c>
       <c r="D75" t="n">
-        <v>343.5219307486607</v>
+        <v>336.3966684056612</v>
       </c>
       <c r="E75" t="n">
-        <v>344.4908843816016</v>
+        <v>339.0295104980469</v>
       </c>
       <c r="F75" t="n">
-        <v>3875200</v>
+        <v>3523700</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2385,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46009</v>
+        <v>46014</v>
       </c>
       <c r="B76" t="n">
-        <v>347.4467468261719</v>
+        <v>336.6902590123812</v>
       </c>
       <c r="C76" t="n">
-        <v>358.5164162998122</v>
+        <v>340.1158866476816</v>
       </c>
       <c r="D76" t="n">
-        <v>347.0258911387745</v>
+        <v>334.6740348508469</v>
       </c>
       <c r="E76" t="n">
-        <v>355.8150843258923</v>
+        <v>337.6396484375</v>
       </c>
       <c r="F76" t="n">
-        <v>4805200</v>
+        <v>3873400</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2411,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46010</v>
+        <v>46015</v>
       </c>
       <c r="B77" t="n">
-        <v>337.6690063476562</v>
+        <v>337.0230372348798</v>
       </c>
       <c r="C77" t="n">
-        <v>346.5854112795514</v>
+        <v>340.8597534033964</v>
       </c>
       <c r="D77" t="n">
-        <v>337.5907194306183</v>
+        <v>336.592384505686</v>
       </c>
       <c r="E77" t="n">
-        <v>346.5854112795514</v>
+        <v>339.9592895507812</v>
       </c>
       <c r="F77" t="n">
-        <v>12825600</v>
+        <v>1368600</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2437,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46013</v>
+        <v>46017</v>
       </c>
       <c r="B78" t="n">
-        <v>339.0295104980469</v>
+        <v>339.6166893452076</v>
       </c>
       <c r="C78" t="n">
-        <v>340.5074039236039</v>
+        <v>342.6116640404491</v>
       </c>
       <c r="D78" t="n">
-        <v>336.3966684056612</v>
+        <v>339.2056307857591</v>
       </c>
       <c r="E78" t="n">
-        <v>337.9724428869297</v>
+        <v>342.347412109375</v>
       </c>
       <c r="F78" t="n">
-        <v>3523700</v>
+        <v>1786900</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2463,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46014</v>
+        <v>46020</v>
       </c>
       <c r="B79" t="n">
-        <v>337.6396484375</v>
+        <v>342.5627579984686</v>
       </c>
       <c r="C79" t="n">
-        <v>340.1158866476816</v>
+        <v>342.8759654029374</v>
       </c>
       <c r="D79" t="n">
-        <v>334.6740348508469</v>
+        <v>337.4243166284915</v>
       </c>
       <c r="E79" t="n">
-        <v>336.6902590123812</v>
+        <v>340.0669555664062</v>
       </c>
       <c r="F79" t="n">
-        <v>3873400</v>
+        <v>3790000</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2489,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46015</v>
+        <v>46021</v>
       </c>
       <c r="B80" t="n">
-        <v>339.9592895507812</v>
+        <v>338.6771490106644</v>
       </c>
       <c r="C80" t="n">
-        <v>340.8597534033964</v>
+        <v>339.6069742481806</v>
       </c>
       <c r="D80" t="n">
-        <v>336.592384505686</v>
+        <v>336.4162369795515</v>
       </c>
       <c r="E80" t="n">
-        <v>337.0230372348798</v>
+        <v>338.9903564453125</v>
       </c>
       <c r="F80" t="n">
-        <v>1368600</v>
+        <v>2392600</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2515,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46017</v>
+        <v>46022</v>
       </c>
       <c r="B81" t="n">
-        <v>342.3474426269531</v>
+        <v>338.1583920810744</v>
       </c>
       <c r="C81" t="n">
-        <v>342.6116945815832</v>
+        <v>339.342672153089</v>
       </c>
       <c r="D81" t="n">
-        <v>339.2056610232721</v>
+        <v>336.6609045931061</v>
       </c>
       <c r="E81" t="n">
-        <v>339.6167196193633</v>
+        <v>336.7881469726562</v>
       </c>
       <c r="F81" t="n">
-        <v>1786900</v>
+        <v>2317500</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2541,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46020</v>
+        <v>46024</v>
       </c>
       <c r="B82" t="n">
-        <v>340.0669555664062</v>
+        <v>336.1323595285862</v>
       </c>
       <c r="C82" t="n">
-        <v>342.8759654029374</v>
+        <v>341.0848358843269</v>
       </c>
       <c r="D82" t="n">
-        <v>337.4243166284915</v>
+        <v>333.6757154817447</v>
       </c>
       <c r="E82" t="n">
-        <v>342.5627579984686</v>
+        <v>338.4715881347656</v>
       </c>
       <c r="F82" t="n">
-        <v>3790000</v>
+        <v>3763000</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2567,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46021</v>
+        <v>46027</v>
       </c>
       <c r="B83" t="n">
-        <v>338.9903564453125</v>
+        <v>335.4178723894742</v>
       </c>
       <c r="C83" t="n">
-        <v>339.6069742481806</v>
+        <v>339.9690571102981</v>
       </c>
       <c r="D83" t="n">
-        <v>336.4162369795515</v>
+        <v>333.9986719456546</v>
       </c>
       <c r="E83" t="n">
-        <v>338.6771490106644</v>
+        <v>336.7783203125</v>
       </c>
       <c r="F83" t="n">
-        <v>2392600</v>
+        <v>4725300</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2593,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46022</v>
+        <v>46028</v>
       </c>
       <c r="B84" t="n">
-        <v>336.7881469726562</v>
+        <v>334.2433821573216</v>
       </c>
       <c r="C84" t="n">
-        <v>339.342672153089</v>
+        <v>343.2283069014873</v>
       </c>
       <c r="D84" t="n">
-        <v>336.6609045931061</v>
+        <v>330.5339084400161</v>
       </c>
       <c r="E84" t="n">
-        <v>338.1583920810744</v>
+        <v>341.8678588867188</v>
       </c>
       <c r="F84" t="n">
-        <v>2317500</v>
+        <v>4680300</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2619,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46024</v>
+        <v>46029</v>
       </c>
       <c r="B85" t="n">
-        <v>338.4715881347656</v>
+        <v>345.8318135746193</v>
       </c>
       <c r="C85" t="n">
-        <v>341.0848358843269</v>
+        <v>350.882171425454</v>
       </c>
       <c r="D85" t="n">
-        <v>333.6757154817447</v>
+        <v>341.6133999004275</v>
       </c>
       <c r="E85" t="n">
-        <v>336.1323595285862</v>
+        <v>341.6427612304688</v>
       </c>
       <c r="F85" t="n">
-        <v>3763000</v>
+        <v>4442700</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2645,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46027</v>
+        <v>46030</v>
       </c>
       <c r="B86" t="n">
-        <v>336.7783508300781</v>
+        <v>337.9724185347548</v>
       </c>
       <c r="C86" t="n">
-        <v>339.9690879170088</v>
+        <v>355.5214122846852</v>
       </c>
       <c r="D86" t="n">
-        <v>333.9987022113515</v>
+        <v>336.7881384925595</v>
       </c>
       <c r="E86" t="n">
-        <v>335.4179027837736</v>
+        <v>351.9196166992188</v>
       </c>
       <c r="F86" t="n">
-        <v>4725300</v>
+        <v>5196500</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2671,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46028</v>
+        <v>46031</v>
       </c>
       <c r="B87" t="n">
-        <v>341.8678588867188</v>
+        <v>355.7759014105663</v>
       </c>
       <c r="C87" t="n">
-        <v>343.2283069014873</v>
+        <v>367.5111134698199</v>
       </c>
       <c r="D87" t="n">
-        <v>330.5339084400161</v>
+        <v>353.632434855731</v>
       </c>
       <c r="E87" t="n">
-        <v>334.2433821573216</v>
+        <v>366.67919921875</v>
       </c>
       <c r="F87" t="n">
-        <v>4680300</v>
+        <v>7093500</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2697,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46029</v>
+        <v>46034</v>
       </c>
       <c r="B88" t="n">
-        <v>341.6427307128906</v>
+        <v>366.6791955603369</v>
       </c>
       <c r="C88" t="n">
-        <v>350.8821400825564</v>
+        <v>368.4213707017282</v>
       </c>
       <c r="D88" t="n">
-        <v>341.6133693854721</v>
+        <v>361.4037146771692</v>
       </c>
       <c r="E88" t="n">
-        <v>345.83178268285</v>
+        <v>366.9728088378906</v>
       </c>
       <c r="F88" t="n">
-        <v>4442700</v>
+        <v>5859800</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2723,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46030</v>
+        <v>46035</v>
       </c>
       <c r="B89" t="n">
-        <v>351.9196166992188</v>
+        <v>367.8830461936743</v>
       </c>
       <c r="C89" t="n">
-        <v>355.5214122846852</v>
+        <v>372.1014596119851</v>
       </c>
       <c r="D89" t="n">
-        <v>336.7881384925595</v>
+        <v>362.9403667655412</v>
       </c>
       <c r="E89" t="n">
-        <v>337.9724185347548</v>
+        <v>371.6708068847656</v>
       </c>
       <c r="F89" t="n">
-        <v>5196500</v>
+        <v>4785800</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2749,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46031</v>
+        <v>46036</v>
       </c>
       <c r="B90" t="n">
-        <v>366.67919921875</v>
+        <v>368.6856307593888</v>
       </c>
       <c r="C90" t="n">
-        <v>367.5111134698199</v>
+        <v>372.0133774109565</v>
       </c>
       <c r="D90" t="n">
-        <v>353.632434855731</v>
+        <v>366.023427464314</v>
       </c>
       <c r="E90" t="n">
-        <v>355.7759014105663</v>
+        <v>367.9613647460938</v>
       </c>
       <c r="F90" t="n">
-        <v>7093500</v>
+        <v>4959900</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2775,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46034</v>
+        <v>46037</v>
       </c>
       <c r="B91" t="n">
-        <v>366.9728088378906</v>
+        <v>368.0298878918359</v>
       </c>
       <c r="C91" t="n">
-        <v>368.4213707017282</v>
+        <v>372.1014950566882</v>
       </c>
       <c r="D91" t="n">
-        <v>361.4037146771692</v>
+        <v>366.5030389386545</v>
       </c>
       <c r="E91" t="n">
-        <v>366.6791955603369</v>
+        <v>371.1031799316406</v>
       </c>
       <c r="F91" t="n">
-        <v>5859800</v>
+        <v>2990100</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2801,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46035</v>
+        <v>46038</v>
       </c>
       <c r="B92" t="n">
-        <v>371.6708374023438</v>
+        <v>371.1912414425437</v>
       </c>
       <c r="C92" t="n">
-        <v>372.1014901649237</v>
+        <v>374.6364335107019</v>
       </c>
       <c r="D92" t="n">
-        <v>362.9403965662702</v>
+        <v>369.4882246061678</v>
       </c>
       <c r="E92" t="n">
-        <v>367.8830764002425</v>
+        <v>372.0917053222656</v>
       </c>
       <c r="F92" t="n">
-        <v>4785800</v>
+        <v>3709000</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2827,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46036</v>
+        <v>46042</v>
       </c>
       <c r="B93" t="n">
-        <v>367.9613647460938</v>
+        <v>364.330180714857</v>
       </c>
       <c r="C93" t="n">
-        <v>372.0133774109565</v>
+        <v>369.3218156656606</v>
       </c>
       <c r="D93" t="n">
-        <v>366.023427464314</v>
+        <v>363.4101525923161</v>
       </c>
       <c r="E93" t="n">
-        <v>368.6856307593888</v>
+        <v>367.1391906738281</v>
       </c>
       <c r="F93" t="n">
-        <v>4959900</v>
+        <v>5353700</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2853,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46037</v>
+        <v>46043</v>
       </c>
       <c r="B94" t="n">
-        <v>371.1031494140625</v>
+        <v>367.8145521660867</v>
       </c>
       <c r="C94" t="n">
-        <v>372.1014644570138</v>
+        <v>377.719535714972</v>
       </c>
       <c r="D94" t="n">
-        <v>366.5030087993679</v>
+        <v>366.7183560089877</v>
       </c>
       <c r="E94" t="n">
-        <v>368.0298576269892</v>
+        <v>376.4667358398438</v>
       </c>
       <c r="F94" t="n">
-        <v>2990100</v>
+        <v>5169800</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2879,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46038</v>
+        <v>46044</v>
       </c>
       <c r="B95" t="n">
-        <v>372.0917053222656</v>
+        <v>378.2382839965987</v>
       </c>
       <c r="C95" t="n">
-        <v>374.6364335107019</v>
+        <v>382.3000941154238</v>
       </c>
       <c r="D95" t="n">
-        <v>369.4882246061678</v>
+        <v>372.4440657292604</v>
       </c>
       <c r="E95" t="n">
-        <v>371.1912414425437</v>
+        <v>372.9334411621094</v>
       </c>
       <c r="F95" t="n">
-        <v>3709000</v>
+        <v>4828100</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2905,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46042</v>
+        <v>46045</v>
       </c>
       <c r="B96" t="n">
-        <v>367.1391906738281</v>
+        <v>373.3934198383746</v>
       </c>
       <c r="C96" t="n">
-        <v>369.3218156656606</v>
+        <v>376.2024297773683</v>
       </c>
       <c r="D96" t="n">
-        <v>363.4101525923161</v>
+        <v>371.1520722052226</v>
       </c>
       <c r="E96" t="n">
-        <v>364.330180714857</v>
+        <v>375.6151733398438</v>
       </c>
       <c r="F96" t="n">
-        <v>5353700</v>
+        <v>3138300</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2931,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46043</v>
+        <v>46048</v>
       </c>
       <c r="B97" t="n">
-        <v>376.4667358398438</v>
+        <v>376.8190712559752</v>
       </c>
       <c r="C97" t="n">
-        <v>377.719535714972</v>
+        <v>379.1876614177048</v>
       </c>
       <c r="D97" t="n">
-        <v>366.7183560089877</v>
+        <v>373.8338931586024</v>
       </c>
       <c r="E97" t="n">
-        <v>367.8145521660867</v>
+        <v>378.3165588378906</v>
       </c>
       <c r="F97" t="n">
-        <v>5169800</v>
+        <v>3984800</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2957,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46044</v>
+        <v>46049</v>
       </c>
       <c r="B98" t="n">
-        <v>372.9334106445312</v>
+        <v>376.7701106050471</v>
       </c>
       <c r="C98" t="n">
-        <v>382.3000628313615</v>
+        <v>378.2871623096181</v>
       </c>
       <c r="D98" t="n">
-        <v>372.4440352517285</v>
+        <v>370.2320329388677</v>
       </c>
       <c r="E98" t="n">
-        <v>378.2382530449191</v>
+        <v>372.2776184082031</v>
       </c>
       <c r="F98" t="n">
-        <v>4828100</v>
+        <v>3466100</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2983,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46045</v>
+        <v>46050</v>
       </c>
       <c r="B99" t="n">
-        <v>375.6151733398438</v>
+        <v>372.1308348268722</v>
       </c>
       <c r="C99" t="n">
-        <v>376.2024297773683</v>
+        <v>372.9040563253842</v>
       </c>
       <c r="D99" t="n">
-        <v>371.1520722052226</v>
+        <v>365.7102319421367</v>
       </c>
       <c r="E99" t="n">
-        <v>373.3934198383746</v>
+        <v>367.3251647949219</v>
       </c>
       <c r="F99" t="n">
-        <v>3138300</v>
+        <v>3371500</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3009,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46048</v>
+        <v>46051</v>
       </c>
       <c r="B100" t="n">
-        <v>378.3165588378906</v>
+        <v>366.9336686607455</v>
       </c>
       <c r="C100" t="n">
-        <v>379.1876614177048</v>
+        <v>369.0771353006065</v>
       </c>
       <c r="D100" t="n">
-        <v>373.8338931586024</v>
+        <v>362.284602364362</v>
       </c>
       <c r="E100" t="n">
-        <v>376.8190712559752</v>
+        <v>363.9093322753906</v>
       </c>
       <c r="F100" t="n">
-        <v>3984800</v>
+        <v>4744500</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3035,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46049</v>
+        <v>46052</v>
       </c>
       <c r="B101" t="n">
-        <v>372.2776489257812</v>
+        <v>364.4965795036834</v>
       </c>
       <c r="C101" t="n">
-        <v>378.2871933198306</v>
+        <v>367.1489857391411</v>
       </c>
       <c r="D101" t="n">
-        <v>370.2320632887583</v>
+        <v>360.7185859823057</v>
       </c>
       <c r="E101" t="n">
-        <v>376.7701414908988</v>
+        <v>366.6302490234375</v>
       </c>
       <c r="F101" t="n">
-        <v>3466100</v>
+        <v>3755600</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3061,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46050</v>
+        <v>46055</v>
       </c>
       <c r="B102" t="n">
-        <v>367.3251647949219</v>
+        <v>366.2876778370263</v>
       </c>
       <c r="C102" t="n">
-        <v>372.9040563253842</v>
+        <v>371.5827230758924</v>
       </c>
       <c r="D102" t="n">
-        <v>365.7102319421367</v>
+        <v>360.4151732293658</v>
       </c>
       <c r="E102" t="n">
-        <v>372.1308348268722</v>
+        <v>370.0852355957031</v>
       </c>
       <c r="F102" t="n">
-        <v>3371500</v>
+        <v>4757200</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3087,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46051</v>
+        <v>46056</v>
       </c>
       <c r="B103" t="n">
-        <v>363.9093322753906</v>
+        <v>369.2728845813793</v>
       </c>
       <c r="C103" t="n">
-        <v>369.0771353006065</v>
+        <v>383.4549736116182</v>
       </c>
       <c r="D103" t="n">
-        <v>362.284602364362</v>
+        <v>368.9890384961104</v>
       </c>
       <c r="E103" t="n">
-        <v>366.9336686607455</v>
+        <v>373.0019226074219</v>
       </c>
       <c r="F103" t="n">
-        <v>4744500</v>
+        <v>5684400</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3113,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46052</v>
+        <v>46057</v>
       </c>
       <c r="B104" t="n">
-        <v>366.6302490234375</v>
+        <v>376.4177351325982</v>
       </c>
       <c r="C104" t="n">
-        <v>367.1489857391411</v>
+        <v>382.2315167883015</v>
       </c>
       <c r="D104" t="n">
-        <v>360.7185859823057</v>
+        <v>376.192611714533</v>
       </c>
       <c r="E104" t="n">
-        <v>364.4965795036834</v>
+        <v>378.9722900390625</v>
       </c>
       <c r="F104" t="n">
-        <v>3755600</v>
+        <v>5574700</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3139,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46055</v>
+        <v>46058</v>
       </c>
       <c r="B105" t="n">
-        <v>370.0852355957031</v>
+        <v>378.4633475893863</v>
       </c>
       <c r="C105" t="n">
-        <v>371.5827230758924</v>
+        <v>378.776555010176</v>
       </c>
       <c r="D105" t="n">
-        <v>360.4151732293658</v>
+        <v>372.7376495049467</v>
       </c>
       <c r="E105" t="n">
-        <v>366.2876778370263</v>
+        <v>374.2449340820312</v>
       </c>
       <c r="F105" t="n">
-        <v>4757200</v>
+        <v>3759700</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3165,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46056</v>
+        <v>46059</v>
       </c>
       <c r="B106" t="n">
-        <v>373.0019226074219</v>
+        <v>373.2368128082787</v>
       </c>
       <c r="C106" t="n">
-        <v>383.4549736116182</v>
+        <v>378.1599279570784</v>
       </c>
       <c r="D106" t="n">
-        <v>368.9890384961104</v>
+        <v>371.0444206547449</v>
       </c>
       <c r="E106" t="n">
-        <v>369.2728845813793</v>
+        <v>376.9658508300781</v>
       </c>
       <c r="F106" t="n">
-        <v>5684400</v>
+        <v>4685400</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3191,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46057</v>
+        <v>46062</v>
       </c>
       <c r="B107" t="n">
-        <v>378.9722900390625</v>
+        <v>376.1926410669886</v>
       </c>
       <c r="C107" t="n">
-        <v>382.2315167883015</v>
+        <v>377.5824803376956</v>
       </c>
       <c r="D107" t="n">
-        <v>376.192611714533</v>
+        <v>370.163562457197</v>
       </c>
       <c r="E107" t="n">
-        <v>376.4177351325982</v>
+        <v>372.904052734375</v>
       </c>
       <c r="F107" t="n">
-        <v>5574700</v>
+        <v>3639300</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3217,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46058</v>
+        <v>46063</v>
       </c>
       <c r="B108" t="n">
-        <v>374.2449035644531</v>
+        <v>375.6543048047358</v>
       </c>
       <c r="C108" t="n">
-        <v>378.7765241230696</v>
+        <v>383.4157907083761</v>
       </c>
       <c r="D108" t="n">
-        <v>372.7376191102791</v>
+        <v>373.8240457697869</v>
       </c>
       <c r="E108" t="n">
-        <v>378.4633167278202</v>
+        <v>381.3995666503906</v>
       </c>
       <c r="F108" t="n">
-        <v>3759700</v>
+        <v>3160800</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3243,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46059</v>
+        <v>46064</v>
       </c>
       <c r="B109" t="n">
-        <v>376.9658508300781</v>
+        <v>376.8190595355247</v>
       </c>
       <c r="C109" t="n">
-        <v>378.1599279570784</v>
+        <v>383.1026528395359</v>
       </c>
       <c r="D109" t="n">
-        <v>371.0444206547449</v>
+        <v>373.9610940454729</v>
       </c>
       <c r="E109" t="n">
-        <v>373.2368128082787</v>
+        <v>382.3783569335938</v>
       </c>
       <c r="F109" t="n">
-        <v>4685400</v>
+        <v>3229900</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3269,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46062</v>
+        <v>46065</v>
       </c>
       <c r="B110" t="n">
-        <v>372.904052734375</v>
+        <v>385.1873888410973</v>
       </c>
       <c r="C110" t="n">
-        <v>377.5824803376956</v>
+        <v>389.1807090748937</v>
       </c>
       <c r="D110" t="n">
-        <v>370.163562457197</v>
+        <v>380.7340843776387</v>
       </c>
       <c r="E110" t="n">
-        <v>376.1926410669886</v>
+        <v>381.9281616210938</v>
       </c>
       <c r="F110" t="n">
-        <v>3639300</v>
+        <v>3702200</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3295,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46063</v>
+        <v>46066</v>
       </c>
       <c r="B111" t="n">
-        <v>381.3995971679688</v>
+        <v>381.908564252376</v>
       </c>
       <c r="C111" t="n">
-        <v>383.4158213872818</v>
+        <v>385.6278052487582</v>
       </c>
       <c r="D111" t="n">
-        <v>373.8240756812119</v>
+        <v>378.8744308768519</v>
       </c>
       <c r="E111" t="n">
-        <v>375.6543348626084</v>
+        <v>382.740478515625</v>
       </c>
       <c r="F111" t="n">
-        <v>3160800</v>
+        <v>2875900</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3321,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46064</v>
+        <v>46070</v>
       </c>
       <c r="B112" t="n">
-        <v>382.3783569335938</v>
+        <v>383.895448836351</v>
       </c>
       <c r="C112" t="n">
-        <v>383.1026528395359</v>
+        <v>385.6278270527202</v>
       </c>
       <c r="D112" t="n">
-        <v>373.9610940454729</v>
+        <v>372.4146908465991</v>
       </c>
       <c r="E112" t="n">
-        <v>376.8190595355247</v>
+        <v>374.9007263183594</v>
       </c>
       <c r="F112" t="n">
-        <v>3229900</v>
+        <v>3485300</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3347,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46065</v>
+        <v>46071</v>
       </c>
       <c r="B113" t="n">
-        <v>381.9281311035156</v>
+        <v>374.6168560607417</v>
       </c>
       <c r="C113" t="n">
-        <v>389.1806779778082</v>
+        <v>376.9364905994225</v>
       </c>
       <c r="D113" t="n">
-        <v>380.7340539554721</v>
+        <v>371.4750744620919</v>
       </c>
       <c r="E113" t="n">
-        <v>385.187358063094</v>
+        <v>375.3704833984375</v>
       </c>
       <c r="F113" t="n">
-        <v>3702200</v>
+        <v>2982600</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3373,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46066</v>
+        <v>46072</v>
       </c>
       <c r="B114" t="n">
-        <v>382.7405090332031</v>
+        <v>375.5858190931522</v>
       </c>
       <c r="C114" t="n">
-        <v>385.6278359965556</v>
+        <v>375.5858190931522</v>
       </c>
       <c r="D114" t="n">
-        <v>378.8744610861731</v>
+        <v>369.3707754637165</v>
       </c>
       <c r="E114" t="n">
-        <v>381.908594703622</v>
+        <v>370.5354614257812</v>
       </c>
       <c r="F114" t="n">
-        <v>2875900</v>
+        <v>2930900</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3399,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46070</v>
+        <v>46073</v>
       </c>
       <c r="B115" t="n">
-        <v>374.9007263183594</v>
+        <v>369.4294802998945</v>
       </c>
       <c r="C115" t="n">
-        <v>385.6278270527202</v>
+        <v>376.6428685046932</v>
       </c>
       <c r="D115" t="n">
-        <v>372.4146908465991</v>
+        <v>367.9613541837774</v>
       </c>
       <c r="E115" t="n">
-        <v>383.895448836351</v>
+        <v>374.1274719238281</v>
       </c>
       <c r="F115" t="n">
-        <v>3485300</v>
+        <v>3984100</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3425,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46071</v>
+        <v>46076</v>
       </c>
       <c r="B116" t="n">
-        <v>375.3704833984375</v>
+        <v>372.8942820194261</v>
       </c>
       <c r="C116" t="n">
-        <v>376.9364905994225</v>
+        <v>375.9773711355021</v>
       </c>
       <c r="D116" t="n">
-        <v>371.4750744620919</v>
+        <v>361.726731079823</v>
       </c>
       <c r="E116" t="n">
-        <v>374.6168560607417</v>
+        <v>368.9792785644531</v>
       </c>
       <c r="F116" t="n">
-        <v>2982600</v>
+        <v>5495700</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3451,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46072</v>
+        <v>46077</v>
       </c>
       <c r="B117" t="n">
-        <v>370.5354614257812</v>
+        <v>380.8417107584177</v>
       </c>
       <c r="C117" t="n">
-        <v>375.5858190931522</v>
+        <v>385.9703852790173</v>
       </c>
       <c r="D117" t="n">
-        <v>369.3707754637165</v>
+        <v>374.0883361890514</v>
       </c>
       <c r="E117" t="n">
-        <v>375.5858190931522</v>
+        <v>376.3101196289062</v>
       </c>
       <c r="F117" t="n">
-        <v>2930900</v>
+        <v>5675800</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3477,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46073</v>
+        <v>46078</v>
       </c>
       <c r="B118" t="n">
-        <v>374.1274719238281</v>
+        <v>372.9725764492633</v>
       </c>
       <c r="C118" t="n">
-        <v>376.6428685046932</v>
+        <v>373.3347094680754</v>
       </c>
       <c r="D118" t="n">
-        <v>367.9613541837774</v>
+        <v>363.4786816926297</v>
       </c>
       <c r="E118" t="n">
-        <v>369.4294802998945</v>
+        <v>367.5894470214844</v>
       </c>
       <c r="F118" t="n">
-        <v>3984100</v>
+        <v>5036900</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3503,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="B119" t="n">
-        <v>368.9792785644531</v>
+        <v>370.3592916198801</v>
       </c>
       <c r="C119" t="n">
-        <v>375.9773711355021</v>
+        <v>373.3738607688525</v>
       </c>
       <c r="D119" t="n">
-        <v>361.726731079823</v>
+        <v>366.9728222621029</v>
       </c>
       <c r="E119" t="n">
-        <v>372.8942820194261</v>
+        <v>367.11962890625</v>
       </c>
       <c r="F119" t="n">
-        <v>5495700</v>
+        <v>2889400</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3529,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46077</v>
+        <v>46080</v>
       </c>
       <c r="B120" t="n">
-        <v>376.3101196289062</v>
+        <v>365.915758878878</v>
       </c>
       <c r="C120" t="n">
-        <v>385.9703852790173</v>
+        <v>374.0687697501482</v>
       </c>
       <c r="D120" t="n">
-        <v>374.0883361890514</v>
+        <v>364.4280684193005</v>
       </c>
       <c r="E120" t="n">
-        <v>380.8417107584177</v>
+        <v>372.6300048828125</v>
       </c>
       <c r="F120" t="n">
-        <v>5675800</v>
+        <v>4819500</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3555,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46078</v>
+        <v>46083</v>
       </c>
       <c r="B121" t="n">
-        <v>367.5894165039062</v>
+        <v>367.0315406467873</v>
       </c>
       <c r="C121" t="n">
-        <v>373.3346784735209</v>
+        <v>367.1391888948742</v>
       </c>
       <c r="D121" t="n">
-        <v>363.4786515163307</v>
+        <v>361.1590359964387</v>
       </c>
       <c r="E121" t="n">
-        <v>372.9725454847734</v>
+        <v>362.9305725097656</v>
       </c>
       <c r="F121" t="n">
-        <v>5036900</v>
+        <v>4537600</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3581,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46079</v>
+        <v>46084</v>
       </c>
       <c r="B122" t="n">
-        <v>367.11962890625</v>
+        <v>356.0010430233106</v>
       </c>
       <c r="C122" t="n">
-        <v>373.3738607688525</v>
+        <v>360.9437226682394</v>
       </c>
       <c r="D122" t="n">
-        <v>366.9728222621029</v>
+        <v>352.4677370657963</v>
       </c>
       <c r="E122" t="n">
-        <v>370.3592916198801</v>
+        <v>359.1232604980469</v>
       </c>
       <c r="F122" t="n">
-        <v>2889400</v>
+        <v>3964700</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3607,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46080</v>
+        <v>46085</v>
       </c>
       <c r="B123" t="n">
-        <v>372.6300048828125</v>
+        <v>358.4185545746917</v>
       </c>
       <c r="C123" t="n">
-        <v>374.0687697501482</v>
+        <v>361.716939988571</v>
       </c>
       <c r="D123" t="n">
-        <v>364.4280684193005</v>
+        <v>353.8282109374275</v>
       </c>
       <c r="E123" t="n">
-        <v>365.915758878878</v>
+        <v>361.2666931152344</v>
       </c>
       <c r="F123" t="n">
-        <v>4819500</v>
+        <v>4324400</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3633,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="B124" t="n">
-        <v>362.9305419921875</v>
+        <v>358.340254529235</v>
       </c>
       <c r="C124" t="n">
-        <v>367.139158023408</v>
+        <v>359.1819957877215</v>
       </c>
       <c r="D124" t="n">
-        <v>361.159005627823</v>
+        <v>351.5673154097268</v>
       </c>
       <c r="E124" t="n">
-        <v>367.0315097843729</v>
+        <v>353.9945983886719</v>
       </c>
       <c r="F124" t="n">
-        <v>4537600</v>
+        <v>4752200</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3659,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="B125" t="n">
-        <v>359.1232604980469</v>
+        <v>349.9425840615119</v>
       </c>
       <c r="C125" t="n">
-        <v>360.9437226682394</v>
+        <v>351.8120017521521</v>
       </c>
       <c r="D125" t="n">
-        <v>352.4677370657963</v>
+        <v>345.7143732597218</v>
       </c>
       <c r="E125" t="n">
-        <v>356.0010430233106</v>
+        <v>350.3145141601562</v>
       </c>
       <c r="F125" t="n">
-        <v>3964700</v>
+        <v>4167400</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3685,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46085</v>
+        <v>46090</v>
       </c>
       <c r="B126" t="n">
-        <v>361.2666931152344</v>
+        <v>348.0437790706712</v>
       </c>
       <c r="C126" t="n">
-        <v>361.716939988571</v>
+        <v>348.9148517222478</v>
       </c>
       <c r="D126" t="n">
-        <v>353.8282109374275</v>
+        <v>338.2954297848507</v>
       </c>
       <c r="E126" t="n">
-        <v>358.4185545746917</v>
+        <v>346.047119140625</v>
       </c>
       <c r="F126" t="n">
-        <v>4324400</v>
+        <v>4224500</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3711,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="B127" t="n">
-        <v>353.9945678710938</v>
+        <v>345.5381703207324</v>
       </c>
       <c r="C127" t="n">
-        <v>359.1819648229422</v>
+        <v>353.9554326757943</v>
       </c>
       <c r="D127" t="n">
-        <v>351.5672851014027</v>
+        <v>343.5610747056572</v>
       </c>
       <c r="E127" t="n">
-        <v>358.3402236370215</v>
+        <v>349.5608215332031</v>
       </c>
       <c r="F127" t="n">
-        <v>4752200</v>
+        <v>3986000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3737,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="B128" t="n">
-        <v>350.3145141601562</v>
+        <v>347.9067729324123</v>
       </c>
       <c r="C128" t="n">
-        <v>351.8120017521521</v>
+        <v>348.7485142053993</v>
       </c>
       <c r="D128" t="n">
-        <v>345.7143732597218</v>
+        <v>341.6916989868697</v>
       </c>
       <c r="E128" t="n">
-        <v>349.9425840615119</v>
+        <v>343.3849487304688</v>
       </c>
       <c r="F128" t="n">
-        <v>4167400</v>
+        <v>3197100</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3763,25 +3771,25 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="B129" t="n">
-        <v>346.047119140625</v>
+        <v>340.9512591186561</v>
       </c>
       <c r="C129" t="n">
-        <v>348.9148517222478</v>
+        <v>343.5425880232349</v>
       </c>
       <c r="D129" t="n">
-        <v>338.2954297848507</v>
+        <v>333.719202328884</v>
       </c>
       <c r="E129" t="n">
-        <v>348.0437790706712</v>
+        <v>333.94580078125</v>
       </c>
       <c r="F129" t="n">
-        <v>4224500</v>
+        <v>3893600</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -3789,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="B130" t="n">
-        <v>349.5608520507812</v>
+        <v>336.6651978613972</v>
       </c>
       <c r="C130" t="n">
-        <v>353.9554635770335</v>
+        <v>338.3697677547303</v>
       </c>
       <c r="D130" t="n">
-        <v>343.5611046994417</v>
+        <v>333.0590172641502</v>
       </c>
       <c r="E130" t="n">
-        <v>345.5382004871225</v>
+        <v>334.0443115234375</v>
       </c>
       <c r="F130" t="n">
-        <v>3986000</v>
+        <v>2531900</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3815,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46092</v>
+        <v>46097</v>
       </c>
       <c r="B131" t="n">
-        <v>343.3849182128906</v>
+        <v>337.4041886890553</v>
       </c>
       <c r="C131" t="n">
-        <v>348.7484832111462</v>
+        <v>340.1630007521627</v>
       </c>
       <c r="D131" t="n">
-        <v>341.6916686197754</v>
+        <v>335.6405034404279</v>
       </c>
       <c r="E131" t="n">
-        <v>347.906742012967</v>
+        <v>337.5421142578125</v>
       </c>
       <c r="F131" t="n">
-        <v>3197100</v>
+        <v>3194400</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3841,25 +3849,25 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46093</v>
+        <v>46098</v>
       </c>
       <c r="B132" t="n">
-        <v>333.94580078125</v>
+        <v>339.81816704201</v>
       </c>
       <c r="C132" t="n">
-        <v>343.5425880232349</v>
+        <v>341.6803576413574</v>
       </c>
       <c r="D132" t="n">
-        <v>333.719202328884</v>
+        <v>335.9262425125186</v>
       </c>
       <c r="E132" t="n">
-        <v>340.9512591186561</v>
+        <v>336.4090270996094</v>
       </c>
       <c r="F132" t="n">
-        <v>3893600</v>
+        <v>3075900</v>
       </c>
       <c r="G132" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -3867,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46094</v>
+        <v>46099</v>
       </c>
       <c r="B133" t="n">
-        <v>334.0443115234375</v>
+        <v>333.6206668009991</v>
       </c>
       <c r="C133" t="n">
-        <v>338.3697677547303</v>
+        <v>334.8030019580219</v>
       </c>
       <c r="D133" t="n">
-        <v>333.0590172641502</v>
+        <v>325.2850851722408</v>
       </c>
       <c r="E133" t="n">
-        <v>336.6651978613972</v>
+        <v>326.0634460449219</v>
       </c>
       <c r="F133" t="n">
-        <v>2531900</v>
+        <v>3592200</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3893,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46097</v>
+        <v>46100</v>
       </c>
       <c r="B134" t="n">
-        <v>337.5421142578125</v>
+        <v>324.1224241388957</v>
       </c>
       <c r="C134" t="n">
-        <v>340.1630007521627</v>
+        <v>325.3737672197113</v>
       </c>
       <c r="D134" t="n">
-        <v>335.6405034404279</v>
+        <v>319.8561127917808</v>
       </c>
       <c r="E134" t="n">
-        <v>337.4041886890553</v>
+        <v>323.3834533691406</v>
       </c>
       <c r="F134" t="n">
-        <v>3194400</v>
+        <v>3845400</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3919,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46098</v>
+        <v>46101</v>
       </c>
       <c r="B135" t="n">
-        <v>336.4090270996094</v>
+        <v>322.930233272276</v>
       </c>
       <c r="C135" t="n">
-        <v>341.6803576413574</v>
+        <v>325.3737741611631</v>
       </c>
       <c r="D135" t="n">
-        <v>335.9262425125186</v>
+        <v>315.5503879828975</v>
       </c>
       <c r="E135" t="n">
-        <v>339.81816704201</v>
+        <v>316.0331726074219</v>
       </c>
       <c r="F135" t="n">
-        <v>3075900</v>
+        <v>9672200</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3945,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46099</v>
+        <v>46104</v>
       </c>
       <c r="B136" t="n">
-        <v>326.0634460449219</v>
+        <v>327.1078722975504</v>
       </c>
       <c r="C136" t="n">
-        <v>334.8030019580219</v>
+        <v>329.7977367855016</v>
       </c>
       <c r="D136" t="n">
-        <v>325.2850851722408</v>
+        <v>323.3834607358939</v>
       </c>
       <c r="E136" t="n">
-        <v>333.6206668009991</v>
+        <v>326.0339050292969</v>
       </c>
       <c r="F136" t="n">
-        <v>3592200</v>
+        <v>5806300</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3971,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46100</v>
+        <v>46105</v>
       </c>
       <c r="B137" t="n">
-        <v>323.3834533691406</v>
+        <v>321.1073977566388</v>
       </c>
       <c r="C137" t="n">
-        <v>325.3737672197113</v>
+        <v>327.6300410369481</v>
       </c>
       <c r="D137" t="n">
-        <v>319.8561127917808</v>
+        <v>318.2697454376269</v>
       </c>
       <c r="E137" t="n">
-        <v>324.1224241388957</v>
+        <v>326.0437316894531</v>
       </c>
       <c r="F137" t="n">
-        <v>3845400</v>
+        <v>4566400</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -3997,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46101</v>
+        <v>46106</v>
       </c>
       <c r="B138" t="n">
-        <v>316.0331726074219</v>
+        <v>330.0736126071158</v>
       </c>
       <c r="C138" t="n">
-        <v>325.3737741611631</v>
+        <v>332.2314096741407</v>
       </c>
       <c r="D138" t="n">
-        <v>315.5503879828975</v>
+        <v>322.1813951135094</v>
       </c>
       <c r="E138" t="n">
-        <v>322.930233272276</v>
+        <v>327.6202392578125</v>
       </c>
       <c r="F138" t="n">
-        <v>9672200</v>
+        <v>4397800</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4023,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46104</v>
+        <v>46107</v>
       </c>
       <c r="B139" t="n">
-        <v>326.0339050292969</v>
+        <v>326.5659345775528</v>
       </c>
       <c r="C139" t="n">
-        <v>329.7977367855016</v>
+        <v>329.2065159991698</v>
       </c>
       <c r="D139" t="n">
-        <v>323.3834607358939</v>
+        <v>321.7872513641968</v>
       </c>
       <c r="E139" t="n">
-        <v>327.1078722975504</v>
+        <v>323.6001892089844</v>
       </c>
       <c r="F139" t="n">
-        <v>5806300</v>
+        <v>3448400</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4049,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46105</v>
+        <v>46108</v>
       </c>
       <c r="B140" t="n">
-        <v>326.0437316894531</v>
+        <v>322.6838998401017</v>
       </c>
       <c r="C140" t="n">
-        <v>327.6300410369481</v>
+        <v>322.7233200333912</v>
       </c>
       <c r="D140" t="n">
-        <v>318.2697454376269</v>
+        <v>316.0233004076466</v>
       </c>
       <c r="E140" t="n">
-        <v>321.1073977566388</v>
+        <v>316.919921875</v>
       </c>
       <c r="F140" t="n">
-        <v>4566400</v>
+        <v>3977400</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4075,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46106</v>
+        <v>46111</v>
       </c>
       <c r="B141" t="n">
-        <v>327.6202392578125</v>
+        <v>320.9300608492875</v>
       </c>
       <c r="C141" t="n">
-        <v>332.2314096741407</v>
+        <v>323.1666680872671</v>
       </c>
       <c r="D141" t="n">
-        <v>322.1813951135094</v>
+        <v>317.8362223118503</v>
       </c>
       <c r="E141" t="n">
-        <v>330.0736126071158</v>
+        <v>318.7427062988281</v>
       </c>
       <c r="F141" t="n">
-        <v>4397800</v>
+        <v>4066000</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4101,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46107</v>
+        <v>46112</v>
       </c>
       <c r="B142" t="n">
-        <v>323.6001892089844</v>
+        <v>323.6593250096307</v>
       </c>
       <c r="C142" t="n">
-        <v>329.2065159991698</v>
+        <v>326.5659553121756</v>
       </c>
       <c r="D142" t="n">
-        <v>321.7872513641968</v>
+        <v>318.6540430408731</v>
       </c>
       <c r="E142" t="n">
-        <v>326.5659345775528</v>
+        <v>324.053466796875</v>
       </c>
       <c r="F142" t="n">
-        <v>3448400</v>
+        <v>5749100</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4127,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46108</v>
+        <v>46113</v>
       </c>
       <c r="B143" t="n">
-        <v>316.919921875</v>
+        <v>324.5263842036645</v>
       </c>
       <c r="C143" t="n">
-        <v>322.7233200333912</v>
+        <v>328.1916802636729</v>
       </c>
       <c r="D143" t="n">
-        <v>316.0233004076466</v>
+        <v>322.98932747548</v>
       </c>
       <c r="E143" t="n">
-        <v>322.6838998401017</v>
+        <v>324.7135925292969</v>
       </c>
       <c r="F143" t="n">
-        <v>3977400</v>
+        <v>3386200</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4153,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46111</v>
+        <v>46114</v>
       </c>
       <c r="B144" t="n">
-        <v>318.7427062988281</v>
+        <v>318.841238474905</v>
       </c>
       <c r="C144" t="n">
-        <v>323.1666680872671</v>
+        <v>321.5015150184395</v>
       </c>
       <c r="D144" t="n">
-        <v>317.8362223118503</v>
+        <v>313.9738822734865</v>
       </c>
       <c r="E144" t="n">
-        <v>320.9300608492875</v>
+        <v>316.9002075195312</v>
       </c>
       <c r="F144" t="n">
-        <v>4066000</v>
+        <v>3732300</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4179,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46112</v>
+        <v>46118</v>
       </c>
       <c r="B145" t="n">
-        <v>324.053466796875</v>
+        <v>314.9985972226668</v>
       </c>
       <c r="C145" t="n">
-        <v>326.5659553121756</v>
+        <v>321.875932137731</v>
       </c>
       <c r="D145" t="n">
-        <v>318.6540430408731</v>
+        <v>314.2300688775543</v>
       </c>
       <c r="E145" t="n">
-        <v>323.6593250096307</v>
+        <v>321.8463745117188</v>
       </c>
       <c r="F145" t="n">
-        <v>5749100</v>
+        <v>2448300</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4205,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="B146" t="n">
-        <v>324.7135925292969</v>
+        <v>318.2500813990391</v>
       </c>
       <c r="C146" t="n">
-        <v>328.1916802636729</v>
+        <v>319.6097924401727</v>
       </c>
       <c r="D146" t="n">
-        <v>322.98932747548</v>
+        <v>310.673165290877</v>
       </c>
       <c r="E146" t="n">
-        <v>324.5263842036645</v>
+        <v>314.082275390625</v>
       </c>
       <c r="F146" t="n">
-        <v>3386200</v>
+        <v>4661600</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4231,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="B147" t="n">
-        <v>316.9002075195312</v>
+        <v>328.3591748751156</v>
       </c>
       <c r="C147" t="n">
-        <v>321.5015150184395</v>
+        <v>333.7979883682909</v>
       </c>
       <c r="D147" t="n">
-        <v>313.9738822734865</v>
+        <v>327.3640180499997</v>
       </c>
       <c r="E147" t="n">
-        <v>318.841238474905</v>
+        <v>331.2165222167969</v>
       </c>
       <c r="F147" t="n">
-        <v>3732300</v>
+        <v>4610600</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4257,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46118</v>
+        <v>46121</v>
       </c>
       <c r="B148" t="n">
-        <v>321.8463745117188</v>
+        <v>326.388616523007</v>
       </c>
       <c r="C148" t="n">
-        <v>321.875932137731</v>
+        <v>335.5617045306175</v>
       </c>
       <c r="D148" t="n">
-        <v>314.2300688775543</v>
+        <v>323.6199418005998</v>
       </c>
       <c r="E148" t="n">
-        <v>314.9985972226668</v>
+        <v>334.5862426757812</v>
       </c>
       <c r="F148" t="n">
-        <v>2448300</v>
+        <v>3002000</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4283,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="B149" t="n">
-        <v>314.082275390625</v>
+        <v>336.0248127567512</v>
       </c>
       <c r="C149" t="n">
-        <v>319.6097924401727</v>
+        <v>336.2120210994593</v>
       </c>
       <c r="D149" t="n">
-        <v>310.673165290877</v>
+        <v>330.8717121868362</v>
       </c>
       <c r="E149" t="n">
-        <v>318.2500813990391</v>
+        <v>332.3792114257812</v>
       </c>
       <c r="F149" t="n">
-        <v>4661600</v>
+        <v>3208300</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4309,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c r="B150" t="n">
-        <v>331.2165222167969</v>
+        <v>330.6056862577288</v>
       </c>
       <c r="C150" t="n">
-        <v>333.7979883682909</v>
+        <v>336.4189171136328</v>
       </c>
       <c r="D150" t="n">
-        <v>327.3640180499997</v>
+        <v>327.0487578932272</v>
       </c>
       <c r="E150" t="n">
-        <v>328.3591748751156</v>
+        <v>336.1430358886719</v>
       </c>
       <c r="F150" t="n">
-        <v>4610600</v>
+        <v>3741200</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4335,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46121</v>
+        <v>46126</v>
       </c>
       <c r="B151" t="n">
-        <v>334.5862426757812</v>
+        <v>335.9853517224209</v>
       </c>
       <c r="C151" t="n">
-        <v>335.5617045306175</v>
+        <v>337.7194792888092</v>
       </c>
       <c r="D151" t="n">
-        <v>323.6199418005998</v>
+        <v>333.3644653118732</v>
       </c>
       <c r="E151" t="n">
-        <v>326.388616523007</v>
+        <v>337.6701965332031</v>
       </c>
       <c r="F151" t="n">
-        <v>3002000</v>
+        <v>2882500</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4361,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46122</v>
+        <v>46127</v>
       </c>
       <c r="B152" t="n">
-        <v>332.3792114257812</v>
+        <v>336.8228847827696</v>
       </c>
       <c r="C152" t="n">
-        <v>336.2120210994593</v>
+        <v>337.236691577658</v>
       </c>
       <c r="D152" t="n">
-        <v>330.8717121868362</v>
+        <v>331.6697844276179</v>
       </c>
       <c r="E152" t="n">
-        <v>336.0248127567512</v>
+        <v>333.9261169433594</v>
       </c>
       <c r="F152" t="n">
-        <v>3208300</v>
+        <v>3365200</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4387,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46125</v>
+        <v>46128</v>
       </c>
       <c r="B153" t="n">
-        <v>336.1430358886719</v>
+        <v>334.9902184465357</v>
       </c>
       <c r="C153" t="n">
-        <v>336.4189171136328</v>
+        <v>336.9509746615948</v>
       </c>
       <c r="D153" t="n">
-        <v>327.0487578932272</v>
+        <v>331.7387590995254</v>
       </c>
       <c r="E153" t="n">
-        <v>330.6056862577288</v>
+        <v>332.1919860839844</v>
       </c>
       <c r="F153" t="n">
-        <v>3741200</v>
+        <v>2856700</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4413,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="B154" t="n">
-        <v>337.6701965332031</v>
+        <v>337.7982823274818</v>
       </c>
       <c r="C154" t="n">
-        <v>337.7194792888092</v>
+        <v>346.8432764669682</v>
       </c>
       <c r="D154" t="n">
-        <v>333.3644653118732</v>
+        <v>337.7982823274818</v>
       </c>
       <c r="E154" t="n">
-        <v>335.9853517224209</v>
+        <v>344.2618103027344</v>
       </c>
       <c r="F154" t="n">
-        <v>2882500</v>
+        <v>4930400</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4439,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46127</v>
+        <v>46132</v>
       </c>
       <c r="B155" t="n">
-        <v>333.9261169433594</v>
+        <v>343.2174366312315</v>
       </c>
       <c r="C155" t="n">
-        <v>337.236691577658</v>
+        <v>346.0058365319325</v>
       </c>
       <c r="D155" t="n">
-        <v>331.6697844276179</v>
+        <v>338.5668460102951</v>
       </c>
       <c r="E155" t="n">
-        <v>336.8228847827696</v>
+        <v>345.8284606933594</v>
       </c>
       <c r="F155" t="n">
-        <v>3365200</v>
+        <v>3260900</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4465,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46128</v>
+        <v>46133</v>
       </c>
       <c r="B156" t="n">
-        <v>332.1919860839844</v>
+        <v>347.7399078982703</v>
       </c>
       <c r="C156" t="n">
-        <v>336.9509746615948</v>
+        <v>348.350785549426</v>
       </c>
       <c r="D156" t="n">
-        <v>331.7387590995254</v>
+        <v>337.9263851511736</v>
       </c>
       <c r="E156" t="n">
-        <v>334.9902184465357</v>
+        <v>338.8624267578125</v>
       </c>
       <c r="F156" t="n">
-        <v>2856700</v>
+        <v>3081000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4491,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="B157" t="n">
-        <v>344.2618103027344</v>
+        <v>338.8920183636698</v>
       </c>
       <c r="C157" t="n">
-        <v>346.8432764669682</v>
+        <v>340.163026480594</v>
       </c>
       <c r="D157" t="n">
-        <v>337.7982823274818</v>
+        <v>332.9506943790196</v>
       </c>
       <c r="E157" t="n">
-        <v>337.7982823274818</v>
+        <v>334.5074462890625</v>
       </c>
       <c r="F157" t="n">
-        <v>4930400</v>
+        <v>2855800</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4517,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="B158" t="n">
-        <v>345.8284606933594</v>
+        <v>334.5074474516935</v>
       </c>
       <c r="C158" t="n">
-        <v>346.0058365319325</v>
+        <v>335.81787576814</v>
       </c>
       <c r="D158" t="n">
-        <v>338.5668460102951</v>
+        <v>331.9259809451064</v>
       </c>
       <c r="E158" t="n">
-        <v>343.2174366312315</v>
+        <v>335.1577453613281</v>
       </c>
       <c r="F158" t="n">
-        <v>3260900</v>
+        <v>2712400</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4543,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="B159" t="n">
-        <v>338.8624267578125</v>
+        <v>332.9112571246521</v>
       </c>
       <c r="C159" t="n">
-        <v>348.350785549426</v>
+        <v>335.2660949665313</v>
       </c>
       <c r="D159" t="n">
-        <v>337.9263851511736</v>
+        <v>329.758303202367</v>
       </c>
       <c r="E159" t="n">
-        <v>347.7399078982703</v>
+        <v>330.9505310058594</v>
       </c>
       <c r="F159" t="n">
-        <v>3081000</v>
+        <v>3255900</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4569,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46134</v>
+        <v>46139</v>
       </c>
       <c r="B160" t="n">
-        <v>334.5074462890625</v>
+        <v>329.5612640898174</v>
       </c>
       <c r="C160" t="n">
-        <v>340.163026480594</v>
+        <v>332.4186116830558</v>
       </c>
       <c r="D160" t="n">
-        <v>332.9506943790196</v>
+        <v>327.2556789255299</v>
       </c>
       <c r="E160" t="n">
-        <v>338.8920183636698</v>
+        <v>327.4132995605469</v>
       </c>
       <c r="F160" t="n">
-        <v>2855800</v>
+        <v>3282900</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4595,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46135</v>
+        <v>46140</v>
       </c>
       <c r="B161" t="n">
-        <v>335.1577453613281</v>
+        <v>329.5316980954363</v>
       </c>
       <c r="C161" t="n">
-        <v>335.81787576814</v>
+        <v>330.9899144482985</v>
       </c>
       <c r="D161" t="n">
-        <v>331.9259809451064</v>
+        <v>322.5459348903251</v>
       </c>
       <c r="E161" t="n">
-        <v>334.5074474516935</v>
+        <v>324.220947265625</v>
       </c>
       <c r="F161" t="n">
-        <v>2712400</v>
+        <v>4279300</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4621,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="B162" t="n">
-        <v>330.9505310058594</v>
+        <v>320.8709611177203</v>
       </c>
       <c r="C162" t="n">
-        <v>335.2660949665313</v>
+        <v>321.0483068839262</v>
       </c>
       <c r="D162" t="n">
-        <v>329.758303202367</v>
+        <v>314.3581498388285</v>
       </c>
       <c r="E162" t="n">
-        <v>332.9112571246521</v>
+        <v>318.0628662109375</v>
       </c>
       <c r="F162" t="n">
-        <v>3255900</v>
+        <v>4150000</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4647,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="B163" t="n">
-        <v>327.4132995605469</v>
+        <v>317.501224026995</v>
       </c>
       <c r="C163" t="n">
-        <v>332.4186116830558</v>
+        <v>325.2653478832921</v>
       </c>
       <c r="D163" t="n">
-        <v>327.2556789255299</v>
+        <v>317.501224026995</v>
       </c>
       <c r="E163" t="n">
-        <v>329.5612640898174</v>
+        <v>323.9647521972656</v>
       </c>
       <c r="F163" t="n">
-        <v>3282900</v>
+        <v>4317900</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4673,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46140</v>
+        <v>46143</v>
       </c>
       <c r="B164" t="n">
-        <v>324.220947265625</v>
+        <v>325.245658285994</v>
       </c>
       <c r="C164" t="n">
-        <v>330.9899144482985</v>
+        <v>325.6594650583568</v>
       </c>
       <c r="D164" t="n">
-        <v>322.5459348903251</v>
+        <v>318.6047541787617</v>
       </c>
       <c r="E164" t="n">
-        <v>329.5316980954363</v>
+        <v>319.1171264648438</v>
       </c>
       <c r="F164" t="n">
-        <v>4279300</v>
+        <v>3865300</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4699,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46141</v>
+        <v>46146</v>
       </c>
       <c r="B165" t="n">
-        <v>318.0628662109375</v>
+        <v>317.3436008490747</v>
       </c>
       <c r="C165" t="n">
-        <v>321.0483068839262</v>
+        <v>317.3436008490747</v>
       </c>
       <c r="D165" t="n">
-        <v>314.3581498388285</v>
+        <v>307.6680328846103</v>
       </c>
       <c r="E165" t="n">
-        <v>320.8709611177203</v>
+        <v>307.82568359375</v>
       </c>
       <c r="F165" t="n">
-        <v>4150000</v>
+        <v>6396100</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4725,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46142</v>
+        <v>46147</v>
       </c>
       <c r="B166" t="n">
-        <v>323.9647521972656</v>
+        <v>308.8011039225745</v>
       </c>
       <c r="C166" t="n">
-        <v>325.2653478832921</v>
+        <v>312.959047256485</v>
       </c>
       <c r="D166" t="n">
-        <v>317.501224026995</v>
+        <v>305.8353583254913</v>
       </c>
       <c r="E166" t="n">
-        <v>317.501224026995</v>
+        <v>310.7815551757812</v>
       </c>
       <c r="F166" t="n">
-        <v>4317900</v>
+        <v>6391400</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4751,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46143</v>
+        <v>46148</v>
       </c>
       <c r="B167" t="n">
-        <v>319.1171264648438</v>
+        <v>317.225379625856</v>
       </c>
       <c r="C167" t="n">
-        <v>325.6594650583568</v>
+        <v>320.457144085882</v>
       </c>
       <c r="D167" t="n">
-        <v>318.6047541787617</v>
+        <v>314.6537756503886</v>
       </c>
       <c r="E167" t="n">
-        <v>325.245658285994</v>
+        <v>318.2993469238281</v>
       </c>
       <c r="F167" t="n">
-        <v>3865300</v>
+        <v>5455900</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4777,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="B168" t="n">
-        <v>307.82568359375</v>
+        <v>320.2305285570251</v>
       </c>
       <c r="C168" t="n">
-        <v>317.3436008490747</v>
+        <v>322.6740393180987</v>
       </c>
       <c r="D168" t="n">
-        <v>307.6680328846103</v>
+        <v>317.688452277705</v>
       </c>
       <c r="E168" t="n">
-        <v>317.3436008490747</v>
+        <v>317.8953857421875</v>
       </c>
       <c r="F168" t="n">
-        <v>6396100</v>
+        <v>4411700</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4803,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46147</v>
+        <v>46150</v>
       </c>
       <c r="B169" t="n">
-        <v>310.7815551757812</v>
+        <v>317.9347780414561</v>
       </c>
       <c r="C169" t="n">
-        <v>312.959047256485</v>
+        <v>319.2353738179666</v>
       </c>
       <c r="D169" t="n">
-        <v>305.8353583254913</v>
+        <v>312.1412423722705</v>
       </c>
       <c r="E169" t="n">
-        <v>308.8011039225745</v>
+        <v>312.7817077636719</v>
       </c>
       <c r="F169" t="n">
-        <v>6391400</v>
+        <v>4995500</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4829,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="B170" t="n">
-        <v>318.2993469238281</v>
+        <v>311.8456552875821</v>
       </c>
       <c r="C170" t="n">
-        <v>320.457144085882</v>
+        <v>312.4565329608662</v>
       </c>
       <c r="D170" t="n">
-        <v>314.6537756503886</v>
+        <v>305.1554983709962</v>
       </c>
       <c r="E170" t="n">
-        <v>317.225379625856</v>
+        <v>306.8206481933594</v>
       </c>
       <c r="F170" t="n">
-        <v>5455900</v>
+        <v>4335700</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4855,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46149</v>
+        <v>46154</v>
       </c>
       <c r="B171" t="n">
-        <v>317.8953857421875</v>
+        <v>308.6237547613812</v>
       </c>
       <c r="C171" t="n">
-        <v>322.6740393180987</v>
+        <v>310.150948950067</v>
       </c>
       <c r="D171" t="n">
-        <v>317.688452277705</v>
+        <v>304.5643168514869</v>
       </c>
       <c r="E171" t="n">
-        <v>320.2305285570251</v>
+        <v>305.8944702148438</v>
       </c>
       <c r="F171" t="n">
-        <v>4411700</v>
+        <v>4225700</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4881,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46150</v>
+        <v>46155</v>
       </c>
       <c r="B172" t="n">
-        <v>312.7817077636719</v>
+        <v>303.0863866663159</v>
       </c>
       <c r="C172" t="n">
-        <v>319.2353738179666</v>
+        <v>303.1652270544281</v>
       </c>
       <c r="D172" t="n">
-        <v>312.1412423722705</v>
+        <v>294.8690352302997</v>
       </c>
       <c r="E172" t="n">
-        <v>317.9347780414561</v>
+        <v>298.1007995605469</v>
       </c>
       <c r="F172" t="n">
-        <v>4995500</v>
+        <v>6307800</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4907,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="B173" t="n">
-        <v>306.8206481933594</v>
+        <v>300.5738791526044</v>
       </c>
       <c r="C173" t="n">
-        <v>312.4565329608662</v>
+        <v>301.4803631461129</v>
       </c>
       <c r="D173" t="n">
-        <v>305.1554983709962</v>
+        <v>296.9874235077401</v>
       </c>
       <c r="E173" t="n">
-        <v>311.8456552875821</v>
+        <v>299.8743286132812</v>
       </c>
       <c r="F173" t="n">
-        <v>4335700</v>
+        <v>5072600</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4933,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="B174" t="n">
-        <v>305.8944702148438</v>
+        <v>295.8937302385283</v>
       </c>
       <c r="C174" t="n">
-        <v>310.150948950067</v>
+        <v>298.4751965058313</v>
       </c>
       <c r="D174" t="n">
-        <v>304.5643168514869</v>
+        <v>292.5141779899232</v>
       </c>
       <c r="E174" t="n">
-        <v>308.6237547613812</v>
+        <v>293.1349182128906</v>
       </c>
       <c r="F174" t="n">
-        <v>4225700</v>
+        <v>6121500</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4959,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="B175" t="n">
-        <v>298.1007995605469</v>
+        <v>294.8493301065311</v>
       </c>
       <c r="C175" t="n">
-        <v>303.1652270544281</v>
+        <v>299.3127122467453</v>
       </c>
       <c r="D175" t="n">
-        <v>294.8690352302997</v>
+        <v>292.9279941234309</v>
       </c>
       <c r="E175" t="n">
-        <v>303.0863866663159</v>
+        <v>295.4010925292969</v>
       </c>
       <c r="F175" t="n">
-        <v>6307800</v>
+        <v>6366100</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4985,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46156</v>
+        <v>46161</v>
       </c>
       <c r="B176" t="n">
-        <v>299.8743286132812</v>
+        <v>287.5778334831647</v>
       </c>
       <c r="C176" t="n">
-        <v>301.4803631461129</v>
+        <v>298.7313718247998</v>
       </c>
       <c r="D176" t="n">
-        <v>296.9874235077401</v>
+        <v>284.84857918279</v>
       </c>
       <c r="E176" t="n">
-        <v>300.5738791526044</v>
+        <v>297.9924011230469</v>
       </c>
       <c r="F176" t="n">
-        <v>5072600</v>
+        <v>8692500</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5011,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="B177" t="n">
-        <v>293.1349182128906</v>
+        <v>296.6327042526405</v>
       </c>
       <c r="C177" t="n">
-        <v>298.4751965058313</v>
+        <v>306.4363947204983</v>
       </c>
       <c r="D177" t="n">
-        <v>292.5141779899232</v>
+        <v>292.307277842878</v>
       </c>
       <c r="E177" t="n">
-        <v>295.8937302385283</v>
+        <v>306.0126953125</v>
       </c>
       <c r="F177" t="n">
-        <v>6121500</v>
+        <v>5810900</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5037,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46160</v>
+        <v>46163</v>
       </c>
       <c r="B178" t="n">
-        <v>295.4010925292969</v>
+        <v>301.8547523557064</v>
       </c>
       <c r="C178" t="n">
-        <v>299.3127122467453</v>
+        <v>309.3725528012548</v>
       </c>
       <c r="D178" t="n">
-        <v>292.9279941234309</v>
+        <v>299.9038888531578</v>
       </c>
       <c r="E178" t="n">
-        <v>294.8493301065311</v>
+        <v>309.1656494140625</v>
       </c>
       <c r="F178" t="n">
-        <v>6366100</v>
+        <v>4516600</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5063,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46161</v>
+        <v>46164</v>
       </c>
       <c r="B179" t="n">
-        <v>297.9924011230469</v>
+        <v>309.8750586089163</v>
       </c>
       <c r="C179" t="n">
-        <v>298.7313718247998</v>
+        <v>310.3282855694948</v>
       </c>
       <c r="D179" t="n">
-        <v>284.84857918279</v>
+        <v>306.8797555054846</v>
       </c>
       <c r="E179" t="n">
-        <v>287.5778334831647</v>
+        <v>308.4660949707031</v>
       </c>
       <c r="F179" t="n">
-        <v>8692500</v>
+        <v>2963800</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5089,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46162</v>
+        <v>46168</v>
       </c>
       <c r="B180" t="n">
-        <v>306.0126953125</v>
+        <v>310.4268164834753</v>
       </c>
       <c r="C180" t="n">
-        <v>306.4363947204983</v>
+        <v>312.1313864292915</v>
       </c>
       <c r="D180" t="n">
-        <v>292.307277842878</v>
+        <v>304.416515303009</v>
       </c>
       <c r="E180" t="n">
-        <v>296.6327042526405</v>
+        <v>305.9732971191406</v>
       </c>
       <c r="F180" t="n">
-        <v>5810900</v>
+        <v>6978200</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5115,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46163</v>
+        <v>46169</v>
       </c>
       <c r="B181" t="n">
-        <v>309.1656494140625</v>
+        <v>310.1213933019174</v>
       </c>
       <c r="C181" t="n">
-        <v>309.3725528012548</v>
+        <v>316.2794829226862</v>
       </c>
       <c r="D181" t="n">
-        <v>299.9038888531578</v>
+        <v>309.8849322824949</v>
       </c>
       <c r="E181" t="n">
-        <v>301.8547523557064</v>
+        <v>313.1758117675781</v>
       </c>
       <c r="F181" t="n">
-        <v>4516600</v>
+        <v>5990100</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5141,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="B182" t="n">
-        <v>308.4660949707031</v>
+        <v>312.7816726974261</v>
       </c>
       <c r="C182" t="n">
-        <v>310.3282855694948</v>
+        <v>317.1465190224739</v>
       </c>
       <c r="D182" t="n">
-        <v>306.8797555054846</v>
+        <v>310.5253404383965</v>
       </c>
       <c r="E182" t="n">
-        <v>309.8750586089163</v>
+        <v>316.4863586425781</v>
       </c>
       <c r="F182" t="n">
-        <v>2963800</v>
+        <v>6818900</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5167,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46168</v>
+        <v>46171</v>
       </c>
       <c r="B183" t="n">
-        <v>305.9732971191406</v>
+        <v>315.7671367684214</v>
       </c>
       <c r="C183" t="n">
-        <v>312.1313864292915</v>
+        <v>317.3633087672889</v>
       </c>
       <c r="D183" t="n">
-        <v>304.416515303009</v>
+        <v>312.3383016854047</v>
       </c>
       <c r="E183" t="n">
-        <v>310.4268164834753</v>
+        <v>312.4762573242188</v>
       </c>
       <c r="F183" t="n">
-        <v>6978200</v>
+        <v>6963300</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5193,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46169</v>
+        <v>46174</v>
       </c>
       <c r="B184" t="n">
-        <v>313.1758117675781</v>
+        <v>310.4958029229232</v>
       </c>
       <c r="C184" t="n">
-        <v>316.2794829226862</v>
+        <v>311.2446362258477</v>
       </c>
       <c r="D184" t="n">
-        <v>309.8849322824949</v>
+        <v>303.1652107990409</v>
       </c>
       <c r="E184" t="n">
-        <v>310.1213933019174</v>
+        <v>306.12109375</v>
       </c>
       <c r="F184" t="n">
-        <v>5990100</v>
+        <v>4544200</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5219,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46170</v>
+        <v>46175</v>
       </c>
       <c r="B185" t="n">
-        <v>316.4863586425781</v>
+        <v>305.4215416998635</v>
       </c>
       <c r="C185" t="n">
-        <v>317.1465190224739</v>
+        <v>307.6088962755514</v>
       </c>
       <c r="D185" t="n">
-        <v>310.5253404383965</v>
+        <v>304.0322731114999</v>
       </c>
       <c r="E185" t="n">
-        <v>312.7816726974261</v>
+        <v>306.9388732910156</v>
       </c>
       <c r="F185" t="n">
-        <v>6818900</v>
+        <v>4310000</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5245,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B186" t="n">
-        <v>312.4762573242188</v>
+        <v>303.411554685127</v>
       </c>
       <c r="C186" t="n">
-        <v>317.3633087672889</v>
+        <v>308.9094841116081</v>
       </c>
       <c r="D186" t="n">
-        <v>312.3383016854047</v>
+        <v>302.6036060746125</v>
       </c>
       <c r="E186" t="n">
-        <v>315.7671367684214</v>
+        <v>308.3675842285156</v>
       </c>
       <c r="F186" t="n">
-        <v>6963300</v>
+        <v>4328300</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5271,25 +5279,25 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46174</v>
+        <v>46177</v>
       </c>
       <c r="B187" t="n">
-        <v>306.12109375</v>
+        <v>315.5049467263879</v>
       </c>
       <c r="C187" t="n">
-        <v>311.2446362258477</v>
+        <v>318.403599213189</v>
       </c>
       <c r="D187" t="n">
-        <v>303.1652107990409</v>
+        <v>305.8560507855353</v>
       </c>
       <c r="E187" t="n">
-        <v>310.4958029229232</v>
+        <v>307.6826171875</v>
       </c>
       <c r="F187" t="n">
-        <v>4544200</v>
+        <v>4558600</v>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5297,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="B188" t="n">
-        <v>306.9388732910156</v>
+        <v>308.5561528759146</v>
       </c>
       <c r="C188" t="n">
-        <v>307.6088962755514</v>
+        <v>311.7525986238699</v>
       </c>
       <c r="D188" t="n">
-        <v>304.0322731114999</v>
+        <v>306.3722648476684</v>
       </c>
       <c r="E188" t="n">
-        <v>305.4215416998635</v>
+        <v>308.5065307617188</v>
       </c>
       <c r="F188" t="n">
-        <v>4310000</v>
+        <v>3946300</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5323,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46176</v>
+        <v>46181</v>
       </c>
       <c r="B189" t="n">
-        <v>308.3675842285156</v>
+        <v>306.6204514929628</v>
       </c>
       <c r="C189" t="n">
-        <v>308.9094841116081</v>
+        <v>311.4746638676563</v>
       </c>
       <c r="D189" t="n">
-        <v>302.6036060746125</v>
+        <v>304.8236946299612</v>
       </c>
       <c r="E189" t="n">
-        <v>303.411554685127</v>
+        <v>307.4443664550781</v>
       </c>
       <c r="F189" t="n">
-        <v>4328300</v>
+        <v>4381800</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5349,25 +5357,25 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46177</v>
+        <v>46182</v>
       </c>
       <c r="B190" t="n">
-        <v>307.6826171875</v>
+        <v>309.0723663566284</v>
       </c>
       <c r="C190" t="n">
-        <v>318.403599213189</v>
+        <v>320.5279554969379</v>
       </c>
       <c r="D190" t="n">
-        <v>305.8560507855353</v>
+        <v>308.000249988811</v>
       </c>
       <c r="E190" t="n">
-        <v>315.5049467263879</v>
+        <v>318.9793395996094</v>
       </c>
       <c r="F190" t="n">
-        <v>4558600</v>
+        <v>4875300</v>
       </c>
       <c r="G190" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5375,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46178</v>
+        <v>46183</v>
       </c>
       <c r="B191" t="n">
-        <v>308.5065307617188</v>
+        <v>320.9051596578416</v>
       </c>
       <c r="C191" t="n">
-        <v>311.7525986238699</v>
+        <v>321.6298303667879</v>
       </c>
       <c r="D191" t="n">
-        <v>306.3722648476684</v>
+        <v>316.4678580086006</v>
       </c>
       <c r="E191" t="n">
-        <v>308.5561528759146</v>
+        <v>316.5870056152344</v>
       </c>
       <c r="F191" t="n">
-        <v>3946300</v>
+        <v>4823800</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5401,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46181</v>
+        <v>46184</v>
       </c>
       <c r="B192" t="n">
-        <v>307.4443664550781</v>
+        <v>319.9323340788724</v>
       </c>
       <c r="C192" t="n">
-        <v>311.4746638676563</v>
+        <v>324.6376494749074</v>
       </c>
       <c r="D192" t="n">
-        <v>304.8236946299612</v>
+        <v>316.2196730066971</v>
       </c>
       <c r="E192" t="n">
-        <v>306.6204514929628</v>
+        <v>323.6251220703125</v>
       </c>
       <c r="F192" t="n">
-        <v>4381800</v>
+        <v>4656600</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5427,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46182</v>
+        <v>46185</v>
       </c>
       <c r="B193" t="n">
-        <v>318.9793395996094</v>
+        <v>326.0969127055492</v>
       </c>
       <c r="C193" t="n">
-        <v>320.5279554969379</v>
+        <v>328.598467157331</v>
       </c>
       <c r="D193" t="n">
-        <v>308.000249988811</v>
+        <v>322.9104034108394</v>
       </c>
       <c r="E193" t="n">
-        <v>309.0723663566284</v>
+        <v>325.9877319335938</v>
       </c>
       <c r="F193" t="n">
-        <v>4875300</v>
+        <v>3649000</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5453,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46183</v>
+        <v>46188</v>
       </c>
       <c r="B194" t="n">
-        <v>316.5870056152344</v>
+        <v>331.3184370072605</v>
       </c>
       <c r="C194" t="n">
-        <v>321.6298303667879</v>
+        <v>335.5274102103883</v>
       </c>
       <c r="D194" t="n">
-        <v>316.4678580086006</v>
+        <v>327.1293065910854</v>
       </c>
       <c r="E194" t="n">
-        <v>320.9051596578416</v>
+        <v>327.4072570800781</v>
       </c>
       <c r="F194" t="n">
-        <v>4823800</v>
+        <v>4695000</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5479,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46184</v>
+        <v>46189</v>
       </c>
       <c r="B195" t="n">
-        <v>323.6251220703125</v>
+        <v>329.4819549089526</v>
       </c>
       <c r="C195" t="n">
-        <v>324.6376494749074</v>
+        <v>335.7954145326594</v>
       </c>
       <c r="D195" t="n">
-        <v>316.2196730066971</v>
+        <v>327.337752500619</v>
       </c>
       <c r="E195" t="n">
-        <v>319.9323340788724</v>
+        <v>334.6240539550781</v>
       </c>
       <c r="F195" t="n">
-        <v>4656600</v>
+        <v>5131500</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5505,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46185</v>
+        <v>46190</v>
       </c>
       <c r="B196" t="n">
-        <v>325.9877319335938</v>
+        <v>333.5519799826949</v>
       </c>
       <c r="C196" t="n">
-        <v>328.598467157331</v>
+        <v>338.6543633465824</v>
       </c>
       <c r="D196" t="n">
-        <v>322.9104034108394</v>
+        <v>323.7839666314997</v>
       </c>
       <c r="E196" t="n">
-        <v>326.0969127055492</v>
+        <v>325.0843811035156</v>
       </c>
       <c r="F196" t="n">
-        <v>3649000</v>
+        <v>6085400</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5531,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="B197" t="n">
-        <v>327.4072570800781</v>
+        <v>329.2735121638814</v>
       </c>
       <c r="C197" t="n">
-        <v>335.5274102103883</v>
+        <v>335.5472561594589</v>
       </c>
       <c r="D197" t="n">
-        <v>327.1293065910854</v>
+        <v>328.4793462633244</v>
       </c>
       <c r="E197" t="n">
-        <v>331.3184370072605</v>
+        <v>331.8346252441406</v>
       </c>
       <c r="F197" t="n">
-        <v>4695000</v>
+        <v>10604400</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5557,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="B198" t="n">
-        <v>334.6240539550781</v>
+        <v>327.585930781475</v>
       </c>
       <c r="C198" t="n">
-        <v>335.7954145326594</v>
+        <v>329.30328611244</v>
       </c>
       <c r="D198" t="n">
-        <v>327.337752500619</v>
+        <v>323.9527013683971</v>
       </c>
       <c r="E198" t="n">
-        <v>329.4819549089526</v>
+        <v>324.2306518554688</v>
       </c>
       <c r="F198" t="n">
-        <v>5131500</v>
+        <v>4713600</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5583,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="B199" t="n">
-        <v>325.0843811035156</v>
+        <v>321.5007640397083</v>
       </c>
       <c r="C199" t="n">
-        <v>338.6543633465824</v>
+        <v>326.6130837898613</v>
       </c>
       <c r="D199" t="n">
-        <v>323.7839666314997</v>
+        <v>319.3466553723836</v>
       </c>
       <c r="E199" t="n">
-        <v>333.5519799826949</v>
+        <v>322.0765380859375</v>
       </c>
       <c r="F199" t="n">
-        <v>6085400</v>
+        <v>4788000</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5609,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46191</v>
+        <v>46197</v>
       </c>
       <c r="B200" t="n">
-        <v>331.8346252441406</v>
+        <v>326.7123600579221</v>
       </c>
       <c r="C200" t="n">
-        <v>335.5472561594589</v>
+        <v>340.4511116799111</v>
       </c>
       <c r="D200" t="n">
-        <v>328.4793462633244</v>
+        <v>325.3126710965327</v>
       </c>
       <c r="E200" t="n">
-        <v>329.2735121638814</v>
+        <v>340.3518371582031</v>
       </c>
       <c r="F200" t="n">
-        <v>10604400</v>
+        <v>6385000</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5635,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46195</v>
+        <v>46198</v>
       </c>
       <c r="B201" t="n">
-        <v>324.2306518554688</v>
+        <v>339.7463135650192</v>
       </c>
       <c r="C201" t="n">
-        <v>329.30328611244</v>
+        <v>346.0895828723475</v>
       </c>
       <c r="D201" t="n">
-        <v>323.9527013683971</v>
+        <v>339.3194664460809</v>
       </c>
       <c r="E201" t="n">
-        <v>327.585930781475</v>
+        <v>342.4761962890625</v>
       </c>
       <c r="F201" t="n">
-        <v>4713600</v>
+        <v>6974100</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5661,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46196</v>
+        <v>46199</v>
       </c>
       <c r="B202" t="n">
-        <v>322.0765380859375</v>
+        <v>345.3549840981078</v>
       </c>
       <c r="C202" t="n">
-        <v>326.6130837898613</v>
+        <v>347.9359702501276</v>
       </c>
       <c r="D202" t="n">
-        <v>319.3466553723836</v>
+        <v>343.3199926808538</v>
       </c>
       <c r="E202" t="n">
-        <v>321.5007640397083</v>
+        <v>346.3079528808594</v>
       </c>
       <c r="F202" t="n">
-        <v>4788000</v>
+        <v>7771700</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5687,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="B203" t="n">
-        <v>340.3518371582031</v>
+        <v>346.307966117321</v>
       </c>
       <c r="C203" t="n">
-        <v>340.4511116799111</v>
+        <v>348.779771593463</v>
       </c>
       <c r="D203" t="n">
-        <v>325.3126710965327</v>
+        <v>343.0122759730193</v>
       </c>
       <c r="E203" t="n">
-        <v>326.7123600579221</v>
+        <v>348.2437133789062</v>
       </c>
       <c r="F203" t="n">
-        <v>6385000</v>
+        <v>5786500</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5713,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46198</v>
+        <v>46203</v>
       </c>
       <c r="B204" t="n">
-        <v>342.4761962890625</v>
+        <v>348.1245733949154</v>
       </c>
       <c r="C204" t="n">
-        <v>346.0895828723475</v>
+        <v>350.9140147662578</v>
       </c>
       <c r="D204" t="n">
-        <v>339.3194664460809</v>
+        <v>344.7593579765289</v>
       </c>
       <c r="E204" t="n">
-        <v>339.7463135650192</v>
+        <v>350.1000061035156</v>
       </c>
       <c r="F204" t="n">
-        <v>6974100</v>
+        <v>4579000</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5739,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46199</v>
+        <v>46204</v>
       </c>
       <c r="B205" t="n">
-        <v>346.3079528808594</v>
+        <v>351.3905430525372</v>
       </c>
       <c r="C205" t="n">
-        <v>347.9359702501276</v>
+        <v>354.507557275585</v>
       </c>
       <c r="D205" t="n">
-        <v>343.3199926808538</v>
+        <v>348.2734985351562</v>
       </c>
       <c r="E205" t="n">
-        <v>345.3549840981078</v>
+        <v>348.2734985351562</v>
       </c>
       <c r="F205" t="n">
-        <v>7771700</v>
+        <v>4041300</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5765,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="B206" t="n">
-        <v>348.2437133789062</v>
+        <v>350.2588479333682</v>
       </c>
       <c r="C206" t="n">
-        <v>348.779771593463</v>
+        <v>355.5697168646199</v>
       </c>
       <c r="D206" t="n">
-        <v>343.0122759730193</v>
+        <v>345.1068121812833</v>
       </c>
       <c r="E206" t="n">
-        <v>346.307966117321</v>
+        <v>355.2818298339844</v>
       </c>
       <c r="F206" t="n">
-        <v>5786500</v>
+        <v>3110500</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5791,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46203</v>
+        <v>46209</v>
       </c>
       <c r="B207" t="n">
-        <v>350.1000061035156</v>
+        <v>355.2024317145021</v>
       </c>
       <c r="C207" t="n">
-        <v>350.9140147662578</v>
+        <v>356.2248957008094</v>
       </c>
       <c r="D207" t="n">
-        <v>344.7593579765289</v>
+        <v>343.2703427329958</v>
       </c>
       <c r="E207" t="n">
-        <v>348.1245733949154</v>
+        <v>348.0848693847656</v>
       </c>
       <c r="F207" t="n">
-        <v>4579000</v>
+        <v>4460800</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5817,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46204</v>
+        <v>46210</v>
       </c>
       <c r="B208" t="n">
-        <v>348.2734985351562</v>
+        <v>352.4626117928308</v>
       </c>
       <c r="C208" t="n">
-        <v>354.507557275585</v>
+        <v>352.8199940223038</v>
       </c>
       <c r="D208" t="n">
-        <v>348.2734985351562</v>
+        <v>341.9600214541982</v>
       </c>
       <c r="E208" t="n">
-        <v>351.3905430525372</v>
+        <v>342.6846618652344</v>
       </c>
       <c r="F208" t="n">
-        <v>4041300</v>
+        <v>3592800</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5843,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="B209" t="n">
-        <v>355.2818298339844</v>
+        <v>335.5174656966423</v>
       </c>
       <c r="C209" t="n">
-        <v>355.5697168646199</v>
+        <v>335.5174656966423</v>
       </c>
       <c r="D209" t="n">
-        <v>345.1068121812833</v>
+        <v>328.241100746865</v>
       </c>
       <c r="E209" t="n">
-        <v>350.2588479333682</v>
+        <v>333.75048828125</v>
       </c>
       <c r="F209" t="n">
-        <v>3110500</v>
+        <v>4192300</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5869,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46209</v>
+        <v>46212</v>
       </c>
       <c r="B210" t="n">
-        <v>348.0848693847656</v>
+        <v>335.2891698936722</v>
       </c>
       <c r="C210" t="n">
-        <v>356.2248957008094</v>
+        <v>338.2374444527704</v>
       </c>
       <c r="D210" t="n">
-        <v>343.2703427329958</v>
+        <v>333.1548737064404</v>
       </c>
       <c r="E210" t="n">
-        <v>355.2024317145021</v>
+        <v>336.2520751953125</v>
       </c>
       <c r="F210" t="n">
-        <v>4460800</v>
+        <v>2780800</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5895,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="B211" t="n">
-        <v>342.6846618652344</v>
+        <v>337.0660677396515</v>
       </c>
       <c r="C211" t="n">
-        <v>352.8199940223038</v>
+        <v>341.8805944502874</v>
       </c>
       <c r="D211" t="n">
-        <v>341.9600214541982</v>
+        <v>335.4281440922459</v>
       </c>
       <c r="E211" t="n">
-        <v>352.4626117928308</v>
+        <v>340.7886352539062</v>
       </c>
       <c r="F211" t="n">
-        <v>3592800</v>
+        <v>2748000</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5921,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46211</v>
+        <v>46216</v>
       </c>
       <c r="B212" t="n">
-        <v>333.75048828125</v>
+        <v>341.4835329455154</v>
       </c>
       <c r="C212" t="n">
-        <v>335.5174656966423</v>
+        <v>342.5853984087983</v>
       </c>
       <c r="D212" t="n">
-        <v>328.241100746865</v>
+        <v>332.9762178919015</v>
       </c>
       <c r="E212" t="n">
-        <v>335.5174656966423</v>
+        <v>334.6439208984375</v>
       </c>
       <c r="F212" t="n">
-        <v>4192300</v>
+        <v>3650400</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5947,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46212</v>
+        <v>46217</v>
       </c>
       <c r="B213" t="n">
-        <v>336.2520751953125</v>
+        <v>337.0362951640151</v>
       </c>
       <c r="C213" t="n">
-        <v>338.2374444527704</v>
+        <v>339.2499929294707</v>
       </c>
       <c r="D213" t="n">
-        <v>333.1548737064404</v>
+        <v>334.1078935040618</v>
       </c>
       <c r="E213" t="n">
-        <v>335.2891698936722</v>
+        <v>335.2693176269531</v>
       </c>
       <c r="F213" t="n">
-        <v>2780800</v>
+        <v>2807300</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5973,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="B214" t="n">
-        <v>340.7886352539062</v>
+        <v>336.5101711499915</v>
       </c>
       <c r="C214" t="n">
-        <v>341.8805944502874</v>
+        <v>343.7170716460562</v>
       </c>
       <c r="D214" t="n">
-        <v>335.4281440922459</v>
+        <v>334.7928460359882</v>
       </c>
       <c r="E214" t="n">
-        <v>337.0660677396515</v>
+        <v>338.9422607421875</v>
       </c>
       <c r="F214" t="n">
-        <v>2748000</v>
+        <v>3953100</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -5999,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="B215" t="n">
-        <v>334.6439208984375</v>
+        <v>339.0514198724459</v>
       </c>
       <c r="C215" t="n">
-        <v>342.5853984087983</v>
+        <v>348.2436891486228</v>
       </c>
       <c r="D215" t="n">
-        <v>332.9762178919015</v>
+        <v>338.148103527179</v>
       </c>
       <c r="E215" t="n">
-        <v>341.4835329455154</v>
+        <v>345.4740905761719</v>
       </c>
       <c r="F215" t="n">
-        <v>3650400</v>
+        <v>3810300</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6025,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46217</v>
+        <v>46220</v>
       </c>
       <c r="B216" t="n">
-        <v>335.2693176269531</v>
+        <v>346.3774576909258</v>
       </c>
       <c r="C216" t="n">
-        <v>339.2499929294707</v>
+        <v>351.3905334952897</v>
       </c>
       <c r="D216" t="n">
-        <v>334.1078935040618</v>
+        <v>335.6167594084301</v>
       </c>
       <c r="E216" t="n">
-        <v>337.0362951640151</v>
+        <v>336.3910522460938</v>
       </c>
       <c r="F216" t="n">
-        <v>2807300</v>
+        <v>4434000</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6051,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="B217" t="n">
-        <v>338.9422607421875</v>
+        <v>337.4829959680537</v>
       </c>
       <c r="C217" t="n">
-        <v>343.7170716460562</v>
+        <v>337.7113243396537</v>
       </c>
       <c r="D217" t="n">
-        <v>334.7928460359882</v>
+        <v>328.985617931225</v>
       </c>
       <c r="E217" t="n">
-        <v>336.5101711499915</v>
+        <v>330.6036987304688</v>
       </c>
       <c r="F217" t="n">
-        <v>3953100</v>
+        <v>4125300</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6077,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="B218" t="n">
-        <v>345.4740905761719</v>
+        <v>328.8764012920007</v>
       </c>
       <c r="C218" t="n">
-        <v>348.2436891486228</v>
+        <v>330.5639772575944</v>
       </c>
       <c r="D218" t="n">
-        <v>338.148103527179</v>
+        <v>324.6078695592594</v>
       </c>
       <c r="E218" t="n">
-        <v>339.0514198724459</v>
+        <v>329.1742248535156</v>
       </c>
       <c r="F218" t="n">
-        <v>3810300</v>
+        <v>3112600</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6103,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="B219" t="n">
-        <v>336.3910522460938</v>
+        <v>331.0901002710247</v>
       </c>
       <c r="C219" t="n">
-        <v>351.3905334952897</v>
+        <v>334.097933459434</v>
       </c>
       <c r="D219" t="n">
-        <v>335.6167594084301</v>
+        <v>328.2907223705125</v>
       </c>
       <c r="E219" t="n">
-        <v>346.3774576909258</v>
+        <v>329.0253295898438</v>
       </c>
       <c r="F219" t="n">
-        <v>4434000</v>
+        <v>2907700</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6129,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B220" t="n">
-        <v>330.6036987304688</v>
+        <v>322.9203055541834</v>
       </c>
       <c r="C220" t="n">
-        <v>337.7113243396537</v>
+        <v>325.8288946116248</v>
       </c>
       <c r="D220" t="n">
-        <v>328.985617931225</v>
+        <v>320.6867650845805</v>
       </c>
       <c r="E220" t="n">
-        <v>337.4829959680537</v>
+        <v>322.3346252441406</v>
       </c>
       <c r="F220" t="n">
-        <v>4125300</v>
+        <v>4523100</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6155,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="B221" t="n">
-        <v>329.1742248535156</v>
+        <v>322.6920194034342</v>
       </c>
       <c r="C221" t="n">
-        <v>330.5639772575944</v>
+        <v>331.0206281983068</v>
       </c>
       <c r="D221" t="n">
-        <v>324.6078695592594</v>
+        <v>320.8654832094117</v>
       </c>
       <c r="E221" t="n">
-        <v>328.8764012920007</v>
+        <v>330.5441589355469</v>
       </c>
       <c r="F221" t="n">
-        <v>3112600</v>
+        <v>3874500</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6181,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46225</v>
+        <v>46230</v>
       </c>
       <c r="B222" t="n">
-        <v>329.0253295898438</v>
+        <v>336.9072556737336</v>
       </c>
       <c r="C222" t="n">
-        <v>334.097933459434</v>
+        <v>339.3889672822994</v>
       </c>
       <c r="D222" t="n">
-        <v>328.2907223705125</v>
+        <v>332.8968012318786</v>
       </c>
       <c r="E222" t="n">
-        <v>331.0901002710247</v>
+        <v>333.6313781738281</v>
       </c>
       <c r="F222" t="n">
-        <v>2907700</v>
+        <v>3622400</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6207,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46226</v>
+        <v>46231</v>
       </c>
       <c r="B223" t="n">
-        <v>322.3346252441406</v>
+        <v>340.133473711892</v>
       </c>
       <c r="C223" t="n">
-        <v>325.8288946116248</v>
+        <v>346.8737804890717</v>
       </c>
       <c r="D223" t="n">
-        <v>320.6867650845805</v>
+        <v>340.0937578445657</v>
       </c>
       <c r="E223" t="n">
-        <v>322.9203055541834</v>
+        <v>341.9500732421875</v>
       </c>
       <c r="F223" t="n">
-        <v>4523100</v>
+        <v>4308000</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6233,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="B224" t="n">
-        <v>330.5441589355469</v>
+        <v>337.8900211320969</v>
       </c>
       <c r="C224" t="n">
-        <v>331.0206281983068</v>
+        <v>342.7442335347337</v>
       </c>
       <c r="D224" t="n">
-        <v>320.8654832094117</v>
+        <v>334.495026147691</v>
       </c>
       <c r="E224" t="n">
-        <v>322.6920194034342</v>
+        <v>335.7954406738281</v>
       </c>
       <c r="F224" t="n">
-        <v>3874500</v>
+        <v>4028500</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6259,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="B225" t="n">
-        <v>333.6313781738281</v>
+        <v>332.5394250801792</v>
       </c>
       <c r="C225" t="n">
-        <v>339.3889672822994</v>
+        <v>333.2343164610006</v>
       </c>
       <c r="D225" t="n">
-        <v>332.8968012318786</v>
+        <v>327.8341094785939</v>
       </c>
       <c r="E225" t="n">
-        <v>336.9072556737336</v>
+        <v>330.9114379882812</v>
       </c>
       <c r="F225" t="n">
-        <v>3622400</v>
+        <v>6275400</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6285,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="B226" t="n">
-        <v>341.9500732421875</v>
+        <v>330.0080852280822</v>
       </c>
       <c r="C226" t="n">
-        <v>346.8737804890717</v>
+        <v>331.5566708480175</v>
       </c>
       <c r="D226" t="n">
-        <v>340.0937578445657</v>
+        <v>326.3946985853459</v>
       </c>
       <c r="E226" t="n">
-        <v>340.133473711892</v>
+        <v>329.5315856933594</v>
       </c>
       <c r="F226" t="n">
-        <v>4308000</v>
+        <v>4961900</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6311,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="B227" t="n">
-        <v>335.7954406738281</v>
+        <v>337.3142314565633</v>
       </c>
       <c r="C227" t="n">
-        <v>342.7442335347337</v>
+        <v>341.126167165973</v>
       </c>
       <c r="D227" t="n">
-        <v>334.495026147691</v>
+        <v>331.2787221229386</v>
       </c>
       <c r="E227" t="n">
-        <v>337.8900211320969</v>
+        <v>337.5326232910156</v>
       </c>
       <c r="F227" t="n">
-        <v>4028500</v>
+        <v>2908100</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6337,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="B228" t="n">
-        <v>330.9114379882812</v>
+        <v>337.741121159039</v>
       </c>
       <c r="C228" t="n">
-        <v>333.2343164610006</v>
+        <v>348.2933339094608</v>
       </c>
       <c r="D228" t="n">
-        <v>327.8341094785939</v>
+        <v>336.8675537894677</v>
       </c>
       <c r="E228" t="n">
-        <v>332.5394250801792</v>
+        <v>345.6925048828125</v>
       </c>
       <c r="F228" t="n">
-        <v>6275400</v>
+        <v>4275000</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6363,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46234</v>
+        <v>46239</v>
       </c>
       <c r="B229" t="n">
-        <v>329.5315856933594</v>
+        <v>347.5984599855233</v>
       </c>
       <c r="C229" t="n">
-        <v>331.5566708480175</v>
+        <v>351.9563298372728</v>
       </c>
       <c r="D229" t="n">
-        <v>326.3946985853459</v>
+        <v>345.6031541488199</v>
       </c>
       <c r="E229" t="n">
-        <v>330.0080852280822</v>
+        <v>350.5566711425781</v>
       </c>
       <c r="F229" t="n">
-        <v>4961900</v>
+        <v>3140400</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6389,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="B230" t="n">
-        <v>337.5326232910156</v>
+        <v>350.9140306560572</v>
       </c>
       <c r="C230" t="n">
-        <v>341.126167165973</v>
+        <v>350.9636527717977</v>
       </c>
       <c r="D230" t="n">
-        <v>331.2787221229386</v>
+        <v>344.967859180145</v>
       </c>
       <c r="E230" t="n">
-        <v>337.3142314565633</v>
+        <v>346.963134765625</v>
       </c>
       <c r="F230" t="n">
-        <v>2908100</v>
+        <v>2622400</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6415,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="B231" t="n">
-        <v>345.6925048828125</v>
+        <v>348.9386046403958</v>
       </c>
       <c r="C231" t="n">
-        <v>348.2933339094608</v>
+        <v>354.219664160909</v>
       </c>
       <c r="D231" t="n">
-        <v>336.8675537894677</v>
+        <v>346.1888486641563</v>
       </c>
       <c r="E231" t="n">
-        <v>337.741121159039</v>
+        <v>353.0185241699219</v>
       </c>
       <c r="F231" t="n">
-        <v>4275000</v>
+        <v>3584800</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6441,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="B232" t="n">
-        <v>350.5566711425781</v>
+        <v>349.524279261052</v>
       </c>
       <c r="C232" t="n">
-        <v>351.9563298372728</v>
+        <v>351.4103740800161</v>
       </c>
       <c r="D232" t="n">
-        <v>345.6031541488199</v>
+        <v>344.5211400290252</v>
       </c>
       <c r="E232" t="n">
-        <v>347.5984599855233</v>
+        <v>348.2139282226562</v>
       </c>
       <c r="F232" t="n">
-        <v>3140400</v>
+        <v>3124800</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6467,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="B233" t="n">
-        <v>346.963134765625</v>
+        <v>349.7128894956296</v>
       </c>
       <c r="C233" t="n">
-        <v>350.9636527717977</v>
+        <v>355.7384623950411</v>
       </c>
       <c r="D233" t="n">
-        <v>344.967859180145</v>
+        <v>348.0352499864083</v>
       </c>
       <c r="E233" t="n">
-        <v>350.9140306560572</v>
+        <v>351.8868713378906</v>
       </c>
       <c r="F233" t="n">
-        <v>2622400</v>
+        <v>2549700</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6493,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="B234" t="n">
-        <v>353.0185241699219</v>
+        <v>349.4250091127092</v>
       </c>
       <c r="C234" t="n">
-        <v>354.219664160909</v>
+        <v>351.2813246265272</v>
       </c>
       <c r="D234" t="n">
-        <v>346.1888486641563</v>
+        <v>340.5206262766717</v>
       </c>
       <c r="E234" t="n">
-        <v>348.9386046403958</v>
+        <v>340.9176940917969</v>
       </c>
       <c r="F234" t="n">
-        <v>3584800</v>
+        <v>3965800</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6519,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="B235" t="n">
-        <v>348.2139282226562</v>
+        <v>344.4615642861647</v>
       </c>
       <c r="C235" t="n">
-        <v>351.4103740800161</v>
+        <v>345.206077753642</v>
       </c>
       <c r="D235" t="n">
-        <v>344.5211400290252</v>
+        <v>338.0190507751135</v>
       </c>
       <c r="E235" t="n">
-        <v>349.524279261052</v>
+        <v>339.2003479003906</v>
       </c>
       <c r="F235" t="n">
-        <v>3124800</v>
+        <v>2439900</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6545,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46245</v>
+        <v>46248</v>
       </c>
       <c r="B236" t="n">
-        <v>351.8868713378906</v>
+        <v>338.3168506868042</v>
       </c>
       <c r="C236" t="n">
-        <v>355.7384623950411</v>
+        <v>338.3168506868042</v>
       </c>
       <c r="D236" t="n">
-        <v>348.0352499864083</v>
+        <v>333.5519765191293</v>
       </c>
       <c r="E236" t="n">
-        <v>349.7128894956296</v>
+        <v>336.381103515625</v>
       </c>
       <c r="F236" t="n">
-        <v>2549700</v>
+        <v>3073100</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6571,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="B237" t="n">
-        <v>340.9176940917969</v>
+        <v>332.2614710050206</v>
       </c>
       <c r="C237" t="n">
-        <v>351.2813246265272</v>
+        <v>336.9568803095206</v>
       </c>
       <c r="D237" t="n">
-        <v>340.5206262766717</v>
+        <v>330.4548079641576</v>
       </c>
       <c r="E237" t="n">
-        <v>349.4250091127092</v>
+        <v>335.4082946777344</v>
       </c>
       <c r="F237" t="n">
-        <v>3965800</v>
+        <v>5580000</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6597,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="B238" t="n">
-        <v>339.2003479003906</v>
+        <v>334.3163510292147</v>
       </c>
       <c r="C238" t="n">
-        <v>345.206077753642</v>
+        <v>342.0195939717831</v>
       </c>
       <c r="D238" t="n">
-        <v>338.0190507751135</v>
+        <v>328.2709048600699</v>
       </c>
       <c r="E238" t="n">
-        <v>344.4615642861647</v>
+        <v>335.0211486816406</v>
       </c>
       <c r="F238" t="n">
-        <v>2439900</v>
+        <v>6603400</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6623,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46248</v>
+        <v>46253</v>
       </c>
       <c r="B239" t="n">
-        <v>336.381103515625</v>
+        <v>338.9224047058033</v>
       </c>
       <c r="C239" t="n">
-        <v>338.3168506868042</v>
+        <v>347.8366934263856</v>
       </c>
       <c r="D239" t="n">
-        <v>333.5519765191293</v>
+        <v>338.9224047058033</v>
       </c>
       <c r="E239" t="n">
-        <v>338.3168506868042</v>
+        <v>341.7813110351562</v>
       </c>
       <c r="F239" t="n">
-        <v>3073100</v>
+        <v>4971000</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6649,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46251</v>
+        <v>46254</v>
       </c>
       <c r="B240" t="n">
-        <v>335.4082946777344</v>
+        <v>333.542054389882</v>
       </c>
       <c r="C240" t="n">
-        <v>336.9568803095206</v>
+        <v>336.4009911317456</v>
       </c>
       <c r="D240" t="n">
-        <v>330.4548079641576</v>
+        <v>329.1643112906949</v>
       </c>
       <c r="E240" t="n">
-        <v>332.2614710050206</v>
+        <v>332.0430908203125</v>
       </c>
       <c r="F240" t="n">
-        <v>5580000</v>
+        <v>4027700</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6675,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="B241" t="n">
-        <v>335.0211486816406</v>
+        <v>334.0582233645888</v>
       </c>
       <c r="C241" t="n">
-        <v>342.0195939717831</v>
+        <v>336.1031512946537</v>
       </c>
       <c r="D241" t="n">
-        <v>328.2709048600699</v>
+        <v>330.5639843459303</v>
       </c>
       <c r="E241" t="n">
-        <v>334.3163510292147</v>
+        <v>333.1548767089844</v>
       </c>
       <c r="F241" t="n">
-        <v>6603400</v>
+        <v>3422800</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6701,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="B242" t="n">
-        <v>341.7813110351562</v>
+        <v>333.4229292601251</v>
       </c>
       <c r="C242" t="n">
-        <v>347.8366934263856</v>
+        <v>339.7165463845368</v>
       </c>
       <c r="D242" t="n">
-        <v>338.9224047058033</v>
+        <v>332.7081950914107</v>
       </c>
       <c r="E242" t="n">
-        <v>338.9224047058033</v>
+        <v>334.9615783691406</v>
       </c>
       <c r="F242" t="n">
-        <v>4971000</v>
+        <v>3298600</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6727,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46254</v>
+        <v>46259</v>
       </c>
       <c r="B243" t="n">
-        <v>332.0430908203125</v>
+        <v>336.8873851133212</v>
       </c>
       <c r="C243" t="n">
-        <v>336.4009911317456</v>
+        <v>337.0065024243307</v>
       </c>
       <c r="D243" t="n">
-        <v>329.1643112906949</v>
+        <v>331.2588801078031</v>
       </c>
       <c r="E243" t="n">
-        <v>333.542054389882</v>
+        <v>335.4082946777344</v>
       </c>
       <c r="F243" t="n">
-        <v>4027700</v>
+        <v>2528100</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6753,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="B244" t="n">
-        <v>333.1548767089844</v>
+        <v>336.9469338983794</v>
       </c>
       <c r="C244" t="n">
-        <v>336.1031512946537</v>
+        <v>336.9568704387829</v>
       </c>
       <c r="D244" t="n">
-        <v>330.5639843459303</v>
+        <v>332.0629425240725</v>
       </c>
       <c r="E244" t="n">
-        <v>334.0582233645888</v>
+        <v>332.4004516601562</v>
       </c>
       <c r="F244" t="n">
-        <v>3422800</v>
+        <v>4258100</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6779,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="B245" t="n">
-        <v>334.9615783691406</v>
+        <v>328.1517689125653</v>
       </c>
       <c r="C245" t="n">
-        <v>339.7165463845368</v>
+        <v>329.5812372185705</v>
       </c>
       <c r="D245" t="n">
-        <v>332.7081950914107</v>
+        <v>325.4814448058147</v>
       </c>
       <c r="E245" t="n">
-        <v>333.4229292601251</v>
+        <v>326.2060852050781</v>
       </c>
       <c r="F245" t="n">
-        <v>3298600</v>
+        <v>3618000</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6805,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="B246" t="n">
-        <v>335.4082946777344</v>
+        <v>328.0822659405567</v>
       </c>
       <c r="C246" t="n">
-        <v>337.0065024243307</v>
+        <v>329.1841313242223</v>
       </c>
       <c r="D246" t="n">
-        <v>331.2588801078031</v>
+        <v>325.1042120893565</v>
       </c>
       <c r="E246" t="n">
-        <v>336.8873851133212</v>
+        <v>327.7745361328125</v>
       </c>
       <c r="F246" t="n">
-        <v>2528100</v>
+        <v>3136100</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6831,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="B247" t="n">
-        <v>332.4004516601562</v>
+        <v>325.838797551875</v>
       </c>
       <c r="C247" t="n">
-        <v>336.9568704387829</v>
+        <v>326.8414187355763</v>
       </c>
       <c r="D247" t="n">
-        <v>332.0629425240725</v>
+        <v>323.3670224847805</v>
       </c>
       <c r="E247" t="n">
-        <v>336.9469338983794</v>
+        <v>325.4317932128906</v>
       </c>
       <c r="F247" t="n">
-        <v>4258100</v>
+        <v>3858700</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6857,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46261</v>
+        <v>46266</v>
       </c>
       <c r="B248" t="n">
-        <v>326.2060852050781</v>
+        <v>323.6251283531417</v>
       </c>
       <c r="C248" t="n">
-        <v>329.5812372185705</v>
+        <v>324.439106732169</v>
       </c>
       <c r="D248" t="n">
-        <v>325.4814448058147</v>
+        <v>316.4678503051231</v>
       </c>
       <c r="E248" t="n">
-        <v>328.1517689125653</v>
+        <v>317.4307556152344</v>
       </c>
       <c r="F248" t="n">
-        <v>3618000</v>
+        <v>3291000</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6883,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46262</v>
+        <v>46267</v>
       </c>
       <c r="B249" t="n">
-        <v>327.7745361328125</v>
+        <v>319.1481100391916</v>
       </c>
       <c r="C249" t="n">
-        <v>329.1841313242223</v>
+        <v>319.813222073911</v>
       </c>
       <c r="D249" t="n">
-        <v>325.1042120893565</v>
+        <v>315.3858267914646</v>
       </c>
       <c r="E249" t="n">
-        <v>328.0822659405567</v>
+        <v>316.1799926757812</v>
       </c>
       <c r="F249" t="n">
-        <v>3136100</v>
+        <v>3499300</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6909,25 +6917,25 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="B250" t="n">
-        <v>325.4317932128906</v>
+        <v>318.2099914550781</v>
       </c>
       <c r="C250" t="n">
-        <v>326.8414187355763</v>
+        <v>320.4400024414062</v>
       </c>
       <c r="D250" t="n">
-        <v>323.3670224847805</v>
+        <v>315.2099914550781</v>
       </c>
       <c r="E250" t="n">
-        <v>325.838797551875</v>
+        <v>318.0700073242188</v>
       </c>
       <c r="F250" t="n">
-        <v>3858700</v>
+        <v>3377700</v>
       </c>
       <c r="G250" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -6935,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="B251" t="n">
-        <v>317.4307556152344</v>
+        <v>316.7000122070312</v>
       </c>
       <c r="C251" t="n">
-        <v>324.439106732169</v>
+        <v>321.7999877929688</v>
       </c>
       <c r="D251" t="n">
-        <v>316.4678503051231</v>
+        <v>316.1000061035156</v>
       </c>
       <c r="E251" t="n">
-        <v>323.6251283531417</v>
+        <v>321.0499877929688</v>
       </c>
       <c r="F251" t="n">
-        <v>3291000</v>
+        <v>2261000</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6961,79 +6969,19 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B252" t="n">
-        <v>316.1799926757812</v>
-      </c>
-      <c r="C252" t="n">
-        <v>319.813222073911</v>
-      </c>
-      <c r="D252" t="n">
-        <v>315.3858267914646</v>
-      </c>
-      <c r="E252" t="n">
-        <v>319.1481100391916</v>
-      </c>
+        <v>46273</v>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="n">
-        <v>3499300</v>
+        <v>5019975</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B253" t="n">
-        <v>318.0700073242188</v>
-      </c>
-      <c r="C253" t="n">
-        <v>320.4400024414062</v>
-      </c>
-      <c r="D253" t="n">
-        <v>315.2099914550781</v>
-      </c>
-      <c r="E253" t="n">
-        <v>318.2099914550781</v>
-      </c>
-      <c r="F253" t="n">
-        <v>3377700</v>
-      </c>
-      <c r="G253" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="H253" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="1" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B254" t="n">
-        <v>321.0499877929688</v>
-      </c>
-      <c r="C254" t="n">
-        <v>321.7999877929688</v>
-      </c>
-      <c r="D254" t="n">
-        <v>316.1000061035156</v>
-      </c>
-      <c r="E254" t="n">
-        <v>316.7000122070312</v>
-      </c>
-      <c r="F254" t="n">
-        <v>2261000</v>
-      </c>
-      <c r="G254" t="n">
-        <v>0</v>
-      </c>
-      <c r="H254" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10638,34 +10586,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>313.7</v>
+      </c>
+      <c r="D2" t="n">
         <v>321.05</v>
       </c>
-      <c r="D2" t="n">
-        <v>318.07</v>
-      </c>
       <c r="E2" t="n">
-        <v>316.7</v>
+        <v>320.73</v>
       </c>
       <c r="F2" t="n">
-        <v>321.79</v>
+        <v>321.5</v>
       </c>
       <c r="G2" t="n">
-        <v>316.5</v>
+        <v>313.24</v>
       </c>
       <c r="H2" t="n">
-        <v>2259444</v>
+        <v>5019975</v>
       </c>
       <c r="I2" t="n">
-        <v>4200590</v>
+        <v>4197667</v>
       </c>
       <c r="J2" t="n">
-        <v>320308248576</v>
+        <v>312975228928</v>
       </c>
       <c r="K2" t="n">
-        <v>22.466759</v>
+        <v>21.952415</v>
       </c>
       <c r="L2" t="n">
-        <v>20.018404</v>
+        <v>19.560112</v>
       </c>
       <c r="M2" t="n">
         <v>14.29</v>
@@ -10704,7 +10652,7 @@
         <v>16.65</v>
       </c>
       <c r="Y2" t="n">
-        <v>19.282282</v>
+        <v>18.840841</v>
       </c>
       <c r="Z2" t="n">
         <v>0.046</v>
@@ -10716,7 +10664,7 @@
         <v>169176006656</v>
       </c>
       <c r="AC2" t="n">
-        <v>381411262464</v>
+        <v>374078242816</v>
       </c>
       <c r="AD2" t="n">
         <v>24647999488</v>
@@ -10743,7 +10691,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-08 08:52:35</t>
+          <t>2026-09-09 09:15:32</t>
         </is>
       </c>
     </row>

--- a/data/HD_data.xlsx
+++ b/data/HD_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="B2" t="n">
-        <v>406.6054488503357</v>
+        <v>404.0770428202423</v>
       </c>
       <c r="C2" t="n">
-        <v>407.1889314722671</v>
+        <v>405.9344471617109</v>
       </c>
       <c r="D2" t="n">
-        <v>401.3833372545098</v>
+        <v>400.4011408925683</v>
       </c>
       <c r="E2" t="n">
-        <v>403.9020080566406</v>
+        <v>401.8501281738281</v>
       </c>
       <c r="F2" t="n">
-        <v>3516000</v>
+        <v>2897800</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B3" t="n">
-        <v>404.0770121335462</v>
+        <v>404.2521200680789</v>
       </c>
       <c r="C3" t="n">
-        <v>405.9344163339586</v>
+        <v>413.5099397187673</v>
       </c>
       <c r="D3" t="n">
-        <v>400.4011104850302</v>
+        <v>402.8420395013142</v>
       </c>
       <c r="E3" t="n">
-        <v>401.85009765625</v>
+        <v>411.759521484375</v>
       </c>
       <c r="F3" t="n">
-        <v>2897800</v>
+        <v>5316400</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B4" t="n">
-        <v>404.2521200680789</v>
+        <v>408.6962221082555</v>
       </c>
       <c r="C4" t="n">
-        <v>413.5099397187673</v>
+        <v>411.8470163012535</v>
       </c>
       <c r="D4" t="n">
-        <v>402.8420395013142</v>
+        <v>407.3445165905575</v>
       </c>
       <c r="E4" t="n">
-        <v>411.759521484375</v>
+        <v>411.0495910644531</v>
       </c>
       <c r="F4" t="n">
-        <v>5316400</v>
+        <v>5004200</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B5" t="n">
-        <v>408.6962221082555</v>
+        <v>410.8356495901566</v>
       </c>
       <c r="C5" t="n">
-        <v>411.8470163012535</v>
+        <v>411.6427792599144</v>
       </c>
       <c r="D5" t="n">
-        <v>407.3445165905575</v>
+        <v>406.245631927433</v>
       </c>
       <c r="E5" t="n">
-        <v>411.0495910644531</v>
+        <v>411.0690307617188</v>
       </c>
       <c r="F5" t="n">
-        <v>5004200</v>
+        <v>4884700</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B6" t="n">
-        <v>410.8356495901566</v>
+        <v>412.0803987002532</v>
       </c>
       <c r="C6" t="n">
-        <v>411.6427792599144</v>
+        <v>412.8389171851107</v>
       </c>
       <c r="D6" t="n">
-        <v>406.245631927433</v>
+        <v>408.5211874475655</v>
       </c>
       <c r="E6" t="n">
-        <v>411.0690307617188</v>
+        <v>409.84375</v>
       </c>
       <c r="F6" t="n">
-        <v>4884700</v>
+        <v>3726700</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B7" t="n">
-        <v>412.0803987002532</v>
+        <v>412.7514096604531</v>
       </c>
       <c r="C7" t="n">
-        <v>412.8389171851107</v>
+        <v>414.9977925252571</v>
       </c>
       <c r="D7" t="n">
-        <v>408.5211874475655</v>
+        <v>404.3590652530731</v>
       </c>
       <c r="E7" t="n">
-        <v>409.84375</v>
+        <v>405.5162963867188</v>
       </c>
       <c r="F7" t="n">
-        <v>3726700</v>
+        <v>4771700</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B8" t="n">
-        <v>412.7514096604531</v>
+        <v>406.0511124651653</v>
       </c>
       <c r="C8" t="n">
-        <v>414.9977925252571</v>
+        <v>409.7853891317768</v>
       </c>
       <c r="D8" t="n">
-        <v>404.3590652530731</v>
+        <v>404.4076508642465</v>
       </c>
       <c r="E8" t="n">
-        <v>405.5162963867188</v>
+        <v>405.9830627441406</v>
       </c>
       <c r="F8" t="n">
-        <v>4771700</v>
+        <v>3677200</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B9" t="n">
-        <v>406.0511124651653</v>
+        <v>405.8760981858028</v>
       </c>
       <c r="C9" t="n">
-        <v>409.7853891317768</v>
+        <v>407.0527678467049</v>
       </c>
       <c r="D9" t="n">
-        <v>404.4076508642465</v>
+        <v>403.6686220984643</v>
       </c>
       <c r="E9" t="n">
-        <v>405.9830627441406</v>
+        <v>404.2423706054688</v>
       </c>
       <c r="F9" t="n">
-        <v>3677200</v>
+        <v>6718400</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B10" t="n">
-        <v>405.8760981858028</v>
+        <v>402.7058704699236</v>
       </c>
       <c r="C10" t="n">
-        <v>407.0527678467049</v>
+        <v>403.4546845448791</v>
       </c>
       <c r="D10" t="n">
-        <v>403.6686220984643</v>
+        <v>399.8079552515003</v>
       </c>
       <c r="E10" t="n">
-        <v>404.2423706054688</v>
+        <v>400.6539916992188</v>
       </c>
       <c r="F10" t="n">
-        <v>6718400</v>
+        <v>2656300</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B11" t="n">
-        <v>402.7058704699236</v>
+        <v>400.6539731783087</v>
       </c>
       <c r="C11" t="n">
-        <v>403.4546845448791</v>
+        <v>402.3363415649943</v>
       </c>
       <c r="D11" t="n">
-        <v>399.8079552515003</v>
+        <v>396.2389914749436</v>
       </c>
       <c r="E11" t="n">
-        <v>400.6539916992188</v>
+        <v>399.593994140625</v>
       </c>
       <c r="F11" t="n">
-        <v>2656300</v>
+        <v>2597000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B12" t="n">
-        <v>400.654003776839</v>
+        <v>395.5874669386123</v>
       </c>
       <c r="C12" t="n">
-        <v>402.3363722920096</v>
+        <v>399.3411526132105</v>
       </c>
       <c r="D12" t="n">
-        <v>396.2390217362953</v>
+        <v>393.856487333743</v>
       </c>
       <c r="E12" t="n">
-        <v>399.5940246582031</v>
+        <v>398.4853820800781</v>
       </c>
       <c r="F12" t="n">
-        <v>2597000</v>
+        <v>3220700</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B13" t="n">
-        <v>395.5874669386123</v>
+        <v>395.4512918948509</v>
       </c>
       <c r="C13" t="n">
-        <v>399.3411526132105</v>
+        <v>399.5453447284057</v>
       </c>
       <c r="D13" t="n">
-        <v>393.856487333743</v>
+        <v>394.4399240629465</v>
       </c>
       <c r="E13" t="n">
-        <v>398.4853820800781</v>
+        <v>396.2292785644531</v>
       </c>
       <c r="F13" t="n">
-        <v>3220700</v>
+        <v>2554300</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B14" t="n">
-        <v>395.4512918948509</v>
+        <v>396.9197270195646</v>
       </c>
       <c r="C14" t="n">
-        <v>399.5453447284057</v>
+        <v>400.08022560159</v>
       </c>
       <c r="D14" t="n">
-        <v>394.4399240629465</v>
+        <v>394.6636101400317</v>
       </c>
       <c r="E14" t="n">
-        <v>396.2292785644531</v>
+        <v>398.7965698242188</v>
       </c>
       <c r="F14" t="n">
-        <v>2554300</v>
+        <v>2316600</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B15" t="n">
-        <v>396.9197270195646</v>
+        <v>398.7576665785797</v>
       </c>
       <c r="C15" t="n">
-        <v>400.08022560159</v>
+        <v>399.6329053199512</v>
       </c>
       <c r="D15" t="n">
-        <v>394.6636101400317</v>
+        <v>392.7284254984301</v>
       </c>
       <c r="E15" t="n">
-        <v>398.7965698242188</v>
+        <v>395.59716796875</v>
       </c>
       <c r="F15" t="n">
-        <v>2316600</v>
+        <v>3008400</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B16" t="n">
-        <v>398.7576665785797</v>
+        <v>395.4318404229484</v>
       </c>
       <c r="C16" t="n">
-        <v>399.6329053199512</v>
+        <v>395.7916462621145</v>
       </c>
       <c r="D16" t="n">
-        <v>392.7284254984301</v>
+        <v>392.3685940592994</v>
       </c>
       <c r="E16" t="n">
-        <v>395.59716796875</v>
+        <v>394.031494140625</v>
       </c>
       <c r="F16" t="n">
-        <v>3008400</v>
+        <v>3211600</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B17" t="n">
-        <v>395.4318710489828</v>
+        <v>393.2535498958814</v>
       </c>
       <c r="C17" t="n">
-        <v>395.7916769160157</v>
+        <v>393.9731615974939</v>
       </c>
       <c r="D17" t="n">
-        <v>392.3686244480866</v>
+        <v>384.4235866812837</v>
       </c>
       <c r="E17" t="n">
-        <v>394.0315246582031</v>
+        <v>386.0864868164062</v>
       </c>
       <c r="F17" t="n">
-        <v>3211600</v>
+        <v>3787800</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B18" t="n">
-        <v>393.2535809799684</v>
+        <v>384.6083628947175</v>
       </c>
       <c r="C18" t="n">
-        <v>393.9731927384614</v>
+        <v>386.4365945008176</v>
       </c>
       <c r="D18" t="n">
-        <v>384.4236170674206</v>
+        <v>382.9454627326402</v>
       </c>
       <c r="E18" t="n">
-        <v>386.0865173339844</v>
+        <v>384.1318664550781</v>
       </c>
       <c r="F18" t="n">
-        <v>3787800</v>
+        <v>2964700</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B19" t="n">
-        <v>384.6083628947175</v>
+        <v>383.2760992538061</v>
       </c>
       <c r="C19" t="n">
-        <v>386.4365945008176</v>
+        <v>386.3782525463874</v>
       </c>
       <c r="D19" t="n">
-        <v>382.9454627326402</v>
+        <v>381.817407599382</v>
       </c>
       <c r="E19" t="n">
-        <v>384.1318664550781</v>
+        <v>384.1804809570312</v>
       </c>
       <c r="F19" t="n">
-        <v>2964700</v>
+        <v>2951300</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B20" t="n">
-        <v>383.2760992538061</v>
+        <v>383.6359134364591</v>
       </c>
       <c r="C20" t="n">
-        <v>386.3782525463874</v>
+        <v>383.6359134364591</v>
       </c>
       <c r="D20" t="n">
-        <v>381.817407599382</v>
+        <v>375.0977059544146</v>
       </c>
       <c r="E20" t="n">
-        <v>384.1804809570312</v>
+        <v>378.6082763671875</v>
       </c>
       <c r="F20" t="n">
-        <v>2951300</v>
+        <v>3653700</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B21" t="n">
-        <v>383.6359134364591</v>
+        <v>378.7250266598306</v>
       </c>
       <c r="C21" t="n">
-        <v>383.6359134364591</v>
+        <v>379.0167531493121</v>
       </c>
       <c r="D21" t="n">
-        <v>375.0977059544146</v>
+        <v>374.8935271531156</v>
       </c>
       <c r="E21" t="n">
-        <v>378.6082763671875</v>
+        <v>376.15771484375</v>
       </c>
       <c r="F21" t="n">
-        <v>3653700</v>
+        <v>2505700</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B22" t="n">
-        <v>378.7249959339671</v>
+        <v>375.8173102434433</v>
       </c>
       <c r="C22" t="n">
-        <v>379.016722399781</v>
+        <v>375.8173102434433</v>
       </c>
       <c r="D22" t="n">
-        <v>374.8934967381007</v>
+        <v>372.4331645921919</v>
       </c>
       <c r="E22" t="n">
-        <v>376.1576843261719</v>
+        <v>373.2208557128906</v>
       </c>
       <c r="F22" t="n">
-        <v>2505700</v>
+        <v>2517600</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B23" t="n">
-        <v>375.8172795135579</v>
+        <v>372.3553630865562</v>
       </c>
       <c r="C23" t="n">
-        <v>375.8172795135579</v>
+        <v>373.7751480356932</v>
       </c>
       <c r="D23" t="n">
-        <v>372.4331341390219</v>
+        <v>367.0651721318674</v>
       </c>
       <c r="E23" t="n">
-        <v>373.2208251953125</v>
+        <v>367.2888488769531</v>
       </c>
       <c r="F23" t="n">
-        <v>2517600</v>
+        <v>3321400</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B24" t="n">
-        <v>372.3553321480077</v>
+        <v>369.7880920652779</v>
       </c>
       <c r="C24" t="n">
-        <v>373.7751169791765</v>
+        <v>369.7880920652779</v>
       </c>
       <c r="D24" t="n">
-        <v>367.0651416328743</v>
+        <v>364.4589941977949</v>
       </c>
       <c r="E24" t="n">
-        <v>367.288818359375</v>
+        <v>365.4022827148438</v>
       </c>
       <c r="F24" t="n">
-        <v>3321400</v>
+        <v>2992400</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B25" t="n">
-        <v>369.7880611814068</v>
+        <v>368.6308504339742</v>
       </c>
       <c r="C25" t="n">
-        <v>369.7880611814068</v>
+        <v>371.7816150220939</v>
       </c>
       <c r="D25" t="n">
-        <v>364.4589637589981</v>
+        <v>366.8026187475289</v>
       </c>
       <c r="E25" t="n">
-        <v>365.4022521972656</v>
+        <v>368.9225769042969</v>
       </c>
       <c r="F25" t="n">
-        <v>2992400</v>
+        <v>2925900</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B26" t="n">
-        <v>368.6308504339742</v>
+        <v>368.4363460625955</v>
       </c>
       <c r="C26" t="n">
-        <v>371.7816150220939</v>
+        <v>378.1804256443732</v>
       </c>
       <c r="D26" t="n">
-        <v>366.8026187475289</v>
+        <v>367.6000437301846</v>
       </c>
       <c r="E26" t="n">
-        <v>368.9225769042969</v>
+        <v>377.0426330566406</v>
       </c>
       <c r="F26" t="n">
-        <v>2925900</v>
+        <v>4399900</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B27" t="n">
-        <v>368.4363162416045</v>
+        <v>378.5110397840133</v>
       </c>
       <c r="C27" t="n">
-        <v>378.1803950347029</v>
+        <v>383.5094743418081</v>
       </c>
       <c r="D27" t="n">
-        <v>367.6000139768833</v>
+        <v>376.0798870651823</v>
       </c>
       <c r="E27" t="n">
-        <v>377.0426025390625</v>
+        <v>377.6066284179688</v>
       </c>
       <c r="F27" t="n">
-        <v>4399900</v>
+        <v>3690100</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B28" t="n">
-        <v>378.5110397840133</v>
+        <v>378.9292168586321</v>
       </c>
       <c r="C28" t="n">
-        <v>383.5094743418081</v>
+        <v>379.259850089759</v>
       </c>
       <c r="D28" t="n">
-        <v>376.0798870651823</v>
+        <v>373.3959105177652</v>
       </c>
       <c r="E28" t="n">
-        <v>377.6066284179688</v>
+        <v>376.7217407226562</v>
       </c>
       <c r="F28" t="n">
-        <v>3690100</v>
+        <v>2783700</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B29" t="n">
-        <v>378.9292168586321</v>
+        <v>377.8011514993366</v>
       </c>
       <c r="C29" t="n">
-        <v>379.259850089759</v>
+        <v>382.2841830931986</v>
       </c>
       <c r="D29" t="n">
-        <v>373.3959105177652</v>
+        <v>376.5369638928536</v>
       </c>
       <c r="E29" t="n">
-        <v>376.7217407226562</v>
+        <v>381.1075134277344</v>
       </c>
       <c r="F29" t="n">
-        <v>2783700</v>
+        <v>2657700</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B30" t="n">
-        <v>377.8011514993366</v>
+        <v>380.6310112651639</v>
       </c>
       <c r="C30" t="n">
-        <v>382.2841830931986</v>
+        <v>382.3522567670641</v>
       </c>
       <c r="D30" t="n">
-        <v>376.5369638928536</v>
+        <v>377.4024332180988</v>
       </c>
       <c r="E30" t="n">
-        <v>381.1075134277344</v>
+        <v>378.180419921875</v>
       </c>
       <c r="F30" t="n">
-        <v>2657700</v>
+        <v>2761100</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B31" t="n">
-        <v>380.6310112651639</v>
+        <v>376.8870237514197</v>
       </c>
       <c r="C31" t="n">
-        <v>382.3522567670641</v>
+        <v>382.7898697855445</v>
       </c>
       <c r="D31" t="n">
-        <v>377.4024332180988</v>
+        <v>375.2338280008644</v>
       </c>
       <c r="E31" t="n">
-        <v>378.180419921875</v>
+        <v>380.1350402832031</v>
       </c>
       <c r="F31" t="n">
-        <v>2761100</v>
+        <v>2306900</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B32" t="n">
-        <v>376.8870540082442</v>
+        <v>380.4754194313423</v>
       </c>
       <c r="C32" t="n">
-        <v>382.7899005162546</v>
+        <v>382.225837605147</v>
       </c>
       <c r="D32" t="n">
-        <v>375.2338581249689</v>
+        <v>377.4802521906377</v>
       </c>
       <c r="E32" t="n">
-        <v>380.1350708007812</v>
+        <v>378.2582092285156</v>
       </c>
       <c r="F32" t="n">
-        <v>2306900</v>
+        <v>2857000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B33" t="n">
-        <v>380.4754194313423</v>
+        <v>376.4689017102443</v>
       </c>
       <c r="C33" t="n">
-        <v>382.225837605147</v>
+        <v>378.0151114266164</v>
       </c>
       <c r="D33" t="n">
-        <v>377.4802521906377</v>
+        <v>370.7994364063865</v>
       </c>
       <c r="E33" t="n">
-        <v>378.2582092285156</v>
+        <v>374.4267272949219</v>
       </c>
       <c r="F33" t="n">
-        <v>2857000</v>
+        <v>2767300</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B34" t="n">
-        <v>376.4688710262192</v>
+        <v>378.9681015073717</v>
       </c>
       <c r="C34" t="n">
-        <v>378.0150806165678</v>
+        <v>378.9681015073717</v>
       </c>
       <c r="D34" t="n">
-        <v>370.79940618445</v>
+        <v>375.0490844721456</v>
       </c>
       <c r="E34" t="n">
-        <v>374.4266967773438</v>
+        <v>376.03125</v>
       </c>
       <c r="F34" t="n">
-        <v>2767300</v>
+        <v>2426800</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B35" t="n">
-        <v>378.968132263296</v>
+        <v>377.0231983553949</v>
       </c>
       <c r="C35" t="n">
-        <v>378.968132263296</v>
+        <v>378.5694080170153</v>
       </c>
       <c r="D35" t="n">
-        <v>375.0491149100141</v>
+        <v>372.3553670460668</v>
       </c>
       <c r="E35" t="n">
-        <v>376.0312805175781</v>
+        <v>374.6600952148438</v>
       </c>
       <c r="F35" t="n">
-        <v>2426800</v>
+        <v>3065800</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B36" t="n">
-        <v>377.0231983553949</v>
+        <v>373.8335013939448</v>
       </c>
       <c r="C36" t="n">
-        <v>378.5694080170153</v>
+        <v>379.2695552693392</v>
       </c>
       <c r="D36" t="n">
-        <v>372.3553670460668</v>
+        <v>372.2872621610022</v>
       </c>
       <c r="E36" t="n">
-        <v>374.6600952148438</v>
+        <v>375.1268615722656</v>
       </c>
       <c r="F36" t="n">
-        <v>3065800</v>
+        <v>2372800</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B37" t="n">
-        <v>373.8335013939448</v>
+        <v>372.45264120656</v>
       </c>
       <c r="C37" t="n">
-        <v>379.2695552693392</v>
+        <v>374.3975636149493</v>
       </c>
       <c r="D37" t="n">
-        <v>372.2872621610022</v>
+        <v>364.8674556847058</v>
       </c>
       <c r="E37" t="n">
-        <v>375.1268615722656</v>
+        <v>367.6292419433594</v>
       </c>
       <c r="F37" t="n">
-        <v>2372800</v>
+        <v>3852300</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B38" t="n">
-        <v>372.4526102885826</v>
+        <v>367.3082703686788</v>
       </c>
       <c r="C38" t="n">
-        <v>374.3975325355203</v>
+        <v>374.1057935751742</v>
       </c>
       <c r="D38" t="n">
-        <v>364.8674253963886</v>
+        <v>365.7523266876615</v>
       </c>
       <c r="E38" t="n">
-        <v>367.6292114257812</v>
+        <v>369.0975952148438</v>
       </c>
       <c r="F38" t="n">
-        <v>3852300</v>
+        <v>2384300</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B39" t="n">
-        <v>367.3082703686788</v>
+        <v>366.5789579935506</v>
       </c>
       <c r="C39" t="n">
-        <v>374.1057935751742</v>
+        <v>370.4493641725706</v>
       </c>
       <c r="D39" t="n">
-        <v>365.7523266876615</v>
+        <v>364.6826764994138</v>
       </c>
       <c r="E39" t="n">
-        <v>369.0975952148438</v>
+        <v>369.1365356445312</v>
       </c>
       <c r="F39" t="n">
-        <v>2384300</v>
+        <v>2643500</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B40" t="n">
-        <v>366.5789579935506</v>
+        <v>366.6275697464224</v>
       </c>
       <c r="C40" t="n">
-        <v>370.4493641725706</v>
+        <v>368.0570887541689</v>
       </c>
       <c r="D40" t="n">
-        <v>364.6826764994138</v>
+        <v>363.3892576559226</v>
       </c>
       <c r="E40" t="n">
-        <v>369.1365356445312</v>
+        <v>367.9306640625</v>
       </c>
       <c r="F40" t="n">
-        <v>2643500</v>
+        <v>2897600</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B41" t="n">
-        <v>366.6275697464224</v>
+        <v>366.9581821818597</v>
       </c>
       <c r="C41" t="n">
-        <v>368.0570887541689</v>
+        <v>373.1138475541215</v>
       </c>
       <c r="D41" t="n">
-        <v>363.3892576559226</v>
+        <v>366.3746996179726</v>
       </c>
       <c r="E41" t="n">
-        <v>367.9306640625</v>
+        <v>372.5303649902344</v>
       </c>
       <c r="F41" t="n">
-        <v>2897600</v>
+        <v>2590000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B42" t="n">
-        <v>366.9581821818597</v>
+        <v>372.2483997179557</v>
       </c>
       <c r="C42" t="n">
-        <v>373.1138475541215</v>
+        <v>372.8610549707219</v>
       </c>
       <c r="D42" t="n">
-        <v>366.3746996179726</v>
+        <v>360.3260169130116</v>
       </c>
       <c r="E42" t="n">
-        <v>372.5303649902344</v>
+        <v>363.5448608398438</v>
       </c>
       <c r="F42" t="n">
-        <v>2590000</v>
+        <v>4763000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B43" t="n">
-        <v>372.2483997179557</v>
+        <v>361.5804874640777</v>
       </c>
       <c r="C43" t="n">
-        <v>372.8610549707219</v>
+        <v>362.3973512135793</v>
       </c>
       <c r="D43" t="n">
-        <v>360.3260169130116</v>
+        <v>357.4280596409988</v>
       </c>
       <c r="E43" t="n">
-        <v>363.5448608398438</v>
+        <v>358.9062194824219</v>
       </c>
       <c r="F43" t="n">
-        <v>4763000</v>
+        <v>3622100</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B44" t="n">
-        <v>361.5805182090473</v>
+        <v>358.8284019214945</v>
       </c>
       <c r="C44" t="n">
-        <v>362.3973820280062</v>
+        <v>363.3600740840942</v>
       </c>
       <c r="D44" t="n">
-        <v>357.4280900328899</v>
+        <v>357.4475238166886</v>
       </c>
       <c r="E44" t="n">
-        <v>358.90625</v>
+        <v>360.8900146484375</v>
       </c>
       <c r="F44" t="n">
-        <v>3622100</v>
+        <v>2766400</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B45" t="n">
-        <v>358.8284019214945</v>
+        <v>359.6064000909565</v>
       </c>
       <c r="C45" t="n">
-        <v>363.3600740840942</v>
+        <v>360.4524365034046</v>
       </c>
       <c r="D45" t="n">
-        <v>357.4475238166886</v>
+        <v>353.4410002505718</v>
       </c>
       <c r="E45" t="n">
-        <v>360.8900146484375</v>
+        <v>360.228759765625</v>
       </c>
       <c r="F45" t="n">
-        <v>2766400</v>
+        <v>3257900</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B46" t="n">
-        <v>359.6064000909565</v>
+        <v>361.745830717721</v>
       </c>
       <c r="C46" t="n">
-        <v>360.4524365034046</v>
+        <v>365.6454096094494</v>
       </c>
       <c r="D46" t="n">
-        <v>353.4410002505718</v>
+        <v>360.6955856842403</v>
       </c>
       <c r="E46" t="n">
-        <v>360.228759765625</v>
+        <v>363.9338684082031</v>
       </c>
       <c r="F46" t="n">
-        <v>3257900</v>
+        <v>2407300</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B47" t="n">
-        <v>361.7458003836202</v>
+        <v>361.8138665438969</v>
       </c>
       <c r="C47" t="n">
-        <v>365.6453789483504</v>
+        <v>363.272558161854</v>
       </c>
       <c r="D47" t="n">
-        <v>360.6955554382075</v>
+        <v>358.8478721249137</v>
       </c>
       <c r="E47" t="n">
-        <v>363.933837890625</v>
+        <v>360.9094848632812</v>
       </c>
       <c r="F47" t="n">
-        <v>2407300</v>
+        <v>3375800</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B48" t="n">
-        <v>361.8138971379473</v>
+        <v>361.4249087666506</v>
       </c>
       <c r="C48" t="n">
-        <v>363.2725888792476</v>
+        <v>363.2336722315698</v>
       </c>
       <c r="D48" t="n">
-        <v>358.8479024681671</v>
+        <v>356.5236963397476</v>
       </c>
       <c r="E48" t="n">
-        <v>360.9095153808594</v>
+        <v>357.9337768554688</v>
       </c>
       <c r="F48" t="n">
-        <v>3375800</v>
+        <v>3034800</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B49" t="n">
-        <v>361.4249087666506</v>
+        <v>355.8332052567208</v>
       </c>
       <c r="C49" t="n">
-        <v>363.2336722315698</v>
+        <v>357.2140832465919</v>
       </c>
       <c r="D49" t="n">
-        <v>356.5236963397476</v>
+        <v>349.891453161598</v>
       </c>
       <c r="E49" t="n">
-        <v>357.9337768554688</v>
+        <v>352.3809509277344</v>
       </c>
       <c r="F49" t="n">
-        <v>3034800</v>
+        <v>3413300</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B50" t="n">
-        <v>355.8332668898346</v>
+        <v>351.1848930100947</v>
       </c>
       <c r="C50" t="n">
-        <v>357.2141451188847</v>
+        <v>353.7619090719871</v>
       </c>
       <c r="D50" t="n">
-        <v>349.8915137655536</v>
+        <v>346.2934147079206</v>
       </c>
       <c r="E50" t="n">
-        <v>352.3810119628906</v>
+        <v>348.1702575683594</v>
       </c>
       <c r="F50" t="n">
-        <v>3413300</v>
+        <v>5127200</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B51" t="n">
-        <v>351.1848930100947</v>
+        <v>330.6173283766702</v>
       </c>
       <c r="C51" t="n">
-        <v>353.7619090719871</v>
+        <v>339.1944125402241</v>
       </c>
       <c r="D51" t="n">
-        <v>346.2934147079206</v>
+        <v>326.7566567053178</v>
       </c>
       <c r="E51" t="n">
-        <v>348.1702575683594</v>
+        <v>327.2137145996094</v>
       </c>
       <c r="F51" t="n">
-        <v>5127200</v>
+        <v>10168500</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B52" t="n">
-        <v>330.6173592116862</v>
+        <v>331.5800941484648</v>
       </c>
       <c r="C52" t="n">
-        <v>339.1944441751817</v>
+        <v>332.3386126918821</v>
       </c>
       <c r="D52" t="n">
-        <v>326.7566871802684</v>
+        <v>322.2444607606784</v>
       </c>
       <c r="E52" t="n">
-        <v>327.2137451171875</v>
+        <v>325.2882690429688</v>
       </c>
       <c r="F52" t="n">
-        <v>10168500</v>
+        <v>7595000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B53" t="n">
-        <v>331.5800630406063</v>
+        <v>327.0969997002432</v>
       </c>
       <c r="C53" t="n">
-        <v>332.3385815128617</v>
+        <v>329.567059191382</v>
       </c>
       <c r="D53" t="n">
-        <v>322.2444305286613</v>
+        <v>322.9835082613831</v>
       </c>
       <c r="E53" t="n">
-        <v>325.2882385253906</v>
+        <v>323.2266235351562</v>
       </c>
       <c r="F53" t="n">
-        <v>7595000</v>
+        <v>4025300</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B54" t="n">
-        <v>327.0970305832446</v>
+        <v>325.356351446162</v>
       </c>
       <c r="C54" t="n">
-        <v>329.567090307595</v>
+        <v>337.3662532252054</v>
       </c>
       <c r="D54" t="n">
-        <v>322.9835387560075</v>
+        <v>323.8295802366419</v>
       </c>
       <c r="E54" t="n">
-        <v>323.2266540527344</v>
+        <v>333.8653869628906</v>
       </c>
       <c r="F54" t="n">
-        <v>4025300</v>
+        <v>7441300</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B55" t="n">
-        <v>325.356351446162</v>
+        <v>332.7761999080408</v>
       </c>
       <c r="C55" t="n">
-        <v>337.3662532252054</v>
+        <v>334.2445959868845</v>
       </c>
       <c r="D55" t="n">
-        <v>323.8295802366419</v>
+        <v>327.2817709576355</v>
       </c>
       <c r="E55" t="n">
-        <v>333.8653869628906</v>
+        <v>327.3109436035156</v>
       </c>
       <c r="F55" t="n">
-        <v>7441300</v>
+        <v>6132900</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B56" t="n">
-        <v>332.7761999080408</v>
+        <v>329.6643336820279</v>
       </c>
       <c r="C56" t="n">
-        <v>334.2445959868845</v>
+        <v>343.2787899402826</v>
       </c>
       <c r="D56" t="n">
-        <v>327.2817709576355</v>
+        <v>329.5184704432642</v>
       </c>
       <c r="E56" t="n">
-        <v>327.3109436035156</v>
+        <v>341.4019470214844</v>
       </c>
       <c r="F56" t="n">
-        <v>6132900</v>
+        <v>6316600</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B57" t="n">
-        <v>329.6643336820279</v>
+        <v>340.6142114178541</v>
       </c>
       <c r="C57" t="n">
-        <v>343.2787899402826</v>
+        <v>347.4894883766705</v>
       </c>
       <c r="D57" t="n">
-        <v>329.5184704432642</v>
+        <v>339.3889010177763</v>
       </c>
       <c r="E57" t="n">
-        <v>341.4019470214844</v>
+        <v>345.6807250976562</v>
       </c>
       <c r="F57" t="n">
-        <v>6316600</v>
+        <v>4517300</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B58" t="n">
-        <v>340.6142414881474</v>
+        <v>345.1556025907452</v>
       </c>
       <c r="C58" t="n">
-        <v>347.4895190539308</v>
+        <v>347.975733775784</v>
       </c>
       <c r="D58" t="n">
-        <v>339.3889309798961</v>
+        <v>343.7649903745483</v>
       </c>
       <c r="E58" t="n">
-        <v>345.6807556152344</v>
+        <v>347.0908203125</v>
       </c>
       <c r="F58" t="n">
-        <v>4517300</v>
+        <v>2119600</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B59" t="n">
-        <v>345.1556025907452</v>
+        <v>344.2998610600955</v>
       </c>
       <c r="C59" t="n">
-        <v>347.975733775784</v>
+        <v>352.3129611811121</v>
       </c>
       <c r="D59" t="n">
-        <v>343.7649903745483</v>
+        <v>343.1620981246396</v>
       </c>
       <c r="E59" t="n">
-        <v>347.0908203125</v>
+        <v>347.4895324707031</v>
       </c>
       <c r="F59" t="n">
-        <v>2119600</v>
+        <v>5107100</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B60" t="n">
-        <v>344.299830822644</v>
+        <v>347.0032746652403</v>
       </c>
       <c r="C60" t="n">
-        <v>352.312930239926</v>
+        <v>347.654836647816</v>
       </c>
       <c r="D60" t="n">
-        <v>343.1620679871098</v>
+        <v>341.6255660714526</v>
       </c>
       <c r="E60" t="n">
-        <v>347.489501953125</v>
+        <v>344.2803955078125</v>
       </c>
       <c r="F60" t="n">
-        <v>5107100</v>
+        <v>3965300</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B61" t="n">
-        <v>347.0033054241789</v>
+        <v>344.7374321868316</v>
       </c>
       <c r="C61" t="n">
-        <v>347.6548674645102</v>
+        <v>350.5430256733688</v>
       </c>
       <c r="D61" t="n">
-        <v>341.6255963537023</v>
+        <v>344.0080864205689</v>
       </c>
       <c r="E61" t="n">
-        <v>344.2804260253906</v>
+        <v>348.0535278320312</v>
       </c>
       <c r="F61" t="n">
-        <v>3965300</v>
+        <v>4166700</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,25 +2029,25 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B62" t="n">
-        <v>344.7374926404726</v>
+        <v>348.719115353366</v>
       </c>
       <c r="C62" t="n">
-        <v>350.5430871450869</v>
+        <v>349.9131924709116</v>
       </c>
       <c r="D62" t="n">
-        <v>344.0081467463108</v>
+        <v>342.5627647323979</v>
       </c>
       <c r="E62" t="n">
-        <v>348.0535888671875</v>
+        <v>343.7079162597656</v>
       </c>
       <c r="F62" t="n">
-        <v>4166700</v>
+        <v>4022800</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2055,25 +2055,25 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B63" t="n">
-        <v>348.7191463158849</v>
+        <v>343.1989538716508</v>
       </c>
       <c r="C63" t="n">
-        <v>349.9132235394517</v>
+        <v>348.0633464265518</v>
       </c>
       <c r="D63" t="n">
-        <v>342.5627951482988</v>
+        <v>342.1027577808173</v>
       </c>
       <c r="E63" t="n">
-        <v>343.7079467773438</v>
+        <v>347.0747985839844</v>
       </c>
       <c r="F63" t="n">
-        <v>4022800</v>
+        <v>5959200</v>
       </c>
       <c r="G63" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B64" t="n">
-        <v>343.1989538716508</v>
+        <v>344.4713302562425</v>
       </c>
       <c r="C64" t="n">
-        <v>348.0633464265518</v>
+        <v>344.6083398260661</v>
       </c>
       <c r="D64" t="n">
-        <v>342.1027577808173</v>
+        <v>338.3541382135411</v>
       </c>
       <c r="E64" t="n">
-        <v>347.0747985839844</v>
+        <v>342.4746704101562</v>
       </c>
       <c r="F64" t="n">
-        <v>5959200</v>
+        <v>7273000</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B65" t="n">
-        <v>344.471360951741</v>
+        <v>340.3703984537347</v>
       </c>
       <c r="C65" t="n">
-        <v>344.6083705337733</v>
+        <v>349.0910719398561</v>
       </c>
       <c r="D65" t="n">
-        <v>338.3541683639427</v>
+        <v>337.62987820622</v>
       </c>
       <c r="E65" t="n">
-        <v>342.4747009277344</v>
+        <v>337.9332885742188</v>
       </c>
       <c r="F65" t="n">
-        <v>7273000</v>
+        <v>5063100</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B66" t="n">
-        <v>340.3703677160696</v>
+        <v>336.7881454975472</v>
       </c>
       <c r="C66" t="n">
-        <v>349.0910404146574</v>
+        <v>344.5398348592771</v>
       </c>
       <c r="D66" t="n">
-        <v>337.6298477160418</v>
+        <v>336.6902644468525</v>
       </c>
       <c r="E66" t="n">
-        <v>337.9332580566406</v>
+        <v>343.6687622070312</v>
       </c>
       <c r="F66" t="n">
-        <v>5063100</v>
+        <v>6316100</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B67" t="n">
-        <v>336.7881155909637</v>
+        <v>348.4352899865784</v>
       </c>
       <c r="C67" t="n">
-        <v>344.5398042643482</v>
+        <v>355.0124966552466</v>
       </c>
       <c r="D67" t="n">
-        <v>336.6902345489607</v>
+        <v>346.4190656980946</v>
       </c>
       <c r="E67" t="n">
-        <v>343.6687316894531</v>
+        <v>349.8642578125</v>
       </c>
       <c r="F67" t="n">
-        <v>6316100</v>
+        <v>6609800</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B68" t="n">
-        <v>348.4352595936447</v>
+        <v>351.6260236653551</v>
       </c>
       <c r="C68" t="n">
-        <v>355.0124656886035</v>
+        <v>353.0941498724499</v>
       </c>
       <c r="D68" t="n">
-        <v>346.4190354810299</v>
+        <v>348.4842120764174</v>
       </c>
       <c r="E68" t="n">
-        <v>349.8642272949219</v>
+        <v>352.0077209472656</v>
       </c>
       <c r="F68" t="n">
-        <v>6609800</v>
+        <v>3861200</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B69" t="n">
-        <v>351.6260236653551</v>
+        <v>351.753261637015</v>
       </c>
       <c r="C69" t="n">
-        <v>353.0941498724499</v>
+        <v>354.9635630414982</v>
       </c>
       <c r="D69" t="n">
-        <v>348.4842120764174</v>
+        <v>348.0633520332391</v>
       </c>
       <c r="E69" t="n">
-        <v>352.0077209472656</v>
+        <v>349.4042358398438</v>
       </c>
       <c r="F69" t="n">
-        <v>3861200</v>
+        <v>4387400</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B70" t="n">
-        <v>351.7532309142689</v>
+        <v>349.3161510627795</v>
       </c>
       <c r="C70" t="n">
-        <v>354.9635320383587</v>
+        <v>351.1170489325283</v>
       </c>
       <c r="D70" t="n">
-        <v>348.0633216327761</v>
+        <v>344.3343131247511</v>
       </c>
       <c r="E70" t="n">
-        <v>349.4042053222656</v>
+        <v>345.1858215332031</v>
       </c>
       <c r="F70" t="n">
-        <v>4387400</v>
+        <v>3497200</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B71" t="n">
-        <v>349.3161510627795</v>
+        <v>344.4909144902828</v>
       </c>
       <c r="C71" t="n">
-        <v>351.1170489325283</v>
+        <v>349.9034051286982</v>
       </c>
       <c r="D71" t="n">
-        <v>344.3343131247511</v>
+        <v>343.5219607726549</v>
       </c>
       <c r="E71" t="n">
-        <v>345.1858215332031</v>
+        <v>349.1693420410156</v>
       </c>
       <c r="F71" t="n">
-        <v>3497200</v>
+        <v>3875200</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B72" t="n">
-        <v>344.4908843816016</v>
+        <v>355.8150530732911</v>
       </c>
       <c r="C72" t="n">
-        <v>349.9033745469626</v>
+        <v>358.5163848099426</v>
       </c>
       <c r="D72" t="n">
-        <v>343.5219307486607</v>
+        <v>347.0258606581617</v>
       </c>
       <c r="E72" t="n">
-        <v>349.1693115234375</v>
+        <v>347.4467163085938</v>
       </c>
       <c r="F72" t="n">
-        <v>3875200</v>
+        <v>4805200</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B73" t="n">
-        <v>355.8150530732911</v>
+        <v>346.5854112795514</v>
       </c>
       <c r="C73" t="n">
-        <v>358.5163848099426</v>
+        <v>346.5854112795514</v>
       </c>
       <c r="D73" t="n">
-        <v>347.0258606581617</v>
+        <v>337.5907194306183</v>
       </c>
       <c r="E73" t="n">
-        <v>347.4467163085938</v>
+        <v>337.6690063476562</v>
       </c>
       <c r="F73" t="n">
-        <v>4805200</v>
+        <v>12825600</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B74" t="n">
-        <v>346.5854112795514</v>
+        <v>337.9724124645031</v>
       </c>
       <c r="C74" t="n">
-        <v>346.5854112795514</v>
+        <v>340.507373272994</v>
       </c>
       <c r="D74" t="n">
-        <v>337.5907194306183</v>
+        <v>336.3966381250771</v>
       </c>
       <c r="E74" t="n">
-        <v>337.6690063476562</v>
+        <v>339.0294799804688</v>
       </c>
       <c r="F74" t="n">
-        <v>12825600</v>
+        <v>3523700</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B75" t="n">
-        <v>337.9724428869297</v>
+        <v>336.6902894441487</v>
       </c>
       <c r="C75" t="n">
-        <v>340.5074039236039</v>
+        <v>340.1159173890746</v>
       </c>
       <c r="D75" t="n">
-        <v>336.3966684056612</v>
+        <v>334.6740651003779</v>
       </c>
       <c r="E75" t="n">
-        <v>339.0295104980469</v>
+        <v>337.6396789550781</v>
       </c>
       <c r="F75" t="n">
-        <v>3523700</v>
+        <v>3873400</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B76" t="n">
-        <v>336.6902590123812</v>
+        <v>337.0230372348798</v>
       </c>
       <c r="C76" t="n">
-        <v>340.1158866476816</v>
+        <v>340.8597534033964</v>
       </c>
       <c r="D76" t="n">
-        <v>334.6740348508469</v>
+        <v>336.592384505686</v>
       </c>
       <c r="E76" t="n">
-        <v>337.6396484375</v>
+        <v>339.9592895507812</v>
       </c>
       <c r="F76" t="n">
-        <v>3873400</v>
+        <v>1368600</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B77" t="n">
-        <v>337.0230372348798</v>
+        <v>339.616749893519</v>
       </c>
       <c r="C77" t="n">
-        <v>340.8597534033964</v>
+        <v>342.6117251227173</v>
       </c>
       <c r="D77" t="n">
-        <v>336.592384505686</v>
+        <v>339.2056912607851</v>
       </c>
       <c r="E77" t="n">
-        <v>339.9592895507812</v>
+        <v>342.3474731445312</v>
       </c>
       <c r="F77" t="n">
-        <v>1368600</v>
+        <v>1786900</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B78" t="n">
-        <v>339.6166893452076</v>
+        <v>342.5627579984686</v>
       </c>
       <c r="C78" t="n">
-        <v>342.6116640404491</v>
+        <v>342.8759654029374</v>
       </c>
       <c r="D78" t="n">
-        <v>339.2056307857591</v>
+        <v>337.4243166284915</v>
       </c>
       <c r="E78" t="n">
-        <v>342.347412109375</v>
+        <v>340.0669555664062</v>
       </c>
       <c r="F78" t="n">
-        <v>1786900</v>
+        <v>3790000</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B79" t="n">
-        <v>342.5627579984686</v>
+        <v>338.6771490106644</v>
       </c>
       <c r="C79" t="n">
-        <v>342.8759654029374</v>
+        <v>339.6069742481806</v>
       </c>
       <c r="D79" t="n">
-        <v>337.4243166284915</v>
+        <v>336.4162369795515</v>
       </c>
       <c r="E79" t="n">
-        <v>340.0669555664062</v>
+        <v>338.9903564453125</v>
       </c>
       <c r="F79" t="n">
-        <v>3790000</v>
+        <v>2392600</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B80" t="n">
-        <v>338.6771490106644</v>
+        <v>338.1583614393335</v>
       </c>
       <c r="C80" t="n">
-        <v>339.6069742481806</v>
+        <v>339.3426414040363</v>
       </c>
       <c r="D80" t="n">
-        <v>336.4162369795515</v>
+        <v>336.6608740870579</v>
       </c>
       <c r="E80" t="n">
-        <v>338.9903564453125</v>
+        <v>336.7881164550781</v>
       </c>
       <c r="F80" t="n">
-        <v>2392600</v>
+        <v>2317500</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B81" t="n">
-        <v>338.1583920810744</v>
+        <v>336.1323898352527</v>
       </c>
       <c r="C81" t="n">
-        <v>339.342672153089</v>
+        <v>341.084866637523</v>
       </c>
       <c r="D81" t="n">
-        <v>336.6609045931061</v>
+        <v>333.6757455669131</v>
       </c>
       <c r="E81" t="n">
-        <v>336.7881469726562</v>
+        <v>338.4716186523438</v>
       </c>
       <c r="F81" t="n">
-        <v>2317500</v>
+        <v>3763000</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B82" t="n">
-        <v>336.1323595285862</v>
+        <v>335.4179331780732</v>
       </c>
       <c r="C82" t="n">
-        <v>341.0848358843269</v>
+        <v>339.9691187237194</v>
       </c>
       <c r="D82" t="n">
-        <v>333.6757154817447</v>
+        <v>333.9987324770484</v>
       </c>
       <c r="E82" t="n">
-        <v>338.4715881347656</v>
+        <v>336.7783813476562</v>
       </c>
       <c r="F82" t="n">
-        <v>3763000</v>
+        <v>4725300</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B83" t="n">
-        <v>335.4178723894742</v>
+        <v>334.2434119942842</v>
       </c>
       <c r="C83" t="n">
-        <v>339.9690571102981</v>
+        <v>343.2283375405087</v>
       </c>
       <c r="D83" t="n">
-        <v>333.9986719456546</v>
+        <v>330.5339379458445</v>
       </c>
       <c r="E83" t="n">
-        <v>336.7783203125</v>
+        <v>341.8678894042969</v>
       </c>
       <c r="F83" t="n">
-        <v>4725300</v>
+        <v>4680300</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B84" t="n">
-        <v>334.2433821573216</v>
+        <v>345.83178268285</v>
       </c>
       <c r="C84" t="n">
-        <v>343.2283069014873</v>
+        <v>350.8821400825564</v>
       </c>
       <c r="D84" t="n">
-        <v>330.5339084400161</v>
+        <v>341.6133693854721</v>
       </c>
       <c r="E84" t="n">
-        <v>341.8678588867188</v>
+        <v>341.6427307128906</v>
       </c>
       <c r="F84" t="n">
-        <v>4680300</v>
+        <v>4442700</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B85" t="n">
-        <v>345.8318135746193</v>
+        <v>337.9724478428672</v>
       </c>
       <c r="C85" t="n">
-        <v>350.882171425454</v>
+        <v>355.5214431146019</v>
       </c>
       <c r="D85" t="n">
-        <v>341.6133999004275</v>
+        <v>336.7881676979742</v>
       </c>
       <c r="E85" t="n">
-        <v>341.6427612304688</v>
+        <v>351.9196472167969</v>
       </c>
       <c r="F85" t="n">
-        <v>4442700</v>
+        <v>5196500</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B86" t="n">
-        <v>337.9724185347548</v>
+        <v>355.7759014105663</v>
       </c>
       <c r="C86" t="n">
-        <v>355.5214122846852</v>
+        <v>367.5111134698199</v>
       </c>
       <c r="D86" t="n">
-        <v>336.7881384925595</v>
+        <v>353.632434855731</v>
       </c>
       <c r="E86" t="n">
-        <v>351.9196166992188</v>
+        <v>366.67919921875</v>
       </c>
       <c r="F86" t="n">
-        <v>5196500</v>
+        <v>7093500</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B87" t="n">
-        <v>355.7759014105663</v>
+        <v>366.679226053498</v>
       </c>
       <c r="C87" t="n">
-        <v>367.5111134698199</v>
+        <v>368.4214013397691</v>
       </c>
       <c r="D87" t="n">
-        <v>353.632434855731</v>
+        <v>361.4037447316197</v>
       </c>
       <c r="E87" t="n">
-        <v>366.67919921875</v>
+        <v>366.9728393554688</v>
       </c>
       <c r="F87" t="n">
-        <v>7093500</v>
+        <v>5859800</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B88" t="n">
-        <v>366.6791955603369</v>
+        <v>367.8830764002425</v>
       </c>
       <c r="C88" t="n">
-        <v>368.4213707017282</v>
+        <v>372.1014901649237</v>
       </c>
       <c r="D88" t="n">
-        <v>361.4037146771692</v>
+        <v>362.9403965662702</v>
       </c>
       <c r="E88" t="n">
-        <v>366.9728088378906</v>
+        <v>371.6708374023438</v>
       </c>
       <c r="F88" t="n">
-        <v>5859800</v>
+        <v>4785800</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B89" t="n">
-        <v>367.8830461936743</v>
+        <v>368.6856001817422</v>
       </c>
       <c r="C89" t="n">
-        <v>372.1014596119851</v>
+        <v>372.0133465573169</v>
       </c>
       <c r="D89" t="n">
-        <v>362.9403667655412</v>
+        <v>366.0233971074624</v>
       </c>
       <c r="E89" t="n">
-        <v>371.6708068847656</v>
+        <v>367.9613342285156</v>
       </c>
       <c r="F89" t="n">
-        <v>4785800</v>
+        <v>4959900</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B90" t="n">
-        <v>368.6856307593888</v>
+        <v>368.0298576269892</v>
       </c>
       <c r="C90" t="n">
-        <v>372.0133774109565</v>
+        <v>372.1014644570138</v>
       </c>
       <c r="D90" t="n">
-        <v>366.023427464314</v>
+        <v>366.5030087993679</v>
       </c>
       <c r="E90" t="n">
-        <v>367.9613647460938</v>
+        <v>371.1031494140625</v>
       </c>
       <c r="F90" t="n">
-        <v>4959900</v>
+        <v>2990100</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B91" t="n">
-        <v>368.0298878918359</v>
+        <v>371.1912414425437</v>
       </c>
       <c r="C91" t="n">
-        <v>372.1014950566882</v>
+        <v>374.6364335107019</v>
       </c>
       <c r="D91" t="n">
-        <v>366.5030389386545</v>
+        <v>369.4882246061678</v>
       </c>
       <c r="E91" t="n">
-        <v>371.1031799316406</v>
+        <v>372.0917053222656</v>
       </c>
       <c r="F91" t="n">
-        <v>2990100</v>
+        <v>3709000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B92" t="n">
-        <v>371.1912414425437</v>
+        <v>364.330180714857</v>
       </c>
       <c r="C92" t="n">
-        <v>374.6364335107019</v>
+        <v>369.3218156656606</v>
       </c>
       <c r="D92" t="n">
-        <v>369.4882246061678</v>
+        <v>363.4101525923161</v>
       </c>
       <c r="E92" t="n">
-        <v>372.0917053222656</v>
+        <v>367.1391906738281</v>
       </c>
       <c r="F92" t="n">
-        <v>3709000</v>
+        <v>5353700</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B93" t="n">
-        <v>364.330180714857</v>
+        <v>367.8145223498818</v>
       </c>
       <c r="C93" t="n">
-        <v>369.3218156656606</v>
+        <v>377.7195050958379</v>
       </c>
       <c r="D93" t="n">
-        <v>363.4101525923161</v>
+        <v>366.7183262816438</v>
       </c>
       <c r="E93" t="n">
-        <v>367.1391906738281</v>
+        <v>376.4667053222656</v>
       </c>
       <c r="F93" t="n">
-        <v>5353700</v>
+        <v>5169800</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B94" t="n">
-        <v>367.8145521660867</v>
+        <v>378.2382530449191</v>
       </c>
       <c r="C94" t="n">
-        <v>377.719535714972</v>
+        <v>382.3000628313615</v>
       </c>
       <c r="D94" t="n">
-        <v>366.7183560089877</v>
+        <v>372.4440352517285</v>
       </c>
       <c r="E94" t="n">
-        <v>376.4667358398438</v>
+        <v>372.9334106445312</v>
       </c>
       <c r="F94" t="n">
-        <v>5169800</v>
+        <v>4828100</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B95" t="n">
-        <v>378.2382839965987</v>
+        <v>373.3934198383746</v>
       </c>
       <c r="C95" t="n">
-        <v>382.3000941154238</v>
+        <v>376.2024297773683</v>
       </c>
       <c r="D95" t="n">
-        <v>372.4440657292604</v>
+        <v>371.1520722052226</v>
       </c>
       <c r="E95" t="n">
-        <v>372.9334411621094</v>
+        <v>375.6151733398438</v>
       </c>
       <c r="F95" t="n">
-        <v>4828100</v>
+        <v>3138300</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B96" t="n">
-        <v>373.3934198383746</v>
+        <v>376.8190408591946</v>
       </c>
       <c r="C96" t="n">
-        <v>376.2024297773683</v>
+        <v>379.1876308298576</v>
       </c>
       <c r="D96" t="n">
-        <v>371.1520722052226</v>
+        <v>373.8338630026265</v>
       </c>
       <c r="E96" t="n">
-        <v>375.6151733398438</v>
+        <v>378.3165283203125</v>
       </c>
       <c r="F96" t="n">
-        <v>3138300</v>
+        <v>3984800</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B97" t="n">
-        <v>376.8190712559752</v>
+        <v>376.7701414908988</v>
       </c>
       <c r="C97" t="n">
-        <v>379.1876614177048</v>
+        <v>378.2871933198306</v>
       </c>
       <c r="D97" t="n">
-        <v>373.8338931586024</v>
+        <v>370.2320632887583</v>
       </c>
       <c r="E97" t="n">
-        <v>378.3165588378906</v>
+        <v>372.2776489257812</v>
       </c>
       <c r="F97" t="n">
-        <v>3984800</v>
+        <v>3466100</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B98" t="n">
-        <v>376.7701106050471</v>
+        <v>372.1308348268722</v>
       </c>
       <c r="C98" t="n">
-        <v>378.2871623096181</v>
+        <v>372.9040563253842</v>
       </c>
       <c r="D98" t="n">
-        <v>370.2320329388677</v>
+        <v>365.7102319421367</v>
       </c>
       <c r="E98" t="n">
-        <v>372.2776184082031</v>
+        <v>367.3251647949219</v>
       </c>
       <c r="F98" t="n">
-        <v>3466100</v>
+        <v>3371500</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B99" t="n">
-        <v>372.1308348268722</v>
+        <v>366.9336686607455</v>
       </c>
       <c r="C99" t="n">
-        <v>372.9040563253842</v>
+        <v>369.0771353006065</v>
       </c>
       <c r="D99" t="n">
-        <v>365.7102319421367</v>
+        <v>362.284602364362</v>
       </c>
       <c r="E99" t="n">
-        <v>367.3251647949219</v>
+        <v>363.9093322753906</v>
       </c>
       <c r="F99" t="n">
-        <v>3371500</v>
+        <v>4744500</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B100" t="n">
-        <v>366.9336686607455</v>
+        <v>364.4965795036834</v>
       </c>
       <c r="C100" t="n">
-        <v>369.0771353006065</v>
+        <v>367.1489857391411</v>
       </c>
       <c r="D100" t="n">
-        <v>362.284602364362</v>
+        <v>360.7185859823057</v>
       </c>
       <c r="E100" t="n">
-        <v>363.9093322753906</v>
+        <v>366.6302490234375</v>
       </c>
       <c r="F100" t="n">
-        <v>4744500</v>
+        <v>3755600</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B101" t="n">
-        <v>364.4965795036834</v>
+        <v>366.2876778370263</v>
       </c>
       <c r="C101" t="n">
-        <v>367.1489857391411</v>
+        <v>371.5827230758924</v>
       </c>
       <c r="D101" t="n">
-        <v>360.7185859823057</v>
+        <v>360.4151732293658</v>
       </c>
       <c r="E101" t="n">
-        <v>366.6302490234375</v>
+        <v>370.0852355957031</v>
       </c>
       <c r="F101" t="n">
-        <v>3755600</v>
+        <v>4757200</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B102" t="n">
-        <v>366.2876778370263</v>
+        <v>369.2728845813793</v>
       </c>
       <c r="C102" t="n">
-        <v>371.5827230758924</v>
+        <v>383.4549736116182</v>
       </c>
       <c r="D102" t="n">
-        <v>360.4151732293658</v>
+        <v>368.9890384961104</v>
       </c>
       <c r="E102" t="n">
-        <v>370.0852355957031</v>
+        <v>373.0019226074219</v>
       </c>
       <c r="F102" t="n">
-        <v>4757200</v>
+        <v>5684400</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B103" t="n">
-        <v>369.2728845813793</v>
+        <v>376.4177654444651</v>
       </c>
       <c r="C103" t="n">
-        <v>383.4549736116182</v>
+        <v>382.2315475683361</v>
       </c>
       <c r="D103" t="n">
-        <v>368.9890384961104</v>
+        <v>376.1926420082714</v>
       </c>
       <c r="E103" t="n">
-        <v>373.0019226074219</v>
+        <v>378.9723205566406</v>
       </c>
       <c r="F103" t="n">
-        <v>5684400</v>
+        <v>5574700</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B104" t="n">
-        <v>376.4177351325982</v>
+        <v>378.4633475893863</v>
       </c>
       <c r="C104" t="n">
-        <v>382.2315167883015</v>
+        <v>378.776555010176</v>
       </c>
       <c r="D104" t="n">
-        <v>376.192611714533</v>
+        <v>372.7376495049467</v>
       </c>
       <c r="E104" t="n">
-        <v>378.9722900390625</v>
+        <v>374.2449340820312</v>
       </c>
       <c r="F104" t="n">
-        <v>5574700</v>
+        <v>3759700</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B105" t="n">
-        <v>378.4633475893863</v>
+        <v>373.2368430239695</v>
       </c>
       <c r="C105" t="n">
-        <v>378.776555010176</v>
+        <v>378.159958571324</v>
       </c>
       <c r="D105" t="n">
-        <v>372.7376495049467</v>
+        <v>371.0444506929488</v>
       </c>
       <c r="E105" t="n">
-        <v>374.2449340820312</v>
+        <v>376.9658813476562</v>
       </c>
       <c r="F105" t="n">
-        <v>3759700</v>
+        <v>4685400</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B106" t="n">
-        <v>373.2368128082787</v>
+        <v>376.1926410669886</v>
       </c>
       <c r="C106" t="n">
-        <v>378.1599279570784</v>
+        <v>377.5824803376956</v>
       </c>
       <c r="D106" t="n">
-        <v>371.0444206547449</v>
+        <v>370.163562457197</v>
       </c>
       <c r="E106" t="n">
-        <v>376.9658508300781</v>
+        <v>372.904052734375</v>
       </c>
       <c r="F106" t="n">
-        <v>4685400</v>
+        <v>3639300</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B107" t="n">
-        <v>376.1926410669886</v>
+        <v>375.6543348626084</v>
       </c>
       <c r="C107" t="n">
-        <v>377.5824803376956</v>
+        <v>383.4158213872818</v>
       </c>
       <c r="D107" t="n">
-        <v>370.163562457197</v>
+        <v>373.8240756812119</v>
       </c>
       <c r="E107" t="n">
-        <v>372.904052734375</v>
+        <v>381.3995971679688</v>
       </c>
       <c r="F107" t="n">
-        <v>3639300</v>
+        <v>3160800</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B108" t="n">
-        <v>375.6543048047358</v>
+        <v>376.8190294616336</v>
       </c>
       <c r="C108" t="n">
-        <v>383.4157907083761</v>
+        <v>383.1026222641518</v>
       </c>
       <c r="D108" t="n">
-        <v>373.8240457697869</v>
+        <v>373.9610641996757</v>
       </c>
       <c r="E108" t="n">
-        <v>381.3995666503906</v>
+        <v>382.3783264160156</v>
       </c>
       <c r="F108" t="n">
-        <v>3160800</v>
+        <v>3229900</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B109" t="n">
-        <v>376.8190595355247</v>
+        <v>385.187358063094</v>
       </c>
       <c r="C109" t="n">
-        <v>383.1026528395359</v>
+        <v>389.1806779778082</v>
       </c>
       <c r="D109" t="n">
-        <v>373.9610940454729</v>
+        <v>380.7340539554721</v>
       </c>
       <c r="E109" t="n">
-        <v>382.3783569335938</v>
+        <v>381.9281311035156</v>
       </c>
       <c r="F109" t="n">
-        <v>3229900</v>
+        <v>3702200</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B110" t="n">
-        <v>385.1873888410973</v>
+        <v>381.908564252376</v>
       </c>
       <c r="C110" t="n">
-        <v>389.1807090748937</v>
+        <v>385.6278052487582</v>
       </c>
       <c r="D110" t="n">
-        <v>380.7340843776387</v>
+        <v>378.8744308768519</v>
       </c>
       <c r="E110" t="n">
-        <v>381.9281616210938</v>
+        <v>382.740478515625</v>
       </c>
       <c r="F110" t="n">
-        <v>3702200</v>
+        <v>2875900</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B111" t="n">
-        <v>381.908564252376</v>
+        <v>383.895448836351</v>
       </c>
       <c r="C111" t="n">
-        <v>385.6278052487582</v>
+        <v>385.6278270527202</v>
       </c>
       <c r="D111" t="n">
-        <v>378.8744308768519</v>
+        <v>372.4146908465991</v>
       </c>
       <c r="E111" t="n">
-        <v>382.740478515625</v>
+        <v>374.9007263183594</v>
       </c>
       <c r="F111" t="n">
-        <v>2875900</v>
+        <v>3485300</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B112" t="n">
-        <v>383.895448836351</v>
+        <v>374.6168560607417</v>
       </c>
       <c r="C112" t="n">
-        <v>385.6278270527202</v>
+        <v>376.9364905994225</v>
       </c>
       <c r="D112" t="n">
-        <v>372.4146908465991</v>
+        <v>371.4750744620919</v>
       </c>
       <c r="E112" t="n">
-        <v>374.9007263183594</v>
+        <v>375.3704833984375</v>
       </c>
       <c r="F112" t="n">
-        <v>3485300</v>
+        <v>2982600</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B113" t="n">
-        <v>374.6168560607417</v>
+        <v>375.5858190931522</v>
       </c>
       <c r="C113" t="n">
-        <v>376.9364905994225</v>
+        <v>375.5858190931522</v>
       </c>
       <c r="D113" t="n">
-        <v>371.4750744620919</v>
+        <v>369.3707754637165</v>
       </c>
       <c r="E113" t="n">
-        <v>375.3704833984375</v>
+        <v>370.5354614257812</v>
       </c>
       <c r="F113" t="n">
-        <v>2982600</v>
+        <v>2930900</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B114" t="n">
-        <v>375.5858190931522</v>
+        <v>369.4294802998945</v>
       </c>
       <c r="C114" t="n">
-        <v>375.5858190931522</v>
+        <v>376.6428685046932</v>
       </c>
       <c r="D114" t="n">
-        <v>369.3707754637165</v>
+        <v>367.9613541837774</v>
       </c>
       <c r="E114" t="n">
-        <v>370.5354614257812</v>
+        <v>374.1274719238281</v>
       </c>
       <c r="F114" t="n">
-        <v>2930900</v>
+        <v>3984100</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B115" t="n">
-        <v>369.4294802998945</v>
+        <v>372.8942511780455</v>
       </c>
       <c r="C115" t="n">
-        <v>376.6428685046932</v>
+        <v>375.977340039125</v>
       </c>
       <c r="D115" t="n">
-        <v>367.9613541837774</v>
+        <v>361.7267011620893</v>
       </c>
       <c r="E115" t="n">
-        <v>374.1274719238281</v>
+        <v>368.979248046875</v>
       </c>
       <c r="F115" t="n">
-        <v>3984100</v>
+        <v>5495700</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B116" t="n">
-        <v>372.8942820194261</v>
+        <v>380.8417107584177</v>
       </c>
       <c r="C116" t="n">
-        <v>375.9773711355021</v>
+        <v>385.9703852790173</v>
       </c>
       <c r="D116" t="n">
-        <v>361.726731079823</v>
+        <v>374.0883361890514</v>
       </c>
       <c r="E116" t="n">
-        <v>368.9792785644531</v>
+        <v>376.3101196289062</v>
       </c>
       <c r="F116" t="n">
-        <v>5495700</v>
+        <v>5675800</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B117" t="n">
-        <v>380.8417107584177</v>
+        <v>372.9725454847734</v>
       </c>
       <c r="C117" t="n">
-        <v>385.9703852790173</v>
+        <v>373.3346784735209</v>
       </c>
       <c r="D117" t="n">
-        <v>374.0883361890514</v>
+        <v>363.4786515163307</v>
       </c>
       <c r="E117" t="n">
-        <v>376.3101196289062</v>
+        <v>367.5894165039062</v>
       </c>
       <c r="F117" t="n">
-        <v>5675800</v>
+        <v>5036900</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B118" t="n">
-        <v>372.9725764492633</v>
+        <v>370.3593224067619</v>
       </c>
       <c r="C118" t="n">
-        <v>373.3347094680754</v>
+        <v>373.3738918063265</v>
       </c>
       <c r="D118" t="n">
-        <v>363.4786816926297</v>
+        <v>366.9728527674773</v>
       </c>
       <c r="E118" t="n">
-        <v>367.5894470214844</v>
+        <v>367.1196594238281</v>
       </c>
       <c r="F118" t="n">
-        <v>5036900</v>
+        <v>2889400</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B119" t="n">
-        <v>370.3592916198801</v>
+        <v>365.9157289111819</v>
       </c>
       <c r="C119" t="n">
-        <v>373.3738607688525</v>
+        <v>374.0687391147384</v>
       </c>
       <c r="D119" t="n">
-        <v>366.9728222621029</v>
+        <v>364.4280385734429</v>
       </c>
       <c r="E119" t="n">
-        <v>367.11962890625</v>
+        <v>372.6299743652344</v>
       </c>
       <c r="F119" t="n">
-        <v>2889400</v>
+        <v>4819500</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B120" t="n">
-        <v>365.915758878878</v>
+        <v>367.0315406467873</v>
       </c>
       <c r="C120" t="n">
-        <v>374.0687697501482</v>
+        <v>367.1391888948742</v>
       </c>
       <c r="D120" t="n">
-        <v>364.4280684193005</v>
+        <v>361.1590359964387</v>
       </c>
       <c r="E120" t="n">
-        <v>372.6300048828125</v>
+        <v>362.9305725097656</v>
       </c>
       <c r="F120" t="n">
-        <v>4819500</v>
+        <v>4537600</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B121" t="n">
-        <v>367.0315406467873</v>
+        <v>356.0010127710523</v>
       </c>
       <c r="C121" t="n">
-        <v>367.1391888948742</v>
+        <v>360.9436919959621</v>
       </c>
       <c r="D121" t="n">
-        <v>361.1590359964387</v>
+        <v>352.4677071137912</v>
       </c>
       <c r="E121" t="n">
-        <v>362.9305725097656</v>
+        <v>359.1232299804688</v>
       </c>
       <c r="F121" t="n">
-        <v>4537600</v>
+        <v>3964700</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B122" t="n">
-        <v>356.0010430233106</v>
+        <v>358.4185545746917</v>
       </c>
       <c r="C122" t="n">
-        <v>360.9437226682394</v>
+        <v>361.716939988571</v>
       </c>
       <c r="D122" t="n">
-        <v>352.4677370657963</v>
+        <v>353.8282109374275</v>
       </c>
       <c r="E122" t="n">
-        <v>359.1232604980469</v>
+        <v>361.2666931152344</v>
       </c>
       <c r="F122" t="n">
-        <v>3964700</v>
+        <v>4324400</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B123" t="n">
-        <v>358.4185545746917</v>
+        <v>358.3402236370215</v>
       </c>
       <c r="C123" t="n">
-        <v>361.716939988571</v>
+        <v>359.1819648229422</v>
       </c>
       <c r="D123" t="n">
-        <v>353.8282109374275</v>
+        <v>351.5672851014027</v>
       </c>
       <c r="E123" t="n">
-        <v>361.2666931152344</v>
+        <v>353.9945678710938</v>
       </c>
       <c r="F123" t="n">
-        <v>4324400</v>
+        <v>4752200</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B124" t="n">
-        <v>358.340254529235</v>
+        <v>349.9425535763344</v>
       </c>
       <c r="C124" t="n">
-        <v>359.1819957877215</v>
+        <v>351.8119711041206</v>
       </c>
       <c r="D124" t="n">
-        <v>351.5673154097268</v>
+        <v>345.714343142884</v>
       </c>
       <c r="E124" t="n">
-        <v>353.9945983886719</v>
+        <v>350.3144836425781</v>
       </c>
       <c r="F124" t="n">
-        <v>4752200</v>
+        <v>4167400</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B125" t="n">
-        <v>349.9425840615119</v>
+        <v>348.0437790706712</v>
       </c>
       <c r="C125" t="n">
-        <v>351.8120017521521</v>
+        <v>348.9148517222478</v>
       </c>
       <c r="D125" t="n">
-        <v>345.7143732597218</v>
+        <v>338.2954297848507</v>
       </c>
       <c r="E125" t="n">
-        <v>350.3145141601562</v>
+        <v>346.047119140625</v>
       </c>
       <c r="F125" t="n">
-        <v>4167400</v>
+        <v>4224500</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B126" t="n">
-        <v>348.0437790706712</v>
+        <v>345.5381703207324</v>
       </c>
       <c r="C126" t="n">
-        <v>348.9148517222478</v>
+        <v>353.9554326757943</v>
       </c>
       <c r="D126" t="n">
-        <v>338.2954297848507</v>
+        <v>343.5610747056572</v>
       </c>
       <c r="E126" t="n">
-        <v>346.047119140625</v>
+        <v>349.5608215332031</v>
       </c>
       <c r="F126" t="n">
-        <v>4224500</v>
+        <v>3986000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B127" t="n">
-        <v>345.5381703207324</v>
+        <v>347.906742012967</v>
       </c>
       <c r="C127" t="n">
-        <v>353.9554326757943</v>
+        <v>348.7484832111462</v>
       </c>
       <c r="D127" t="n">
-        <v>343.5610747056572</v>
+        <v>341.6916686197754</v>
       </c>
       <c r="E127" t="n">
-        <v>349.5608215332031</v>
+        <v>343.3849182128906</v>
       </c>
       <c r="F127" t="n">
-        <v>3986000</v>
+        <v>3197100</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,25 +3745,25 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B128" t="n">
-        <v>347.9067729324123</v>
+        <v>340.9512279608855</v>
       </c>
       <c r="C128" t="n">
-        <v>348.7485142053993</v>
+        <v>343.5425566286561</v>
       </c>
       <c r="D128" t="n">
-        <v>341.6916989868697</v>
+        <v>333.7191718320135</v>
       </c>
       <c r="E128" t="n">
-        <v>343.3849487304688</v>
+        <v>333.9457702636719</v>
       </c>
       <c r="F128" t="n">
-        <v>3197100</v>
+        <v>3893600</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -3771,25 +3771,25 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B129" t="n">
-        <v>340.9512591186561</v>
+        <v>336.6651978613972</v>
       </c>
       <c r="C129" t="n">
-        <v>343.5425880232349</v>
+        <v>338.3697677547303</v>
       </c>
       <c r="D129" t="n">
-        <v>333.719202328884</v>
+        <v>333.0590172641502</v>
       </c>
       <c r="E129" t="n">
-        <v>333.94580078125</v>
+        <v>334.0443115234375</v>
       </c>
       <c r="F129" t="n">
-        <v>3893600</v>
+        <v>2531900</v>
       </c>
       <c r="G129" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B130" t="n">
-        <v>336.6651978613972</v>
+        <v>337.4041886890553</v>
       </c>
       <c r="C130" t="n">
-        <v>338.3697677547303</v>
+        <v>340.1630007521627</v>
       </c>
       <c r="D130" t="n">
-        <v>333.0590172641502</v>
+        <v>335.6405034404279</v>
       </c>
       <c r="E130" t="n">
-        <v>334.0443115234375</v>
+        <v>337.5421142578125</v>
       </c>
       <c r="F130" t="n">
-        <v>2531900</v>
+        <v>3194400</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B131" t="n">
-        <v>337.4041886890553</v>
+        <v>339.81816704201</v>
       </c>
       <c r="C131" t="n">
-        <v>340.1630007521627</v>
+        <v>341.6803576413574</v>
       </c>
       <c r="D131" t="n">
-        <v>335.6405034404279</v>
+        <v>335.9262425125186</v>
       </c>
       <c r="E131" t="n">
-        <v>337.5421142578125</v>
+        <v>336.4090270996094</v>
       </c>
       <c r="F131" t="n">
-        <v>3194400</v>
+        <v>3075900</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B132" t="n">
-        <v>339.81816704201</v>
+        <v>333.6206668009991</v>
       </c>
       <c r="C132" t="n">
-        <v>341.6803576413574</v>
+        <v>334.8030019580219</v>
       </c>
       <c r="D132" t="n">
-        <v>335.9262425125186</v>
+        <v>325.2850851722408</v>
       </c>
       <c r="E132" t="n">
-        <v>336.4090270996094</v>
+        <v>326.0634460449219</v>
       </c>
       <c r="F132" t="n">
-        <v>3075900</v>
+        <v>3592200</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B133" t="n">
-        <v>333.6206668009991</v>
+        <v>324.1224241388957</v>
       </c>
       <c r="C133" t="n">
-        <v>334.8030019580219</v>
+        <v>325.3737672197113</v>
       </c>
       <c r="D133" t="n">
-        <v>325.2850851722408</v>
+        <v>319.8561127917808</v>
       </c>
       <c r="E133" t="n">
-        <v>326.0634460449219</v>
+        <v>323.3834533691406</v>
       </c>
       <c r="F133" t="n">
-        <v>3592200</v>
+        <v>3845400</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B134" t="n">
-        <v>324.1224241388957</v>
+        <v>322.9302020886868</v>
       </c>
       <c r="C134" t="n">
-        <v>325.3737672197113</v>
+        <v>325.3737427416146</v>
       </c>
       <c r="D134" t="n">
-        <v>319.8561127917808</v>
+        <v>315.5503575119392</v>
       </c>
       <c r="E134" t="n">
-        <v>323.3834533691406</v>
+        <v>316.0331420898438</v>
       </c>
       <c r="F134" t="n">
-        <v>3845400</v>
+        <v>9672200</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B135" t="n">
-        <v>322.930233272276</v>
+        <v>327.1078416794463</v>
       </c>
       <c r="C135" t="n">
-        <v>325.3737741611631</v>
+        <v>329.7977059156196</v>
       </c>
       <c r="D135" t="n">
-        <v>315.5503879828975</v>
+        <v>323.3834304664039</v>
       </c>
       <c r="E135" t="n">
-        <v>316.0331726074219</v>
+        <v>326.0338745117188</v>
       </c>
       <c r="F135" t="n">
-        <v>9672200</v>
+        <v>5806300</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B136" t="n">
-        <v>327.1078722975504</v>
+        <v>321.1074278121778</v>
       </c>
       <c r="C136" t="n">
-        <v>329.7977367855016</v>
+        <v>327.6300717030042</v>
       </c>
       <c r="D136" t="n">
-        <v>323.3834607358939</v>
+        <v>318.2697752275627</v>
       </c>
       <c r="E136" t="n">
-        <v>326.0339050292969</v>
+        <v>326.0437622070312</v>
       </c>
       <c r="F136" t="n">
-        <v>5806300</v>
+        <v>4566400</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B137" t="n">
-        <v>321.1073977566388</v>
+        <v>330.0735818610078</v>
       </c>
       <c r="C137" t="n">
-        <v>327.6300410369481</v>
+        <v>332.2313787270356</v>
       </c>
       <c r="D137" t="n">
-        <v>318.2697454376269</v>
+        <v>322.1813651025556</v>
       </c>
       <c r="E137" t="n">
-        <v>326.0437316894531</v>
+        <v>327.6202087402344</v>
       </c>
       <c r="F137" t="n">
-        <v>4566400</v>
+        <v>4397800</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B138" t="n">
-        <v>330.0736126071158</v>
+        <v>326.5659345775528</v>
       </c>
       <c r="C138" t="n">
-        <v>332.2314096741407</v>
+        <v>329.2065159991698</v>
       </c>
       <c r="D138" t="n">
-        <v>322.1813951135094</v>
+        <v>321.7872513641968</v>
       </c>
       <c r="E138" t="n">
-        <v>327.6202392578125</v>
+        <v>323.6001892089844</v>
       </c>
       <c r="F138" t="n">
-        <v>4397800</v>
+        <v>3448400</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B139" t="n">
-        <v>326.5659345775528</v>
+        <v>322.6838998401017</v>
       </c>
       <c r="C139" t="n">
-        <v>329.2065159991698</v>
+        <v>322.7233200333912</v>
       </c>
       <c r="D139" t="n">
-        <v>321.7872513641968</v>
+        <v>316.0233004076466</v>
       </c>
       <c r="E139" t="n">
-        <v>323.6001892089844</v>
+        <v>316.919921875</v>
       </c>
       <c r="F139" t="n">
-        <v>3448400</v>
+        <v>3977400</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B140" t="n">
-        <v>322.6838998401017</v>
+        <v>320.9300608492875</v>
       </c>
       <c r="C140" t="n">
-        <v>322.7233200333912</v>
+        <v>323.1666680872671</v>
       </c>
       <c r="D140" t="n">
-        <v>316.0233004076466</v>
+        <v>317.8362223118503</v>
       </c>
       <c r="E140" t="n">
-        <v>316.919921875</v>
+        <v>318.7427062988281</v>
       </c>
       <c r="F140" t="n">
-        <v>3977400</v>
+        <v>4066000</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B141" t="n">
-        <v>320.9300608492875</v>
+        <v>323.6593250096307</v>
       </c>
       <c r="C141" t="n">
-        <v>323.1666680872671</v>
+        <v>326.5659553121756</v>
       </c>
       <c r="D141" t="n">
-        <v>317.8362223118503</v>
+        <v>318.6540430408731</v>
       </c>
       <c r="E141" t="n">
-        <v>318.7427062988281</v>
+        <v>324.053466796875</v>
       </c>
       <c r="F141" t="n">
-        <v>4066000</v>
+        <v>5749100</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B142" t="n">
-        <v>323.6593250096307</v>
+        <v>324.5264147036482</v>
       </c>
       <c r="C142" t="n">
-        <v>326.5659553121756</v>
+        <v>328.1917111081323</v>
       </c>
       <c r="D142" t="n">
-        <v>318.6540430408731</v>
+        <v>322.9893578310064</v>
       </c>
       <c r="E142" t="n">
-        <v>324.053466796875</v>
+        <v>324.713623046875</v>
       </c>
       <c r="F142" t="n">
-        <v>5749100</v>
+        <v>3386200</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B143" t="n">
-        <v>324.5263842036645</v>
+        <v>318.841238474905</v>
       </c>
       <c r="C143" t="n">
-        <v>328.1916802636729</v>
+        <v>321.5015150184395</v>
       </c>
       <c r="D143" t="n">
-        <v>322.98932747548</v>
+        <v>313.9738822734865</v>
       </c>
       <c r="E143" t="n">
-        <v>324.7135925292969</v>
+        <v>316.9002075195312</v>
       </c>
       <c r="F143" t="n">
-        <v>3386200</v>
+        <v>3732300</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B144" t="n">
-        <v>318.841238474905</v>
+        <v>314.9985972226668</v>
       </c>
       <c r="C144" t="n">
-        <v>321.5015150184395</v>
+        <v>321.875932137731</v>
       </c>
       <c r="D144" t="n">
-        <v>313.9738822734865</v>
+        <v>314.2300688775543</v>
       </c>
       <c r="E144" t="n">
-        <v>316.9002075195312</v>
+        <v>321.8463745117188</v>
       </c>
       <c r="F144" t="n">
-        <v>3732300</v>
+        <v>2448300</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B145" t="n">
-        <v>314.9985972226668</v>
+        <v>318.2500813990391</v>
       </c>
       <c r="C145" t="n">
-        <v>321.875932137731</v>
+        <v>319.6097924401727</v>
       </c>
       <c r="D145" t="n">
-        <v>314.2300688775543</v>
+        <v>310.673165290877</v>
       </c>
       <c r="E145" t="n">
-        <v>321.8463745117188</v>
+        <v>314.082275390625</v>
       </c>
       <c r="F145" t="n">
-        <v>2448300</v>
+        <v>4661600</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B146" t="n">
-        <v>318.2500813990391</v>
+        <v>328.3591748751156</v>
       </c>
       <c r="C146" t="n">
-        <v>319.6097924401727</v>
+        <v>333.7979883682909</v>
       </c>
       <c r="D146" t="n">
-        <v>310.673165290877</v>
+        <v>327.3640180499997</v>
       </c>
       <c r="E146" t="n">
-        <v>314.082275390625</v>
+        <v>331.2165222167969</v>
       </c>
       <c r="F146" t="n">
-        <v>4661600</v>
+        <v>4610600</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B147" t="n">
-        <v>328.3591748751156</v>
+        <v>326.388616523007</v>
       </c>
       <c r="C147" t="n">
-        <v>333.7979883682909</v>
+        <v>335.5617045306175</v>
       </c>
       <c r="D147" t="n">
-        <v>327.3640180499997</v>
+        <v>323.6199418005998</v>
       </c>
       <c r="E147" t="n">
-        <v>331.2165222167969</v>
+        <v>334.5862426757812</v>
       </c>
       <c r="F147" t="n">
-        <v>4610600</v>
+        <v>3002000</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B148" t="n">
-        <v>326.388616523007</v>
+        <v>336.0248127567512</v>
       </c>
       <c r="C148" t="n">
-        <v>335.5617045306175</v>
+        <v>336.2120210994593</v>
       </c>
       <c r="D148" t="n">
-        <v>323.6199418005998</v>
+        <v>330.8717121868362</v>
       </c>
       <c r="E148" t="n">
-        <v>334.5862426757812</v>
+        <v>332.3792114257812</v>
       </c>
       <c r="F148" t="n">
-        <v>3002000</v>
+        <v>3208300</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B149" t="n">
-        <v>336.0248127567512</v>
+        <v>330.6056562428727</v>
       </c>
       <c r="C149" t="n">
-        <v>336.2120210994593</v>
+        <v>336.4188865710081</v>
       </c>
       <c r="D149" t="n">
-        <v>330.8717121868362</v>
+        <v>327.0487282012957</v>
       </c>
       <c r="E149" t="n">
-        <v>332.3792114257812</v>
+        <v>336.1430053710938</v>
       </c>
       <c r="F149" t="n">
-        <v>3208300</v>
+        <v>3741200</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B150" t="n">
-        <v>330.6056862577288</v>
+        <v>335.9853517224209</v>
       </c>
       <c r="C150" t="n">
-        <v>336.4189171136328</v>
+        <v>337.7194792888092</v>
       </c>
       <c r="D150" t="n">
-        <v>327.0487578932272</v>
+        <v>333.3644653118732</v>
       </c>
       <c r="E150" t="n">
-        <v>336.1430358886719</v>
+        <v>337.6701965332031</v>
       </c>
       <c r="F150" t="n">
-        <v>3741200</v>
+        <v>2882500</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B151" t="n">
-        <v>335.9853517224209</v>
+        <v>336.8228540004552</v>
       </c>
       <c r="C151" t="n">
-        <v>337.7194792888092</v>
+        <v>337.2366607575258</v>
       </c>
       <c r="D151" t="n">
-        <v>333.3644653118732</v>
+        <v>331.6697541162465</v>
       </c>
       <c r="E151" t="n">
-        <v>337.6701965332031</v>
+        <v>333.9260864257812</v>
       </c>
       <c r="F151" t="n">
-        <v>2882500</v>
+        <v>3365200</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B152" t="n">
-        <v>336.8228847827696</v>
+        <v>334.9902184465357</v>
       </c>
       <c r="C152" t="n">
-        <v>337.236691577658</v>
+        <v>336.9509746615948</v>
       </c>
       <c r="D152" t="n">
-        <v>331.6697844276179</v>
+        <v>331.7387590995254</v>
       </c>
       <c r="E152" t="n">
-        <v>333.9261169433594</v>
+        <v>332.1919860839844</v>
       </c>
       <c r="F152" t="n">
-        <v>3365200</v>
+        <v>2856700</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B153" t="n">
-        <v>334.9902184465357</v>
+        <v>337.7983122720913</v>
       </c>
       <c r="C153" t="n">
-        <v>336.9509746615948</v>
+        <v>346.8433072133841</v>
       </c>
       <c r="D153" t="n">
-        <v>331.7387590995254</v>
+        <v>337.7983122720913</v>
       </c>
       <c r="E153" t="n">
-        <v>332.1919860839844</v>
+        <v>344.2618408203125</v>
       </c>
       <c r="F153" t="n">
-        <v>2856700</v>
+        <v>4930400</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B154" t="n">
-        <v>337.7982823274818</v>
+        <v>343.2174366312315</v>
       </c>
       <c r="C154" t="n">
-        <v>346.8432764669682</v>
+        <v>346.0058365319325</v>
       </c>
       <c r="D154" t="n">
-        <v>337.7982823274818</v>
+        <v>338.5668460102951</v>
       </c>
       <c r="E154" t="n">
-        <v>344.2618103027344</v>
+        <v>345.8284606933594</v>
       </c>
       <c r="F154" t="n">
-        <v>4930400</v>
+        <v>3260900</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B155" t="n">
-        <v>343.2174366312315</v>
+        <v>347.7399078982703</v>
       </c>
       <c r="C155" t="n">
-        <v>346.0058365319325</v>
+        <v>348.350785549426</v>
       </c>
       <c r="D155" t="n">
-        <v>338.5668460102951</v>
+        <v>337.9263851511736</v>
       </c>
       <c r="E155" t="n">
-        <v>345.8284606933594</v>
+        <v>338.8624267578125</v>
       </c>
       <c r="F155" t="n">
-        <v>3260900</v>
+        <v>3081000</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B156" t="n">
-        <v>347.7399078982703</v>
+        <v>338.8919874460811</v>
       </c>
       <c r="C156" t="n">
-        <v>348.350785549426</v>
+        <v>340.1629954470494</v>
       </c>
       <c r="D156" t="n">
-        <v>337.9263851511736</v>
+        <v>332.950664003466</v>
       </c>
       <c r="E156" t="n">
-        <v>338.8624267578125</v>
+        <v>334.5074157714844</v>
       </c>
       <c r="F156" t="n">
-        <v>3081000</v>
+        <v>2855800</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B157" t="n">
-        <v>338.8920183636698</v>
+        <v>334.5074474516935</v>
       </c>
       <c r="C157" t="n">
-        <v>340.163026480594</v>
+        <v>335.81787576814</v>
       </c>
       <c r="D157" t="n">
-        <v>332.9506943790196</v>
+        <v>331.9259809451064</v>
       </c>
       <c r="E157" t="n">
-        <v>334.5074462890625</v>
+        <v>335.1577453613281</v>
       </c>
       <c r="F157" t="n">
-        <v>2855800</v>
+        <v>2712400</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B158" t="n">
-        <v>334.5074474516935</v>
+        <v>332.9112571246521</v>
       </c>
       <c r="C158" t="n">
-        <v>335.81787576814</v>
+        <v>335.2660949665313</v>
       </c>
       <c r="D158" t="n">
-        <v>331.9259809451064</v>
+        <v>329.758303202367</v>
       </c>
       <c r="E158" t="n">
-        <v>335.1577453613281</v>
+        <v>330.9505310058594</v>
       </c>
       <c r="F158" t="n">
-        <v>2712400</v>
+        <v>3255900</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B159" t="n">
-        <v>332.9112571246521</v>
+        <v>329.5612640898174</v>
       </c>
       <c r="C159" t="n">
-        <v>335.2660949665313</v>
+        <v>332.4186116830558</v>
       </c>
       <c r="D159" t="n">
-        <v>329.758303202367</v>
+        <v>327.2556789255299</v>
       </c>
       <c r="E159" t="n">
-        <v>330.9505310058594</v>
+        <v>327.4132995605469</v>
       </c>
       <c r="F159" t="n">
-        <v>3255900</v>
+        <v>3282900</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B160" t="n">
-        <v>329.5612640898174</v>
+        <v>329.5316980954363</v>
       </c>
       <c r="C160" t="n">
-        <v>332.4186116830558</v>
+        <v>330.9899144482985</v>
       </c>
       <c r="D160" t="n">
-        <v>327.2556789255299</v>
+        <v>322.5459348903251</v>
       </c>
       <c r="E160" t="n">
-        <v>327.4132995605469</v>
+        <v>324.220947265625</v>
       </c>
       <c r="F160" t="n">
-        <v>3282900</v>
+        <v>4279300</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B161" t="n">
-        <v>329.5316980954363</v>
+        <v>320.8709611177203</v>
       </c>
       <c r="C161" t="n">
-        <v>330.9899144482985</v>
+        <v>321.0483068839262</v>
       </c>
       <c r="D161" t="n">
-        <v>322.5459348903251</v>
+        <v>314.3581498388285</v>
       </c>
       <c r="E161" t="n">
-        <v>324.220947265625</v>
+        <v>318.0628662109375</v>
       </c>
       <c r="F161" t="n">
-        <v>4279300</v>
+        <v>4150000</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B162" t="n">
-        <v>320.8709611177203</v>
+        <v>317.5012539357068</v>
       </c>
       <c r="C162" t="n">
-        <v>321.0483068839262</v>
+        <v>325.2653785233867</v>
       </c>
       <c r="D162" t="n">
-        <v>314.3581498388285</v>
+        <v>317.5012539357068</v>
       </c>
       <c r="E162" t="n">
-        <v>318.0628662109375</v>
+        <v>323.9647827148438</v>
       </c>
       <c r="F162" t="n">
-        <v>4150000</v>
+        <v>4317900</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B163" t="n">
-        <v>317.501224026995</v>
+        <v>325.245658285994</v>
       </c>
       <c r="C163" t="n">
-        <v>325.2653478832921</v>
+        <v>325.6594650583568</v>
       </c>
       <c r="D163" t="n">
-        <v>317.501224026995</v>
+        <v>318.6047541787617</v>
       </c>
       <c r="E163" t="n">
-        <v>323.9647521972656</v>
+        <v>319.1171264648438</v>
       </c>
       <c r="F163" t="n">
-        <v>4317900</v>
+        <v>3865300</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B164" t="n">
-        <v>325.245658285994</v>
+        <v>317.3435693878982</v>
       </c>
       <c r="C164" t="n">
-        <v>325.6594650583568</v>
+        <v>317.3435693878982</v>
       </c>
       <c r="D164" t="n">
-        <v>318.6047541787617</v>
+        <v>307.6680023826615</v>
       </c>
       <c r="E164" t="n">
-        <v>319.1171264648438</v>
+        <v>307.8256530761719</v>
       </c>
       <c r="F164" t="n">
-        <v>3865300</v>
+        <v>6396100</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B165" t="n">
-        <v>317.3436008490747</v>
+        <v>308.8011039225745</v>
       </c>
       <c r="C165" t="n">
-        <v>317.3436008490747</v>
+        <v>312.959047256485</v>
       </c>
       <c r="D165" t="n">
-        <v>307.6680328846103</v>
+        <v>305.8353583254913</v>
       </c>
       <c r="E165" t="n">
-        <v>307.82568359375</v>
+        <v>310.7815551757812</v>
       </c>
       <c r="F165" t="n">
-        <v>6396100</v>
+        <v>6391400</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B166" t="n">
-        <v>308.8011039225745</v>
+        <v>317.2253492112466</v>
       </c>
       <c r="C166" t="n">
-        <v>312.959047256485</v>
+        <v>320.4571133614208</v>
       </c>
       <c r="D166" t="n">
-        <v>305.8353583254913</v>
+        <v>314.6537454823368</v>
       </c>
       <c r="E166" t="n">
-        <v>310.7815551757812</v>
+        <v>318.29931640625</v>
       </c>
       <c r="F166" t="n">
-        <v>6391400</v>
+        <v>5455900</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B167" t="n">
-        <v>317.225379625856</v>
+        <v>320.2304978152761</v>
       </c>
       <c r="C167" t="n">
-        <v>320.457144085882</v>
+        <v>322.6740083417755</v>
       </c>
       <c r="D167" t="n">
-        <v>314.6537756503886</v>
+        <v>317.6884217799922</v>
       </c>
       <c r="E167" t="n">
-        <v>318.2993469238281</v>
+        <v>317.8953552246094</v>
       </c>
       <c r="F167" t="n">
-        <v>5455900</v>
+        <v>4411700</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B168" t="n">
-        <v>320.2305285570251</v>
+        <v>317.9347470211017</v>
       </c>
       <c r="C168" t="n">
-        <v>322.6740393180987</v>
+        <v>319.2353426707153</v>
       </c>
       <c r="D168" t="n">
-        <v>317.688452277705</v>
+        <v>312.1412119171815</v>
       </c>
       <c r="E168" t="n">
-        <v>317.8953857421875</v>
+        <v>312.7816772460938</v>
       </c>
       <c r="F168" t="n">
-        <v>4411700</v>
+        <v>4995500</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B169" t="n">
-        <v>317.9347780414561</v>
+        <v>311.8456552875821</v>
       </c>
       <c r="C169" t="n">
-        <v>319.2353738179666</v>
+        <v>312.4565329608662</v>
       </c>
       <c r="D169" t="n">
-        <v>312.1412423722705</v>
+        <v>305.1554983709962</v>
       </c>
       <c r="E169" t="n">
-        <v>312.7817077636719</v>
+        <v>306.8206481933594</v>
       </c>
       <c r="F169" t="n">
-        <v>4995500</v>
+        <v>4335700</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B170" t="n">
-        <v>311.8456552875821</v>
+        <v>308.6237547613812</v>
       </c>
       <c r="C170" t="n">
-        <v>312.4565329608662</v>
+        <v>310.150948950067</v>
       </c>
       <c r="D170" t="n">
-        <v>305.1554983709962</v>
+        <v>304.5643168514869</v>
       </c>
       <c r="E170" t="n">
-        <v>306.8206481933594</v>
+        <v>305.8944702148438</v>
       </c>
       <c r="F170" t="n">
-        <v>4335700</v>
+        <v>4225700</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B171" t="n">
-        <v>308.6237547613812</v>
+        <v>303.0863866663159</v>
       </c>
       <c r="C171" t="n">
-        <v>310.150948950067</v>
+        <v>303.1652270544281</v>
       </c>
       <c r="D171" t="n">
-        <v>304.5643168514869</v>
+        <v>294.8690352302997</v>
       </c>
       <c r="E171" t="n">
-        <v>305.8944702148438</v>
+        <v>298.1007995605469</v>
       </c>
       <c r="F171" t="n">
-        <v>4225700</v>
+        <v>6307800</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B172" t="n">
-        <v>303.0863866663159</v>
+        <v>300.5739097413743</v>
       </c>
       <c r="C172" t="n">
-        <v>303.1652270544281</v>
+        <v>301.4803938271338</v>
       </c>
       <c r="D172" t="n">
-        <v>294.8690352302997</v>
+        <v>296.9874537315239</v>
       </c>
       <c r="E172" t="n">
-        <v>298.1007995605469</v>
+        <v>299.8743591308594</v>
       </c>
       <c r="F172" t="n">
-        <v>6307800</v>
+        <v>5072600</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B173" t="n">
-        <v>300.5738791526044</v>
+        <v>295.8937302385283</v>
       </c>
       <c r="C173" t="n">
-        <v>301.4803631461129</v>
+        <v>298.4751965058313</v>
       </c>
       <c r="D173" t="n">
-        <v>296.9874235077401</v>
+        <v>292.5141779899232</v>
       </c>
       <c r="E173" t="n">
-        <v>299.8743286132812</v>
+        <v>293.1349182128906</v>
       </c>
       <c r="F173" t="n">
-        <v>5072600</v>
+        <v>6121500</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B174" t="n">
-        <v>295.8937302385283</v>
+        <v>294.8493301065311</v>
       </c>
       <c r="C174" t="n">
-        <v>298.4751965058313</v>
+        <v>299.3127122467453</v>
       </c>
       <c r="D174" t="n">
-        <v>292.5141779899232</v>
+        <v>292.9279941234309</v>
       </c>
       <c r="E174" t="n">
-        <v>293.1349182128906</v>
+        <v>295.4010925292969</v>
       </c>
       <c r="F174" t="n">
-        <v>6121500</v>
+        <v>6366100</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B175" t="n">
-        <v>294.8493301065311</v>
+        <v>287.5778334831647</v>
       </c>
       <c r="C175" t="n">
-        <v>299.3127122467453</v>
+        <v>298.7313718247998</v>
       </c>
       <c r="D175" t="n">
-        <v>292.9279941234309</v>
+        <v>284.84857918279</v>
       </c>
       <c r="E175" t="n">
-        <v>295.4010925292969</v>
+        <v>297.9924011230469</v>
       </c>
       <c r="F175" t="n">
-        <v>6366100</v>
+        <v>8692500</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B176" t="n">
-        <v>287.5778334831647</v>
+        <v>296.6327042526405</v>
       </c>
       <c r="C176" t="n">
-        <v>298.7313718247998</v>
+        <v>306.4363947204983</v>
       </c>
       <c r="D176" t="n">
-        <v>284.84857918279</v>
+        <v>292.307277842878</v>
       </c>
       <c r="E176" t="n">
-        <v>297.9924011230469</v>
+        <v>306.0126953125</v>
       </c>
       <c r="F176" t="n">
-        <v>8692500</v>
+        <v>5810900</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B177" t="n">
-        <v>296.6327042526405</v>
+        <v>301.8547523557064</v>
       </c>
       <c r="C177" t="n">
-        <v>306.4363947204983</v>
+        <v>309.3725528012548</v>
       </c>
       <c r="D177" t="n">
-        <v>292.307277842878</v>
+        <v>299.9038888531578</v>
       </c>
       <c r="E177" t="n">
-        <v>306.0126953125</v>
+        <v>309.1656494140625</v>
       </c>
       <c r="F177" t="n">
-        <v>5810900</v>
+        <v>4516600</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B178" t="n">
-        <v>301.8547523557064</v>
+        <v>309.8750586089163</v>
       </c>
       <c r="C178" t="n">
-        <v>309.3725528012548</v>
+        <v>310.3282855694948</v>
       </c>
       <c r="D178" t="n">
-        <v>299.9038888531578</v>
+        <v>306.8797555054846</v>
       </c>
       <c r="E178" t="n">
-        <v>309.1656494140625</v>
+        <v>308.4660949707031</v>
       </c>
       <c r="F178" t="n">
-        <v>4516600</v>
+        <v>2963800</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B179" t="n">
-        <v>309.8750586089163</v>
+        <v>310.4268474452446</v>
       </c>
       <c r="C179" t="n">
-        <v>310.3282855694948</v>
+        <v>312.1314175610734</v>
       </c>
       <c r="D179" t="n">
-        <v>306.8797555054846</v>
+        <v>304.4165456653147</v>
       </c>
       <c r="E179" t="n">
-        <v>308.4660949707031</v>
+        <v>305.9733276367188</v>
       </c>
       <c r="F179" t="n">
-        <v>2963800</v>
+        <v>6978200</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B180" t="n">
-        <v>310.4268164834753</v>
+        <v>310.1213630819786</v>
       </c>
       <c r="C180" t="n">
-        <v>312.1313864292915</v>
+        <v>316.2794521026693</v>
       </c>
       <c r="D180" t="n">
-        <v>304.416515303009</v>
+        <v>309.8849020855982</v>
       </c>
       <c r="E180" t="n">
-        <v>305.9732971191406</v>
+        <v>313.17578125</v>
       </c>
       <c r="F180" t="n">
-        <v>6978200</v>
+        <v>5990100</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B181" t="n">
-        <v>310.1213933019174</v>
+        <v>312.7817028577755</v>
       </c>
       <c r="C181" t="n">
-        <v>316.2794829226862</v>
+        <v>317.1465496037087</v>
       </c>
       <c r="D181" t="n">
-        <v>309.8849322824949</v>
+        <v>310.5253703811763</v>
       </c>
       <c r="E181" t="n">
-        <v>313.1758117675781</v>
+        <v>316.4863891601562</v>
       </c>
       <c r="F181" t="n">
-        <v>5990100</v>
+        <v>6818900</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B182" t="n">
-        <v>312.7816726974261</v>
+        <v>315.7671367684214</v>
       </c>
       <c r="C182" t="n">
-        <v>317.1465190224739</v>
+        <v>317.3633087672889</v>
       </c>
       <c r="D182" t="n">
-        <v>310.5253404383965</v>
+        <v>312.3383016854047</v>
       </c>
       <c r="E182" t="n">
-        <v>316.4863586425781</v>
+        <v>312.4762573242188</v>
       </c>
       <c r="F182" t="n">
-        <v>6818900</v>
+        <v>6963300</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B183" t="n">
-        <v>315.7671367684214</v>
+        <v>310.4958029229232</v>
       </c>
       <c r="C183" t="n">
-        <v>317.3633087672889</v>
+        <v>311.2446362258477</v>
       </c>
       <c r="D183" t="n">
-        <v>312.3383016854047</v>
+        <v>303.1652107990409</v>
       </c>
       <c r="E183" t="n">
-        <v>312.4762573242188</v>
+        <v>306.12109375</v>
       </c>
       <c r="F183" t="n">
-        <v>6963300</v>
+        <v>4544200</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B184" t="n">
-        <v>310.4958029229232</v>
+        <v>305.4215416998635</v>
       </c>
       <c r="C184" t="n">
-        <v>311.2446362258477</v>
+        <v>307.6088962755514</v>
       </c>
       <c r="D184" t="n">
-        <v>303.1652107990409</v>
+        <v>304.0322731114999</v>
       </c>
       <c r="E184" t="n">
-        <v>306.12109375</v>
+        <v>306.9388732910156</v>
       </c>
       <c r="F184" t="n">
-        <v>4544200</v>
+        <v>4310000</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B185" t="n">
-        <v>305.4215416998635</v>
+        <v>303.4115246580221</v>
       </c>
       <c r="C185" t="n">
-        <v>307.6088962755514</v>
+        <v>308.9094535404009</v>
       </c>
       <c r="D185" t="n">
-        <v>304.0322731114999</v>
+        <v>302.6035761274661</v>
       </c>
       <c r="E185" t="n">
-        <v>306.9388732910156</v>
+        <v>308.3675537109375</v>
       </c>
       <c r="F185" t="n">
-        <v>4310000</v>
+        <v>4328300</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,25 +5253,25 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B186" t="n">
-        <v>303.411554685127</v>
+        <v>315.5049467263879</v>
       </c>
       <c r="C186" t="n">
-        <v>308.9094841116081</v>
+        <v>318.403599213189</v>
       </c>
       <c r="D186" t="n">
-        <v>302.6036060746125</v>
+        <v>305.8560507855353</v>
       </c>
       <c r="E186" t="n">
-        <v>308.3675842285156</v>
+        <v>307.6826171875</v>
       </c>
       <c r="F186" t="n">
-        <v>4328300</v>
+        <v>4558600</v>
       </c>
       <c r="G186" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -5279,25 +5279,25 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B187" t="n">
-        <v>315.5049467263879</v>
+        <v>308.5561528759146</v>
       </c>
       <c r="C187" t="n">
-        <v>318.403599213189</v>
+        <v>311.7525986238699</v>
       </c>
       <c r="D187" t="n">
-        <v>305.8560507855353</v>
+        <v>306.3722648476684</v>
       </c>
       <c r="E187" t="n">
-        <v>307.6826171875</v>
+        <v>308.5065307617188</v>
       </c>
       <c r="F187" t="n">
-        <v>4558600</v>
+        <v>3946300</v>
       </c>
       <c r="G187" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B188" t="n">
-        <v>308.5561528759146</v>
+        <v>306.6204514929628</v>
       </c>
       <c r="C188" t="n">
-        <v>311.7525986238699</v>
+        <v>311.4746638676563</v>
       </c>
       <c r="D188" t="n">
-        <v>306.3722648476684</v>
+        <v>304.8236946299612</v>
       </c>
       <c r="E188" t="n">
-        <v>308.5065307617188</v>
+        <v>307.4443664550781</v>
       </c>
       <c r="F188" t="n">
-        <v>3946300</v>
+        <v>4381800</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B189" t="n">
-        <v>306.6204514929628</v>
+        <v>309.0723663566284</v>
       </c>
       <c r="C189" t="n">
-        <v>311.4746638676563</v>
+        <v>320.5279554969379</v>
       </c>
       <c r="D189" t="n">
-        <v>304.8236946299612</v>
+        <v>308.000249988811</v>
       </c>
       <c r="E189" t="n">
-        <v>307.4443664550781</v>
+        <v>318.9793395996094</v>
       </c>
       <c r="F189" t="n">
-        <v>4381800</v>
+        <v>4875300</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B190" t="n">
-        <v>309.0723663566284</v>
+        <v>320.9051596578416</v>
       </c>
       <c r="C190" t="n">
-        <v>320.5279554969379</v>
+        <v>321.6298303667879</v>
       </c>
       <c r="D190" t="n">
-        <v>308.000249988811</v>
+        <v>316.4678580086006</v>
       </c>
       <c r="E190" t="n">
-        <v>318.9793395996094</v>
+        <v>316.5870056152344</v>
       </c>
       <c r="F190" t="n">
-        <v>4875300</v>
+        <v>4823800</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B191" t="n">
-        <v>320.9051596578416</v>
+        <v>319.9323340788724</v>
       </c>
       <c r="C191" t="n">
-        <v>321.6298303667879</v>
+        <v>324.6376494749074</v>
       </c>
       <c r="D191" t="n">
-        <v>316.4678580086006</v>
+        <v>316.2196730066971</v>
       </c>
       <c r="E191" t="n">
-        <v>316.5870056152344</v>
+        <v>323.6251220703125</v>
       </c>
       <c r="F191" t="n">
-        <v>4823800</v>
+        <v>4656600</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B192" t="n">
-        <v>319.9323340788724</v>
+        <v>326.0969127055492</v>
       </c>
       <c r="C192" t="n">
-        <v>324.6376494749074</v>
+        <v>328.598467157331</v>
       </c>
       <c r="D192" t="n">
-        <v>316.2196730066971</v>
+        <v>322.9104034108394</v>
       </c>
       <c r="E192" t="n">
-        <v>323.6251220703125</v>
+        <v>325.9877319335938</v>
       </c>
       <c r="F192" t="n">
-        <v>4656600</v>
+        <v>3649000</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B193" t="n">
-        <v>326.0969127055492</v>
+        <v>331.3184370072605</v>
       </c>
       <c r="C193" t="n">
-        <v>328.598467157331</v>
+        <v>335.5274102103883</v>
       </c>
       <c r="D193" t="n">
-        <v>322.9104034108394</v>
+        <v>327.1293065910854</v>
       </c>
       <c r="E193" t="n">
-        <v>325.9877319335938</v>
+        <v>327.4072570800781</v>
       </c>
       <c r="F193" t="n">
-        <v>3649000</v>
+        <v>4695000</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B194" t="n">
-        <v>331.3184370072605</v>
+        <v>329.4819549089526</v>
       </c>
       <c r="C194" t="n">
-        <v>335.5274102103883</v>
+        <v>335.7954145326594</v>
       </c>
       <c r="D194" t="n">
-        <v>327.1293065910854</v>
+        <v>327.337752500619</v>
       </c>
       <c r="E194" t="n">
-        <v>327.4072570800781</v>
+        <v>334.6240539550781</v>
       </c>
       <c r="F194" t="n">
-        <v>4695000</v>
+        <v>5131500</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B195" t="n">
-        <v>329.4819549089526</v>
+        <v>333.5519799826949</v>
       </c>
       <c r="C195" t="n">
-        <v>335.7954145326594</v>
+        <v>338.6543633465824</v>
       </c>
       <c r="D195" t="n">
-        <v>327.337752500619</v>
+        <v>323.7839666314997</v>
       </c>
       <c r="E195" t="n">
-        <v>334.6240539550781</v>
+        <v>325.0843811035156</v>
       </c>
       <c r="F195" t="n">
-        <v>5131500</v>
+        <v>6085400</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B196" t="n">
-        <v>333.5519799826949</v>
+        <v>329.2735121638814</v>
       </c>
       <c r="C196" t="n">
-        <v>338.6543633465824</v>
+        <v>335.5472561594589</v>
       </c>
       <c r="D196" t="n">
-        <v>323.7839666314997</v>
+        <v>328.4793462633244</v>
       </c>
       <c r="E196" t="n">
-        <v>325.0843811035156</v>
+        <v>331.8346252441406</v>
       </c>
       <c r="F196" t="n">
-        <v>6085400</v>
+        <v>10604400</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B197" t="n">
-        <v>329.2735121638814</v>
+        <v>327.585930781475</v>
       </c>
       <c r="C197" t="n">
-        <v>335.5472561594589</v>
+        <v>329.30328611244</v>
       </c>
       <c r="D197" t="n">
-        <v>328.4793462633244</v>
+        <v>323.9527013683971</v>
       </c>
       <c r="E197" t="n">
-        <v>331.8346252441406</v>
+        <v>324.2306518554688</v>
       </c>
       <c r="F197" t="n">
-        <v>10604400</v>
+        <v>4713600</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B198" t="n">
-        <v>327.585930781475</v>
+        <v>321.5007640397083</v>
       </c>
       <c r="C198" t="n">
-        <v>329.30328611244</v>
+        <v>326.6130837898613</v>
       </c>
       <c r="D198" t="n">
-        <v>323.9527013683971</v>
+        <v>319.3466553723836</v>
       </c>
       <c r="E198" t="n">
-        <v>324.2306518554688</v>
+        <v>322.0765380859375</v>
       </c>
       <c r="F198" t="n">
-        <v>4713600</v>
+        <v>4788000</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B199" t="n">
-        <v>321.5007640397083</v>
+        <v>326.7123600579221</v>
       </c>
       <c r="C199" t="n">
-        <v>326.6130837898613</v>
+        <v>340.4511116799111</v>
       </c>
       <c r="D199" t="n">
-        <v>319.3466553723836</v>
+        <v>325.3126710965327</v>
       </c>
       <c r="E199" t="n">
-        <v>322.0765380859375</v>
+        <v>340.3518371582031</v>
       </c>
       <c r="F199" t="n">
-        <v>4788000</v>
+        <v>6385000</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B200" t="n">
-        <v>326.7123600579221</v>
+        <v>339.7463135650192</v>
       </c>
       <c r="C200" t="n">
-        <v>340.4511116799111</v>
+        <v>346.0895828723475</v>
       </c>
       <c r="D200" t="n">
-        <v>325.3126710965327</v>
+        <v>339.3194664460809</v>
       </c>
       <c r="E200" t="n">
-        <v>340.3518371582031</v>
+        <v>342.4761962890625</v>
       </c>
       <c r="F200" t="n">
-        <v>6385000</v>
+        <v>6974100</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B201" t="n">
-        <v>339.7463135650192</v>
+        <v>345.3549840981078</v>
       </c>
       <c r="C201" t="n">
-        <v>346.0895828723475</v>
+        <v>347.9359702501276</v>
       </c>
       <c r="D201" t="n">
-        <v>339.3194664460809</v>
+        <v>343.3199926808538</v>
       </c>
       <c r="E201" t="n">
-        <v>342.4761962890625</v>
+        <v>346.3079528808594</v>
       </c>
       <c r="F201" t="n">
-        <v>6974100</v>
+        <v>7771700</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B202" t="n">
-        <v>345.3549840981078</v>
+        <v>346.307966117321</v>
       </c>
       <c r="C202" t="n">
-        <v>347.9359702501276</v>
+        <v>348.779771593463</v>
       </c>
       <c r="D202" t="n">
-        <v>343.3199926808538</v>
+        <v>343.0122759730193</v>
       </c>
       <c r="E202" t="n">
-        <v>346.3079528808594</v>
+        <v>348.2437133789062</v>
       </c>
       <c r="F202" t="n">
-        <v>7771700</v>
+        <v>5786500</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B203" t="n">
-        <v>346.307966117321</v>
+        <v>348.1245733949154</v>
       </c>
       <c r="C203" t="n">
-        <v>348.779771593463</v>
+        <v>350.9140147662578</v>
       </c>
       <c r="D203" t="n">
-        <v>343.0122759730193</v>
+        <v>344.7593579765289</v>
       </c>
       <c r="E203" t="n">
-        <v>348.2437133789062</v>
+        <v>350.1000061035156</v>
       </c>
       <c r="F203" t="n">
-        <v>5786500</v>
+        <v>4579000</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B204" t="n">
-        <v>348.1245733949154</v>
+        <v>351.3905430525372</v>
       </c>
       <c r="C204" t="n">
-        <v>350.9140147662578</v>
+        <v>354.507557275585</v>
       </c>
       <c r="D204" t="n">
-        <v>344.7593579765289</v>
+        <v>348.2734985351562</v>
       </c>
       <c r="E204" t="n">
-        <v>350.1000061035156</v>
+        <v>348.2734985351562</v>
       </c>
       <c r="F204" t="n">
-        <v>4579000</v>
+        <v>4041300</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B205" t="n">
-        <v>351.3905430525372</v>
+        <v>350.2588479333682</v>
       </c>
       <c r="C205" t="n">
-        <v>354.507557275585</v>
+        <v>355.5697168646199</v>
       </c>
       <c r="D205" t="n">
-        <v>348.2734985351562</v>
+        <v>345.1068121812833</v>
       </c>
       <c r="E205" t="n">
-        <v>348.2734985351562</v>
+        <v>355.2818298339844</v>
       </c>
       <c r="F205" t="n">
-        <v>4041300</v>
+        <v>3110500</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B206" t="n">
-        <v>350.2588479333682</v>
+        <v>355.2024317145021</v>
       </c>
       <c r="C206" t="n">
-        <v>355.5697168646199</v>
+        <v>356.2248957008094</v>
       </c>
       <c r="D206" t="n">
-        <v>345.1068121812833</v>
+        <v>343.2703427329958</v>
       </c>
       <c r="E206" t="n">
-        <v>355.2818298339844</v>
+        <v>348.0848693847656</v>
       </c>
       <c r="F206" t="n">
-        <v>3110500</v>
+        <v>4460800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B207" t="n">
-        <v>355.2024317145021</v>
+        <v>352.4626117928308</v>
       </c>
       <c r="C207" t="n">
-        <v>356.2248957008094</v>
+        <v>352.8199940223038</v>
       </c>
       <c r="D207" t="n">
-        <v>343.2703427329958</v>
+        <v>341.9600214541982</v>
       </c>
       <c r="E207" t="n">
-        <v>348.0848693847656</v>
+        <v>342.6846618652344</v>
       </c>
       <c r="F207" t="n">
-        <v>4460800</v>
+        <v>3592800</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B208" t="n">
-        <v>352.4626117928308</v>
+        <v>335.5174656966423</v>
       </c>
       <c r="C208" t="n">
-        <v>352.8199940223038</v>
+        <v>335.5174656966423</v>
       </c>
       <c r="D208" t="n">
-        <v>341.9600214541982</v>
+        <v>328.241100746865</v>
       </c>
       <c r="E208" t="n">
-        <v>342.6846618652344</v>
+        <v>333.75048828125</v>
       </c>
       <c r="F208" t="n">
-        <v>3592800</v>
+        <v>4192300</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B209" t="n">
-        <v>335.5174656966423</v>
+        <v>335.2891698936722</v>
       </c>
       <c r="C209" t="n">
-        <v>335.5174656966423</v>
+        <v>338.2374444527704</v>
       </c>
       <c r="D209" t="n">
-        <v>328.241100746865</v>
+        <v>333.1548737064404</v>
       </c>
       <c r="E209" t="n">
-        <v>333.75048828125</v>
+        <v>336.2520751953125</v>
       </c>
       <c r="F209" t="n">
-        <v>4192300</v>
+        <v>2780800</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B210" t="n">
-        <v>335.2891698936722</v>
+        <v>337.0660677396515</v>
       </c>
       <c r="C210" t="n">
-        <v>338.2374444527704</v>
+        <v>341.8805944502874</v>
       </c>
       <c r="D210" t="n">
-        <v>333.1548737064404</v>
+        <v>335.4281440922459</v>
       </c>
       <c r="E210" t="n">
-        <v>336.2520751953125</v>
+        <v>340.7886352539062</v>
       </c>
       <c r="F210" t="n">
-        <v>2780800</v>
+        <v>2748000</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B211" t="n">
-        <v>337.0660677396515</v>
+        <v>341.4835329455154</v>
       </c>
       <c r="C211" t="n">
-        <v>341.8805944502874</v>
+        <v>342.5853984087983</v>
       </c>
       <c r="D211" t="n">
-        <v>335.4281440922459</v>
+        <v>332.9762178919015</v>
       </c>
       <c r="E211" t="n">
-        <v>340.7886352539062</v>
+        <v>334.6439208984375</v>
       </c>
       <c r="F211" t="n">
-        <v>2748000</v>
+        <v>3650400</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B212" t="n">
-        <v>341.4835329455154</v>
+        <v>337.0362951640151</v>
       </c>
       <c r="C212" t="n">
-        <v>342.5853984087983</v>
+        <v>339.2499929294707</v>
       </c>
       <c r="D212" t="n">
-        <v>332.9762178919015</v>
+        <v>334.1078935040618</v>
       </c>
       <c r="E212" t="n">
-        <v>334.6439208984375</v>
+        <v>335.2693176269531</v>
       </c>
       <c r="F212" t="n">
-        <v>3650400</v>
+        <v>2807300</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B213" t="n">
-        <v>337.0362951640151</v>
+        <v>336.5101711499915</v>
       </c>
       <c r="C213" t="n">
-        <v>339.2499929294707</v>
+        <v>343.7170716460562</v>
       </c>
       <c r="D213" t="n">
-        <v>334.1078935040618</v>
+        <v>334.7928460359882</v>
       </c>
       <c r="E213" t="n">
-        <v>335.2693176269531</v>
+        <v>338.9422607421875</v>
       </c>
       <c r="F213" t="n">
-        <v>2807300</v>
+        <v>3953100</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B214" t="n">
-        <v>336.5101711499915</v>
+        <v>339.0514198724459</v>
       </c>
       <c r="C214" t="n">
-        <v>343.7170716460562</v>
+        <v>348.2436891486228</v>
       </c>
       <c r="D214" t="n">
-        <v>334.7928460359882</v>
+        <v>338.148103527179</v>
       </c>
       <c r="E214" t="n">
-        <v>338.9422607421875</v>
+        <v>345.4740905761719</v>
       </c>
       <c r="F214" t="n">
-        <v>3953100</v>
+        <v>3810300</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B215" t="n">
-        <v>339.0514198724459</v>
+        <v>346.3774576909258</v>
       </c>
       <c r="C215" t="n">
-        <v>348.2436891486228</v>
+        <v>351.3905334952897</v>
       </c>
       <c r="D215" t="n">
-        <v>338.148103527179</v>
+        <v>335.6167594084301</v>
       </c>
       <c r="E215" t="n">
-        <v>345.4740905761719</v>
+        <v>336.3910522460938</v>
       </c>
       <c r="F215" t="n">
-        <v>3810300</v>
+        <v>4434000</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B216" t="n">
-        <v>346.3774576909258</v>
+        <v>337.4829959680537</v>
       </c>
       <c r="C216" t="n">
-        <v>351.3905334952897</v>
+        <v>337.7113243396537</v>
       </c>
       <c r="D216" t="n">
-        <v>335.6167594084301</v>
+        <v>328.985617931225</v>
       </c>
       <c r="E216" t="n">
-        <v>336.3910522460938</v>
+        <v>330.6036987304688</v>
       </c>
       <c r="F216" t="n">
-        <v>4434000</v>
+        <v>4125300</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B217" t="n">
-        <v>337.4829959680537</v>
+        <v>328.8764012920007</v>
       </c>
       <c r="C217" t="n">
-        <v>337.7113243396537</v>
+        <v>330.5639772575944</v>
       </c>
       <c r="D217" t="n">
-        <v>328.985617931225</v>
+        <v>324.6078695592594</v>
       </c>
       <c r="E217" t="n">
-        <v>330.6036987304688</v>
+        <v>329.1742248535156</v>
       </c>
       <c r="F217" t="n">
-        <v>4125300</v>
+        <v>3112600</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B218" t="n">
-        <v>328.8764012920007</v>
+        <v>331.0901002710247</v>
       </c>
       <c r="C218" t="n">
-        <v>330.5639772575944</v>
+        <v>334.097933459434</v>
       </c>
       <c r="D218" t="n">
-        <v>324.6078695592594</v>
+        <v>328.2907223705125</v>
       </c>
       <c r="E218" t="n">
-        <v>329.1742248535156</v>
+        <v>329.0253295898438</v>
       </c>
       <c r="F218" t="n">
-        <v>3112600</v>
+        <v>2907700</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B219" t="n">
-        <v>331.0901002710247</v>
+        <v>322.9203055541834</v>
       </c>
       <c r="C219" t="n">
-        <v>334.097933459434</v>
+        <v>325.8288946116248</v>
       </c>
       <c r="D219" t="n">
-        <v>328.2907223705125</v>
+        <v>320.6867650845805</v>
       </c>
       <c r="E219" t="n">
-        <v>329.0253295898438</v>
+        <v>322.3346252441406</v>
       </c>
       <c r="F219" t="n">
-        <v>2907700</v>
+        <v>4523100</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B220" t="n">
-        <v>322.9203055541834</v>
+        <v>322.6920194034342</v>
       </c>
       <c r="C220" t="n">
-        <v>325.8288946116248</v>
+        <v>331.0206281983068</v>
       </c>
       <c r="D220" t="n">
-        <v>320.6867650845805</v>
+        <v>320.8654832094117</v>
       </c>
       <c r="E220" t="n">
-        <v>322.3346252441406</v>
+        <v>330.5441589355469</v>
       </c>
       <c r="F220" t="n">
-        <v>4523100</v>
+        <v>3874500</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B221" t="n">
-        <v>322.6920194034342</v>
+        <v>336.9072556737336</v>
       </c>
       <c r="C221" t="n">
-        <v>331.0206281983068</v>
+        <v>339.3889672822994</v>
       </c>
       <c r="D221" t="n">
-        <v>320.8654832094117</v>
+        <v>332.8968012318786</v>
       </c>
       <c r="E221" t="n">
-        <v>330.5441589355469</v>
+        <v>333.6313781738281</v>
       </c>
       <c r="F221" t="n">
-        <v>3874500</v>
+        <v>3622400</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B222" t="n">
-        <v>336.9072556737336</v>
+        <v>340.133473711892</v>
       </c>
       <c r="C222" t="n">
-        <v>339.3889672822994</v>
+        <v>346.8737804890717</v>
       </c>
       <c r="D222" t="n">
-        <v>332.8968012318786</v>
+        <v>340.0937578445657</v>
       </c>
       <c r="E222" t="n">
-        <v>333.6313781738281</v>
+        <v>341.9500732421875</v>
       </c>
       <c r="F222" t="n">
-        <v>3622400</v>
+        <v>4308000</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B223" t="n">
-        <v>340.133473711892</v>
+        <v>337.8900211320969</v>
       </c>
       <c r="C223" t="n">
-        <v>346.8737804890717</v>
+        <v>342.7442335347337</v>
       </c>
       <c r="D223" t="n">
-        <v>340.0937578445657</v>
+        <v>334.495026147691</v>
       </c>
       <c r="E223" t="n">
-        <v>341.9500732421875</v>
+        <v>335.7954406738281</v>
       </c>
       <c r="F223" t="n">
-        <v>4308000</v>
+        <v>4028500</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B224" t="n">
-        <v>337.8900211320969</v>
+        <v>332.5394250801792</v>
       </c>
       <c r="C224" t="n">
-        <v>342.7442335347337</v>
+        <v>333.2343164610006</v>
       </c>
       <c r="D224" t="n">
-        <v>334.495026147691</v>
+        <v>327.8341094785939</v>
       </c>
       <c r="E224" t="n">
-        <v>335.7954406738281</v>
+        <v>330.9114379882812</v>
       </c>
       <c r="F224" t="n">
-        <v>4028500</v>
+        <v>6275400</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B225" t="n">
-        <v>332.5394250801792</v>
+        <v>330.0080852280822</v>
       </c>
       <c r="C225" t="n">
-        <v>333.2343164610006</v>
+        <v>331.5566708480175</v>
       </c>
       <c r="D225" t="n">
-        <v>327.8341094785939</v>
+        <v>326.3946985853459</v>
       </c>
       <c r="E225" t="n">
-        <v>330.9114379882812</v>
+        <v>329.5315856933594</v>
       </c>
       <c r="F225" t="n">
-        <v>6275400</v>
+        <v>4961900</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B226" t="n">
-        <v>330.0080852280822</v>
+        <v>337.3142314565633</v>
       </c>
       <c r="C226" t="n">
-        <v>331.5566708480175</v>
+        <v>341.126167165973</v>
       </c>
       <c r="D226" t="n">
-        <v>326.3946985853459</v>
+        <v>331.2787221229386</v>
       </c>
       <c r="E226" t="n">
-        <v>329.5315856933594</v>
+        <v>337.5326232910156</v>
       </c>
       <c r="F226" t="n">
-        <v>4961900</v>
+        <v>2908100</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B227" t="n">
-        <v>337.3142314565633</v>
+        <v>337.741121159039</v>
       </c>
       <c r="C227" t="n">
-        <v>341.126167165973</v>
+        <v>348.2933339094608</v>
       </c>
       <c r="D227" t="n">
-        <v>331.2787221229386</v>
+        <v>336.8675537894677</v>
       </c>
       <c r="E227" t="n">
-        <v>337.5326232910156</v>
+        <v>345.6925048828125</v>
       </c>
       <c r="F227" t="n">
-        <v>2908100</v>
+        <v>4275000</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B228" t="n">
-        <v>337.741121159039</v>
+        <v>347.5984599855233</v>
       </c>
       <c r="C228" t="n">
-        <v>348.2933339094608</v>
+        <v>351.9563298372728</v>
       </c>
       <c r="D228" t="n">
-        <v>336.8675537894677</v>
+        <v>345.6031541488199</v>
       </c>
       <c r="E228" t="n">
-        <v>345.6925048828125</v>
+        <v>350.5566711425781</v>
       </c>
       <c r="F228" t="n">
-        <v>4275000</v>
+        <v>3140400</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B229" t="n">
-        <v>347.5984599855233</v>
+        <v>350.9140306560572</v>
       </c>
       <c r="C229" t="n">
-        <v>351.9563298372728</v>
+        <v>350.9636527717977</v>
       </c>
       <c r="D229" t="n">
-        <v>345.6031541488199</v>
+        <v>344.967859180145</v>
       </c>
       <c r="E229" t="n">
-        <v>350.5566711425781</v>
+        <v>346.963134765625</v>
       </c>
       <c r="F229" t="n">
-        <v>3140400</v>
+        <v>2622400</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B230" t="n">
-        <v>350.9140306560572</v>
+        <v>348.9386046403958</v>
       </c>
       <c r="C230" t="n">
-        <v>350.9636527717977</v>
+        <v>354.219664160909</v>
       </c>
       <c r="D230" t="n">
-        <v>344.967859180145</v>
+        <v>346.1888486641563</v>
       </c>
       <c r="E230" t="n">
-        <v>346.963134765625</v>
+        <v>353.0185241699219</v>
       </c>
       <c r="F230" t="n">
-        <v>2622400</v>
+        <v>3584800</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B231" t="n">
-        <v>348.9386046403958</v>
+        <v>349.524279261052</v>
       </c>
       <c r="C231" t="n">
-        <v>354.219664160909</v>
+        <v>351.4103740800161</v>
       </c>
       <c r="D231" t="n">
-        <v>346.1888486641563</v>
+        <v>344.5211400290252</v>
       </c>
       <c r="E231" t="n">
-        <v>353.0185241699219</v>
+        <v>348.2139282226562</v>
       </c>
       <c r="F231" t="n">
-        <v>3584800</v>
+        <v>3124800</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B232" t="n">
-        <v>349.524279261052</v>
+        <v>349.7128894956296</v>
       </c>
       <c r="C232" t="n">
-        <v>351.4103740800161</v>
+        <v>355.7384623950411</v>
       </c>
       <c r="D232" t="n">
-        <v>344.5211400290252</v>
+        <v>348.0352499864083</v>
       </c>
       <c r="E232" t="n">
-        <v>348.2139282226562</v>
+        <v>351.8868713378906</v>
       </c>
       <c r="F232" t="n">
-        <v>3124800</v>
+        <v>2549700</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B233" t="n">
-        <v>349.7128894956296</v>
+        <v>349.4250091127092</v>
       </c>
       <c r="C233" t="n">
-        <v>355.7384623950411</v>
+        <v>351.2813246265272</v>
       </c>
       <c r="D233" t="n">
-        <v>348.0352499864083</v>
+        <v>340.5206262766717</v>
       </c>
       <c r="E233" t="n">
-        <v>351.8868713378906</v>
+        <v>340.9176940917969</v>
       </c>
       <c r="F233" t="n">
-        <v>2549700</v>
+        <v>3965800</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B234" t="n">
-        <v>349.4250091127092</v>
+        <v>344.4615642861647</v>
       </c>
       <c r="C234" t="n">
-        <v>351.2813246265272</v>
+        <v>345.206077753642</v>
       </c>
       <c r="D234" t="n">
-        <v>340.5206262766717</v>
+        <v>338.0190507751135</v>
       </c>
       <c r="E234" t="n">
-        <v>340.9176940917969</v>
+        <v>339.2003479003906</v>
       </c>
       <c r="F234" t="n">
-        <v>3965800</v>
+        <v>2439900</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B235" t="n">
-        <v>344.4615642861647</v>
+        <v>338.3168506868042</v>
       </c>
       <c r="C235" t="n">
-        <v>345.206077753642</v>
+        <v>338.3168506868042</v>
       </c>
       <c r="D235" t="n">
-        <v>338.0190507751135</v>
+        <v>333.5519765191293</v>
       </c>
       <c r="E235" t="n">
-        <v>339.2003479003906</v>
+        <v>336.381103515625</v>
       </c>
       <c r="F235" t="n">
-        <v>2439900</v>
+        <v>3073100</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B236" t="n">
-        <v>338.3168506868042</v>
+        <v>332.2614710050206</v>
       </c>
       <c r="C236" t="n">
-        <v>338.3168506868042</v>
+        <v>336.9568803095206</v>
       </c>
       <c r="D236" t="n">
-        <v>333.5519765191293</v>
+        <v>330.4548079641576</v>
       </c>
       <c r="E236" t="n">
-        <v>336.381103515625</v>
+        <v>335.4082946777344</v>
       </c>
       <c r="F236" t="n">
-        <v>3073100</v>
+        <v>5580000</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B237" t="n">
-        <v>332.2614710050206</v>
+        <v>334.3163510292147</v>
       </c>
       <c r="C237" t="n">
-        <v>336.9568803095206</v>
+        <v>342.0195939717831</v>
       </c>
       <c r="D237" t="n">
-        <v>330.4548079641576</v>
+        <v>328.2709048600699</v>
       </c>
       <c r="E237" t="n">
-        <v>335.4082946777344</v>
+        <v>335.0211486816406</v>
       </c>
       <c r="F237" t="n">
-        <v>5580000</v>
+        <v>6603400</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B238" t="n">
-        <v>334.3163510292147</v>
+        <v>338.9224047058033</v>
       </c>
       <c r="C238" t="n">
-        <v>342.0195939717831</v>
+        <v>347.8366934263856</v>
       </c>
       <c r="D238" t="n">
-        <v>328.2709048600699</v>
+        <v>338.9224047058033</v>
       </c>
       <c r="E238" t="n">
-        <v>335.0211486816406</v>
+        <v>341.7813110351562</v>
       </c>
       <c r="F238" t="n">
-        <v>6603400</v>
+        <v>4971000</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B239" t="n">
-        <v>338.9224047058033</v>
+        <v>333.542054389882</v>
       </c>
       <c r="C239" t="n">
-        <v>347.8366934263856</v>
+        <v>336.4009911317456</v>
       </c>
       <c r="D239" t="n">
-        <v>338.9224047058033</v>
+        <v>329.1643112906949</v>
       </c>
       <c r="E239" t="n">
-        <v>341.7813110351562</v>
+        <v>332.0430908203125</v>
       </c>
       <c r="F239" t="n">
-        <v>4971000</v>
+        <v>4027700</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B240" t="n">
-        <v>333.542054389882</v>
+        <v>334.0582233645888</v>
       </c>
       <c r="C240" t="n">
-        <v>336.4009911317456</v>
+        <v>336.1031512946537</v>
       </c>
       <c r="D240" t="n">
-        <v>329.1643112906949</v>
+        <v>330.5639843459303</v>
       </c>
       <c r="E240" t="n">
-        <v>332.0430908203125</v>
+        <v>333.1548767089844</v>
       </c>
       <c r="F240" t="n">
-        <v>4027700</v>
+        <v>3422800</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B241" t="n">
-        <v>334.0582233645888</v>
+        <v>333.4229292601251</v>
       </c>
       <c r="C241" t="n">
-        <v>336.1031512946537</v>
+        <v>339.7165463845368</v>
       </c>
       <c r="D241" t="n">
-        <v>330.5639843459303</v>
+        <v>332.7081950914107</v>
       </c>
       <c r="E241" t="n">
-        <v>333.1548767089844</v>
+        <v>334.9615783691406</v>
       </c>
       <c r="F241" t="n">
-        <v>3422800</v>
+        <v>3298600</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B242" t="n">
-        <v>333.4229292601251</v>
+        <v>336.8873851133212</v>
       </c>
       <c r="C242" t="n">
-        <v>339.7165463845368</v>
+        <v>337.0065024243307</v>
       </c>
       <c r="D242" t="n">
-        <v>332.7081950914107</v>
+        <v>331.2588801078031</v>
       </c>
       <c r="E242" t="n">
-        <v>334.9615783691406</v>
+        <v>335.4082946777344</v>
       </c>
       <c r="F242" t="n">
-        <v>3298600</v>
+        <v>2528100</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B243" t="n">
-        <v>336.8873851133212</v>
+        <v>336.9469338983794</v>
       </c>
       <c r="C243" t="n">
-        <v>337.0065024243307</v>
+        <v>336.9568704387829</v>
       </c>
       <c r="D243" t="n">
-        <v>331.2588801078031</v>
+        <v>332.0629425240725</v>
       </c>
       <c r="E243" t="n">
-        <v>335.4082946777344</v>
+        <v>332.4004516601562</v>
       </c>
       <c r="F243" t="n">
-        <v>2528100</v>
+        <v>4258100</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B244" t="n">
-        <v>336.9469338983794</v>
+        <v>328.1517689125653</v>
       </c>
       <c r="C244" t="n">
-        <v>336.9568704387829</v>
+        <v>329.5812372185705</v>
       </c>
       <c r="D244" t="n">
-        <v>332.0629425240725</v>
+        <v>325.4814448058147</v>
       </c>
       <c r="E244" t="n">
-        <v>332.4004516601562</v>
+        <v>326.2060852050781</v>
       </c>
       <c r="F244" t="n">
-        <v>4258100</v>
+        <v>3618000</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B245" t="n">
-        <v>328.1517689125653</v>
+        <v>328.0822659405567</v>
       </c>
       <c r="C245" t="n">
-        <v>329.5812372185705</v>
+        <v>329.1841313242223</v>
       </c>
       <c r="D245" t="n">
-        <v>325.4814448058147</v>
+        <v>325.1042120893565</v>
       </c>
       <c r="E245" t="n">
-        <v>326.2060852050781</v>
+        <v>327.7745361328125</v>
       </c>
       <c r="F245" t="n">
-        <v>3618000</v>
+        <v>3136100</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B246" t="n">
-        <v>328.0822659405567</v>
+        <v>325.838797551875</v>
       </c>
       <c r="C246" t="n">
-        <v>329.1841313242223</v>
+        <v>326.8414187355763</v>
       </c>
       <c r="D246" t="n">
-        <v>325.1042120893565</v>
+        <v>323.3670224847805</v>
       </c>
       <c r="E246" t="n">
-        <v>327.7745361328125</v>
+        <v>325.4317932128906</v>
       </c>
       <c r="F246" t="n">
-        <v>3136100</v>
+        <v>3858700</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B247" t="n">
-        <v>325.838797551875</v>
+        <v>323.6251283531417</v>
       </c>
       <c r="C247" t="n">
-        <v>326.8414187355763</v>
+        <v>324.439106732169</v>
       </c>
       <c r="D247" t="n">
-        <v>323.3670224847805</v>
+        <v>316.4678503051231</v>
       </c>
       <c r="E247" t="n">
-        <v>325.4317932128906</v>
+        <v>317.4307556152344</v>
       </c>
       <c r="F247" t="n">
-        <v>3858700</v>
+        <v>3291000</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B248" t="n">
-        <v>323.6251283531417</v>
+        <v>319.1481100391916</v>
       </c>
       <c r="C248" t="n">
-        <v>324.439106732169</v>
+        <v>319.813222073911</v>
       </c>
       <c r="D248" t="n">
-        <v>316.4678503051231</v>
+        <v>315.3858267914646</v>
       </c>
       <c r="E248" t="n">
-        <v>317.4307556152344</v>
+        <v>316.1799926757812</v>
       </c>
       <c r="F248" t="n">
-        <v>3291000</v>
+        <v>3499300</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,25 +6891,25 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B249" t="n">
-        <v>319.1481100391916</v>
+        <v>318.2099914550781</v>
       </c>
       <c r="C249" t="n">
-        <v>319.813222073911</v>
+        <v>320.4400024414062</v>
       </c>
       <c r="D249" t="n">
-        <v>315.3858267914646</v>
+        <v>315.2099914550781</v>
       </c>
       <c r="E249" t="n">
-        <v>316.1799926757812</v>
+        <v>318.0700073242188</v>
       </c>
       <c r="F249" t="n">
-        <v>3499300</v>
+        <v>3377700</v>
       </c>
       <c r="G249" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -6917,25 +6917,25 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B250" t="n">
-        <v>318.2099914550781</v>
+        <v>316.7000122070312</v>
       </c>
       <c r="C250" t="n">
-        <v>320.4400024414062</v>
+        <v>321.7999877929688</v>
       </c>
       <c r="D250" t="n">
-        <v>315.2099914550781</v>
+        <v>316.1000061035156</v>
       </c>
       <c r="E250" t="n">
-        <v>318.0700073242188</v>
+        <v>321.0499877929688</v>
       </c>
       <c r="F250" t="n">
-        <v>3377700</v>
+        <v>2261000</v>
       </c>
       <c r="G250" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B251" t="n">
-        <v>316.7000122070312</v>
+        <v>320.7300109863281</v>
       </c>
       <c r="C251" t="n">
-        <v>321.7999877929688</v>
+        <v>321.5</v>
       </c>
       <c r="D251" t="n">
-        <v>316.1000061035156</v>
+        <v>313.239990234375</v>
       </c>
       <c r="E251" t="n">
-        <v>321.0499877929688</v>
+        <v>313.7000122070312</v>
       </c>
       <c r="F251" t="n">
-        <v>2261000</v>
+        <v>5655700</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,14 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B252" t="inlineStr"/>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+        <v>46274</v>
+      </c>
+      <c r="B252" t="n">
+        <v>310.4700012207031</v>
+      </c>
+      <c r="C252" t="n">
+        <v>313.3900146484375</v>
+      </c>
+      <c r="D252" t="n">
+        <v>309.8399963378906</v>
+      </c>
+      <c r="E252" t="n">
+        <v>310.4500122070312</v>
+      </c>
       <c r="F252" t="n">
-        <v>5019975</v>
+        <v>3611700</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10586,37 +10594,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>310.45</v>
+      </c>
+      <c r="D2" t="n">
         <v>313.7</v>
       </c>
-      <c r="D2" t="n">
-        <v>321.05</v>
-      </c>
       <c r="E2" t="n">
-        <v>320.73</v>
+        <v>310.47</v>
       </c>
       <c r="F2" t="n">
-        <v>321.5</v>
+        <v>313.385</v>
       </c>
       <c r="G2" t="n">
-        <v>313.24</v>
+        <v>309.84</v>
       </c>
       <c r="H2" t="n">
-        <v>5019975</v>
+        <v>3357754</v>
       </c>
       <c r="I2" t="n">
-        <v>4197667</v>
+        <v>4210254</v>
       </c>
       <c r="J2" t="n">
-        <v>312975228928</v>
+        <v>309732737024</v>
       </c>
       <c r="K2" t="n">
-        <v>21.952415</v>
+        <v>21.740198</v>
       </c>
       <c r="L2" t="n">
-        <v>19.560112</v>
+        <v>19.373098</v>
       </c>
       <c r="M2" t="n">
-        <v>14.29</v>
+        <v>14.28</v>
       </c>
       <c r="N2" t="n">
         <v>426.75</v>
@@ -10628,7 +10636,7 @@
         <v>0.955</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>0.08409999999999999</v>
@@ -10652,7 +10660,7 @@
         <v>16.65</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.840841</v>
+        <v>18.645647</v>
       </c>
       <c r="Z2" t="n">
         <v>0.046</v>
@@ -10664,7 +10672,7 @@
         <v>169176006656</v>
       </c>
       <c r="AC2" t="n">
-        <v>374078242816</v>
+        <v>370835750912</v>
       </c>
       <c r="AD2" t="n">
         <v>24647999488</v>
@@ -10691,7 +10699,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-09 09:15:32</t>
+          <t>2026-09-10 18:59:50</t>
         </is>
       </c>
     </row>

--- a/data/HD_data.xlsx
+++ b/data/HD_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B2" t="n">
-        <v>404.0770428202423</v>
+        <v>404.2520901069122</v>
       </c>
       <c r="C2" t="n">
-        <v>405.9344471617109</v>
+        <v>413.5099090714568</v>
       </c>
       <c r="D2" t="n">
-        <v>400.4011408925683</v>
+        <v>402.8420096446557</v>
       </c>
       <c r="E2" t="n">
-        <v>401.8501281738281</v>
+        <v>411.7594909667969</v>
       </c>
       <c r="F2" t="n">
-        <v>2897800</v>
+        <v>5316400</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B3" t="n">
-        <v>404.2521200680789</v>
+        <v>408.6961917653987</v>
       </c>
       <c r="C3" t="n">
-        <v>413.5099397187673</v>
+        <v>411.846985724472</v>
       </c>
       <c r="D3" t="n">
-        <v>402.8420395013142</v>
+        <v>407.3444863480555</v>
       </c>
       <c r="E3" t="n">
-        <v>411.759521484375</v>
+        <v>411.049560546875</v>
       </c>
       <c r="F3" t="n">
-        <v>5316400</v>
+        <v>5004200</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B4" t="n">
-        <v>408.6962221082555</v>
+        <v>410.8356495901566</v>
       </c>
       <c r="C4" t="n">
-        <v>411.8470163012535</v>
+        <v>411.6427792599144</v>
       </c>
       <c r="D4" t="n">
-        <v>407.3445165905575</v>
+        <v>406.245631927433</v>
       </c>
       <c r="E4" t="n">
-        <v>411.0495910644531</v>
+        <v>411.0690307617188</v>
       </c>
       <c r="F4" t="n">
-        <v>5004200</v>
+        <v>4884700</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B5" t="n">
-        <v>410.8356495901566</v>
+        <v>412.0803987002532</v>
       </c>
       <c r="C5" t="n">
-        <v>411.6427792599144</v>
+        <v>412.8389171851107</v>
       </c>
       <c r="D5" t="n">
-        <v>406.245631927433</v>
+        <v>408.5211874475655</v>
       </c>
       <c r="E5" t="n">
-        <v>411.0690307617188</v>
+        <v>409.84375</v>
       </c>
       <c r="F5" t="n">
-        <v>4884700</v>
+        <v>3726700</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B6" t="n">
-        <v>412.0803987002532</v>
+        <v>412.7514096604531</v>
       </c>
       <c r="C6" t="n">
-        <v>412.8389171851107</v>
+        <v>414.9977925252571</v>
       </c>
       <c r="D6" t="n">
-        <v>408.5211874475655</v>
+        <v>404.3590652530731</v>
       </c>
       <c r="E6" t="n">
-        <v>409.84375</v>
+        <v>405.5162963867188</v>
       </c>
       <c r="F6" t="n">
-        <v>3726700</v>
+        <v>4771700</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B7" t="n">
-        <v>412.7514096604531</v>
+        <v>406.0511124651653</v>
       </c>
       <c r="C7" t="n">
-        <v>414.9977925252571</v>
+        <v>409.7853891317768</v>
       </c>
       <c r="D7" t="n">
-        <v>404.3590652530731</v>
+        <v>404.4076508642465</v>
       </c>
       <c r="E7" t="n">
-        <v>405.5162963867188</v>
+        <v>405.9830627441406</v>
       </c>
       <c r="F7" t="n">
-        <v>4771700</v>
+        <v>3677200</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B8" t="n">
-        <v>406.0511124651653</v>
+        <v>405.8760981858028</v>
       </c>
       <c r="C8" t="n">
-        <v>409.7853891317768</v>
+        <v>407.0527678467049</v>
       </c>
       <c r="D8" t="n">
-        <v>404.4076508642465</v>
+        <v>403.6686220984643</v>
       </c>
       <c r="E8" t="n">
-        <v>405.9830627441406</v>
+        <v>404.2423706054688</v>
       </c>
       <c r="F8" t="n">
-        <v>3677200</v>
+        <v>6718400</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B9" t="n">
-        <v>405.8760981858028</v>
+        <v>402.7058704699236</v>
       </c>
       <c r="C9" t="n">
-        <v>407.0527678467049</v>
+        <v>403.4546845448791</v>
       </c>
       <c r="D9" t="n">
-        <v>403.6686220984643</v>
+        <v>399.8079552515003</v>
       </c>
       <c r="E9" t="n">
-        <v>404.2423706054688</v>
+        <v>400.6539916992188</v>
       </c>
       <c r="F9" t="n">
-        <v>6718400</v>
+        <v>2656300</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B10" t="n">
-        <v>402.7058704699236</v>
+        <v>400.6539425797785</v>
       </c>
       <c r="C10" t="n">
-        <v>403.4546845448791</v>
+        <v>402.3363108379792</v>
       </c>
       <c r="D10" t="n">
-        <v>399.8079552515003</v>
+        <v>396.2389612135919</v>
       </c>
       <c r="E10" t="n">
-        <v>400.6539916992188</v>
+        <v>399.5939636230469</v>
       </c>
       <c r="F10" t="n">
-        <v>2656300</v>
+        <v>2597000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B11" t="n">
-        <v>400.6539731783087</v>
+        <v>395.5874669386123</v>
       </c>
       <c r="C11" t="n">
-        <v>402.3363415649943</v>
+        <v>399.3411526132105</v>
       </c>
       <c r="D11" t="n">
-        <v>396.2389914749436</v>
+        <v>393.856487333743</v>
       </c>
       <c r="E11" t="n">
-        <v>399.593994140625</v>
+        <v>398.4853820800781</v>
       </c>
       <c r="F11" t="n">
-        <v>2597000</v>
+        <v>3220700</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B12" t="n">
-        <v>395.5874669386123</v>
+        <v>395.4513223525085</v>
       </c>
       <c r="C12" t="n">
-        <v>399.3411526132105</v>
+        <v>399.5453755013872</v>
       </c>
       <c r="D12" t="n">
-        <v>393.856487333743</v>
+        <v>394.4399544427085</v>
       </c>
       <c r="E12" t="n">
-        <v>398.4853820800781</v>
+        <v>396.2293090820312</v>
       </c>
       <c r="F12" t="n">
-        <v>3220700</v>
+        <v>2554300</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B13" t="n">
-        <v>395.4512918948509</v>
+        <v>396.9197270195646</v>
       </c>
       <c r="C13" t="n">
-        <v>399.5453447284057</v>
+        <v>400.08022560159</v>
       </c>
       <c r="D13" t="n">
-        <v>394.4399240629465</v>
+        <v>394.6636101400317</v>
       </c>
       <c r="E13" t="n">
-        <v>396.2292785644531</v>
+        <v>398.7965698242188</v>
       </c>
       <c r="F13" t="n">
-        <v>2554300</v>
+        <v>2316600</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B14" t="n">
-        <v>396.9197270195646</v>
+        <v>398.7576665785797</v>
       </c>
       <c r="C14" t="n">
-        <v>400.08022560159</v>
+        <v>399.6329053199512</v>
       </c>
       <c r="D14" t="n">
-        <v>394.6636101400317</v>
+        <v>392.7284254984301</v>
       </c>
       <c r="E14" t="n">
-        <v>398.7965698242188</v>
+        <v>395.59716796875</v>
       </c>
       <c r="F14" t="n">
-        <v>2316600</v>
+        <v>3008400</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B15" t="n">
-        <v>398.7576665785797</v>
+        <v>395.4318710489828</v>
       </c>
       <c r="C15" t="n">
-        <v>399.6329053199512</v>
+        <v>395.7916769160157</v>
       </c>
       <c r="D15" t="n">
-        <v>392.7284254984301</v>
+        <v>392.3686244480866</v>
       </c>
       <c r="E15" t="n">
-        <v>395.59716796875</v>
+        <v>394.0315246582031</v>
       </c>
       <c r="F15" t="n">
-        <v>3008400</v>
+        <v>3211600</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B16" t="n">
-        <v>395.4318404229484</v>
+        <v>393.2535809799684</v>
       </c>
       <c r="C16" t="n">
-        <v>395.7916462621145</v>
+        <v>393.9731927384614</v>
       </c>
       <c r="D16" t="n">
-        <v>392.3685940592994</v>
+        <v>384.4236170674206</v>
       </c>
       <c r="E16" t="n">
-        <v>394.031494140625</v>
+        <v>386.0865173339844</v>
       </c>
       <c r="F16" t="n">
-        <v>3211600</v>
+        <v>3787800</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B17" t="n">
-        <v>393.2535498958814</v>
+        <v>384.6083934501511</v>
       </c>
       <c r="C17" t="n">
-        <v>393.9731615974939</v>
+        <v>386.4366252014962</v>
       </c>
       <c r="D17" t="n">
-        <v>384.4235866812837</v>
+        <v>382.9454931559638</v>
       </c>
       <c r="E17" t="n">
-        <v>386.0864868164062</v>
+        <v>384.1318969726562</v>
       </c>
       <c r="F17" t="n">
-        <v>3787800</v>
+        <v>2964700</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B18" t="n">
-        <v>384.6083628947175</v>
+        <v>383.2761296995442</v>
       </c>
       <c r="C18" t="n">
-        <v>386.4365945008176</v>
+        <v>386.3782832385467</v>
       </c>
       <c r="D18" t="n">
-        <v>382.9454627326402</v>
+        <v>381.8174379292481</v>
       </c>
       <c r="E18" t="n">
-        <v>384.1318664550781</v>
+        <v>384.1805114746094</v>
       </c>
       <c r="F18" t="n">
-        <v>2964700</v>
+        <v>2951300</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B19" t="n">
-        <v>383.2760992538061</v>
+        <v>383.6358825136301</v>
       </c>
       <c r="C19" t="n">
-        <v>386.3782525463874</v>
+        <v>383.6358825136301</v>
       </c>
       <c r="D19" t="n">
-        <v>381.817407599382</v>
+        <v>375.0976757198047</v>
       </c>
       <c r="E19" t="n">
-        <v>384.1804809570312</v>
+        <v>378.6082458496094</v>
       </c>
       <c r="F19" t="n">
-        <v>2951300</v>
+        <v>3653700</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B20" t="n">
-        <v>383.6359134364591</v>
+        <v>378.7250266598306</v>
       </c>
       <c r="C20" t="n">
-        <v>383.6359134364591</v>
+        <v>379.0167531493121</v>
       </c>
       <c r="D20" t="n">
-        <v>375.0977059544146</v>
+        <v>374.8935271531156</v>
       </c>
       <c r="E20" t="n">
-        <v>378.6082763671875</v>
+        <v>376.15771484375</v>
       </c>
       <c r="F20" t="n">
-        <v>3653700</v>
+        <v>2505700</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B21" t="n">
-        <v>378.7250266598306</v>
+        <v>375.8173102434433</v>
       </c>
       <c r="C21" t="n">
-        <v>379.0167531493121</v>
+        <v>375.8173102434433</v>
       </c>
       <c r="D21" t="n">
-        <v>374.8935271531156</v>
+        <v>372.4331645921919</v>
       </c>
       <c r="E21" t="n">
-        <v>376.15771484375</v>
+        <v>373.2208557128906</v>
       </c>
       <c r="F21" t="n">
-        <v>2505700</v>
+        <v>2517600</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B22" t="n">
-        <v>375.8173102434433</v>
+        <v>372.3553321480077</v>
       </c>
       <c r="C22" t="n">
-        <v>375.8173102434433</v>
+        <v>373.7751169791765</v>
       </c>
       <c r="D22" t="n">
-        <v>372.4331645921919</v>
+        <v>367.0651416328743</v>
       </c>
       <c r="E22" t="n">
-        <v>373.2208557128906</v>
+        <v>367.288818359375</v>
       </c>
       <c r="F22" t="n">
-        <v>2517600</v>
+        <v>3321400</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B23" t="n">
-        <v>372.3553630865562</v>
+        <v>369.7880611814068</v>
       </c>
       <c r="C23" t="n">
-        <v>373.7751480356932</v>
+        <v>369.7880611814068</v>
       </c>
       <c r="D23" t="n">
-        <v>367.0651721318674</v>
+        <v>364.4589637589981</v>
       </c>
       <c r="E23" t="n">
-        <v>367.2888488769531</v>
+        <v>365.4022521972656</v>
       </c>
       <c r="F23" t="n">
-        <v>3321400</v>
+        <v>2992400</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B24" t="n">
-        <v>369.7880920652779</v>
+        <v>368.6308809274205</v>
       </c>
       <c r="C24" t="n">
-        <v>369.7880920652779</v>
+        <v>371.7816457761741</v>
       </c>
       <c r="D24" t="n">
-        <v>364.4589941977949</v>
+        <v>366.8026490897424</v>
       </c>
       <c r="E24" t="n">
-        <v>365.4022827148438</v>
+        <v>368.922607421875</v>
       </c>
       <c r="F24" t="n">
-        <v>2992400</v>
+        <v>2925900</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B25" t="n">
-        <v>368.6308504339742</v>
+        <v>368.4363460625955</v>
       </c>
       <c r="C25" t="n">
-        <v>371.7816150220939</v>
+        <v>378.1804256443732</v>
       </c>
       <c r="D25" t="n">
-        <v>366.8026187475289</v>
+        <v>367.6000437301846</v>
       </c>
       <c r="E25" t="n">
-        <v>368.9225769042969</v>
+        <v>377.0426330566406</v>
       </c>
       <c r="F25" t="n">
-        <v>2925900</v>
+        <v>4399900</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B26" t="n">
-        <v>368.4363460625955</v>
+        <v>378.5110397840133</v>
       </c>
       <c r="C26" t="n">
-        <v>378.1804256443732</v>
+        <v>383.5094743418081</v>
       </c>
       <c r="D26" t="n">
-        <v>367.6000437301846</v>
+        <v>376.0798870651823</v>
       </c>
       <c r="E26" t="n">
-        <v>377.0426330566406</v>
+        <v>377.6066284179688</v>
       </c>
       <c r="F26" t="n">
-        <v>4399900</v>
+        <v>3690100</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B27" t="n">
-        <v>378.5110397840133</v>
+        <v>378.9291861622302</v>
       </c>
       <c r="C27" t="n">
-        <v>383.5094743418081</v>
+        <v>379.259819366573</v>
       </c>
       <c r="D27" t="n">
-        <v>376.0798870651823</v>
+        <v>373.3958802696069</v>
       </c>
       <c r="E27" t="n">
-        <v>377.6066284179688</v>
+        <v>376.7217102050781</v>
       </c>
       <c r="F27" t="n">
-        <v>3690100</v>
+        <v>2783700</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B28" t="n">
-        <v>378.9292168586321</v>
+        <v>377.8011514993366</v>
       </c>
       <c r="C28" t="n">
-        <v>379.259850089759</v>
+        <v>382.2841830931986</v>
       </c>
       <c r="D28" t="n">
-        <v>373.3959105177652</v>
+        <v>376.5369638928536</v>
       </c>
       <c r="E28" t="n">
-        <v>376.7217407226562</v>
+        <v>381.1075134277344</v>
       </c>
       <c r="F28" t="n">
-        <v>2783700</v>
+        <v>2657700</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B29" t="n">
-        <v>377.8011514993366</v>
+        <v>380.6310112651639</v>
       </c>
       <c r="C29" t="n">
-        <v>382.2841830931986</v>
+        <v>382.3522567670641</v>
       </c>
       <c r="D29" t="n">
-        <v>376.5369638928536</v>
+        <v>377.4024332180988</v>
       </c>
       <c r="E29" t="n">
-        <v>381.1075134277344</v>
+        <v>378.180419921875</v>
       </c>
       <c r="F29" t="n">
-        <v>2657700</v>
+        <v>2761100</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B30" t="n">
-        <v>380.6310112651639</v>
+        <v>376.8870237514197</v>
       </c>
       <c r="C30" t="n">
-        <v>382.3522567670641</v>
+        <v>382.7898697855445</v>
       </c>
       <c r="D30" t="n">
-        <v>377.4024332180988</v>
+        <v>375.2338280008644</v>
       </c>
       <c r="E30" t="n">
-        <v>378.180419921875</v>
+        <v>380.1350402832031</v>
       </c>
       <c r="F30" t="n">
-        <v>2761100</v>
+        <v>2306900</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B31" t="n">
-        <v>376.8870237514197</v>
+        <v>380.4753887348813</v>
       </c>
       <c r="C31" t="n">
-        <v>382.7898697855445</v>
+        <v>382.2258067674637</v>
       </c>
       <c r="D31" t="n">
-        <v>375.2338280008644</v>
+        <v>377.4802217358246</v>
       </c>
       <c r="E31" t="n">
-        <v>380.1350402832031</v>
+        <v>378.2581787109375</v>
       </c>
       <c r="F31" t="n">
-        <v>2306900</v>
+        <v>2857000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B32" t="n">
-        <v>380.4754194313423</v>
+        <v>376.4688710262192</v>
       </c>
       <c r="C32" t="n">
-        <v>382.225837605147</v>
+        <v>378.0150806165678</v>
       </c>
       <c r="D32" t="n">
-        <v>377.4802521906377</v>
+        <v>370.79940618445</v>
       </c>
       <c r="E32" t="n">
-        <v>378.2582092285156</v>
+        <v>374.4266967773438</v>
       </c>
       <c r="F32" t="n">
-        <v>2857000</v>
+        <v>2767300</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B33" t="n">
-        <v>376.4689017102443</v>
+        <v>378.968132263296</v>
       </c>
       <c r="C33" t="n">
-        <v>378.0151114266164</v>
+        <v>378.968132263296</v>
       </c>
       <c r="D33" t="n">
-        <v>370.7994364063865</v>
+        <v>375.0491149100141</v>
       </c>
       <c r="E33" t="n">
-        <v>374.4267272949219</v>
+        <v>376.0312805175781</v>
       </c>
       <c r="F33" t="n">
-        <v>2767300</v>
+        <v>2426800</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B34" t="n">
-        <v>378.9681015073717</v>
+        <v>377.0231676453325</v>
       </c>
       <c r="C34" t="n">
-        <v>378.9681015073717</v>
+        <v>378.5693771810079</v>
       </c>
       <c r="D34" t="n">
-        <v>375.0490844721456</v>
+        <v>372.3553367162181</v>
       </c>
       <c r="E34" t="n">
-        <v>376.03125</v>
+        <v>374.6600646972656</v>
       </c>
       <c r="F34" t="n">
-        <v>2426800</v>
+        <v>3065800</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B35" t="n">
-        <v>377.0231983553949</v>
+        <v>373.8335318063046</v>
       </c>
       <c r="C35" t="n">
-        <v>378.5694080170153</v>
+        <v>379.2695861239365</v>
       </c>
       <c r="D35" t="n">
-        <v>372.3553670460668</v>
+        <v>372.2872924475712</v>
       </c>
       <c r="E35" t="n">
-        <v>374.6600952148438</v>
+        <v>375.1268920898438</v>
       </c>
       <c r="F35" t="n">
-        <v>3065800</v>
+        <v>2372800</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B36" t="n">
-        <v>373.8335013939448</v>
+        <v>372.4526102885826</v>
       </c>
       <c r="C36" t="n">
-        <v>379.2695552693392</v>
+        <v>374.3975325355203</v>
       </c>
       <c r="D36" t="n">
-        <v>372.2872621610022</v>
+        <v>364.8674253963886</v>
       </c>
       <c r="E36" t="n">
-        <v>375.1268615722656</v>
+        <v>367.6292114257812</v>
       </c>
       <c r="F36" t="n">
-        <v>2372800</v>
+        <v>3852300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B37" t="n">
-        <v>372.45264120656</v>
+        <v>367.3082703686788</v>
       </c>
       <c r="C37" t="n">
-        <v>374.3975636149493</v>
+        <v>374.1057935751742</v>
       </c>
       <c r="D37" t="n">
-        <v>364.8674556847058</v>
+        <v>365.7523266876615</v>
       </c>
       <c r="E37" t="n">
-        <v>367.6292419433594</v>
+        <v>369.0975952148438</v>
       </c>
       <c r="F37" t="n">
-        <v>3852300</v>
+        <v>2384300</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B38" t="n">
-        <v>367.3082703686788</v>
+        <v>366.5789276874148</v>
       </c>
       <c r="C38" t="n">
-        <v>374.1057935751742</v>
+        <v>370.4493335464572</v>
       </c>
       <c r="D38" t="n">
-        <v>365.7523266876615</v>
+        <v>364.682646350049</v>
       </c>
       <c r="E38" t="n">
-        <v>369.0975952148438</v>
+        <v>369.1365051269531</v>
       </c>
       <c r="F38" t="n">
-        <v>2384300</v>
+        <v>2643500</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B39" t="n">
-        <v>366.5789579935506</v>
+        <v>366.6275697464224</v>
       </c>
       <c r="C39" t="n">
-        <v>370.4493641725706</v>
+        <v>368.0570887541689</v>
       </c>
       <c r="D39" t="n">
-        <v>364.6826764994138</v>
+        <v>363.3892576559226</v>
       </c>
       <c r="E39" t="n">
-        <v>369.1365356445312</v>
+        <v>367.9306640625</v>
       </c>
       <c r="F39" t="n">
-        <v>2643500</v>
+        <v>2897600</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B40" t="n">
-        <v>366.6275697464224</v>
+        <v>366.9581821818597</v>
       </c>
       <c r="C40" t="n">
-        <v>368.0570887541689</v>
+        <v>373.1138475541215</v>
       </c>
       <c r="D40" t="n">
-        <v>363.3892576559226</v>
+        <v>366.3746996179726</v>
       </c>
       <c r="E40" t="n">
-        <v>367.9306640625</v>
+        <v>372.5303649902344</v>
       </c>
       <c r="F40" t="n">
-        <v>2897600</v>
+        <v>2590000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B41" t="n">
-        <v>366.9581821818597</v>
+        <v>372.2483997179557</v>
       </c>
       <c r="C41" t="n">
-        <v>373.1138475541215</v>
+        <v>372.8610549707219</v>
       </c>
       <c r="D41" t="n">
-        <v>366.3746996179726</v>
+        <v>360.3260169130116</v>
       </c>
       <c r="E41" t="n">
-        <v>372.5303649902344</v>
+        <v>363.5448608398438</v>
       </c>
       <c r="F41" t="n">
-        <v>2590000</v>
+        <v>4763000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B42" t="n">
-        <v>372.2483997179557</v>
+        <v>361.5805182090473</v>
       </c>
       <c r="C42" t="n">
-        <v>372.8610549707219</v>
+        <v>362.3973820280062</v>
       </c>
       <c r="D42" t="n">
-        <v>360.3260169130116</v>
+        <v>357.4280900328899</v>
       </c>
       <c r="E42" t="n">
-        <v>363.5448608398438</v>
+        <v>358.90625</v>
       </c>
       <c r="F42" t="n">
-        <v>4763000</v>
+        <v>3622100</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B43" t="n">
-        <v>361.5804874640777</v>
+        <v>358.8284322647385</v>
       </c>
       <c r="C43" t="n">
-        <v>362.3973512135793</v>
+        <v>363.3601048105454</v>
       </c>
       <c r="D43" t="n">
-        <v>357.4280596409988</v>
+        <v>357.4475540431628</v>
       </c>
       <c r="E43" t="n">
-        <v>358.9062194824219</v>
+        <v>360.8900451660156</v>
       </c>
       <c r="F43" t="n">
-        <v>3622100</v>
+        <v>2766400</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B44" t="n">
-        <v>358.8284019214945</v>
+        <v>359.6064305558101</v>
       </c>
       <c r="C44" t="n">
-        <v>363.3600740840942</v>
+        <v>360.452467039932</v>
       </c>
       <c r="D44" t="n">
-        <v>357.4475238166886</v>
+        <v>353.4410301931099</v>
       </c>
       <c r="E44" t="n">
-        <v>360.8900146484375</v>
+        <v>360.2287902832031</v>
       </c>
       <c r="F44" t="n">
-        <v>2766400</v>
+        <v>3257900</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B45" t="n">
-        <v>359.6064000909565</v>
+        <v>361.7458003836202</v>
       </c>
       <c r="C45" t="n">
-        <v>360.4524365034046</v>
+        <v>365.6453789483504</v>
       </c>
       <c r="D45" t="n">
-        <v>353.4410002505718</v>
+        <v>360.6955554382075</v>
       </c>
       <c r="E45" t="n">
-        <v>360.228759765625</v>
+        <v>363.933837890625</v>
       </c>
       <c r="F45" t="n">
-        <v>3257900</v>
+        <v>2407300</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B46" t="n">
-        <v>361.745830717721</v>
+        <v>361.8138665438969</v>
       </c>
       <c r="C46" t="n">
-        <v>365.6454096094494</v>
+        <v>363.272558161854</v>
       </c>
       <c r="D46" t="n">
-        <v>360.6955856842403</v>
+        <v>358.8478721249137</v>
       </c>
       <c r="E46" t="n">
-        <v>363.9338684082031</v>
+        <v>360.9094848632812</v>
       </c>
       <c r="F46" t="n">
-        <v>2407300</v>
+        <v>3375800</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B47" t="n">
-        <v>361.8138665438969</v>
+        <v>361.4249087666506</v>
       </c>
       <c r="C47" t="n">
-        <v>363.272558161854</v>
+        <v>363.2336722315698</v>
       </c>
       <c r="D47" t="n">
-        <v>358.8478721249137</v>
+        <v>356.5236963397476</v>
       </c>
       <c r="E47" t="n">
-        <v>360.9094848632812</v>
+        <v>357.9337768554688</v>
       </c>
       <c r="F47" t="n">
-        <v>3375800</v>
+        <v>3034800</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B48" t="n">
-        <v>361.4249087666506</v>
+        <v>355.8332360732777</v>
       </c>
       <c r="C48" t="n">
-        <v>363.2336722315698</v>
+        <v>357.2141141827383</v>
       </c>
       <c r="D48" t="n">
-        <v>356.5236963397476</v>
+        <v>349.8914834635758</v>
       </c>
       <c r="E48" t="n">
-        <v>357.9337768554688</v>
+        <v>352.3809814453125</v>
       </c>
       <c r="F48" t="n">
-        <v>3034800</v>
+        <v>3413300</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B49" t="n">
-        <v>355.8332052567208</v>
+        <v>351.1848930100947</v>
       </c>
       <c r="C49" t="n">
-        <v>357.2140832465919</v>
+        <v>353.7619090719871</v>
       </c>
       <c r="D49" t="n">
-        <v>349.891453161598</v>
+        <v>346.2934147079206</v>
       </c>
       <c r="E49" t="n">
-        <v>352.3809509277344</v>
+        <v>348.1702575683594</v>
       </c>
       <c r="F49" t="n">
-        <v>3413300</v>
+        <v>5127200</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B50" t="n">
-        <v>351.1848930100947</v>
+        <v>330.6173283766702</v>
       </c>
       <c r="C50" t="n">
-        <v>353.7619090719871</v>
+        <v>339.1944125402241</v>
       </c>
       <c r="D50" t="n">
-        <v>346.2934147079206</v>
+        <v>326.7566567053178</v>
       </c>
       <c r="E50" t="n">
-        <v>348.1702575683594</v>
+        <v>327.2137145996094</v>
       </c>
       <c r="F50" t="n">
-        <v>5127200</v>
+        <v>10168500</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B51" t="n">
-        <v>330.6173283766702</v>
+        <v>331.5800630406063</v>
       </c>
       <c r="C51" t="n">
-        <v>339.1944125402241</v>
+        <v>332.3385815128617</v>
       </c>
       <c r="D51" t="n">
-        <v>326.7566567053178</v>
+        <v>322.2444305286613</v>
       </c>
       <c r="E51" t="n">
-        <v>327.2137145996094</v>
+        <v>325.2882385253906</v>
       </c>
       <c r="F51" t="n">
-        <v>10168500</v>
+        <v>7595000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B52" t="n">
-        <v>331.5800941484648</v>
+        <v>327.0970305832446</v>
       </c>
       <c r="C52" t="n">
-        <v>332.3386126918821</v>
+        <v>329.567090307595</v>
       </c>
       <c r="D52" t="n">
-        <v>322.2444607606784</v>
+        <v>322.9835387560075</v>
       </c>
       <c r="E52" t="n">
-        <v>325.2882690429688</v>
+        <v>323.2266540527344</v>
       </c>
       <c r="F52" t="n">
-        <v>7595000</v>
+        <v>4025300</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B53" t="n">
-        <v>327.0969997002432</v>
+        <v>325.3563217063679</v>
       </c>
       <c r="C53" t="n">
-        <v>329.567059191382</v>
+        <v>337.3662223876241</v>
       </c>
       <c r="D53" t="n">
-        <v>322.9835082613831</v>
+        <v>323.8295506364051</v>
       </c>
       <c r="E53" t="n">
-        <v>323.2266235351562</v>
+        <v>333.8653564453125</v>
       </c>
       <c r="F53" t="n">
-        <v>4025300</v>
+        <v>7441300</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B54" t="n">
-        <v>325.356351446162</v>
+        <v>332.7762309351845</v>
       </c>
       <c r="C54" t="n">
-        <v>337.3662532252054</v>
+        <v>334.2446271509373</v>
       </c>
       <c r="D54" t="n">
-        <v>323.8295802366419</v>
+        <v>327.2818014724936</v>
       </c>
       <c r="E54" t="n">
-        <v>333.8653869628906</v>
+        <v>327.3109741210938</v>
       </c>
       <c r="F54" t="n">
-        <v>7441300</v>
+        <v>6132900</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B55" t="n">
-        <v>332.7761999080408</v>
+        <v>329.6643042136632</v>
       </c>
       <c r="C55" t="n">
-        <v>334.2445959868845</v>
+        <v>343.2787592549354</v>
       </c>
       <c r="D55" t="n">
-        <v>327.2817709576355</v>
+        <v>329.518440987938</v>
       </c>
       <c r="E55" t="n">
-        <v>327.3109436035156</v>
+        <v>341.4019165039062</v>
       </c>
       <c r="F55" t="n">
-        <v>6132900</v>
+        <v>6316600</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B56" t="n">
-        <v>329.6643336820279</v>
+        <v>340.6142414881474</v>
       </c>
       <c r="C56" t="n">
-        <v>343.2787899402826</v>
+        <v>347.4895190539308</v>
       </c>
       <c r="D56" t="n">
-        <v>329.5184704432642</v>
+        <v>339.3889309798961</v>
       </c>
       <c r="E56" t="n">
-        <v>341.4019470214844</v>
+        <v>345.6807556152344</v>
       </c>
       <c r="F56" t="n">
-        <v>6316600</v>
+        <v>4517300</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B57" t="n">
-        <v>340.6142114178541</v>
+        <v>345.1556329381714</v>
       </c>
       <c r="C57" t="n">
-        <v>347.4894883766705</v>
+        <v>347.9757643711671</v>
       </c>
       <c r="D57" t="n">
-        <v>339.3889010177763</v>
+        <v>343.7650205997065</v>
       </c>
       <c r="E57" t="n">
-        <v>345.6807250976562</v>
+        <v>347.0908508300781</v>
       </c>
       <c r="F57" t="n">
-        <v>4517300</v>
+        <v>2119600</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B58" t="n">
-        <v>345.1556025907452</v>
+        <v>344.2998610600955</v>
       </c>
       <c r="C58" t="n">
-        <v>347.975733775784</v>
+        <v>352.3129611811121</v>
       </c>
       <c r="D58" t="n">
-        <v>343.7649903745483</v>
+        <v>343.1620981246396</v>
       </c>
       <c r="E58" t="n">
-        <v>347.0908203125</v>
+        <v>347.4895324707031</v>
       </c>
       <c r="F58" t="n">
-        <v>2119600</v>
+        <v>5107100</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B59" t="n">
-        <v>344.2998610600955</v>
+        <v>347.0032746652403</v>
       </c>
       <c r="C59" t="n">
-        <v>352.3129611811121</v>
+        <v>347.654836647816</v>
       </c>
       <c r="D59" t="n">
-        <v>343.1620981246396</v>
+        <v>341.6255660714526</v>
       </c>
       <c r="E59" t="n">
-        <v>347.4895324707031</v>
+        <v>344.2803955078125</v>
       </c>
       <c r="F59" t="n">
-        <v>5107100</v>
+        <v>3965300</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B60" t="n">
-        <v>347.0032746652403</v>
+        <v>344.7374926404726</v>
       </c>
       <c r="C60" t="n">
-        <v>347.654836647816</v>
+        <v>350.5430871450869</v>
       </c>
       <c r="D60" t="n">
-        <v>341.6255660714526</v>
+        <v>344.0081467463108</v>
       </c>
       <c r="E60" t="n">
-        <v>344.2803955078125</v>
+        <v>348.0535888671875</v>
       </c>
       <c r="F60" t="n">
-        <v>3965300</v>
+        <v>4166700</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,25 +2003,25 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B61" t="n">
-        <v>344.7374321868316</v>
+        <v>348.719115353366</v>
       </c>
       <c r="C61" t="n">
-        <v>350.5430256733688</v>
+        <v>349.9131924709116</v>
       </c>
       <c r="D61" t="n">
-        <v>344.0080864205689</v>
+        <v>342.5627647323979</v>
       </c>
       <c r="E61" t="n">
-        <v>348.0535278320312</v>
+        <v>343.7079162597656</v>
       </c>
       <c r="F61" t="n">
-        <v>4166700</v>
+        <v>4022800</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2029,25 +2029,25 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B62" t="n">
-        <v>348.719115353366</v>
+        <v>343.1989840484338</v>
       </c>
       <c r="C62" t="n">
-        <v>349.9131924709116</v>
+        <v>348.0633770310509</v>
       </c>
       <c r="D62" t="n">
-        <v>342.5627647323979</v>
+        <v>342.102787861214</v>
       </c>
       <c r="E62" t="n">
-        <v>343.7079162597656</v>
+        <v>347.0748291015625</v>
       </c>
       <c r="F62" t="n">
-        <v>4022800</v>
+        <v>5959200</v>
       </c>
       <c r="G62" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B63" t="n">
-        <v>343.1989538716508</v>
+        <v>344.4713302562425</v>
       </c>
       <c r="C63" t="n">
-        <v>348.0633464265518</v>
+        <v>344.6083398260661</v>
       </c>
       <c r="D63" t="n">
-        <v>342.1027577808173</v>
+        <v>338.3541382135411</v>
       </c>
       <c r="E63" t="n">
-        <v>347.0747985839844</v>
+        <v>342.4746704101562</v>
       </c>
       <c r="F63" t="n">
-        <v>5959200</v>
+        <v>7273000</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B64" t="n">
-        <v>344.4713302562425</v>
+        <v>340.3703677160696</v>
       </c>
       <c r="C64" t="n">
-        <v>344.6083398260661</v>
+        <v>349.0910404146574</v>
       </c>
       <c r="D64" t="n">
-        <v>338.3541382135411</v>
+        <v>337.6298477160418</v>
       </c>
       <c r="E64" t="n">
-        <v>342.4746704101562</v>
+        <v>337.9332580566406</v>
       </c>
       <c r="F64" t="n">
-        <v>7273000</v>
+        <v>5063100</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B65" t="n">
-        <v>340.3703984537347</v>
+        <v>336.7881454975472</v>
       </c>
       <c r="C65" t="n">
-        <v>349.0910719398561</v>
+        <v>344.5398348592771</v>
       </c>
       <c r="D65" t="n">
-        <v>337.62987820622</v>
+        <v>336.6902644468525</v>
       </c>
       <c r="E65" t="n">
-        <v>337.9332885742188</v>
+        <v>343.6687622070312</v>
       </c>
       <c r="F65" t="n">
-        <v>5063100</v>
+        <v>6316100</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B66" t="n">
-        <v>336.7881454975472</v>
+        <v>348.4352899865784</v>
       </c>
       <c r="C66" t="n">
-        <v>344.5398348592771</v>
+        <v>355.0124966552466</v>
       </c>
       <c r="D66" t="n">
-        <v>336.6902644468525</v>
+        <v>346.4190656980946</v>
       </c>
       <c r="E66" t="n">
-        <v>343.6687622070312</v>
+        <v>349.8642578125</v>
       </c>
       <c r="F66" t="n">
-        <v>6316100</v>
+        <v>6609800</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B67" t="n">
-        <v>348.4352899865784</v>
+        <v>351.6260236653551</v>
       </c>
       <c r="C67" t="n">
-        <v>355.0124966552466</v>
+        <v>353.0941498724499</v>
       </c>
       <c r="D67" t="n">
-        <v>346.4190656980946</v>
+        <v>348.4842120764174</v>
       </c>
       <c r="E67" t="n">
-        <v>349.8642578125</v>
+        <v>352.0077209472656</v>
       </c>
       <c r="F67" t="n">
-        <v>6609800</v>
+        <v>3861200</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B68" t="n">
-        <v>351.6260236653551</v>
+        <v>351.7532309142689</v>
       </c>
       <c r="C68" t="n">
-        <v>353.0941498724499</v>
+        <v>354.9635320383587</v>
       </c>
       <c r="D68" t="n">
-        <v>348.4842120764174</v>
+        <v>348.0633216327761</v>
       </c>
       <c r="E68" t="n">
-        <v>352.0077209472656</v>
+        <v>349.4042053222656</v>
       </c>
       <c r="F68" t="n">
-        <v>3861200</v>
+        <v>4387400</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B69" t="n">
-        <v>351.753261637015</v>
+        <v>349.3161510627795</v>
       </c>
       <c r="C69" t="n">
-        <v>354.9635630414982</v>
+        <v>351.1170489325283</v>
       </c>
       <c r="D69" t="n">
-        <v>348.0633520332391</v>
+        <v>344.3343131247511</v>
       </c>
       <c r="E69" t="n">
-        <v>349.4042358398438</v>
+        <v>345.1858215332031</v>
       </c>
       <c r="F69" t="n">
-        <v>4387400</v>
+        <v>3497200</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B70" t="n">
-        <v>349.3161510627795</v>
+        <v>344.4909144902828</v>
       </c>
       <c r="C70" t="n">
-        <v>351.1170489325283</v>
+        <v>349.9034051286982</v>
       </c>
       <c r="D70" t="n">
-        <v>344.3343131247511</v>
+        <v>343.5219607726549</v>
       </c>
       <c r="E70" t="n">
-        <v>345.1858215332031</v>
+        <v>349.1693420410156</v>
       </c>
       <c r="F70" t="n">
-        <v>3497200</v>
+        <v>3875200</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B71" t="n">
-        <v>344.4909144902828</v>
+        <v>355.8150843258923</v>
       </c>
       <c r="C71" t="n">
-        <v>349.9034051286982</v>
+        <v>358.5164162998122</v>
       </c>
       <c r="D71" t="n">
-        <v>343.5219607726549</v>
+        <v>347.0258911387745</v>
       </c>
       <c r="E71" t="n">
-        <v>349.1693420410156</v>
+        <v>347.4467468261719</v>
       </c>
       <c r="F71" t="n">
-        <v>3875200</v>
+        <v>4805200</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B72" t="n">
-        <v>355.8150530732911</v>
+        <v>346.5854112795514</v>
       </c>
       <c r="C72" t="n">
-        <v>358.5163848099426</v>
+        <v>346.5854112795514</v>
       </c>
       <c r="D72" t="n">
-        <v>347.0258606581617</v>
+        <v>337.5907194306183</v>
       </c>
       <c r="E72" t="n">
-        <v>347.4467163085938</v>
+        <v>337.6690063476562</v>
       </c>
       <c r="F72" t="n">
-        <v>4805200</v>
+        <v>12825600</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B73" t="n">
-        <v>346.5854112795514</v>
+        <v>337.9724124645031</v>
       </c>
       <c r="C73" t="n">
-        <v>346.5854112795514</v>
+        <v>340.507373272994</v>
       </c>
       <c r="D73" t="n">
-        <v>337.5907194306183</v>
+        <v>336.3966381250771</v>
       </c>
       <c r="E73" t="n">
-        <v>337.6690063476562</v>
+        <v>339.0294799804688</v>
       </c>
       <c r="F73" t="n">
-        <v>12825600</v>
+        <v>3523700</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B74" t="n">
-        <v>337.9724124645031</v>
+        <v>336.6902894441487</v>
       </c>
       <c r="C74" t="n">
-        <v>340.507373272994</v>
+        <v>340.1159173890746</v>
       </c>
       <c r="D74" t="n">
-        <v>336.3966381250771</v>
+        <v>334.6740651003779</v>
       </c>
       <c r="E74" t="n">
-        <v>339.0294799804688</v>
+        <v>337.6396789550781</v>
       </c>
       <c r="F74" t="n">
-        <v>3523700</v>
+        <v>3873400</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B75" t="n">
-        <v>336.6902894441487</v>
+        <v>337.0230069808841</v>
       </c>
       <c r="C75" t="n">
-        <v>340.1159173890746</v>
+        <v>340.8597228049852</v>
       </c>
       <c r="D75" t="n">
-        <v>334.6740651003779</v>
+        <v>336.5923542903493</v>
       </c>
       <c r="E75" t="n">
-        <v>337.6396789550781</v>
+        <v>339.9592590332031</v>
       </c>
       <c r="F75" t="n">
-        <v>3873400</v>
+        <v>1368600</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B76" t="n">
-        <v>337.0230372348798</v>
+        <v>339.616749893519</v>
       </c>
       <c r="C76" t="n">
-        <v>340.8597534033964</v>
+        <v>342.6117251227173</v>
       </c>
       <c r="D76" t="n">
-        <v>336.592384505686</v>
+        <v>339.2056912607851</v>
       </c>
       <c r="E76" t="n">
-        <v>339.9592895507812</v>
+        <v>342.3474731445312</v>
       </c>
       <c r="F76" t="n">
-        <v>1368600</v>
+        <v>1786900</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B77" t="n">
-        <v>339.616749893519</v>
+        <v>342.5627579984686</v>
       </c>
       <c r="C77" t="n">
-        <v>342.6117251227173</v>
+        <v>342.8759654029374</v>
       </c>
       <c r="D77" t="n">
-        <v>339.2056912607851</v>
+        <v>337.4243166284915</v>
       </c>
       <c r="E77" t="n">
-        <v>342.3474731445312</v>
+        <v>340.0669555664062</v>
       </c>
       <c r="F77" t="n">
-        <v>1786900</v>
+        <v>3790000</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B78" t="n">
-        <v>342.5627579984686</v>
+        <v>338.6771490106644</v>
       </c>
       <c r="C78" t="n">
-        <v>342.8759654029374</v>
+        <v>339.6069742481806</v>
       </c>
       <c r="D78" t="n">
-        <v>337.4243166284915</v>
+        <v>336.4162369795515</v>
       </c>
       <c r="E78" t="n">
-        <v>340.0669555664062</v>
+        <v>338.9903564453125</v>
       </c>
       <c r="F78" t="n">
-        <v>3790000</v>
+        <v>2392600</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B79" t="n">
-        <v>338.6771490106644</v>
+        <v>338.1583920810744</v>
       </c>
       <c r="C79" t="n">
-        <v>339.6069742481806</v>
+        <v>339.342672153089</v>
       </c>
       <c r="D79" t="n">
-        <v>336.4162369795515</v>
+        <v>336.6609045931061</v>
       </c>
       <c r="E79" t="n">
-        <v>338.9903564453125</v>
+        <v>336.7881469726562</v>
       </c>
       <c r="F79" t="n">
-        <v>2392600</v>
+        <v>2317500</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B80" t="n">
-        <v>338.1583614393335</v>
+        <v>336.1323595285862</v>
       </c>
       <c r="C80" t="n">
-        <v>339.3426414040363</v>
+        <v>341.0848358843269</v>
       </c>
       <c r="D80" t="n">
-        <v>336.6608740870579</v>
+        <v>333.6757154817447</v>
       </c>
       <c r="E80" t="n">
-        <v>336.7881164550781</v>
+        <v>338.4715881347656</v>
       </c>
       <c r="F80" t="n">
-        <v>2317500</v>
+        <v>3763000</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B81" t="n">
-        <v>336.1323898352527</v>
+        <v>335.4179027837736</v>
       </c>
       <c r="C81" t="n">
-        <v>341.084866637523</v>
+        <v>339.9690879170088</v>
       </c>
       <c r="D81" t="n">
-        <v>333.6757455669131</v>
+        <v>333.9987022113515</v>
       </c>
       <c r="E81" t="n">
-        <v>338.4716186523438</v>
+        <v>336.7783508300781</v>
       </c>
       <c r="F81" t="n">
-        <v>3763000</v>
+        <v>4725300</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B82" t="n">
-        <v>335.4179331780732</v>
+        <v>334.2433821573216</v>
       </c>
       <c r="C82" t="n">
-        <v>339.9691187237194</v>
+        <v>343.2283069014873</v>
       </c>
       <c r="D82" t="n">
-        <v>333.9987324770484</v>
+        <v>330.5339084400161</v>
       </c>
       <c r="E82" t="n">
-        <v>336.7783813476562</v>
+        <v>341.8678588867188</v>
       </c>
       <c r="F82" t="n">
-        <v>4725300</v>
+        <v>4680300</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B83" t="n">
-        <v>334.2434119942842</v>
+        <v>345.8318135746193</v>
       </c>
       <c r="C83" t="n">
-        <v>343.2283375405087</v>
+        <v>350.882171425454</v>
       </c>
       <c r="D83" t="n">
-        <v>330.5339379458445</v>
+        <v>341.6133999004275</v>
       </c>
       <c r="E83" t="n">
-        <v>341.8678894042969</v>
+        <v>341.6427612304688</v>
       </c>
       <c r="F83" t="n">
-        <v>4680300</v>
+        <v>4442700</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B84" t="n">
-        <v>345.83178268285</v>
+        <v>337.9724185347548</v>
       </c>
       <c r="C84" t="n">
-        <v>350.8821400825564</v>
+        <v>355.5214122846852</v>
       </c>
       <c r="D84" t="n">
-        <v>341.6133693854721</v>
+        <v>336.7881384925595</v>
       </c>
       <c r="E84" t="n">
-        <v>341.6427307128906</v>
+        <v>351.9196166992188</v>
       </c>
       <c r="F84" t="n">
-        <v>4442700</v>
+        <v>5196500</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B85" t="n">
-        <v>337.9724478428672</v>
+        <v>355.7759014105663</v>
       </c>
       <c r="C85" t="n">
-        <v>355.5214431146019</v>
+        <v>367.5111134698199</v>
       </c>
       <c r="D85" t="n">
-        <v>336.7881676979742</v>
+        <v>353.632434855731</v>
       </c>
       <c r="E85" t="n">
-        <v>351.9196472167969</v>
+        <v>366.67919921875</v>
       </c>
       <c r="F85" t="n">
-        <v>5196500</v>
+        <v>7093500</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B86" t="n">
-        <v>355.7759014105663</v>
+        <v>366.679226053498</v>
       </c>
       <c r="C86" t="n">
-        <v>367.5111134698199</v>
+        <v>368.4214013397691</v>
       </c>
       <c r="D86" t="n">
-        <v>353.632434855731</v>
+        <v>361.4037447316197</v>
       </c>
       <c r="E86" t="n">
-        <v>366.67919921875</v>
+        <v>366.9728393554688</v>
       </c>
       <c r="F86" t="n">
-        <v>7093500</v>
+        <v>5859800</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B87" t="n">
-        <v>366.679226053498</v>
+        <v>367.8830461936743</v>
       </c>
       <c r="C87" t="n">
-        <v>368.4214013397691</v>
+        <v>372.1014596119851</v>
       </c>
       <c r="D87" t="n">
-        <v>361.4037447316197</v>
+        <v>362.9403667655412</v>
       </c>
       <c r="E87" t="n">
-        <v>366.9728393554688</v>
+        <v>371.6708068847656</v>
       </c>
       <c r="F87" t="n">
-        <v>5859800</v>
+        <v>4785800</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B88" t="n">
-        <v>367.8830764002425</v>
+        <v>368.6856307593888</v>
       </c>
       <c r="C88" t="n">
-        <v>372.1014901649237</v>
+        <v>372.0133774109565</v>
       </c>
       <c r="D88" t="n">
-        <v>362.9403965662702</v>
+        <v>366.023427464314</v>
       </c>
       <c r="E88" t="n">
-        <v>371.6708374023438</v>
+        <v>367.9613647460938</v>
       </c>
       <c r="F88" t="n">
-        <v>4785800</v>
+        <v>4959900</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B89" t="n">
-        <v>368.6856001817422</v>
+        <v>368.0298576269892</v>
       </c>
       <c r="C89" t="n">
-        <v>372.0133465573169</v>
+        <v>372.1014644570138</v>
       </c>
       <c r="D89" t="n">
-        <v>366.0233971074624</v>
+        <v>366.5030087993679</v>
       </c>
       <c r="E89" t="n">
-        <v>367.9613342285156</v>
+        <v>371.1031494140625</v>
       </c>
       <c r="F89" t="n">
-        <v>4959900</v>
+        <v>2990100</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B90" t="n">
-        <v>368.0298576269892</v>
+        <v>371.1912414425437</v>
       </c>
       <c r="C90" t="n">
-        <v>372.1014644570138</v>
+        <v>374.6364335107019</v>
       </c>
       <c r="D90" t="n">
-        <v>366.5030087993679</v>
+        <v>369.4882246061678</v>
       </c>
       <c r="E90" t="n">
-        <v>371.1031494140625</v>
+        <v>372.0917053222656</v>
       </c>
       <c r="F90" t="n">
-        <v>2990100</v>
+        <v>3709000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B91" t="n">
-        <v>371.1912414425437</v>
+        <v>364.330180714857</v>
       </c>
       <c r="C91" t="n">
-        <v>374.6364335107019</v>
+        <v>369.3218156656606</v>
       </c>
       <c r="D91" t="n">
-        <v>369.4882246061678</v>
+        <v>363.4101525923161</v>
       </c>
       <c r="E91" t="n">
-        <v>372.0917053222656</v>
+        <v>367.1391906738281</v>
       </c>
       <c r="F91" t="n">
-        <v>3709000</v>
+        <v>5353700</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B92" t="n">
-        <v>364.330180714857</v>
+        <v>367.8145223498818</v>
       </c>
       <c r="C92" t="n">
-        <v>369.3218156656606</v>
+        <v>377.7195050958379</v>
       </c>
       <c r="D92" t="n">
-        <v>363.4101525923161</v>
+        <v>366.7183262816438</v>
       </c>
       <c r="E92" t="n">
-        <v>367.1391906738281</v>
+        <v>376.4667053222656</v>
       </c>
       <c r="F92" t="n">
-        <v>5353700</v>
+        <v>5169800</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B93" t="n">
-        <v>367.8145223498818</v>
+        <v>378.2382530449191</v>
       </c>
       <c r="C93" t="n">
-        <v>377.7195050958379</v>
+        <v>382.3000628313615</v>
       </c>
       <c r="D93" t="n">
-        <v>366.7183262816438</v>
+        <v>372.4440352517285</v>
       </c>
       <c r="E93" t="n">
-        <v>376.4667053222656</v>
+        <v>372.9334106445312</v>
       </c>
       <c r="F93" t="n">
-        <v>5169800</v>
+        <v>4828100</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B94" t="n">
-        <v>378.2382530449191</v>
+        <v>373.3934198383746</v>
       </c>
       <c r="C94" t="n">
-        <v>382.3000628313615</v>
+        <v>376.2024297773683</v>
       </c>
       <c r="D94" t="n">
-        <v>372.4440352517285</v>
+        <v>371.1520722052226</v>
       </c>
       <c r="E94" t="n">
-        <v>372.9334106445312</v>
+        <v>375.6151733398438</v>
       </c>
       <c r="F94" t="n">
-        <v>4828100</v>
+        <v>3138300</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B95" t="n">
-        <v>373.3934198383746</v>
+        <v>376.8190408591946</v>
       </c>
       <c r="C95" t="n">
-        <v>376.2024297773683</v>
+        <v>379.1876308298576</v>
       </c>
       <c r="D95" t="n">
-        <v>371.1520722052226</v>
+        <v>373.8338630026265</v>
       </c>
       <c r="E95" t="n">
-        <v>375.6151733398438</v>
+        <v>378.3165283203125</v>
       </c>
       <c r="F95" t="n">
-        <v>3138300</v>
+        <v>3984800</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B96" t="n">
-        <v>376.8190408591946</v>
+        <v>376.7701106050471</v>
       </c>
       <c r="C96" t="n">
-        <v>379.1876308298576</v>
+        <v>378.2871623096181</v>
       </c>
       <c r="D96" t="n">
-        <v>373.8338630026265</v>
+        <v>370.2320329388677</v>
       </c>
       <c r="E96" t="n">
-        <v>378.3165283203125</v>
+        <v>372.2776184082031</v>
       </c>
       <c r="F96" t="n">
-        <v>3984800</v>
+        <v>3466100</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B97" t="n">
-        <v>376.7701414908988</v>
+        <v>372.1308039100364</v>
       </c>
       <c r="C97" t="n">
-        <v>378.2871933198306</v>
+        <v>372.9040253443087</v>
       </c>
       <c r="D97" t="n">
-        <v>370.2320632887583</v>
+        <v>365.7102015587281</v>
       </c>
       <c r="E97" t="n">
-        <v>372.2776489257812</v>
+        <v>367.3251342773438</v>
       </c>
       <c r="F97" t="n">
-        <v>3466100</v>
+        <v>3371500</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B98" t="n">
-        <v>372.1308348268722</v>
+        <v>366.9336686607455</v>
       </c>
       <c r="C98" t="n">
-        <v>372.9040563253842</v>
+        <v>369.0771353006065</v>
       </c>
       <c r="D98" t="n">
-        <v>365.7102319421367</v>
+        <v>362.284602364362</v>
       </c>
       <c r="E98" t="n">
-        <v>367.3251647949219</v>
+        <v>363.9093322753906</v>
       </c>
       <c r="F98" t="n">
-        <v>3371500</v>
+        <v>4744500</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B99" t="n">
-        <v>366.9336686607455</v>
+        <v>364.4965491637078</v>
       </c>
       <c r="C99" t="n">
-        <v>369.0771353006065</v>
+        <v>367.1489551783843</v>
       </c>
       <c r="D99" t="n">
-        <v>362.284602364362</v>
+        <v>360.7185559568027</v>
       </c>
       <c r="E99" t="n">
-        <v>363.9093322753906</v>
+        <v>366.6302185058594</v>
       </c>
       <c r="F99" t="n">
-        <v>4744500</v>
+        <v>3755600</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B100" t="n">
-        <v>364.4965795036834</v>
+        <v>366.2876778370263</v>
       </c>
       <c r="C100" t="n">
-        <v>367.1489857391411</v>
+        <v>371.5827230758924</v>
       </c>
       <c r="D100" t="n">
-        <v>360.7185859823057</v>
+        <v>360.4151732293658</v>
       </c>
       <c r="E100" t="n">
-        <v>366.6302490234375</v>
+        <v>370.0852355957031</v>
       </c>
       <c r="F100" t="n">
-        <v>3755600</v>
+        <v>4757200</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B101" t="n">
-        <v>366.2876778370263</v>
+        <v>369.2728845813793</v>
       </c>
       <c r="C101" t="n">
-        <v>371.5827230758924</v>
+        <v>383.4549736116182</v>
       </c>
       <c r="D101" t="n">
-        <v>360.4151732293658</v>
+        <v>368.9890384961104</v>
       </c>
       <c r="E101" t="n">
-        <v>370.0852355957031</v>
+        <v>373.0019226074219</v>
       </c>
       <c r="F101" t="n">
-        <v>4757200</v>
+        <v>5684400</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B102" t="n">
-        <v>369.2728845813793</v>
+        <v>376.4177654444651</v>
       </c>
       <c r="C102" t="n">
-        <v>383.4549736116182</v>
+        <v>382.2315475683361</v>
       </c>
       <c r="D102" t="n">
-        <v>368.9890384961104</v>
+        <v>376.1926420082714</v>
       </c>
       <c r="E102" t="n">
-        <v>373.0019226074219</v>
+        <v>378.9723205566406</v>
       </c>
       <c r="F102" t="n">
-        <v>5684400</v>
+        <v>5574700</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B103" t="n">
-        <v>376.4177654444651</v>
+        <v>378.4633475893863</v>
       </c>
       <c r="C103" t="n">
-        <v>382.2315475683361</v>
+        <v>378.776555010176</v>
       </c>
       <c r="D103" t="n">
-        <v>376.1926420082714</v>
+        <v>372.7376495049467</v>
       </c>
       <c r="E103" t="n">
-        <v>378.9723205566406</v>
+        <v>374.2449340820312</v>
       </c>
       <c r="F103" t="n">
-        <v>5574700</v>
+        <v>3759700</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B104" t="n">
-        <v>378.4633475893863</v>
+        <v>373.2368128082787</v>
       </c>
       <c r="C104" t="n">
-        <v>378.776555010176</v>
+        <v>378.1599279570784</v>
       </c>
       <c r="D104" t="n">
-        <v>372.7376495049467</v>
+        <v>371.0444206547449</v>
       </c>
       <c r="E104" t="n">
-        <v>374.2449340820312</v>
+        <v>376.9658508300781</v>
       </c>
       <c r="F104" t="n">
-        <v>3759700</v>
+        <v>4685400</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B105" t="n">
-        <v>373.2368430239695</v>
+        <v>376.1926410669886</v>
       </c>
       <c r="C105" t="n">
-        <v>378.159958571324</v>
+        <v>377.5824803376956</v>
       </c>
       <c r="D105" t="n">
-        <v>371.0444506929488</v>
+        <v>370.163562457197</v>
       </c>
       <c r="E105" t="n">
-        <v>376.9658813476562</v>
+        <v>372.904052734375</v>
       </c>
       <c r="F105" t="n">
-        <v>4685400</v>
+        <v>3639300</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B106" t="n">
-        <v>376.1926410669886</v>
+        <v>375.6543348626084</v>
       </c>
       <c r="C106" t="n">
-        <v>377.5824803376956</v>
+        <v>383.4158213872818</v>
       </c>
       <c r="D106" t="n">
-        <v>370.163562457197</v>
+        <v>373.8240756812119</v>
       </c>
       <c r="E106" t="n">
-        <v>372.904052734375</v>
+        <v>381.3995971679688</v>
       </c>
       <c r="F106" t="n">
-        <v>3639300</v>
+        <v>3160800</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B107" t="n">
-        <v>375.6543348626084</v>
+        <v>376.8190595355247</v>
       </c>
       <c r="C107" t="n">
-        <v>383.4158213872818</v>
+        <v>383.1026528395359</v>
       </c>
       <c r="D107" t="n">
-        <v>373.8240756812119</v>
+        <v>373.9610940454729</v>
       </c>
       <c r="E107" t="n">
-        <v>381.3995971679688</v>
+        <v>382.3783569335938</v>
       </c>
       <c r="F107" t="n">
-        <v>3160800</v>
+        <v>3229900</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B108" t="n">
-        <v>376.8190294616336</v>
+        <v>385.187358063094</v>
       </c>
       <c r="C108" t="n">
-        <v>383.1026222641518</v>
+        <v>389.1806779778082</v>
       </c>
       <c r="D108" t="n">
-        <v>373.9610641996757</v>
+        <v>380.7340539554721</v>
       </c>
       <c r="E108" t="n">
-        <v>382.3783264160156</v>
+        <v>381.9281311035156</v>
       </c>
       <c r="F108" t="n">
-        <v>3229900</v>
+        <v>3702200</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B109" t="n">
-        <v>385.187358063094</v>
+        <v>381.908594703622</v>
       </c>
       <c r="C109" t="n">
-        <v>389.1806779778082</v>
+        <v>385.6278359965556</v>
       </c>
       <c r="D109" t="n">
-        <v>380.7340539554721</v>
+        <v>378.8744610861731</v>
       </c>
       <c r="E109" t="n">
-        <v>381.9281311035156</v>
+        <v>382.7405090332031</v>
       </c>
       <c r="F109" t="n">
-        <v>3702200</v>
+        <v>2875900</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B110" t="n">
-        <v>381.908564252376</v>
+        <v>383.895448836351</v>
       </c>
       <c r="C110" t="n">
-        <v>385.6278052487582</v>
+        <v>385.6278270527202</v>
       </c>
       <c r="D110" t="n">
-        <v>378.8744308768519</v>
+        <v>372.4146908465991</v>
       </c>
       <c r="E110" t="n">
-        <v>382.740478515625</v>
+        <v>374.9007263183594</v>
       </c>
       <c r="F110" t="n">
-        <v>2875900</v>
+        <v>3485300</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B111" t="n">
-        <v>383.895448836351</v>
+        <v>374.6168560607417</v>
       </c>
       <c r="C111" t="n">
-        <v>385.6278270527202</v>
+        <v>376.9364905994225</v>
       </c>
       <c r="D111" t="n">
-        <v>372.4146908465991</v>
+        <v>371.4750744620919</v>
       </c>
       <c r="E111" t="n">
-        <v>374.9007263183594</v>
+        <v>375.3704833984375</v>
       </c>
       <c r="F111" t="n">
-        <v>3485300</v>
+        <v>2982600</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B112" t="n">
-        <v>374.6168560607417</v>
+        <v>375.5857881596228</v>
       </c>
       <c r="C112" t="n">
-        <v>376.9364905994225</v>
+        <v>375.5857881596228</v>
       </c>
       <c r="D112" t="n">
-        <v>371.4750744620919</v>
+        <v>369.3707450420628</v>
       </c>
       <c r="E112" t="n">
-        <v>375.3704833984375</v>
+        <v>370.5354309082031</v>
       </c>
       <c r="F112" t="n">
-        <v>2982600</v>
+        <v>2930900</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B113" t="n">
-        <v>375.5858190931522</v>
+        <v>369.4295104342575</v>
       </c>
       <c r="C113" t="n">
-        <v>375.5858190931522</v>
+        <v>376.6428992274523</v>
       </c>
       <c r="D113" t="n">
-        <v>369.3707754637165</v>
+        <v>367.9613841983854</v>
       </c>
       <c r="E113" t="n">
-        <v>370.5354614257812</v>
+        <v>374.1275024414062</v>
       </c>
       <c r="F113" t="n">
-        <v>2930900</v>
+        <v>3984100</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B114" t="n">
-        <v>369.4294802998945</v>
+        <v>372.8942511780455</v>
       </c>
       <c r="C114" t="n">
-        <v>376.6428685046932</v>
+        <v>375.977340039125</v>
       </c>
       <c r="D114" t="n">
-        <v>367.9613541837774</v>
+        <v>361.7267011620893</v>
       </c>
       <c r="E114" t="n">
-        <v>374.1274719238281</v>
+        <v>368.979248046875</v>
       </c>
       <c r="F114" t="n">
-        <v>3984100</v>
+        <v>5495700</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B115" t="n">
-        <v>372.8942511780455</v>
+        <v>380.8417107584177</v>
       </c>
       <c r="C115" t="n">
-        <v>375.977340039125</v>
+        <v>385.9703852790173</v>
       </c>
       <c r="D115" t="n">
-        <v>361.7267011620893</v>
+        <v>374.0883361890514</v>
       </c>
       <c r="E115" t="n">
-        <v>368.979248046875</v>
+        <v>376.3101196289062</v>
       </c>
       <c r="F115" t="n">
-        <v>5495700</v>
+        <v>5675800</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B116" t="n">
-        <v>380.8417107584177</v>
+        <v>372.9725764492633</v>
       </c>
       <c r="C116" t="n">
-        <v>385.9703852790173</v>
+        <v>373.3347094680754</v>
       </c>
       <c r="D116" t="n">
-        <v>374.0883361890514</v>
+        <v>363.4786816926297</v>
       </c>
       <c r="E116" t="n">
-        <v>376.3101196289062</v>
+        <v>367.5894470214844</v>
       </c>
       <c r="F116" t="n">
-        <v>5675800</v>
+        <v>5036900</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B117" t="n">
-        <v>372.9725454847734</v>
+        <v>370.3592916198801</v>
       </c>
       <c r="C117" t="n">
-        <v>373.3346784735209</v>
+        <v>373.3738607688525</v>
       </c>
       <c r="D117" t="n">
-        <v>363.4786515163307</v>
+        <v>366.9728222621029</v>
       </c>
       <c r="E117" t="n">
-        <v>367.5894165039062</v>
+        <v>367.11962890625</v>
       </c>
       <c r="F117" t="n">
-        <v>5036900</v>
+        <v>2889400</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B118" t="n">
-        <v>370.3593224067619</v>
+        <v>365.915758878878</v>
       </c>
       <c r="C118" t="n">
-        <v>373.3738918063265</v>
+        <v>374.0687697501482</v>
       </c>
       <c r="D118" t="n">
-        <v>366.9728527674773</v>
+        <v>364.4280684193005</v>
       </c>
       <c r="E118" t="n">
-        <v>367.1196594238281</v>
+        <v>372.6300048828125</v>
       </c>
       <c r="F118" t="n">
-        <v>2889400</v>
+        <v>4819500</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B119" t="n">
-        <v>365.9157289111819</v>
+        <v>367.0315715092017</v>
       </c>
       <c r="C119" t="n">
-        <v>374.0687391147384</v>
+        <v>367.1392197663403</v>
       </c>
       <c r="D119" t="n">
-        <v>364.4280385734429</v>
+        <v>361.1590663650545</v>
       </c>
       <c r="E119" t="n">
-        <v>372.6299743652344</v>
+        <v>362.9306030273438</v>
       </c>
       <c r="F119" t="n">
-        <v>4819500</v>
+        <v>4537600</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B120" t="n">
-        <v>367.0315406467873</v>
+        <v>356.0010127710523</v>
       </c>
       <c r="C120" t="n">
-        <v>367.1391888948742</v>
+        <v>360.9436919959621</v>
       </c>
       <c r="D120" t="n">
-        <v>361.1590359964387</v>
+        <v>352.4677071137912</v>
       </c>
       <c r="E120" t="n">
-        <v>362.9305725097656</v>
+        <v>359.1232299804688</v>
       </c>
       <c r="F120" t="n">
-        <v>4537600</v>
+        <v>3964700</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B121" t="n">
-        <v>356.0010127710523</v>
+        <v>358.4185545746917</v>
       </c>
       <c r="C121" t="n">
-        <v>360.9436919959621</v>
+        <v>361.716939988571</v>
       </c>
       <c r="D121" t="n">
-        <v>352.4677071137912</v>
+        <v>353.8282109374275</v>
       </c>
       <c r="E121" t="n">
-        <v>359.1232299804688</v>
+        <v>361.2666931152344</v>
       </c>
       <c r="F121" t="n">
-        <v>3964700</v>
+        <v>4324400</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B122" t="n">
-        <v>358.4185545746917</v>
+        <v>358.3402236370215</v>
       </c>
       <c r="C122" t="n">
-        <v>361.716939988571</v>
+        <v>359.1819648229422</v>
       </c>
       <c r="D122" t="n">
-        <v>353.8282109374275</v>
+        <v>351.5672851014027</v>
       </c>
       <c r="E122" t="n">
-        <v>361.2666931152344</v>
+        <v>353.9945678710938</v>
       </c>
       <c r="F122" t="n">
-        <v>4324400</v>
+        <v>4752200</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B123" t="n">
-        <v>358.3402236370215</v>
+        <v>349.9425535763344</v>
       </c>
       <c r="C123" t="n">
-        <v>359.1819648229422</v>
+        <v>351.8119711041206</v>
       </c>
       <c r="D123" t="n">
-        <v>351.5672851014027</v>
+        <v>345.714343142884</v>
       </c>
       <c r="E123" t="n">
-        <v>353.9945678710938</v>
+        <v>350.3144836425781</v>
       </c>
       <c r="F123" t="n">
-        <v>4752200</v>
+        <v>4167400</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B124" t="n">
-        <v>349.9425535763344</v>
+        <v>348.0437483770095</v>
       </c>
       <c r="C124" t="n">
-        <v>351.8119711041206</v>
+        <v>348.9148209517669</v>
       </c>
       <c r="D124" t="n">
-        <v>345.714343142884</v>
+        <v>338.2953999508869</v>
       </c>
       <c r="E124" t="n">
-        <v>350.3144836425781</v>
+        <v>346.0470886230469</v>
       </c>
       <c r="F124" t="n">
-        <v>4167400</v>
+        <v>4224500</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B125" t="n">
-        <v>348.0437790706712</v>
+        <v>345.5382004871225</v>
       </c>
       <c r="C125" t="n">
-        <v>348.9148517222478</v>
+        <v>353.9554635770335</v>
       </c>
       <c r="D125" t="n">
-        <v>338.2954297848507</v>
+        <v>343.5611046994417</v>
       </c>
       <c r="E125" t="n">
-        <v>346.047119140625</v>
+        <v>349.5608520507812</v>
       </c>
       <c r="F125" t="n">
-        <v>4224500</v>
+        <v>3986000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B126" t="n">
-        <v>345.5381703207324</v>
+        <v>347.9067729324123</v>
       </c>
       <c r="C126" t="n">
-        <v>353.9554326757943</v>
+        <v>348.7485142053993</v>
       </c>
       <c r="D126" t="n">
-        <v>343.5610747056572</v>
+        <v>341.6916989868697</v>
       </c>
       <c r="E126" t="n">
-        <v>349.5608215332031</v>
+        <v>343.3849487304688</v>
       </c>
       <c r="F126" t="n">
-        <v>3986000</v>
+        <v>3197100</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,25 +3719,25 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B127" t="n">
-        <v>347.906742012967</v>
+        <v>340.9512279608855</v>
       </c>
       <c r="C127" t="n">
-        <v>348.7484832111462</v>
+        <v>343.5425566286561</v>
       </c>
       <c r="D127" t="n">
-        <v>341.6916686197754</v>
+        <v>333.7191718320135</v>
       </c>
       <c r="E127" t="n">
-        <v>343.3849182128906</v>
+        <v>333.9457702636719</v>
       </c>
       <c r="F127" t="n">
-        <v>3197100</v>
+        <v>3893600</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -3745,25 +3745,25 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B128" t="n">
-        <v>340.9512279608855</v>
+        <v>336.6651978613972</v>
       </c>
       <c r="C128" t="n">
-        <v>343.5425566286561</v>
+        <v>338.3697677547303</v>
       </c>
       <c r="D128" t="n">
-        <v>333.7191718320135</v>
+        <v>333.0590172641502</v>
       </c>
       <c r="E128" t="n">
-        <v>333.9457702636719</v>
+        <v>334.0443115234375</v>
       </c>
       <c r="F128" t="n">
-        <v>3893600</v>
+        <v>2531900</v>
       </c>
       <c r="G128" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B129" t="n">
-        <v>336.6651978613972</v>
+        <v>337.4041886890553</v>
       </c>
       <c r="C129" t="n">
-        <v>338.3697677547303</v>
+        <v>340.1630007521627</v>
       </c>
       <c r="D129" t="n">
-        <v>333.0590172641502</v>
+        <v>335.6405034404279</v>
       </c>
       <c r="E129" t="n">
-        <v>334.0443115234375</v>
+        <v>337.5421142578125</v>
       </c>
       <c r="F129" t="n">
-        <v>2531900</v>
+        <v>3194400</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B130" t="n">
-        <v>337.4041886890553</v>
+        <v>339.81816704201</v>
       </c>
       <c r="C130" t="n">
-        <v>340.1630007521627</v>
+        <v>341.6803576413574</v>
       </c>
       <c r="D130" t="n">
-        <v>335.6405034404279</v>
+        <v>335.9262425125186</v>
       </c>
       <c r="E130" t="n">
-        <v>337.5421142578125</v>
+        <v>336.4090270996094</v>
       </c>
       <c r="F130" t="n">
-        <v>3194400</v>
+        <v>3075900</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B131" t="n">
-        <v>339.81816704201</v>
+        <v>333.6206668009991</v>
       </c>
       <c r="C131" t="n">
-        <v>341.6803576413574</v>
+        <v>334.8030019580219</v>
       </c>
       <c r="D131" t="n">
-        <v>335.9262425125186</v>
+        <v>325.2850851722408</v>
       </c>
       <c r="E131" t="n">
-        <v>336.4090270996094</v>
+        <v>326.0634460449219</v>
       </c>
       <c r="F131" t="n">
-        <v>3075900</v>
+        <v>3592200</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B132" t="n">
-        <v>333.6206668009991</v>
+        <v>324.1224241388957</v>
       </c>
       <c r="C132" t="n">
-        <v>334.8030019580219</v>
+        <v>325.3737672197113</v>
       </c>
       <c r="D132" t="n">
-        <v>325.2850851722408</v>
+        <v>319.8561127917808</v>
       </c>
       <c r="E132" t="n">
-        <v>326.0634460449219</v>
+        <v>323.3834533691406</v>
       </c>
       <c r="F132" t="n">
-        <v>3592200</v>
+        <v>3845400</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B133" t="n">
-        <v>324.1224241388957</v>
+        <v>322.9302020886868</v>
       </c>
       <c r="C133" t="n">
-        <v>325.3737672197113</v>
+        <v>325.3737427416146</v>
       </c>
       <c r="D133" t="n">
-        <v>319.8561127917808</v>
+        <v>315.5503575119392</v>
       </c>
       <c r="E133" t="n">
-        <v>323.3834533691406</v>
+        <v>316.0331420898438</v>
       </c>
       <c r="F133" t="n">
-        <v>3845400</v>
+        <v>9672200</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B134" t="n">
-        <v>322.9302020886868</v>
+        <v>327.1078416794463</v>
       </c>
       <c r="C134" t="n">
-        <v>325.3737427416146</v>
+        <v>329.7977059156196</v>
       </c>
       <c r="D134" t="n">
-        <v>315.5503575119392</v>
+        <v>323.3834304664039</v>
       </c>
       <c r="E134" t="n">
-        <v>316.0331420898438</v>
+        <v>326.0338745117188</v>
       </c>
       <c r="F134" t="n">
-        <v>9672200</v>
+        <v>5806300</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B135" t="n">
-        <v>327.1078416794463</v>
+        <v>321.1074278121778</v>
       </c>
       <c r="C135" t="n">
-        <v>329.7977059156196</v>
+        <v>327.6300717030042</v>
       </c>
       <c r="D135" t="n">
-        <v>323.3834304664039</v>
+        <v>318.2697752275627</v>
       </c>
       <c r="E135" t="n">
-        <v>326.0338745117188</v>
+        <v>326.0437622070312</v>
       </c>
       <c r="F135" t="n">
-        <v>5806300</v>
+        <v>4566400</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B136" t="n">
-        <v>321.1074278121778</v>
+        <v>330.0735818610078</v>
       </c>
       <c r="C136" t="n">
-        <v>327.6300717030042</v>
+        <v>332.2313787270356</v>
       </c>
       <c r="D136" t="n">
-        <v>318.2697752275627</v>
+        <v>322.1813651025556</v>
       </c>
       <c r="E136" t="n">
-        <v>326.0437622070312</v>
+        <v>327.6202087402344</v>
       </c>
       <c r="F136" t="n">
-        <v>4566400</v>
+        <v>4397800</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B137" t="n">
-        <v>330.0735818610078</v>
+        <v>326.5659345775528</v>
       </c>
       <c r="C137" t="n">
-        <v>332.2313787270356</v>
+        <v>329.2065159991698</v>
       </c>
       <c r="D137" t="n">
-        <v>322.1813651025556</v>
+        <v>321.7872513641968</v>
       </c>
       <c r="E137" t="n">
-        <v>327.6202087402344</v>
+        <v>323.6001892089844</v>
       </c>
       <c r="F137" t="n">
-        <v>4397800</v>
+        <v>3448400</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B138" t="n">
-        <v>326.5659345775528</v>
+        <v>322.6838998401017</v>
       </c>
       <c r="C138" t="n">
-        <v>329.2065159991698</v>
+        <v>322.7233200333912</v>
       </c>
       <c r="D138" t="n">
-        <v>321.7872513641968</v>
+        <v>316.0233004076466</v>
       </c>
       <c r="E138" t="n">
-        <v>323.6001892089844</v>
+        <v>316.919921875</v>
       </c>
       <c r="F138" t="n">
-        <v>3448400</v>
+        <v>3977400</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B139" t="n">
-        <v>322.6838998401017</v>
+        <v>320.9300608492875</v>
       </c>
       <c r="C139" t="n">
-        <v>322.7233200333912</v>
+        <v>323.1666680872671</v>
       </c>
       <c r="D139" t="n">
-        <v>316.0233004076466</v>
+        <v>317.8362223118503</v>
       </c>
       <c r="E139" t="n">
-        <v>316.919921875</v>
+        <v>318.7427062988281</v>
       </c>
       <c r="F139" t="n">
-        <v>3977400</v>
+        <v>4066000</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B140" t="n">
-        <v>320.9300608492875</v>
+        <v>323.6593250096307</v>
       </c>
       <c r="C140" t="n">
-        <v>323.1666680872671</v>
+        <v>326.5659553121756</v>
       </c>
       <c r="D140" t="n">
-        <v>317.8362223118503</v>
+        <v>318.6540430408731</v>
       </c>
       <c r="E140" t="n">
-        <v>318.7427062988281</v>
+        <v>324.053466796875</v>
       </c>
       <c r="F140" t="n">
-        <v>4066000</v>
+        <v>5749100</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B141" t="n">
-        <v>323.6593250096307</v>
+        <v>324.5264147036482</v>
       </c>
       <c r="C141" t="n">
-        <v>326.5659553121756</v>
+        <v>328.1917111081323</v>
       </c>
       <c r="D141" t="n">
-        <v>318.6540430408731</v>
+        <v>322.9893578310064</v>
       </c>
       <c r="E141" t="n">
-        <v>324.053466796875</v>
+        <v>324.713623046875</v>
       </c>
       <c r="F141" t="n">
-        <v>5749100</v>
+        <v>3386200</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B142" t="n">
-        <v>324.5264147036482</v>
+        <v>318.841238474905</v>
       </c>
       <c r="C142" t="n">
-        <v>328.1917111081323</v>
+        <v>321.5015150184395</v>
       </c>
       <c r="D142" t="n">
-        <v>322.9893578310064</v>
+        <v>313.9738822734865</v>
       </c>
       <c r="E142" t="n">
-        <v>324.713623046875</v>
+        <v>316.9002075195312</v>
       </c>
       <c r="F142" t="n">
-        <v>3386200</v>
+        <v>3732300</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B143" t="n">
-        <v>318.841238474905</v>
+        <v>314.9985972226668</v>
       </c>
       <c r="C143" t="n">
-        <v>321.5015150184395</v>
+        <v>321.875932137731</v>
       </c>
       <c r="D143" t="n">
-        <v>313.9738822734865</v>
+        <v>314.2300688775543</v>
       </c>
       <c r="E143" t="n">
-        <v>316.9002075195312</v>
+        <v>321.8463745117188</v>
       </c>
       <c r="F143" t="n">
-        <v>3732300</v>
+        <v>2448300</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B144" t="n">
-        <v>314.9985972226668</v>
+        <v>318.2500813990391</v>
       </c>
       <c r="C144" t="n">
-        <v>321.875932137731</v>
+        <v>319.6097924401727</v>
       </c>
       <c r="D144" t="n">
-        <v>314.2300688775543</v>
+        <v>310.673165290877</v>
       </c>
       <c r="E144" t="n">
-        <v>321.8463745117188</v>
+        <v>314.082275390625</v>
       </c>
       <c r="F144" t="n">
-        <v>2448300</v>
+        <v>4661600</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B145" t="n">
-        <v>318.2500813990391</v>
+        <v>328.3591748751156</v>
       </c>
       <c r="C145" t="n">
-        <v>319.6097924401727</v>
+        <v>333.7979883682909</v>
       </c>
       <c r="D145" t="n">
-        <v>310.673165290877</v>
+        <v>327.3640180499997</v>
       </c>
       <c r="E145" t="n">
-        <v>314.082275390625</v>
+        <v>331.2165222167969</v>
       </c>
       <c r="F145" t="n">
-        <v>4661600</v>
+        <v>4610600</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B146" t="n">
-        <v>328.3591748751156</v>
+        <v>326.388616523007</v>
       </c>
       <c r="C146" t="n">
-        <v>333.7979883682909</v>
+        <v>335.5617045306175</v>
       </c>
       <c r="D146" t="n">
-        <v>327.3640180499997</v>
+        <v>323.6199418005998</v>
       </c>
       <c r="E146" t="n">
-        <v>331.2165222167969</v>
+        <v>334.5862426757812</v>
       </c>
       <c r="F146" t="n">
-        <v>4610600</v>
+        <v>3002000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B147" t="n">
-        <v>326.388616523007</v>
+        <v>336.0248127567512</v>
       </c>
       <c r="C147" t="n">
-        <v>335.5617045306175</v>
+        <v>336.2120210994593</v>
       </c>
       <c r="D147" t="n">
-        <v>323.6199418005998</v>
+        <v>330.8717121868362</v>
       </c>
       <c r="E147" t="n">
-        <v>334.5862426757812</v>
+        <v>332.3792114257812</v>
       </c>
       <c r="F147" t="n">
-        <v>3002000</v>
+        <v>3208300</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B148" t="n">
-        <v>336.0248127567512</v>
+        <v>330.6056562428727</v>
       </c>
       <c r="C148" t="n">
-        <v>336.2120210994593</v>
+        <v>336.4188865710081</v>
       </c>
       <c r="D148" t="n">
-        <v>330.8717121868362</v>
+        <v>327.0487282012957</v>
       </c>
       <c r="E148" t="n">
-        <v>332.3792114257812</v>
+        <v>336.1430053710938</v>
       </c>
       <c r="F148" t="n">
-        <v>3208300</v>
+        <v>3741200</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B149" t="n">
-        <v>330.6056562428727</v>
+        <v>335.9853517224209</v>
       </c>
       <c r="C149" t="n">
-        <v>336.4188865710081</v>
+        <v>337.7194792888092</v>
       </c>
       <c r="D149" t="n">
-        <v>327.0487282012957</v>
+        <v>333.3644653118732</v>
       </c>
       <c r="E149" t="n">
-        <v>336.1430053710938</v>
+        <v>337.6701965332031</v>
       </c>
       <c r="F149" t="n">
-        <v>3741200</v>
+        <v>2882500</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B150" t="n">
-        <v>335.9853517224209</v>
+        <v>336.8228540004552</v>
       </c>
       <c r="C150" t="n">
-        <v>337.7194792888092</v>
+        <v>337.2366607575258</v>
       </c>
       <c r="D150" t="n">
-        <v>333.3644653118732</v>
+        <v>331.6697541162465</v>
       </c>
       <c r="E150" t="n">
-        <v>337.6701965332031</v>
+        <v>333.9260864257812</v>
       </c>
       <c r="F150" t="n">
-        <v>2882500</v>
+        <v>3365200</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B151" t="n">
-        <v>336.8228540004552</v>
+        <v>334.9902184465357</v>
       </c>
       <c r="C151" t="n">
-        <v>337.2366607575258</v>
+        <v>336.9509746615948</v>
       </c>
       <c r="D151" t="n">
-        <v>331.6697541162465</v>
+        <v>331.7387590995254</v>
       </c>
       <c r="E151" t="n">
-        <v>333.9260864257812</v>
+        <v>332.1919860839844</v>
       </c>
       <c r="F151" t="n">
-        <v>3365200</v>
+        <v>2856700</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B152" t="n">
-        <v>334.9902184465357</v>
+        <v>337.7983122720913</v>
       </c>
       <c r="C152" t="n">
-        <v>336.9509746615948</v>
+        <v>346.8433072133841</v>
       </c>
       <c r="D152" t="n">
-        <v>331.7387590995254</v>
+        <v>337.7983122720913</v>
       </c>
       <c r="E152" t="n">
-        <v>332.1919860839844</v>
+        <v>344.2618408203125</v>
       </c>
       <c r="F152" t="n">
-        <v>2856700</v>
+        <v>4930400</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B153" t="n">
-        <v>337.7983122720913</v>
+        <v>343.2174366312315</v>
       </c>
       <c r="C153" t="n">
-        <v>346.8433072133841</v>
+        <v>346.0058365319325</v>
       </c>
       <c r="D153" t="n">
-        <v>337.7983122720913</v>
+        <v>338.5668460102951</v>
       </c>
       <c r="E153" t="n">
-        <v>344.2618408203125</v>
+        <v>345.8284606933594</v>
       </c>
       <c r="F153" t="n">
-        <v>4930400</v>
+        <v>3260900</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B154" t="n">
-        <v>343.2174366312315</v>
+        <v>347.7399078982703</v>
       </c>
       <c r="C154" t="n">
-        <v>346.0058365319325</v>
+        <v>348.350785549426</v>
       </c>
       <c r="D154" t="n">
-        <v>338.5668460102951</v>
+        <v>337.9263851511736</v>
       </c>
       <c r="E154" t="n">
-        <v>345.8284606933594</v>
+        <v>338.8624267578125</v>
       </c>
       <c r="F154" t="n">
-        <v>3260900</v>
+        <v>3081000</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B155" t="n">
-        <v>347.7399078982703</v>
+        <v>338.8919874460811</v>
       </c>
       <c r="C155" t="n">
-        <v>348.350785549426</v>
+        <v>340.1629954470494</v>
       </c>
       <c r="D155" t="n">
-        <v>337.9263851511736</v>
+        <v>332.950664003466</v>
       </c>
       <c r="E155" t="n">
-        <v>338.8624267578125</v>
+        <v>334.5074157714844</v>
       </c>
       <c r="F155" t="n">
-        <v>3081000</v>
+        <v>2855800</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B156" t="n">
-        <v>338.8919874460811</v>
+        <v>334.5074474516935</v>
       </c>
       <c r="C156" t="n">
-        <v>340.1629954470494</v>
+        <v>335.81787576814</v>
       </c>
       <c r="D156" t="n">
-        <v>332.950664003466</v>
+        <v>331.9259809451064</v>
       </c>
       <c r="E156" t="n">
-        <v>334.5074157714844</v>
+        <v>335.1577453613281</v>
       </c>
       <c r="F156" t="n">
-        <v>2855800</v>
+        <v>2712400</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B157" t="n">
-        <v>334.5074474516935</v>
+        <v>332.9112571246521</v>
       </c>
       <c r="C157" t="n">
-        <v>335.81787576814</v>
+        <v>335.2660949665313</v>
       </c>
       <c r="D157" t="n">
-        <v>331.9259809451064</v>
+        <v>329.758303202367</v>
       </c>
       <c r="E157" t="n">
-        <v>335.1577453613281</v>
+        <v>330.9505310058594</v>
       </c>
       <c r="F157" t="n">
-        <v>2712400</v>
+        <v>3255900</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B158" t="n">
-        <v>332.9112571246521</v>
+        <v>329.5612640898174</v>
       </c>
       <c r="C158" t="n">
-        <v>335.2660949665313</v>
+        <v>332.4186116830558</v>
       </c>
       <c r="D158" t="n">
-        <v>329.758303202367</v>
+        <v>327.2556789255299</v>
       </c>
       <c r="E158" t="n">
-        <v>330.9505310058594</v>
+        <v>327.4132995605469</v>
       </c>
       <c r="F158" t="n">
-        <v>3255900</v>
+        <v>3282900</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B159" t="n">
-        <v>329.5612640898174</v>
+        <v>329.5316980954363</v>
       </c>
       <c r="C159" t="n">
-        <v>332.4186116830558</v>
+        <v>330.9899144482985</v>
       </c>
       <c r="D159" t="n">
-        <v>327.2556789255299</v>
+        <v>322.5459348903251</v>
       </c>
       <c r="E159" t="n">
-        <v>327.4132995605469</v>
+        <v>324.220947265625</v>
       </c>
       <c r="F159" t="n">
-        <v>3282900</v>
+        <v>4279300</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B160" t="n">
-        <v>329.5316980954363</v>
+        <v>320.8709611177203</v>
       </c>
       <c r="C160" t="n">
-        <v>330.9899144482985</v>
+        <v>321.0483068839262</v>
       </c>
       <c r="D160" t="n">
-        <v>322.5459348903251</v>
+        <v>314.3581498388285</v>
       </c>
       <c r="E160" t="n">
-        <v>324.220947265625</v>
+        <v>318.0628662109375</v>
       </c>
       <c r="F160" t="n">
-        <v>4279300</v>
+        <v>4150000</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B161" t="n">
-        <v>320.8709611177203</v>
+        <v>317.5012539357068</v>
       </c>
       <c r="C161" t="n">
-        <v>321.0483068839262</v>
+        <v>325.2653785233867</v>
       </c>
       <c r="D161" t="n">
-        <v>314.3581498388285</v>
+        <v>317.5012539357068</v>
       </c>
       <c r="E161" t="n">
-        <v>318.0628662109375</v>
+        <v>323.9647827148438</v>
       </c>
       <c r="F161" t="n">
-        <v>4150000</v>
+        <v>4317900</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B162" t="n">
-        <v>317.5012539357068</v>
+        <v>325.245658285994</v>
       </c>
       <c r="C162" t="n">
-        <v>325.2653785233867</v>
+        <v>325.6594650583568</v>
       </c>
       <c r="D162" t="n">
-        <v>317.5012539357068</v>
+        <v>318.6047541787617</v>
       </c>
       <c r="E162" t="n">
-        <v>323.9647827148438</v>
+        <v>319.1171264648438</v>
       </c>
       <c r="F162" t="n">
-        <v>4317900</v>
+        <v>3865300</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B163" t="n">
-        <v>325.245658285994</v>
+        <v>317.3435693878982</v>
       </c>
       <c r="C163" t="n">
-        <v>325.6594650583568</v>
+        <v>317.3435693878982</v>
       </c>
       <c r="D163" t="n">
-        <v>318.6047541787617</v>
+        <v>307.6680023826615</v>
       </c>
       <c r="E163" t="n">
-        <v>319.1171264648438</v>
+        <v>307.8256530761719</v>
       </c>
       <c r="F163" t="n">
-        <v>3865300</v>
+        <v>6396100</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B164" t="n">
-        <v>317.3435693878982</v>
+        <v>308.8011039225745</v>
       </c>
       <c r="C164" t="n">
-        <v>317.3435693878982</v>
+        <v>312.959047256485</v>
       </c>
       <c r="D164" t="n">
-        <v>307.6680023826615</v>
+        <v>305.8353583254913</v>
       </c>
       <c r="E164" t="n">
-        <v>307.8256530761719</v>
+        <v>310.7815551757812</v>
       </c>
       <c r="F164" t="n">
-        <v>6396100</v>
+        <v>6391400</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B165" t="n">
-        <v>308.8011039225745</v>
+        <v>317.2253492112466</v>
       </c>
       <c r="C165" t="n">
-        <v>312.959047256485</v>
+        <v>320.4571133614208</v>
       </c>
       <c r="D165" t="n">
-        <v>305.8353583254913</v>
+        <v>314.6537454823368</v>
       </c>
       <c r="E165" t="n">
-        <v>310.7815551757812</v>
+        <v>318.29931640625</v>
       </c>
       <c r="F165" t="n">
-        <v>6391400</v>
+        <v>5455900</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B166" t="n">
-        <v>317.2253492112466</v>
+        <v>320.2304978152761</v>
       </c>
       <c r="C166" t="n">
-        <v>320.4571133614208</v>
+        <v>322.6740083417755</v>
       </c>
       <c r="D166" t="n">
-        <v>314.6537454823368</v>
+        <v>317.6884217799922</v>
       </c>
       <c r="E166" t="n">
-        <v>318.29931640625</v>
+        <v>317.8953552246094</v>
       </c>
       <c r="F166" t="n">
-        <v>5455900</v>
+        <v>4411700</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B167" t="n">
-        <v>320.2304978152761</v>
+        <v>317.9347470211017</v>
       </c>
       <c r="C167" t="n">
-        <v>322.6740083417755</v>
+        <v>319.2353426707153</v>
       </c>
       <c r="D167" t="n">
-        <v>317.6884217799922</v>
+        <v>312.1412119171815</v>
       </c>
       <c r="E167" t="n">
-        <v>317.8953552246094</v>
+        <v>312.7816772460938</v>
       </c>
       <c r="F167" t="n">
-        <v>4411700</v>
+        <v>4995500</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B168" t="n">
-        <v>317.9347470211017</v>
+        <v>311.8456552875821</v>
       </c>
       <c r="C168" t="n">
-        <v>319.2353426707153</v>
+        <v>312.4565329608662</v>
       </c>
       <c r="D168" t="n">
-        <v>312.1412119171815</v>
+        <v>305.1554983709962</v>
       </c>
       <c r="E168" t="n">
-        <v>312.7816772460938</v>
+        <v>306.8206481933594</v>
       </c>
       <c r="F168" t="n">
-        <v>4995500</v>
+        <v>4335700</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B169" t="n">
-        <v>311.8456552875821</v>
+        <v>308.6237547613812</v>
       </c>
       <c r="C169" t="n">
-        <v>312.4565329608662</v>
+        <v>310.150948950067</v>
       </c>
       <c r="D169" t="n">
-        <v>305.1554983709962</v>
+        <v>304.5643168514869</v>
       </c>
       <c r="E169" t="n">
-        <v>306.8206481933594</v>
+        <v>305.8944702148438</v>
       </c>
       <c r="F169" t="n">
-        <v>4335700</v>
+        <v>4225700</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B170" t="n">
-        <v>308.6237547613812</v>
+        <v>303.0863866663159</v>
       </c>
       <c r="C170" t="n">
-        <v>310.150948950067</v>
+        <v>303.1652270544281</v>
       </c>
       <c r="D170" t="n">
-        <v>304.5643168514869</v>
+        <v>294.8690352302997</v>
       </c>
       <c r="E170" t="n">
-        <v>305.8944702148438</v>
+        <v>298.1007995605469</v>
       </c>
       <c r="F170" t="n">
-        <v>4225700</v>
+        <v>6307800</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B171" t="n">
-        <v>303.0863866663159</v>
+        <v>300.5739097413743</v>
       </c>
       <c r="C171" t="n">
-        <v>303.1652270544281</v>
+        <v>301.4803938271338</v>
       </c>
       <c r="D171" t="n">
-        <v>294.8690352302997</v>
+        <v>296.9874537315239</v>
       </c>
       <c r="E171" t="n">
-        <v>298.1007995605469</v>
+        <v>299.8743591308594</v>
       </c>
       <c r="F171" t="n">
-        <v>6307800</v>
+        <v>5072600</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B172" t="n">
-        <v>300.5739097413743</v>
+        <v>295.8937302385283</v>
       </c>
       <c r="C172" t="n">
-        <v>301.4803938271338</v>
+        <v>298.4751965058313</v>
       </c>
       <c r="D172" t="n">
-        <v>296.9874537315239</v>
+        <v>292.5141779899232</v>
       </c>
       <c r="E172" t="n">
-        <v>299.8743591308594</v>
+        <v>293.1349182128906</v>
       </c>
       <c r="F172" t="n">
-        <v>5072600</v>
+        <v>6121500</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B173" t="n">
-        <v>295.8937302385283</v>
+        <v>294.8493301065311</v>
       </c>
       <c r="C173" t="n">
-        <v>298.4751965058313</v>
+        <v>299.3127122467453</v>
       </c>
       <c r="D173" t="n">
-        <v>292.5141779899232</v>
+        <v>292.9279941234309</v>
       </c>
       <c r="E173" t="n">
-        <v>293.1349182128906</v>
+        <v>295.4010925292969</v>
       </c>
       <c r="F173" t="n">
-        <v>6121500</v>
+        <v>6366100</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B174" t="n">
-        <v>294.8493301065311</v>
+        <v>287.5778334831647</v>
       </c>
       <c r="C174" t="n">
-        <v>299.3127122467453</v>
+        <v>298.7313718247998</v>
       </c>
       <c r="D174" t="n">
-        <v>292.9279941234309</v>
+        <v>284.84857918279</v>
       </c>
       <c r="E174" t="n">
-        <v>295.4010925292969</v>
+        <v>297.9924011230469</v>
       </c>
       <c r="F174" t="n">
-        <v>6366100</v>
+        <v>8692500</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B175" t="n">
-        <v>287.5778334831647</v>
+        <v>296.6327042526405</v>
       </c>
       <c r="C175" t="n">
-        <v>298.7313718247998</v>
+        <v>306.4363947204983</v>
       </c>
       <c r="D175" t="n">
-        <v>284.84857918279</v>
+        <v>292.307277842878</v>
       </c>
       <c r="E175" t="n">
-        <v>297.9924011230469</v>
+        <v>306.0126953125</v>
       </c>
       <c r="F175" t="n">
-        <v>8692500</v>
+        <v>5810900</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B176" t="n">
-        <v>296.6327042526405</v>
+        <v>301.8547523557064</v>
       </c>
       <c r="C176" t="n">
-        <v>306.4363947204983</v>
+        <v>309.3725528012548</v>
       </c>
       <c r="D176" t="n">
-        <v>292.307277842878</v>
+        <v>299.9038888531578</v>
       </c>
       <c r="E176" t="n">
-        <v>306.0126953125</v>
+        <v>309.1656494140625</v>
       </c>
       <c r="F176" t="n">
-        <v>5810900</v>
+        <v>4516600</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B177" t="n">
-        <v>301.8547523557064</v>
+        <v>309.8750586089163</v>
       </c>
       <c r="C177" t="n">
-        <v>309.3725528012548</v>
+        <v>310.3282855694948</v>
       </c>
       <c r="D177" t="n">
-        <v>299.9038888531578</v>
+        <v>306.8797555054846</v>
       </c>
       <c r="E177" t="n">
-        <v>309.1656494140625</v>
+        <v>308.4660949707031</v>
       </c>
       <c r="F177" t="n">
-        <v>4516600</v>
+        <v>2963800</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B178" t="n">
-        <v>309.8750586089163</v>
+        <v>310.4268474452446</v>
       </c>
       <c r="C178" t="n">
-        <v>310.3282855694948</v>
+        <v>312.1314175610734</v>
       </c>
       <c r="D178" t="n">
-        <v>306.8797555054846</v>
+        <v>304.4165456653147</v>
       </c>
       <c r="E178" t="n">
-        <v>308.4660949707031</v>
+        <v>305.9733276367188</v>
       </c>
       <c r="F178" t="n">
-        <v>2963800</v>
+        <v>6978200</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B179" t="n">
-        <v>310.4268474452446</v>
+        <v>310.1213630819786</v>
       </c>
       <c r="C179" t="n">
-        <v>312.1314175610734</v>
+        <v>316.2794521026693</v>
       </c>
       <c r="D179" t="n">
-        <v>304.4165456653147</v>
+        <v>309.8849020855982</v>
       </c>
       <c r="E179" t="n">
-        <v>305.9733276367188</v>
+        <v>313.17578125</v>
       </c>
       <c r="F179" t="n">
-        <v>6978200</v>
+        <v>5990100</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B180" t="n">
-        <v>310.1213630819786</v>
+        <v>312.7817028577755</v>
       </c>
       <c r="C180" t="n">
-        <v>316.2794521026693</v>
+        <v>317.1465496037087</v>
       </c>
       <c r="D180" t="n">
-        <v>309.8849020855982</v>
+        <v>310.5253703811763</v>
       </c>
       <c r="E180" t="n">
-        <v>313.17578125</v>
+        <v>316.4863891601562</v>
       </c>
       <c r="F180" t="n">
-        <v>5990100</v>
+        <v>6818900</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B181" t="n">
-        <v>312.7817028577755</v>
+        <v>315.7671367684214</v>
       </c>
       <c r="C181" t="n">
-        <v>317.1465496037087</v>
+        <v>317.3633087672889</v>
       </c>
       <c r="D181" t="n">
-        <v>310.5253703811763</v>
+        <v>312.3383016854047</v>
       </c>
       <c r="E181" t="n">
-        <v>316.4863891601562</v>
+        <v>312.4762573242188</v>
       </c>
       <c r="F181" t="n">
-        <v>6818900</v>
+        <v>6963300</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B182" t="n">
-        <v>315.7671367684214</v>
+        <v>310.4958029229232</v>
       </c>
       <c r="C182" t="n">
-        <v>317.3633087672889</v>
+        <v>311.2446362258477</v>
       </c>
       <c r="D182" t="n">
-        <v>312.3383016854047</v>
+        <v>303.1652107990409</v>
       </c>
       <c r="E182" t="n">
-        <v>312.4762573242188</v>
+        <v>306.12109375</v>
       </c>
       <c r="F182" t="n">
-        <v>6963300</v>
+        <v>4544200</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B183" t="n">
-        <v>310.4958029229232</v>
+        <v>305.4215416998635</v>
       </c>
       <c r="C183" t="n">
-        <v>311.2446362258477</v>
+        <v>307.6088962755514</v>
       </c>
       <c r="D183" t="n">
-        <v>303.1652107990409</v>
+        <v>304.0322731114999</v>
       </c>
       <c r="E183" t="n">
-        <v>306.12109375</v>
+        <v>306.9388732910156</v>
       </c>
       <c r="F183" t="n">
-        <v>4544200</v>
+        <v>4310000</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B184" t="n">
-        <v>305.4215416998635</v>
+        <v>303.4115246580221</v>
       </c>
       <c r="C184" t="n">
-        <v>307.6088962755514</v>
+        <v>308.9094535404009</v>
       </c>
       <c r="D184" t="n">
-        <v>304.0322731114999</v>
+        <v>302.6035761274661</v>
       </c>
       <c r="E184" t="n">
-        <v>306.9388732910156</v>
+        <v>308.3675537109375</v>
       </c>
       <c r="F184" t="n">
-        <v>4310000</v>
+        <v>4328300</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,25 +5227,25 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B185" t="n">
-        <v>303.4115246580221</v>
+        <v>315.5049467263879</v>
       </c>
       <c r="C185" t="n">
-        <v>308.9094535404009</v>
+        <v>318.403599213189</v>
       </c>
       <c r="D185" t="n">
-        <v>302.6035761274661</v>
+        <v>305.8560507855353</v>
       </c>
       <c r="E185" t="n">
-        <v>308.3675537109375</v>
+        <v>307.6826171875</v>
       </c>
       <c r="F185" t="n">
-        <v>4328300</v>
+        <v>4558600</v>
       </c>
       <c r="G185" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5253,25 +5253,25 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B186" t="n">
-        <v>315.5049467263879</v>
+        <v>308.5561528759146</v>
       </c>
       <c r="C186" t="n">
-        <v>318.403599213189</v>
+        <v>311.7525986238699</v>
       </c>
       <c r="D186" t="n">
-        <v>305.8560507855353</v>
+        <v>306.3722648476684</v>
       </c>
       <c r="E186" t="n">
-        <v>307.6826171875</v>
+        <v>308.5065307617188</v>
       </c>
       <c r="F186" t="n">
-        <v>4558600</v>
+        <v>3946300</v>
       </c>
       <c r="G186" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B187" t="n">
-        <v>308.5561528759146</v>
+        <v>306.6204514929628</v>
       </c>
       <c r="C187" t="n">
-        <v>311.7525986238699</v>
+        <v>311.4746638676563</v>
       </c>
       <c r="D187" t="n">
-        <v>306.3722648476684</v>
+        <v>304.8236946299612</v>
       </c>
       <c r="E187" t="n">
-        <v>308.5065307617188</v>
+        <v>307.4443664550781</v>
       </c>
       <c r="F187" t="n">
-        <v>3946300</v>
+        <v>4381800</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B188" t="n">
-        <v>306.6204514929628</v>
+        <v>309.0723663566284</v>
       </c>
       <c r="C188" t="n">
-        <v>311.4746638676563</v>
+        <v>320.5279554969379</v>
       </c>
       <c r="D188" t="n">
-        <v>304.8236946299612</v>
+        <v>308.000249988811</v>
       </c>
       <c r="E188" t="n">
-        <v>307.4443664550781</v>
+        <v>318.9793395996094</v>
       </c>
       <c r="F188" t="n">
-        <v>4381800</v>
+        <v>4875300</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B189" t="n">
-        <v>309.0723663566284</v>
+        <v>320.9051596578416</v>
       </c>
       <c r="C189" t="n">
-        <v>320.5279554969379</v>
+        <v>321.6298303667879</v>
       </c>
       <c r="D189" t="n">
-        <v>308.000249988811</v>
+        <v>316.4678580086006</v>
       </c>
       <c r="E189" t="n">
-        <v>318.9793395996094</v>
+        <v>316.5870056152344</v>
       </c>
       <c r="F189" t="n">
-        <v>4875300</v>
+        <v>4823800</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B190" t="n">
-        <v>320.9051596578416</v>
+        <v>319.9323340788724</v>
       </c>
       <c r="C190" t="n">
-        <v>321.6298303667879</v>
+        <v>324.6376494749074</v>
       </c>
       <c r="D190" t="n">
-        <v>316.4678580086006</v>
+        <v>316.2196730066971</v>
       </c>
       <c r="E190" t="n">
-        <v>316.5870056152344</v>
+        <v>323.6251220703125</v>
       </c>
       <c r="F190" t="n">
-        <v>4823800</v>
+        <v>4656600</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B191" t="n">
-        <v>319.9323340788724</v>
+        <v>326.0969127055492</v>
       </c>
       <c r="C191" t="n">
-        <v>324.6376494749074</v>
+        <v>328.598467157331</v>
       </c>
       <c r="D191" t="n">
-        <v>316.2196730066971</v>
+        <v>322.9104034108394</v>
       </c>
       <c r="E191" t="n">
-        <v>323.6251220703125</v>
+        <v>325.9877319335938</v>
       </c>
       <c r="F191" t="n">
-        <v>4656600</v>
+        <v>3649000</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B192" t="n">
-        <v>326.0969127055492</v>
+        <v>331.3184370072605</v>
       </c>
       <c r="C192" t="n">
-        <v>328.598467157331</v>
+        <v>335.5274102103883</v>
       </c>
       <c r="D192" t="n">
-        <v>322.9104034108394</v>
+        <v>327.1293065910854</v>
       </c>
       <c r="E192" t="n">
-        <v>325.9877319335938</v>
+        <v>327.4072570800781</v>
       </c>
       <c r="F192" t="n">
-        <v>3649000</v>
+        <v>4695000</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B193" t="n">
-        <v>331.3184370072605</v>
+        <v>329.4819549089526</v>
       </c>
       <c r="C193" t="n">
-        <v>335.5274102103883</v>
+        <v>335.7954145326594</v>
       </c>
       <c r="D193" t="n">
-        <v>327.1293065910854</v>
+        <v>327.337752500619</v>
       </c>
       <c r="E193" t="n">
-        <v>327.4072570800781</v>
+        <v>334.6240539550781</v>
       </c>
       <c r="F193" t="n">
-        <v>4695000</v>
+        <v>5131500</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B194" t="n">
-        <v>329.4819549089526</v>
+        <v>333.5519799826949</v>
       </c>
       <c r="C194" t="n">
-        <v>335.7954145326594</v>
+        <v>338.6543633465824</v>
       </c>
       <c r="D194" t="n">
-        <v>327.337752500619</v>
+        <v>323.7839666314997</v>
       </c>
       <c r="E194" t="n">
-        <v>334.6240539550781</v>
+        <v>325.0843811035156</v>
       </c>
       <c r="F194" t="n">
-        <v>5131500</v>
+        <v>6085400</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B195" t="n">
-        <v>333.5519799826949</v>
+        <v>329.2735121638814</v>
       </c>
       <c r="C195" t="n">
-        <v>338.6543633465824</v>
+        <v>335.5472561594589</v>
       </c>
       <c r="D195" t="n">
-        <v>323.7839666314997</v>
+        <v>328.4793462633244</v>
       </c>
       <c r="E195" t="n">
-        <v>325.0843811035156</v>
+        <v>331.8346252441406</v>
       </c>
       <c r="F195" t="n">
-        <v>6085400</v>
+        <v>10604400</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B196" t="n">
-        <v>329.2735121638814</v>
+        <v>327.585930781475</v>
       </c>
       <c r="C196" t="n">
-        <v>335.5472561594589</v>
+        <v>329.30328611244</v>
       </c>
       <c r="D196" t="n">
-        <v>328.4793462633244</v>
+        <v>323.9527013683971</v>
       </c>
       <c r="E196" t="n">
-        <v>331.8346252441406</v>
+        <v>324.2306518554688</v>
       </c>
       <c r="F196" t="n">
-        <v>10604400</v>
+        <v>4713600</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B197" t="n">
-        <v>327.585930781475</v>
+        <v>321.5007640397083</v>
       </c>
       <c r="C197" t="n">
-        <v>329.30328611244</v>
+        <v>326.6130837898613</v>
       </c>
       <c r="D197" t="n">
-        <v>323.9527013683971</v>
+        <v>319.3466553723836</v>
       </c>
       <c r="E197" t="n">
-        <v>324.2306518554688</v>
+        <v>322.0765380859375</v>
       </c>
       <c r="F197" t="n">
-        <v>4713600</v>
+        <v>4788000</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B198" t="n">
-        <v>321.5007640397083</v>
+        <v>326.7123600579221</v>
       </c>
       <c r="C198" t="n">
-        <v>326.6130837898613</v>
+        <v>340.4511116799111</v>
       </c>
       <c r="D198" t="n">
-        <v>319.3466553723836</v>
+        <v>325.3126710965327</v>
       </c>
       <c r="E198" t="n">
-        <v>322.0765380859375</v>
+        <v>340.3518371582031</v>
       </c>
       <c r="F198" t="n">
-        <v>4788000</v>
+        <v>6385000</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B199" t="n">
-        <v>326.7123600579221</v>
+        <v>339.7463135650192</v>
       </c>
       <c r="C199" t="n">
-        <v>340.4511116799111</v>
+        <v>346.0895828723475</v>
       </c>
       <c r="D199" t="n">
-        <v>325.3126710965327</v>
+        <v>339.3194664460809</v>
       </c>
       <c r="E199" t="n">
-        <v>340.3518371582031</v>
+        <v>342.4761962890625</v>
       </c>
       <c r="F199" t="n">
-        <v>6385000</v>
+        <v>6974100</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B200" t="n">
-        <v>339.7463135650192</v>
+        <v>345.3549840981078</v>
       </c>
       <c r="C200" t="n">
-        <v>346.0895828723475</v>
+        <v>347.9359702501276</v>
       </c>
       <c r="D200" t="n">
-        <v>339.3194664460809</v>
+        <v>343.3199926808538</v>
       </c>
       <c r="E200" t="n">
-        <v>342.4761962890625</v>
+        <v>346.3079528808594</v>
       </c>
       <c r="F200" t="n">
-        <v>6974100</v>
+        <v>7771700</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B201" t="n">
-        <v>345.3549840981078</v>
+        <v>346.307966117321</v>
       </c>
       <c r="C201" t="n">
-        <v>347.9359702501276</v>
+        <v>348.779771593463</v>
       </c>
       <c r="D201" t="n">
-        <v>343.3199926808538</v>
+        <v>343.0122759730193</v>
       </c>
       <c r="E201" t="n">
-        <v>346.3079528808594</v>
+        <v>348.2437133789062</v>
       </c>
       <c r="F201" t="n">
-        <v>7771700</v>
+        <v>5786500</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B202" t="n">
-        <v>346.307966117321</v>
+        <v>348.1245733949154</v>
       </c>
       <c r="C202" t="n">
-        <v>348.779771593463</v>
+        <v>350.9140147662578</v>
       </c>
       <c r="D202" t="n">
-        <v>343.0122759730193</v>
+        <v>344.7593579765289</v>
       </c>
       <c r="E202" t="n">
-        <v>348.2437133789062</v>
+        <v>350.1000061035156</v>
       </c>
       <c r="F202" t="n">
-        <v>5786500</v>
+        <v>4579000</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B203" t="n">
-        <v>348.1245733949154</v>
+        <v>351.3905430525372</v>
       </c>
       <c r="C203" t="n">
-        <v>350.9140147662578</v>
+        <v>354.507557275585</v>
       </c>
       <c r="D203" t="n">
-        <v>344.7593579765289</v>
+        <v>348.2734985351562</v>
       </c>
       <c r="E203" t="n">
-        <v>350.1000061035156</v>
+        <v>348.2734985351562</v>
       </c>
       <c r="F203" t="n">
-        <v>4579000</v>
+        <v>4041300</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B204" t="n">
-        <v>351.3905430525372</v>
+        <v>350.2588479333682</v>
       </c>
       <c r="C204" t="n">
-        <v>354.507557275585</v>
+        <v>355.5697168646199</v>
       </c>
       <c r="D204" t="n">
-        <v>348.2734985351562</v>
+        <v>345.1068121812833</v>
       </c>
       <c r="E204" t="n">
-        <v>348.2734985351562</v>
+        <v>355.2818298339844</v>
       </c>
       <c r="F204" t="n">
-        <v>4041300</v>
+        <v>3110500</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B205" t="n">
-        <v>350.2588479333682</v>
+        <v>355.2024317145021</v>
       </c>
       <c r="C205" t="n">
-        <v>355.5697168646199</v>
+        <v>356.2248957008094</v>
       </c>
       <c r="D205" t="n">
-        <v>345.1068121812833</v>
+        <v>343.2703427329958</v>
       </c>
       <c r="E205" t="n">
-        <v>355.2818298339844</v>
+        <v>348.0848693847656</v>
       </c>
       <c r="F205" t="n">
-        <v>3110500</v>
+        <v>4460800</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B206" t="n">
-        <v>355.2024317145021</v>
+        <v>352.4626117928308</v>
       </c>
       <c r="C206" t="n">
-        <v>356.2248957008094</v>
+        <v>352.8199940223038</v>
       </c>
       <c r="D206" t="n">
-        <v>343.2703427329958</v>
+        <v>341.9600214541982</v>
       </c>
       <c r="E206" t="n">
-        <v>348.0848693847656</v>
+        <v>342.6846618652344</v>
       </c>
       <c r="F206" t="n">
-        <v>4460800</v>
+        <v>3592800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B207" t="n">
-        <v>352.4626117928308</v>
+        <v>335.5174656966423</v>
       </c>
       <c r="C207" t="n">
-        <v>352.8199940223038</v>
+        <v>335.5174656966423</v>
       </c>
       <c r="D207" t="n">
-        <v>341.9600214541982</v>
+        <v>328.241100746865</v>
       </c>
       <c r="E207" t="n">
-        <v>342.6846618652344</v>
+        <v>333.75048828125</v>
       </c>
       <c r="F207" t="n">
-        <v>3592800</v>
+        <v>4192300</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B208" t="n">
-        <v>335.5174656966423</v>
+        <v>335.2891698936722</v>
       </c>
       <c r="C208" t="n">
-        <v>335.5174656966423</v>
+        <v>338.2374444527704</v>
       </c>
       <c r="D208" t="n">
-        <v>328.241100746865</v>
+        <v>333.1548737064404</v>
       </c>
       <c r="E208" t="n">
-        <v>333.75048828125</v>
+        <v>336.2520751953125</v>
       </c>
       <c r="F208" t="n">
-        <v>4192300</v>
+        <v>2780800</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B209" t="n">
-        <v>335.2891698936722</v>
+        <v>337.0660677396515</v>
       </c>
       <c r="C209" t="n">
-        <v>338.2374444527704</v>
+        <v>341.8805944502874</v>
       </c>
       <c r="D209" t="n">
-        <v>333.1548737064404</v>
+        <v>335.4281440922459</v>
       </c>
       <c r="E209" t="n">
-        <v>336.2520751953125</v>
+        <v>340.7886352539062</v>
       </c>
       <c r="F209" t="n">
-        <v>2780800</v>
+        <v>2748000</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B210" t="n">
-        <v>337.0660677396515</v>
+        <v>341.4835329455154</v>
       </c>
       <c r="C210" t="n">
-        <v>341.8805944502874</v>
+        <v>342.5853984087983</v>
       </c>
       <c r="D210" t="n">
-        <v>335.4281440922459</v>
+        <v>332.9762178919015</v>
       </c>
       <c r="E210" t="n">
-        <v>340.7886352539062</v>
+        <v>334.6439208984375</v>
       </c>
       <c r="F210" t="n">
-        <v>2748000</v>
+        <v>3650400</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B211" t="n">
-        <v>341.4835329455154</v>
+        <v>337.0362951640151</v>
       </c>
       <c r="C211" t="n">
-        <v>342.5853984087983</v>
+        <v>339.2499929294707</v>
       </c>
       <c r="D211" t="n">
-        <v>332.9762178919015</v>
+        <v>334.1078935040618</v>
       </c>
       <c r="E211" t="n">
-        <v>334.6439208984375</v>
+        <v>335.2693176269531</v>
       </c>
       <c r="F211" t="n">
-        <v>3650400</v>
+        <v>2807300</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B212" t="n">
-        <v>337.0362951640151</v>
+        <v>336.5101711499915</v>
       </c>
       <c r="C212" t="n">
-        <v>339.2499929294707</v>
+        <v>343.7170716460562</v>
       </c>
       <c r="D212" t="n">
-        <v>334.1078935040618</v>
+        <v>334.7928460359882</v>
       </c>
       <c r="E212" t="n">
-        <v>335.2693176269531</v>
+        <v>338.9422607421875</v>
       </c>
       <c r="F212" t="n">
-        <v>2807300</v>
+        <v>3953100</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B213" t="n">
-        <v>336.5101711499915</v>
+        <v>339.0514198724459</v>
       </c>
       <c r="C213" t="n">
-        <v>343.7170716460562</v>
+        <v>348.2436891486228</v>
       </c>
       <c r="D213" t="n">
-        <v>334.7928460359882</v>
+        <v>338.148103527179</v>
       </c>
       <c r="E213" t="n">
-        <v>338.9422607421875</v>
+        <v>345.4740905761719</v>
       </c>
       <c r="F213" t="n">
-        <v>3953100</v>
+        <v>3810300</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B214" t="n">
-        <v>339.0514198724459</v>
+        <v>346.3774576909258</v>
       </c>
       <c r="C214" t="n">
-        <v>348.2436891486228</v>
+        <v>351.3905334952897</v>
       </c>
       <c r="D214" t="n">
-        <v>338.148103527179</v>
+        <v>335.6167594084301</v>
       </c>
       <c r="E214" t="n">
-        <v>345.4740905761719</v>
+        <v>336.3910522460938</v>
       </c>
       <c r="F214" t="n">
-        <v>3810300</v>
+        <v>4434000</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B215" t="n">
-        <v>346.3774576909258</v>
+        <v>337.4829959680537</v>
       </c>
       <c r="C215" t="n">
-        <v>351.3905334952897</v>
+        <v>337.7113243396537</v>
       </c>
       <c r="D215" t="n">
-        <v>335.6167594084301</v>
+        <v>328.985617931225</v>
       </c>
       <c r="E215" t="n">
-        <v>336.3910522460938</v>
+        <v>330.6036987304688</v>
       </c>
       <c r="F215" t="n">
-        <v>4434000</v>
+        <v>4125300</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B216" t="n">
-        <v>337.4829959680537</v>
+        <v>328.8764012920007</v>
       </c>
       <c r="C216" t="n">
-        <v>337.7113243396537</v>
+        <v>330.5639772575944</v>
       </c>
       <c r="D216" t="n">
-        <v>328.985617931225</v>
+        <v>324.6078695592594</v>
       </c>
       <c r="E216" t="n">
-        <v>330.6036987304688</v>
+        <v>329.1742248535156</v>
       </c>
       <c r="F216" t="n">
-        <v>4125300</v>
+        <v>3112600</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B217" t="n">
-        <v>328.8764012920007</v>
+        <v>331.0901002710247</v>
       </c>
       <c r="C217" t="n">
-        <v>330.5639772575944</v>
+        <v>334.097933459434</v>
       </c>
       <c r="D217" t="n">
-        <v>324.6078695592594</v>
+        <v>328.2907223705125</v>
       </c>
       <c r="E217" t="n">
-        <v>329.1742248535156</v>
+        <v>329.0253295898438</v>
       </c>
       <c r="F217" t="n">
-        <v>3112600</v>
+        <v>2907700</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B218" t="n">
-        <v>331.0901002710247</v>
+        <v>322.9203055541834</v>
       </c>
       <c r="C218" t="n">
-        <v>334.097933459434</v>
+        <v>325.8288946116248</v>
       </c>
       <c r="D218" t="n">
-        <v>328.2907223705125</v>
+        <v>320.6867650845805</v>
       </c>
       <c r="E218" t="n">
-        <v>329.0253295898438</v>
+        <v>322.3346252441406</v>
       </c>
       <c r="F218" t="n">
-        <v>2907700</v>
+        <v>4523100</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B219" t="n">
-        <v>322.9203055541834</v>
+        <v>322.6920194034342</v>
       </c>
       <c r="C219" t="n">
-        <v>325.8288946116248</v>
+        <v>331.0206281983068</v>
       </c>
       <c r="D219" t="n">
-        <v>320.6867650845805</v>
+        <v>320.8654832094117</v>
       </c>
       <c r="E219" t="n">
-        <v>322.3346252441406</v>
+        <v>330.5441589355469</v>
       </c>
       <c r="F219" t="n">
-        <v>4523100</v>
+        <v>3874500</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B220" t="n">
-        <v>322.6920194034342</v>
+        <v>336.9072556737336</v>
       </c>
       <c r="C220" t="n">
-        <v>331.0206281983068</v>
+        <v>339.3889672822994</v>
       </c>
       <c r="D220" t="n">
-        <v>320.8654832094117</v>
+        <v>332.8968012318786</v>
       </c>
       <c r="E220" t="n">
-        <v>330.5441589355469</v>
+        <v>333.6313781738281</v>
       </c>
       <c r="F220" t="n">
-        <v>3874500</v>
+        <v>3622400</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B221" t="n">
-        <v>336.9072556737336</v>
+        <v>340.133473711892</v>
       </c>
       <c r="C221" t="n">
-        <v>339.3889672822994</v>
+        <v>346.8737804890717</v>
       </c>
       <c r="D221" t="n">
-        <v>332.8968012318786</v>
+        <v>340.0937578445657</v>
       </c>
       <c r="E221" t="n">
-        <v>333.6313781738281</v>
+        <v>341.9500732421875</v>
       </c>
       <c r="F221" t="n">
-        <v>3622400</v>
+        <v>4308000</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B222" t="n">
-        <v>340.133473711892</v>
+        <v>337.8900211320969</v>
       </c>
       <c r="C222" t="n">
-        <v>346.8737804890717</v>
+        <v>342.7442335347337</v>
       </c>
       <c r="D222" t="n">
-        <v>340.0937578445657</v>
+        <v>334.495026147691</v>
       </c>
       <c r="E222" t="n">
-        <v>341.9500732421875</v>
+        <v>335.7954406738281</v>
       </c>
       <c r="F222" t="n">
-        <v>4308000</v>
+        <v>4028500</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B223" t="n">
-        <v>337.8900211320969</v>
+        <v>332.5394250801792</v>
       </c>
       <c r="C223" t="n">
-        <v>342.7442335347337</v>
+        <v>333.2343164610006</v>
       </c>
       <c r="D223" t="n">
-        <v>334.495026147691</v>
+        <v>327.8341094785939</v>
       </c>
       <c r="E223" t="n">
-        <v>335.7954406738281</v>
+        <v>330.9114379882812</v>
       </c>
       <c r="F223" t="n">
-        <v>4028500</v>
+        <v>6275400</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B224" t="n">
-        <v>332.5394250801792</v>
+        <v>330.0080852280822</v>
       </c>
       <c r="C224" t="n">
-        <v>333.2343164610006</v>
+        <v>331.5566708480175</v>
       </c>
       <c r="D224" t="n">
-        <v>327.8341094785939</v>
+        <v>326.3946985853459</v>
       </c>
       <c r="E224" t="n">
-        <v>330.9114379882812</v>
+        <v>329.5315856933594</v>
       </c>
       <c r="F224" t="n">
-        <v>6275400</v>
+        <v>4961900</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B225" t="n">
-        <v>330.0080852280822</v>
+        <v>337.3142314565633</v>
       </c>
       <c r="C225" t="n">
-        <v>331.5566708480175</v>
+        <v>341.126167165973</v>
       </c>
       <c r="D225" t="n">
-        <v>326.3946985853459</v>
+        <v>331.2787221229386</v>
       </c>
       <c r="E225" t="n">
-        <v>329.5315856933594</v>
+        <v>337.5326232910156</v>
       </c>
       <c r="F225" t="n">
-        <v>4961900</v>
+        <v>2908100</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B226" t="n">
-        <v>337.3142314565633</v>
+        <v>337.741121159039</v>
       </c>
       <c r="C226" t="n">
-        <v>341.126167165973</v>
+        <v>348.2933339094608</v>
       </c>
       <c r="D226" t="n">
-        <v>331.2787221229386</v>
+        <v>336.8675537894677</v>
       </c>
       <c r="E226" t="n">
-        <v>337.5326232910156</v>
+        <v>345.6925048828125</v>
       </c>
       <c r="F226" t="n">
-        <v>2908100</v>
+        <v>4275000</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B227" t="n">
-        <v>337.741121159039</v>
+        <v>347.5984599855233</v>
       </c>
       <c r="C227" t="n">
-        <v>348.2933339094608</v>
+        <v>351.9563298372728</v>
       </c>
       <c r="D227" t="n">
-        <v>336.8675537894677</v>
+        <v>345.6031541488199</v>
       </c>
       <c r="E227" t="n">
-        <v>345.6925048828125</v>
+        <v>350.5566711425781</v>
       </c>
       <c r="F227" t="n">
-        <v>4275000</v>
+        <v>3140400</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B228" t="n">
-        <v>347.5984599855233</v>
+        <v>350.9140306560572</v>
       </c>
       <c r="C228" t="n">
-        <v>351.9563298372728</v>
+        <v>350.9636527717977</v>
       </c>
       <c r="D228" t="n">
-        <v>345.6031541488199</v>
+        <v>344.967859180145</v>
       </c>
       <c r="E228" t="n">
-        <v>350.5566711425781</v>
+        <v>346.963134765625</v>
       </c>
       <c r="F228" t="n">
-        <v>3140400</v>
+        <v>2622400</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B229" t="n">
-        <v>350.9140306560572</v>
+        <v>348.9386046403958</v>
       </c>
       <c r="C229" t="n">
-        <v>350.9636527717977</v>
+        <v>354.219664160909</v>
       </c>
       <c r="D229" t="n">
-        <v>344.967859180145</v>
+        <v>346.1888486641563</v>
       </c>
       <c r="E229" t="n">
-        <v>346.963134765625</v>
+        <v>353.0185241699219</v>
       </c>
       <c r="F229" t="n">
-        <v>2622400</v>
+        <v>3584800</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B230" t="n">
-        <v>348.9386046403958</v>
+        <v>349.524279261052</v>
       </c>
       <c r="C230" t="n">
-        <v>354.219664160909</v>
+        <v>351.4103740800161</v>
       </c>
       <c r="D230" t="n">
-        <v>346.1888486641563</v>
+        <v>344.5211400290252</v>
       </c>
       <c r="E230" t="n">
-        <v>353.0185241699219</v>
+        <v>348.2139282226562</v>
       </c>
       <c r="F230" t="n">
-        <v>3584800</v>
+        <v>3124800</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B231" t="n">
-        <v>349.524279261052</v>
+        <v>349.7128894956296</v>
       </c>
       <c r="C231" t="n">
-        <v>351.4103740800161</v>
+        <v>355.7384623950411</v>
       </c>
       <c r="D231" t="n">
-        <v>344.5211400290252</v>
+        <v>348.0352499864083</v>
       </c>
       <c r="E231" t="n">
-        <v>348.2139282226562</v>
+        <v>351.8868713378906</v>
       </c>
       <c r="F231" t="n">
-        <v>3124800</v>
+        <v>2549700</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B232" t="n">
-        <v>349.7128894956296</v>
+        <v>349.4250091127092</v>
       </c>
       <c r="C232" t="n">
-        <v>355.7384623950411</v>
+        <v>351.2813246265272</v>
       </c>
       <c r="D232" t="n">
-        <v>348.0352499864083</v>
+        <v>340.5206262766717</v>
       </c>
       <c r="E232" t="n">
-        <v>351.8868713378906</v>
+        <v>340.9176940917969</v>
       </c>
       <c r="F232" t="n">
-        <v>2549700</v>
+        <v>3965800</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B233" t="n">
-        <v>349.4250091127092</v>
+        <v>344.4615642861647</v>
       </c>
       <c r="C233" t="n">
-        <v>351.2813246265272</v>
+        <v>345.206077753642</v>
       </c>
       <c r="D233" t="n">
-        <v>340.5206262766717</v>
+        <v>338.0190507751135</v>
       </c>
       <c r="E233" t="n">
-        <v>340.9176940917969</v>
+        <v>339.2003479003906</v>
       </c>
       <c r="F233" t="n">
-        <v>3965800</v>
+        <v>2439900</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B234" t="n">
-        <v>344.4615642861647</v>
+        <v>338.3168506868042</v>
       </c>
       <c r="C234" t="n">
-        <v>345.206077753642</v>
+        <v>338.3168506868042</v>
       </c>
       <c r="D234" t="n">
-        <v>338.0190507751135</v>
+        <v>333.5519765191293</v>
       </c>
       <c r="E234" t="n">
-        <v>339.2003479003906</v>
+        <v>336.381103515625</v>
       </c>
       <c r="F234" t="n">
-        <v>2439900</v>
+        <v>3073100</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B235" t="n">
-        <v>338.3168506868042</v>
+        <v>332.2614710050206</v>
       </c>
       <c r="C235" t="n">
-        <v>338.3168506868042</v>
+        <v>336.9568803095206</v>
       </c>
       <c r="D235" t="n">
-        <v>333.5519765191293</v>
+        <v>330.4548079641576</v>
       </c>
       <c r="E235" t="n">
-        <v>336.381103515625</v>
+        <v>335.4082946777344</v>
       </c>
       <c r="F235" t="n">
-        <v>3073100</v>
+        <v>5580000</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B236" t="n">
-        <v>332.2614710050206</v>
+        <v>334.3163510292147</v>
       </c>
       <c r="C236" t="n">
-        <v>336.9568803095206</v>
+        <v>342.0195939717831</v>
       </c>
       <c r="D236" t="n">
-        <v>330.4548079641576</v>
+        <v>328.2709048600699</v>
       </c>
       <c r="E236" t="n">
-        <v>335.4082946777344</v>
+        <v>335.0211486816406</v>
       </c>
       <c r="F236" t="n">
-        <v>5580000</v>
+        <v>6603400</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B237" t="n">
-        <v>334.3163510292147</v>
+        <v>338.9224047058033</v>
       </c>
       <c r="C237" t="n">
-        <v>342.0195939717831</v>
+        <v>347.8366934263856</v>
       </c>
       <c r="D237" t="n">
-        <v>328.2709048600699</v>
+        <v>338.9224047058033</v>
       </c>
       <c r="E237" t="n">
-        <v>335.0211486816406</v>
+        <v>341.7813110351562</v>
       </c>
       <c r="F237" t="n">
-        <v>6603400</v>
+        <v>4971000</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B238" t="n">
-        <v>338.9224047058033</v>
+        <v>333.542054389882</v>
       </c>
       <c r="C238" t="n">
-        <v>347.8366934263856</v>
+        <v>336.4009911317456</v>
       </c>
       <c r="D238" t="n">
-        <v>338.9224047058033</v>
+        <v>329.1643112906949</v>
       </c>
       <c r="E238" t="n">
-        <v>341.7813110351562</v>
+        <v>332.0430908203125</v>
       </c>
       <c r="F238" t="n">
-        <v>4971000</v>
+        <v>4027700</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B239" t="n">
-        <v>333.542054389882</v>
+        <v>334.0582233645888</v>
       </c>
       <c r="C239" t="n">
-        <v>336.4009911317456</v>
+        <v>336.1031512946537</v>
       </c>
       <c r="D239" t="n">
-        <v>329.1643112906949</v>
+        <v>330.5639843459303</v>
       </c>
       <c r="E239" t="n">
-        <v>332.0430908203125</v>
+        <v>333.1548767089844</v>
       </c>
       <c r="F239" t="n">
-        <v>4027700</v>
+        <v>3422800</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B240" t="n">
-        <v>334.0582233645888</v>
+        <v>333.4229292601251</v>
       </c>
       <c r="C240" t="n">
-        <v>336.1031512946537</v>
+        <v>339.7165463845368</v>
       </c>
       <c r="D240" t="n">
-        <v>330.5639843459303</v>
+        <v>332.7081950914107</v>
       </c>
       <c r="E240" t="n">
-        <v>333.1548767089844</v>
+        <v>334.9615783691406</v>
       </c>
       <c r="F240" t="n">
-        <v>3422800</v>
+        <v>3298600</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B241" t="n">
-        <v>333.4229292601251</v>
+        <v>336.8873851133212</v>
       </c>
       <c r="C241" t="n">
-        <v>339.7165463845368</v>
+        <v>337.0065024243307</v>
       </c>
       <c r="D241" t="n">
-        <v>332.7081950914107</v>
+        <v>331.2588801078031</v>
       </c>
       <c r="E241" t="n">
-        <v>334.9615783691406</v>
+        <v>335.4082946777344</v>
       </c>
       <c r="F241" t="n">
-        <v>3298600</v>
+        <v>2528100</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B242" t="n">
-        <v>336.8873851133212</v>
+        <v>336.9469338983794</v>
       </c>
       <c r="C242" t="n">
-        <v>337.0065024243307</v>
+        <v>336.9568704387829</v>
       </c>
       <c r="D242" t="n">
-        <v>331.2588801078031</v>
+        <v>332.0629425240725</v>
       </c>
       <c r="E242" t="n">
-        <v>335.4082946777344</v>
+        <v>332.4004516601562</v>
       </c>
       <c r="F242" t="n">
-        <v>2528100</v>
+        <v>4258100</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B243" t="n">
-        <v>336.9469338983794</v>
+        <v>328.1517689125653</v>
       </c>
       <c r="C243" t="n">
-        <v>336.9568704387829</v>
+        <v>329.5812372185705</v>
       </c>
       <c r="D243" t="n">
-        <v>332.0629425240725</v>
+        <v>325.4814448058147</v>
       </c>
       <c r="E243" t="n">
-        <v>332.4004516601562</v>
+        <v>326.2060852050781</v>
       </c>
       <c r="F243" t="n">
-        <v>4258100</v>
+        <v>3618000</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B244" t="n">
-        <v>328.1517689125653</v>
+        <v>328.0822659405567</v>
       </c>
       <c r="C244" t="n">
-        <v>329.5812372185705</v>
+        <v>329.1841313242223</v>
       </c>
       <c r="D244" t="n">
-        <v>325.4814448058147</v>
+        <v>325.1042120893565</v>
       </c>
       <c r="E244" t="n">
-        <v>326.2060852050781</v>
+        <v>327.7745361328125</v>
       </c>
       <c r="F244" t="n">
-        <v>3618000</v>
+        <v>3136100</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B245" t="n">
-        <v>328.0822659405567</v>
+        <v>325.838797551875</v>
       </c>
       <c r="C245" t="n">
-        <v>329.1841313242223</v>
+        <v>326.8414187355763</v>
       </c>
       <c r="D245" t="n">
-        <v>325.1042120893565</v>
+        <v>323.3670224847805</v>
       </c>
       <c r="E245" t="n">
-        <v>327.7745361328125</v>
+        <v>325.4317932128906</v>
       </c>
       <c r="F245" t="n">
-        <v>3136100</v>
+        <v>3858700</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B246" t="n">
-        <v>325.838797551875</v>
+        <v>323.6251283531417</v>
       </c>
       <c r="C246" t="n">
-        <v>326.8414187355763</v>
+        <v>324.439106732169</v>
       </c>
       <c r="D246" t="n">
-        <v>323.3670224847805</v>
+        <v>316.4678503051231</v>
       </c>
       <c r="E246" t="n">
-        <v>325.4317932128906</v>
+        <v>317.4307556152344</v>
       </c>
       <c r="F246" t="n">
-        <v>3858700</v>
+        <v>3291000</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B247" t="n">
-        <v>323.6251283531417</v>
+        <v>319.1481100391916</v>
       </c>
       <c r="C247" t="n">
-        <v>324.439106732169</v>
+        <v>319.813222073911</v>
       </c>
       <c r="D247" t="n">
-        <v>316.4678503051231</v>
+        <v>315.3858267914646</v>
       </c>
       <c r="E247" t="n">
-        <v>317.4307556152344</v>
+        <v>316.1799926757812</v>
       </c>
       <c r="F247" t="n">
-        <v>3291000</v>
+        <v>3499300</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,25 +6865,25 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B248" t="n">
-        <v>319.1481100391916</v>
+        <v>318.2099914550781</v>
       </c>
       <c r="C248" t="n">
-        <v>319.813222073911</v>
+        <v>320.4400024414062</v>
       </c>
       <c r="D248" t="n">
-        <v>315.3858267914646</v>
+        <v>315.2099914550781</v>
       </c>
       <c r="E248" t="n">
-        <v>316.1799926757812</v>
+        <v>318.0700073242188</v>
       </c>
       <c r="F248" t="n">
-        <v>3499300</v>
+        <v>3377700</v>
       </c>
       <c r="G248" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -6891,25 +6891,25 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B249" t="n">
-        <v>318.2099914550781</v>
+        <v>316.7000122070312</v>
       </c>
       <c r="C249" t="n">
-        <v>320.4400024414062</v>
+        <v>321.7999877929688</v>
       </c>
       <c r="D249" t="n">
-        <v>315.2099914550781</v>
+        <v>316.1000061035156</v>
       </c>
       <c r="E249" t="n">
-        <v>318.0700073242188</v>
+        <v>321.0499877929688</v>
       </c>
       <c r="F249" t="n">
-        <v>3377700</v>
+        <v>2261000</v>
       </c>
       <c r="G249" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B250" t="n">
-        <v>316.7000122070312</v>
+        <v>320.7300109863281</v>
       </c>
       <c r="C250" t="n">
-        <v>321.7999877929688</v>
+        <v>321.5</v>
       </c>
       <c r="D250" t="n">
-        <v>316.1000061035156</v>
+        <v>313.239990234375</v>
       </c>
       <c r="E250" t="n">
-        <v>321.0499877929688</v>
+        <v>313.7000122070312</v>
       </c>
       <c r="F250" t="n">
-        <v>2261000</v>
+        <v>5655700</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B251" t="n">
-        <v>320.7300109863281</v>
+        <v>310.4700012207031</v>
       </c>
       <c r="C251" t="n">
-        <v>321.5</v>
+        <v>313.3900146484375</v>
       </c>
       <c r="D251" t="n">
-        <v>313.239990234375</v>
+        <v>309.8399963378906</v>
       </c>
       <c r="E251" t="n">
-        <v>313.7000122070312</v>
+        <v>310.4500122070312</v>
       </c>
       <c r="F251" t="n">
-        <v>5655700</v>
+        <v>3611700</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B252" t="n">
-        <v>310.4700012207031</v>
+        <v>308.1300048828125</v>
       </c>
       <c r="C252" t="n">
-        <v>313.3900146484375</v>
+        <v>308.2799987792969</v>
       </c>
       <c r="D252" t="n">
-        <v>309.8399963378906</v>
+        <v>304.2999877929688</v>
       </c>
       <c r="E252" t="n">
-        <v>310.4500122070312</v>
+        <v>305.6900024414062</v>
       </c>
       <c r="F252" t="n">
-        <v>3611700</v>
+        <v>4482300</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10594,37 +10594,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>305.69</v>
+      </c>
+      <c r="D2" t="n">
         <v>310.45</v>
       </c>
-      <c r="D2" t="n">
-        <v>313.7</v>
-      </c>
       <c r="E2" t="n">
-        <v>310.47</v>
+        <v>308.13</v>
       </c>
       <c r="F2" t="n">
-        <v>313.385</v>
+        <v>308.28</v>
       </c>
       <c r="G2" t="n">
-        <v>309.84</v>
+        <v>304.3</v>
       </c>
       <c r="H2" t="n">
-        <v>3357754</v>
+        <v>4307096</v>
       </c>
       <c r="I2" t="n">
-        <v>4210254</v>
+        <v>4190704</v>
       </c>
       <c r="J2" t="n">
-        <v>309732737024</v>
+        <v>304983736320</v>
       </c>
       <c r="K2" t="n">
-        <v>21.740198</v>
+        <v>21.74182</v>
       </c>
       <c r="L2" t="n">
-        <v>19.373098</v>
+        <v>19.076057</v>
       </c>
       <c r="M2" t="n">
-        <v>14.28</v>
+        <v>14.06</v>
       </c>
       <c r="N2" t="n">
         <v>426.75</v>
@@ -10660,7 +10660,7 @@
         <v>16.65</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.645647</v>
+        <v>18.35976</v>
       </c>
       <c r="Z2" t="n">
         <v>0.046</v>
@@ -10672,7 +10672,7 @@
         <v>169176006656</v>
       </c>
       <c r="AC2" t="n">
-        <v>370835750912</v>
+        <v>366086750208</v>
       </c>
       <c r="AD2" t="n">
         <v>24647999488</v>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-10 18:59:50</t>
+          <t>2026-09-11 19:03:26</t>
         </is>
       </c>
     </row>

--- a/data/HD_data.xlsx
+++ b/data/HD_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B2" t="n">
-        <v>404.2520901069122</v>
+        <v>408.6962221082555</v>
       </c>
       <c r="C2" t="n">
-        <v>413.5099090714568</v>
+        <v>411.8470163012535</v>
       </c>
       <c r="D2" t="n">
-        <v>402.8420096446557</v>
+        <v>407.3445165905575</v>
       </c>
       <c r="E2" t="n">
-        <v>411.7594909667969</v>
+        <v>411.0495910644531</v>
       </c>
       <c r="F2" t="n">
-        <v>5316400</v>
+        <v>5004200</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B3" t="n">
-        <v>408.6961917653987</v>
+        <v>410.8356495901566</v>
       </c>
       <c r="C3" t="n">
-        <v>411.846985724472</v>
+        <v>411.6427792599144</v>
       </c>
       <c r="D3" t="n">
-        <v>407.3444863480555</v>
+        <v>406.245631927433</v>
       </c>
       <c r="E3" t="n">
-        <v>411.049560546875</v>
+        <v>411.0690307617188</v>
       </c>
       <c r="F3" t="n">
-        <v>5004200</v>
+        <v>4884700</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B4" t="n">
-        <v>410.8356495901566</v>
+        <v>412.0803987002532</v>
       </c>
       <c r="C4" t="n">
-        <v>411.6427792599144</v>
+        <v>412.8389171851107</v>
       </c>
       <c r="D4" t="n">
-        <v>406.245631927433</v>
+        <v>408.5211874475655</v>
       </c>
       <c r="E4" t="n">
-        <v>411.0690307617188</v>
+        <v>409.84375</v>
       </c>
       <c r="F4" t="n">
-        <v>4884700</v>
+        <v>3726700</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B5" t="n">
-        <v>412.0803987002532</v>
+        <v>412.7514096604531</v>
       </c>
       <c r="C5" t="n">
-        <v>412.8389171851107</v>
+        <v>414.9977925252571</v>
       </c>
       <c r="D5" t="n">
-        <v>408.5211874475655</v>
+        <v>404.3590652530731</v>
       </c>
       <c r="E5" t="n">
-        <v>409.84375</v>
+        <v>405.5162963867188</v>
       </c>
       <c r="F5" t="n">
-        <v>3726700</v>
+        <v>4771700</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B6" t="n">
-        <v>412.7514096604531</v>
+        <v>406.0511429878587</v>
       </c>
       <c r="C6" t="n">
-        <v>414.9977925252571</v>
+        <v>409.7854199351742</v>
       </c>
       <c r="D6" t="n">
-        <v>404.3590652530731</v>
+        <v>404.4076812634016</v>
       </c>
       <c r="E6" t="n">
-        <v>405.5162963867188</v>
+        <v>405.9830932617188</v>
       </c>
       <c r="F6" t="n">
-        <v>4771700</v>
+        <v>3677200</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B7" t="n">
-        <v>406.0511124651653</v>
+        <v>405.8760981858028</v>
       </c>
       <c r="C7" t="n">
-        <v>409.7853891317768</v>
+        <v>407.0527678467049</v>
       </c>
       <c r="D7" t="n">
-        <v>404.4076508642465</v>
+        <v>403.6686220984643</v>
       </c>
       <c r="E7" t="n">
-        <v>405.9830627441406</v>
+        <v>404.2423706054688</v>
       </c>
       <c r="F7" t="n">
-        <v>3677200</v>
+        <v>6718400</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B8" t="n">
-        <v>405.8760981858028</v>
+        <v>402.7058704699236</v>
       </c>
       <c r="C8" t="n">
-        <v>407.0527678467049</v>
+        <v>403.4546845448791</v>
       </c>
       <c r="D8" t="n">
-        <v>403.6686220984643</v>
+        <v>399.8079552515003</v>
       </c>
       <c r="E8" t="n">
-        <v>404.2423706054688</v>
+        <v>400.6539916992188</v>
       </c>
       <c r="F8" t="n">
-        <v>6718400</v>
+        <v>2656300</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B9" t="n">
-        <v>402.7058704699236</v>
+        <v>400.6539731783087</v>
       </c>
       <c r="C9" t="n">
-        <v>403.4546845448791</v>
+        <v>402.3363415649943</v>
       </c>
       <c r="D9" t="n">
-        <v>399.8079552515003</v>
+        <v>396.2389914749436</v>
       </c>
       <c r="E9" t="n">
-        <v>400.6539916992188</v>
+        <v>399.593994140625</v>
       </c>
       <c r="F9" t="n">
-        <v>2656300</v>
+        <v>2597000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B10" t="n">
-        <v>400.6539425797785</v>
+        <v>395.5874366429679</v>
       </c>
       <c r="C10" t="n">
-        <v>402.3363108379792</v>
+        <v>399.3411220300941</v>
       </c>
       <c r="D10" t="n">
-        <v>396.2389612135919</v>
+        <v>393.8564571706638</v>
       </c>
       <c r="E10" t="n">
-        <v>399.5939636230469</v>
+        <v>398.4853515625</v>
       </c>
       <c r="F10" t="n">
-        <v>2597000</v>
+        <v>3220700</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B11" t="n">
-        <v>395.5874669386123</v>
+        <v>395.4512918948509</v>
       </c>
       <c r="C11" t="n">
-        <v>399.3411526132105</v>
+        <v>399.5453447284057</v>
       </c>
       <c r="D11" t="n">
-        <v>393.856487333743</v>
+        <v>394.4399240629465</v>
       </c>
       <c r="E11" t="n">
-        <v>398.4853820800781</v>
+        <v>396.2292785644531</v>
       </c>
       <c r="F11" t="n">
-        <v>3220700</v>
+        <v>2554300</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B12" t="n">
-        <v>395.4513223525085</v>
+        <v>396.9197270195646</v>
       </c>
       <c r="C12" t="n">
-        <v>399.5453755013872</v>
+        <v>400.08022560159</v>
       </c>
       <c r="D12" t="n">
-        <v>394.4399544427085</v>
+        <v>394.6636101400317</v>
       </c>
       <c r="E12" t="n">
-        <v>396.2293090820312</v>
+        <v>398.7965698242188</v>
       </c>
       <c r="F12" t="n">
-        <v>2554300</v>
+        <v>2316600</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B13" t="n">
-        <v>396.9197270195646</v>
+        <v>398.7576665785797</v>
       </c>
       <c r="C13" t="n">
-        <v>400.08022560159</v>
+        <v>399.6329053199512</v>
       </c>
       <c r="D13" t="n">
-        <v>394.6636101400317</v>
+        <v>392.7284254984301</v>
       </c>
       <c r="E13" t="n">
-        <v>398.7965698242188</v>
+        <v>395.59716796875</v>
       </c>
       <c r="F13" t="n">
-        <v>2316600</v>
+        <v>3008400</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B14" t="n">
-        <v>398.7576665785797</v>
+        <v>395.4318710489828</v>
       </c>
       <c r="C14" t="n">
-        <v>399.6329053199512</v>
+        <v>395.7916769160157</v>
       </c>
       <c r="D14" t="n">
-        <v>392.7284254984301</v>
+        <v>392.3686244480866</v>
       </c>
       <c r="E14" t="n">
-        <v>395.59716796875</v>
+        <v>394.0315246582031</v>
       </c>
       <c r="F14" t="n">
-        <v>3008400</v>
+        <v>3211600</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B15" t="n">
-        <v>395.4318710489828</v>
+        <v>393.2535498958814</v>
       </c>
       <c r="C15" t="n">
-        <v>395.7916769160157</v>
+        <v>393.9731615974939</v>
       </c>
       <c r="D15" t="n">
-        <v>392.3686244480866</v>
+        <v>384.4235866812837</v>
       </c>
       <c r="E15" t="n">
-        <v>394.0315246582031</v>
+        <v>386.0864868164062</v>
       </c>
       <c r="F15" t="n">
-        <v>3211600</v>
+        <v>3787800</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B16" t="n">
-        <v>393.2535809799684</v>
+        <v>384.6083934501511</v>
       </c>
       <c r="C16" t="n">
-        <v>393.9731927384614</v>
+        <v>386.4366252014962</v>
       </c>
       <c r="D16" t="n">
-        <v>384.4236170674206</v>
+        <v>382.9454931559638</v>
       </c>
       <c r="E16" t="n">
-        <v>386.0865173339844</v>
+        <v>384.1318969726562</v>
       </c>
       <c r="F16" t="n">
-        <v>3787800</v>
+        <v>2964700</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B17" t="n">
-        <v>384.6083934501511</v>
+        <v>383.2761296995442</v>
       </c>
       <c r="C17" t="n">
-        <v>386.4366252014962</v>
+        <v>386.3782832385467</v>
       </c>
       <c r="D17" t="n">
-        <v>382.9454931559638</v>
+        <v>381.8174379292481</v>
       </c>
       <c r="E17" t="n">
-        <v>384.1318969726562</v>
+        <v>384.1805114746094</v>
       </c>
       <c r="F17" t="n">
-        <v>2964700</v>
+        <v>2951300</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B18" t="n">
-        <v>383.2761296995442</v>
+        <v>383.6359134364591</v>
       </c>
       <c r="C18" t="n">
-        <v>386.3782832385467</v>
+        <v>383.6359134364591</v>
       </c>
       <c r="D18" t="n">
-        <v>381.8174379292481</v>
+        <v>375.0977059544146</v>
       </c>
       <c r="E18" t="n">
-        <v>384.1805114746094</v>
+        <v>378.6082763671875</v>
       </c>
       <c r="F18" t="n">
-        <v>2951300</v>
+        <v>3653700</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B19" t="n">
-        <v>383.6358825136301</v>
+        <v>378.7250266598306</v>
       </c>
       <c r="C19" t="n">
-        <v>383.6358825136301</v>
+        <v>379.0167531493121</v>
       </c>
       <c r="D19" t="n">
-        <v>375.0976757198047</v>
+        <v>374.8935271531156</v>
       </c>
       <c r="E19" t="n">
-        <v>378.6082458496094</v>
+        <v>376.15771484375</v>
       </c>
       <c r="F19" t="n">
-        <v>3653700</v>
+        <v>2505700</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B20" t="n">
-        <v>378.7250266598306</v>
+        <v>375.8173102434433</v>
       </c>
       <c r="C20" t="n">
-        <v>379.0167531493121</v>
+        <v>375.8173102434433</v>
       </c>
       <c r="D20" t="n">
-        <v>374.8935271531156</v>
+        <v>372.4331645921919</v>
       </c>
       <c r="E20" t="n">
-        <v>376.15771484375</v>
+        <v>373.2208557128906</v>
       </c>
       <c r="F20" t="n">
-        <v>2505700</v>
+        <v>2517600</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B21" t="n">
-        <v>375.8173102434433</v>
+        <v>372.3553321480077</v>
       </c>
       <c r="C21" t="n">
-        <v>375.8173102434433</v>
+        <v>373.7751169791765</v>
       </c>
       <c r="D21" t="n">
-        <v>372.4331645921919</v>
+        <v>367.0651416328743</v>
       </c>
       <c r="E21" t="n">
-        <v>373.2208557128906</v>
+        <v>367.288818359375</v>
       </c>
       <c r="F21" t="n">
-        <v>2517600</v>
+        <v>3321400</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B22" t="n">
-        <v>372.3553321480077</v>
+        <v>369.7880611814068</v>
       </c>
       <c r="C22" t="n">
-        <v>373.7751169791765</v>
+        <v>369.7880611814068</v>
       </c>
       <c r="D22" t="n">
-        <v>367.0651416328743</v>
+        <v>364.4589637589981</v>
       </c>
       <c r="E22" t="n">
-        <v>367.288818359375</v>
+        <v>365.4022521972656</v>
       </c>
       <c r="F22" t="n">
-        <v>3321400</v>
+        <v>2992400</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B23" t="n">
-        <v>369.7880611814068</v>
+        <v>368.6308504339742</v>
       </c>
       <c r="C23" t="n">
-        <v>369.7880611814068</v>
+        <v>371.7816150220939</v>
       </c>
       <c r="D23" t="n">
-        <v>364.4589637589981</v>
+        <v>366.8026187475289</v>
       </c>
       <c r="E23" t="n">
-        <v>365.4022521972656</v>
+        <v>368.9225769042969</v>
       </c>
       <c r="F23" t="n">
-        <v>2992400</v>
+        <v>2925900</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B24" t="n">
-        <v>368.6308809274205</v>
+        <v>368.4363162416045</v>
       </c>
       <c r="C24" t="n">
-        <v>371.7816457761741</v>
+        <v>378.1803950347029</v>
       </c>
       <c r="D24" t="n">
-        <v>366.8026490897424</v>
+        <v>367.6000139768833</v>
       </c>
       <c r="E24" t="n">
-        <v>368.922607421875</v>
+        <v>377.0426025390625</v>
       </c>
       <c r="F24" t="n">
-        <v>2925900</v>
+        <v>4399900</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B25" t="n">
-        <v>368.4363460625955</v>
+        <v>378.5110397840133</v>
       </c>
       <c r="C25" t="n">
-        <v>378.1804256443732</v>
+        <v>383.5094743418081</v>
       </c>
       <c r="D25" t="n">
-        <v>367.6000437301846</v>
+        <v>376.0798870651823</v>
       </c>
       <c r="E25" t="n">
-        <v>377.0426330566406</v>
+        <v>377.6066284179688</v>
       </c>
       <c r="F25" t="n">
-        <v>4399900</v>
+        <v>3690100</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B26" t="n">
-        <v>378.5110397840133</v>
+        <v>378.9291861622302</v>
       </c>
       <c r="C26" t="n">
-        <v>383.5094743418081</v>
+        <v>379.259819366573</v>
       </c>
       <c r="D26" t="n">
-        <v>376.0798870651823</v>
+        <v>373.3958802696069</v>
       </c>
       <c r="E26" t="n">
-        <v>377.6066284179688</v>
+        <v>376.7217102050781</v>
       </c>
       <c r="F26" t="n">
-        <v>3690100</v>
+        <v>2783700</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B27" t="n">
-        <v>378.9291861622302</v>
+        <v>377.8011514993366</v>
       </c>
       <c r="C27" t="n">
-        <v>379.259819366573</v>
+        <v>382.2841830931986</v>
       </c>
       <c r="D27" t="n">
-        <v>373.3958802696069</v>
+        <v>376.5369638928536</v>
       </c>
       <c r="E27" t="n">
-        <v>376.7217102050781</v>
+        <v>381.1075134277344</v>
       </c>
       <c r="F27" t="n">
-        <v>2783700</v>
+        <v>2657700</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B28" t="n">
-        <v>377.8011514993366</v>
+        <v>380.6310112651639</v>
       </c>
       <c r="C28" t="n">
-        <v>382.2841830931986</v>
+        <v>382.3522567670641</v>
       </c>
       <c r="D28" t="n">
-        <v>376.5369638928536</v>
+        <v>377.4024332180988</v>
       </c>
       <c r="E28" t="n">
-        <v>381.1075134277344</v>
+        <v>378.180419921875</v>
       </c>
       <c r="F28" t="n">
-        <v>2657700</v>
+        <v>2761100</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B29" t="n">
-        <v>380.6310112651639</v>
+        <v>376.8870540082442</v>
       </c>
       <c r="C29" t="n">
-        <v>382.3522567670641</v>
+        <v>382.7899005162546</v>
       </c>
       <c r="D29" t="n">
-        <v>377.4024332180988</v>
+        <v>375.2338581249689</v>
       </c>
       <c r="E29" t="n">
-        <v>378.180419921875</v>
+        <v>380.1350708007812</v>
       </c>
       <c r="F29" t="n">
-        <v>2761100</v>
+        <v>2306900</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B30" t="n">
-        <v>376.8870237514197</v>
+        <v>380.4753887348813</v>
       </c>
       <c r="C30" t="n">
-        <v>382.7898697855445</v>
+        <v>382.2258067674637</v>
       </c>
       <c r="D30" t="n">
-        <v>375.2338280008644</v>
+        <v>377.4802217358246</v>
       </c>
       <c r="E30" t="n">
-        <v>380.1350402832031</v>
+        <v>378.2581787109375</v>
       </c>
       <c r="F30" t="n">
-        <v>2306900</v>
+        <v>2857000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B31" t="n">
-        <v>380.4753887348813</v>
+        <v>376.4689017102443</v>
       </c>
       <c r="C31" t="n">
-        <v>382.2258067674637</v>
+        <v>378.0151114266164</v>
       </c>
       <c r="D31" t="n">
-        <v>377.4802217358246</v>
+        <v>370.7994364063865</v>
       </c>
       <c r="E31" t="n">
-        <v>378.2581787109375</v>
+        <v>374.4267272949219</v>
       </c>
       <c r="F31" t="n">
-        <v>2857000</v>
+        <v>2767300</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B32" t="n">
-        <v>376.4688710262192</v>
+        <v>378.9681015073717</v>
       </c>
       <c r="C32" t="n">
-        <v>378.0150806165678</v>
+        <v>378.9681015073717</v>
       </c>
       <c r="D32" t="n">
-        <v>370.79940618445</v>
+        <v>375.0490844721456</v>
       </c>
       <c r="E32" t="n">
-        <v>374.4266967773438</v>
+        <v>376.03125</v>
       </c>
       <c r="F32" t="n">
-        <v>2767300</v>
+        <v>2426800</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B33" t="n">
-        <v>378.968132263296</v>
+        <v>377.0231983553949</v>
       </c>
       <c r="C33" t="n">
-        <v>378.968132263296</v>
+        <v>378.5694080170153</v>
       </c>
       <c r="D33" t="n">
-        <v>375.0491149100141</v>
+        <v>372.3553670460668</v>
       </c>
       <c r="E33" t="n">
-        <v>376.0312805175781</v>
+        <v>374.6600952148438</v>
       </c>
       <c r="F33" t="n">
-        <v>2426800</v>
+        <v>3065800</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B34" t="n">
-        <v>377.0231676453325</v>
+        <v>373.8335013939448</v>
       </c>
       <c r="C34" t="n">
-        <v>378.5693771810079</v>
+        <v>379.2695552693392</v>
       </c>
       <c r="D34" t="n">
-        <v>372.3553367162181</v>
+        <v>372.2872621610022</v>
       </c>
       <c r="E34" t="n">
-        <v>374.6600646972656</v>
+        <v>375.1268615722656</v>
       </c>
       <c r="F34" t="n">
-        <v>3065800</v>
+        <v>2372800</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B35" t="n">
-        <v>373.8335318063046</v>
+        <v>372.4526102885826</v>
       </c>
       <c r="C35" t="n">
-        <v>379.2695861239365</v>
+        <v>374.3975325355203</v>
       </c>
       <c r="D35" t="n">
-        <v>372.2872924475712</v>
+        <v>364.8674253963886</v>
       </c>
       <c r="E35" t="n">
-        <v>375.1268920898438</v>
+        <v>367.6292114257812</v>
       </c>
       <c r="F35" t="n">
-        <v>2372800</v>
+        <v>3852300</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B36" t="n">
-        <v>372.4526102885826</v>
+        <v>367.3082703686788</v>
       </c>
       <c r="C36" t="n">
-        <v>374.3975325355203</v>
+        <v>374.1057935751742</v>
       </c>
       <c r="D36" t="n">
-        <v>364.8674253963886</v>
+        <v>365.7523266876615</v>
       </c>
       <c r="E36" t="n">
-        <v>367.6292114257812</v>
+        <v>369.0975952148438</v>
       </c>
       <c r="F36" t="n">
-        <v>3852300</v>
+        <v>2384300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B37" t="n">
-        <v>367.3082703686788</v>
+        <v>366.5789276874148</v>
       </c>
       <c r="C37" t="n">
-        <v>374.1057935751742</v>
+        <v>370.4493335464572</v>
       </c>
       <c r="D37" t="n">
-        <v>365.7523266876615</v>
+        <v>364.682646350049</v>
       </c>
       <c r="E37" t="n">
-        <v>369.0975952148438</v>
+        <v>369.1365051269531</v>
       </c>
       <c r="F37" t="n">
-        <v>2384300</v>
+        <v>2643500</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B38" t="n">
-        <v>366.5789276874148</v>
+        <v>366.6275697464224</v>
       </c>
       <c r="C38" t="n">
-        <v>370.4493335464572</v>
+        <v>368.0570887541689</v>
       </c>
       <c r="D38" t="n">
-        <v>364.682646350049</v>
+        <v>363.3892576559226</v>
       </c>
       <c r="E38" t="n">
-        <v>369.1365051269531</v>
+        <v>367.9306640625</v>
       </c>
       <c r="F38" t="n">
-        <v>2643500</v>
+        <v>2897600</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B39" t="n">
-        <v>366.6275697464224</v>
+        <v>366.9581821818597</v>
       </c>
       <c r="C39" t="n">
-        <v>368.0570887541689</v>
+        <v>373.1138475541215</v>
       </c>
       <c r="D39" t="n">
-        <v>363.3892576559226</v>
+        <v>366.3746996179726</v>
       </c>
       <c r="E39" t="n">
-        <v>367.9306640625</v>
+        <v>372.5303649902344</v>
       </c>
       <c r="F39" t="n">
-        <v>2897600</v>
+        <v>2590000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B40" t="n">
-        <v>366.9581821818597</v>
+        <v>372.2483997179557</v>
       </c>
       <c r="C40" t="n">
-        <v>373.1138475541215</v>
+        <v>372.8610549707219</v>
       </c>
       <c r="D40" t="n">
-        <v>366.3746996179726</v>
+        <v>360.3260169130116</v>
       </c>
       <c r="E40" t="n">
-        <v>372.5303649902344</v>
+        <v>363.5448608398438</v>
       </c>
       <c r="F40" t="n">
-        <v>2590000</v>
+        <v>4763000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B41" t="n">
-        <v>372.2483997179557</v>
+        <v>361.5805182090473</v>
       </c>
       <c r="C41" t="n">
-        <v>372.8610549707219</v>
+        <v>362.3973820280062</v>
       </c>
       <c r="D41" t="n">
-        <v>360.3260169130116</v>
+        <v>357.4280900328899</v>
       </c>
       <c r="E41" t="n">
-        <v>363.5448608398438</v>
+        <v>358.90625</v>
       </c>
       <c r="F41" t="n">
-        <v>4763000</v>
+        <v>3622100</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B42" t="n">
-        <v>361.5805182090473</v>
+        <v>358.8284019214945</v>
       </c>
       <c r="C42" t="n">
-        <v>362.3973820280062</v>
+        <v>363.3600740840942</v>
       </c>
       <c r="D42" t="n">
-        <v>357.4280900328899</v>
+        <v>357.4475238166886</v>
       </c>
       <c r="E42" t="n">
-        <v>358.90625</v>
+        <v>360.8900146484375</v>
       </c>
       <c r="F42" t="n">
-        <v>3622100</v>
+        <v>2766400</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B43" t="n">
-        <v>358.8284322647385</v>
+        <v>359.6064305558101</v>
       </c>
       <c r="C43" t="n">
-        <v>363.3601048105454</v>
+        <v>360.452467039932</v>
       </c>
       <c r="D43" t="n">
-        <v>357.4475540431628</v>
+        <v>353.4410301931099</v>
       </c>
       <c r="E43" t="n">
-        <v>360.8900451660156</v>
+        <v>360.2287902832031</v>
       </c>
       <c r="F43" t="n">
-        <v>2766400</v>
+        <v>3257900</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B44" t="n">
-        <v>359.6064305558101</v>
+        <v>361.7458003836202</v>
       </c>
       <c r="C44" t="n">
-        <v>360.452467039932</v>
+        <v>365.6453789483504</v>
       </c>
       <c r="D44" t="n">
-        <v>353.4410301931099</v>
+        <v>360.6955554382075</v>
       </c>
       <c r="E44" t="n">
-        <v>360.2287902832031</v>
+        <v>363.933837890625</v>
       </c>
       <c r="F44" t="n">
-        <v>3257900</v>
+        <v>2407300</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B45" t="n">
-        <v>361.7458003836202</v>
+        <v>361.8138665438969</v>
       </c>
       <c r="C45" t="n">
-        <v>365.6453789483504</v>
+        <v>363.272558161854</v>
       </c>
       <c r="D45" t="n">
-        <v>360.6955554382075</v>
+        <v>358.8478721249137</v>
       </c>
       <c r="E45" t="n">
-        <v>363.933837890625</v>
+        <v>360.9094848632812</v>
       </c>
       <c r="F45" t="n">
-        <v>2407300</v>
+        <v>3375800</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B46" t="n">
-        <v>361.8138665438969</v>
+        <v>361.4249087666506</v>
       </c>
       <c r="C46" t="n">
-        <v>363.272558161854</v>
+        <v>363.2336722315698</v>
       </c>
       <c r="D46" t="n">
-        <v>358.8478721249137</v>
+        <v>356.5236963397476</v>
       </c>
       <c r="E46" t="n">
-        <v>360.9094848632812</v>
+        <v>357.9337768554688</v>
       </c>
       <c r="F46" t="n">
-        <v>3375800</v>
+        <v>3034800</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B47" t="n">
-        <v>361.4249087666506</v>
+        <v>355.8332360732777</v>
       </c>
       <c r="C47" t="n">
-        <v>363.2336722315698</v>
+        <v>357.2141141827383</v>
       </c>
       <c r="D47" t="n">
-        <v>356.5236963397476</v>
+        <v>349.8914834635758</v>
       </c>
       <c r="E47" t="n">
-        <v>357.9337768554688</v>
+        <v>352.3809814453125</v>
       </c>
       <c r="F47" t="n">
-        <v>3034800</v>
+        <v>3413300</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B48" t="n">
-        <v>355.8332360732777</v>
+        <v>351.1848930100947</v>
       </c>
       <c r="C48" t="n">
-        <v>357.2141141827383</v>
+        <v>353.7619090719871</v>
       </c>
       <c r="D48" t="n">
-        <v>349.8914834635758</v>
+        <v>346.2934147079206</v>
       </c>
       <c r="E48" t="n">
-        <v>352.3809814453125</v>
+        <v>348.1702575683594</v>
       </c>
       <c r="F48" t="n">
-        <v>3413300</v>
+        <v>5127200</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B49" t="n">
-        <v>351.1848930100947</v>
+        <v>330.6173283766702</v>
       </c>
       <c r="C49" t="n">
-        <v>353.7619090719871</v>
+        <v>339.1944125402241</v>
       </c>
       <c r="D49" t="n">
-        <v>346.2934147079206</v>
+        <v>326.7566567053178</v>
       </c>
       <c r="E49" t="n">
-        <v>348.1702575683594</v>
+        <v>327.2137145996094</v>
       </c>
       <c r="F49" t="n">
-        <v>5127200</v>
+        <v>10168500</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B50" t="n">
-        <v>330.6173283766702</v>
+        <v>331.5800319327479</v>
       </c>
       <c r="C50" t="n">
-        <v>339.1944125402241</v>
+        <v>332.3385503338413</v>
       </c>
       <c r="D50" t="n">
-        <v>326.7566567053178</v>
+        <v>322.2444002966442</v>
       </c>
       <c r="E50" t="n">
-        <v>327.2137145996094</v>
+        <v>325.2882080078125</v>
       </c>
       <c r="F50" t="n">
-        <v>10168500</v>
+        <v>7595000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B51" t="n">
-        <v>331.5800630406063</v>
+        <v>327.0969997002432</v>
       </c>
       <c r="C51" t="n">
-        <v>332.3385815128617</v>
+        <v>329.567059191382</v>
       </c>
       <c r="D51" t="n">
-        <v>322.2444305286613</v>
+        <v>322.9835082613831</v>
       </c>
       <c r="E51" t="n">
-        <v>325.2882385253906</v>
+        <v>323.2266235351562</v>
       </c>
       <c r="F51" t="n">
-        <v>7595000</v>
+        <v>4025300</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B52" t="n">
-        <v>327.0970305832446</v>
+        <v>325.3563217063679</v>
       </c>
       <c r="C52" t="n">
-        <v>329.567090307595</v>
+        <v>337.3662223876241</v>
       </c>
       <c r="D52" t="n">
-        <v>322.9835387560075</v>
+        <v>323.8295506364051</v>
       </c>
       <c r="E52" t="n">
-        <v>323.2266540527344</v>
+        <v>333.8653564453125</v>
       </c>
       <c r="F52" t="n">
-        <v>4025300</v>
+        <v>7441300</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B53" t="n">
-        <v>325.3563217063679</v>
+        <v>332.7761999080408</v>
       </c>
       <c r="C53" t="n">
-        <v>337.3662223876241</v>
+        <v>334.2445959868845</v>
       </c>
       <c r="D53" t="n">
-        <v>323.8295506364051</v>
+        <v>327.2817709576355</v>
       </c>
       <c r="E53" t="n">
-        <v>333.8653564453125</v>
+        <v>327.3109436035156</v>
       </c>
       <c r="F53" t="n">
-        <v>7441300</v>
+        <v>6132900</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B54" t="n">
-        <v>332.7762309351845</v>
+        <v>329.6643336820279</v>
       </c>
       <c r="C54" t="n">
-        <v>334.2446271509373</v>
+        <v>343.2787899402826</v>
       </c>
       <c r="D54" t="n">
-        <v>327.2818014724936</v>
+        <v>329.5184704432642</v>
       </c>
       <c r="E54" t="n">
-        <v>327.3109741210938</v>
+        <v>341.4019470214844</v>
       </c>
       <c r="F54" t="n">
-        <v>6132900</v>
+        <v>6316600</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B55" t="n">
-        <v>329.6643042136632</v>
+        <v>340.6142414881474</v>
       </c>
       <c r="C55" t="n">
-        <v>343.2787592549354</v>
+        <v>347.4895190539308</v>
       </c>
       <c r="D55" t="n">
-        <v>329.518440987938</v>
+        <v>339.3889309798961</v>
       </c>
       <c r="E55" t="n">
-        <v>341.4019165039062</v>
+        <v>345.6807556152344</v>
       </c>
       <c r="F55" t="n">
-        <v>6316600</v>
+        <v>4517300</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B56" t="n">
-        <v>340.6142414881474</v>
+        <v>345.1556329381714</v>
       </c>
       <c r="C56" t="n">
-        <v>347.4895190539308</v>
+        <v>347.9757643711671</v>
       </c>
       <c r="D56" t="n">
-        <v>339.3889309798961</v>
+        <v>343.7650205997065</v>
       </c>
       <c r="E56" t="n">
-        <v>345.6807556152344</v>
+        <v>347.0908508300781</v>
       </c>
       <c r="F56" t="n">
-        <v>4517300</v>
+        <v>2119600</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B57" t="n">
-        <v>345.1556329381714</v>
+        <v>344.2998610600955</v>
       </c>
       <c r="C57" t="n">
-        <v>347.9757643711671</v>
+        <v>352.3129611811121</v>
       </c>
       <c r="D57" t="n">
-        <v>343.7650205997065</v>
+        <v>343.1620981246396</v>
       </c>
       <c r="E57" t="n">
-        <v>347.0908508300781</v>
+        <v>347.4895324707031</v>
       </c>
       <c r="F57" t="n">
-        <v>2119600</v>
+        <v>5107100</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B58" t="n">
-        <v>344.2998610600955</v>
+        <v>347.0032746652403</v>
       </c>
       <c r="C58" t="n">
-        <v>352.3129611811121</v>
+        <v>347.654836647816</v>
       </c>
       <c r="D58" t="n">
-        <v>343.1620981246396</v>
+        <v>341.6255660714526</v>
       </c>
       <c r="E58" t="n">
-        <v>347.4895324707031</v>
+        <v>344.2803955078125</v>
       </c>
       <c r="F58" t="n">
-        <v>5107100</v>
+        <v>3965300</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B59" t="n">
-        <v>347.0032746652403</v>
+        <v>344.7374926404726</v>
       </c>
       <c r="C59" t="n">
-        <v>347.654836647816</v>
+        <v>350.5430871450869</v>
       </c>
       <c r="D59" t="n">
-        <v>341.6255660714526</v>
+        <v>344.0081467463108</v>
       </c>
       <c r="E59" t="n">
-        <v>344.2803955078125</v>
+        <v>348.0535888671875</v>
       </c>
       <c r="F59" t="n">
-        <v>3965300</v>
+        <v>4166700</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,25 +1977,25 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B60" t="n">
-        <v>344.7374926404726</v>
+        <v>348.719115353366</v>
       </c>
       <c r="C60" t="n">
-        <v>350.5430871450869</v>
+        <v>349.9131924709116</v>
       </c>
       <c r="D60" t="n">
-        <v>344.0081467463108</v>
+        <v>342.5627647323979</v>
       </c>
       <c r="E60" t="n">
-        <v>348.0535888671875</v>
+        <v>343.7079162597656</v>
       </c>
       <c r="F60" t="n">
-        <v>4166700</v>
+        <v>4022800</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2003,25 +2003,25 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B61" t="n">
-        <v>348.719115353366</v>
+        <v>343.1989840484338</v>
       </c>
       <c r="C61" t="n">
-        <v>349.9131924709116</v>
+        <v>348.0633770310509</v>
       </c>
       <c r="D61" t="n">
-        <v>342.5627647323979</v>
+        <v>342.102787861214</v>
       </c>
       <c r="E61" t="n">
-        <v>343.7079162597656</v>
+        <v>347.0748291015625</v>
       </c>
       <c r="F61" t="n">
-        <v>4022800</v>
+        <v>5959200</v>
       </c>
       <c r="G61" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B62" t="n">
-        <v>343.1989840484338</v>
+        <v>344.4713302562425</v>
       </c>
       <c r="C62" t="n">
-        <v>348.0633770310509</v>
+        <v>344.6083398260661</v>
       </c>
       <c r="D62" t="n">
-        <v>342.102787861214</v>
+        <v>338.3541382135411</v>
       </c>
       <c r="E62" t="n">
-        <v>347.0748291015625</v>
+        <v>342.4746704101562</v>
       </c>
       <c r="F62" t="n">
-        <v>5959200</v>
+        <v>7273000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B63" t="n">
-        <v>344.4713302562425</v>
+        <v>340.3703677160696</v>
       </c>
       <c r="C63" t="n">
-        <v>344.6083398260661</v>
+        <v>349.0910404146574</v>
       </c>
       <c r="D63" t="n">
-        <v>338.3541382135411</v>
+        <v>337.6298477160418</v>
       </c>
       <c r="E63" t="n">
-        <v>342.4746704101562</v>
+        <v>337.9332580566406</v>
       </c>
       <c r="F63" t="n">
-        <v>7273000</v>
+        <v>5063100</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B64" t="n">
-        <v>340.3703677160696</v>
+        <v>336.7881454975472</v>
       </c>
       <c r="C64" t="n">
-        <v>349.0910404146574</v>
+        <v>344.5398348592771</v>
       </c>
       <c r="D64" t="n">
-        <v>337.6298477160418</v>
+        <v>336.6902644468525</v>
       </c>
       <c r="E64" t="n">
-        <v>337.9332580566406</v>
+        <v>343.6687622070312</v>
       </c>
       <c r="F64" t="n">
-        <v>5063100</v>
+        <v>6316100</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B65" t="n">
-        <v>336.7881454975472</v>
+        <v>348.4352899865784</v>
       </c>
       <c r="C65" t="n">
-        <v>344.5398348592771</v>
+        <v>355.0124966552466</v>
       </c>
       <c r="D65" t="n">
-        <v>336.6902644468525</v>
+        <v>346.4190656980946</v>
       </c>
       <c r="E65" t="n">
-        <v>343.6687622070312</v>
+        <v>349.8642578125</v>
       </c>
       <c r="F65" t="n">
-        <v>6316100</v>
+        <v>6609800</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B66" t="n">
-        <v>348.4352899865784</v>
+        <v>351.6260236653551</v>
       </c>
       <c r="C66" t="n">
-        <v>355.0124966552466</v>
+        <v>353.0941498724499</v>
       </c>
       <c r="D66" t="n">
-        <v>346.4190656980946</v>
+        <v>348.4842120764174</v>
       </c>
       <c r="E66" t="n">
-        <v>349.8642578125</v>
+        <v>352.0077209472656</v>
       </c>
       <c r="F66" t="n">
-        <v>6609800</v>
+        <v>3861200</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B67" t="n">
-        <v>351.6260236653551</v>
+        <v>351.7532309142689</v>
       </c>
       <c r="C67" t="n">
-        <v>353.0941498724499</v>
+        <v>354.9635320383587</v>
       </c>
       <c r="D67" t="n">
-        <v>348.4842120764174</v>
+        <v>348.0633216327761</v>
       </c>
       <c r="E67" t="n">
-        <v>352.0077209472656</v>
+        <v>349.4042053222656</v>
       </c>
       <c r="F67" t="n">
-        <v>3861200</v>
+        <v>4387400</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B68" t="n">
-        <v>351.7532309142689</v>
+        <v>349.3161510627795</v>
       </c>
       <c r="C68" t="n">
-        <v>354.9635320383587</v>
+        <v>351.1170489325283</v>
       </c>
       <c r="D68" t="n">
-        <v>348.0633216327761</v>
+        <v>344.3343131247511</v>
       </c>
       <c r="E68" t="n">
-        <v>349.4042053222656</v>
+        <v>345.1858215332031</v>
       </c>
       <c r="F68" t="n">
-        <v>4387400</v>
+        <v>3497200</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B69" t="n">
-        <v>349.3161510627795</v>
+        <v>344.4909144902828</v>
       </c>
       <c r="C69" t="n">
-        <v>351.1170489325283</v>
+        <v>349.9034051286982</v>
       </c>
       <c r="D69" t="n">
-        <v>344.3343131247511</v>
+        <v>343.5219607726549</v>
       </c>
       <c r="E69" t="n">
-        <v>345.1858215332031</v>
+        <v>349.1693420410156</v>
       </c>
       <c r="F69" t="n">
-        <v>3497200</v>
+        <v>3875200</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B70" t="n">
-        <v>344.4909144902828</v>
+        <v>355.8150843258923</v>
       </c>
       <c r="C70" t="n">
-        <v>349.9034051286982</v>
+        <v>358.5164162998122</v>
       </c>
       <c r="D70" t="n">
-        <v>343.5219607726549</v>
+        <v>347.0258911387745</v>
       </c>
       <c r="E70" t="n">
-        <v>349.1693420410156</v>
+        <v>347.4467468261719</v>
       </c>
       <c r="F70" t="n">
-        <v>3875200</v>
+        <v>4805200</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B71" t="n">
-        <v>355.8150843258923</v>
+        <v>346.5854112795514</v>
       </c>
       <c r="C71" t="n">
-        <v>358.5164162998122</v>
+        <v>346.5854112795514</v>
       </c>
       <c r="D71" t="n">
-        <v>347.0258911387745</v>
+        <v>337.5907194306183</v>
       </c>
       <c r="E71" t="n">
-        <v>347.4467468261719</v>
+        <v>337.6690063476562</v>
       </c>
       <c r="F71" t="n">
-        <v>4805200</v>
+        <v>12825600</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B72" t="n">
-        <v>346.5854112795514</v>
+        <v>337.9724124645031</v>
       </c>
       <c r="C72" t="n">
-        <v>346.5854112795514</v>
+        <v>340.507373272994</v>
       </c>
       <c r="D72" t="n">
-        <v>337.5907194306183</v>
+        <v>336.3966381250771</v>
       </c>
       <c r="E72" t="n">
-        <v>337.6690063476562</v>
+        <v>339.0294799804688</v>
       </c>
       <c r="F72" t="n">
-        <v>12825600</v>
+        <v>3523700</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B73" t="n">
-        <v>337.9724124645031</v>
+        <v>336.6902894441487</v>
       </c>
       <c r="C73" t="n">
-        <v>340.507373272994</v>
+        <v>340.1159173890746</v>
       </c>
       <c r="D73" t="n">
-        <v>336.3966381250771</v>
+        <v>334.6740651003779</v>
       </c>
       <c r="E73" t="n">
-        <v>339.0294799804688</v>
+        <v>337.6396789550781</v>
       </c>
       <c r="F73" t="n">
-        <v>3523700</v>
+        <v>3873400</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B74" t="n">
-        <v>336.6902894441487</v>
+        <v>337.0230069808841</v>
       </c>
       <c r="C74" t="n">
-        <v>340.1159173890746</v>
+        <v>340.8597228049852</v>
       </c>
       <c r="D74" t="n">
-        <v>334.6740651003779</v>
+        <v>336.5923542903493</v>
       </c>
       <c r="E74" t="n">
-        <v>337.6396789550781</v>
+        <v>339.9592590332031</v>
       </c>
       <c r="F74" t="n">
-        <v>3873400</v>
+        <v>1368600</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B75" t="n">
-        <v>337.0230069808841</v>
+        <v>339.616749893519</v>
       </c>
       <c r="C75" t="n">
-        <v>340.8597228049852</v>
+        <v>342.6117251227173</v>
       </c>
       <c r="D75" t="n">
-        <v>336.5923542903493</v>
+        <v>339.2056912607851</v>
       </c>
       <c r="E75" t="n">
-        <v>339.9592590332031</v>
+        <v>342.3474731445312</v>
       </c>
       <c r="F75" t="n">
-        <v>1368600</v>
+        <v>1786900</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B76" t="n">
-        <v>339.616749893519</v>
+        <v>342.5627579984686</v>
       </c>
       <c r="C76" t="n">
-        <v>342.6117251227173</v>
+        <v>342.8759654029374</v>
       </c>
       <c r="D76" t="n">
-        <v>339.2056912607851</v>
+        <v>337.4243166284915</v>
       </c>
       <c r="E76" t="n">
-        <v>342.3474731445312</v>
+        <v>340.0669555664062</v>
       </c>
       <c r="F76" t="n">
-        <v>1786900</v>
+        <v>3790000</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B77" t="n">
-        <v>342.5627579984686</v>
+        <v>338.6771490106644</v>
       </c>
       <c r="C77" t="n">
-        <v>342.8759654029374</v>
+        <v>339.6069742481806</v>
       </c>
       <c r="D77" t="n">
-        <v>337.4243166284915</v>
+        <v>336.4162369795515</v>
       </c>
       <c r="E77" t="n">
-        <v>340.0669555664062</v>
+        <v>338.9903564453125</v>
       </c>
       <c r="F77" t="n">
-        <v>3790000</v>
+        <v>2392600</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B78" t="n">
-        <v>338.6771490106644</v>
+        <v>338.1583920810744</v>
       </c>
       <c r="C78" t="n">
-        <v>339.6069742481806</v>
+        <v>339.342672153089</v>
       </c>
       <c r="D78" t="n">
-        <v>336.4162369795515</v>
+        <v>336.6609045931061</v>
       </c>
       <c r="E78" t="n">
-        <v>338.9903564453125</v>
+        <v>336.7881469726562</v>
       </c>
       <c r="F78" t="n">
-        <v>2392600</v>
+        <v>2317500</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B79" t="n">
-        <v>338.1583920810744</v>
+        <v>336.1323595285862</v>
       </c>
       <c r="C79" t="n">
-        <v>339.342672153089</v>
+        <v>341.0848358843269</v>
       </c>
       <c r="D79" t="n">
-        <v>336.6609045931061</v>
+        <v>333.6757154817447</v>
       </c>
       <c r="E79" t="n">
-        <v>336.7881469726562</v>
+        <v>338.4715881347656</v>
       </c>
       <c r="F79" t="n">
-        <v>2317500</v>
+        <v>3763000</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B80" t="n">
-        <v>336.1323595285862</v>
+        <v>335.4179027837736</v>
       </c>
       <c r="C80" t="n">
-        <v>341.0848358843269</v>
+        <v>339.9690879170088</v>
       </c>
       <c r="D80" t="n">
-        <v>333.6757154817447</v>
+        <v>333.9987022113515</v>
       </c>
       <c r="E80" t="n">
-        <v>338.4715881347656</v>
+        <v>336.7783508300781</v>
       </c>
       <c r="F80" t="n">
-        <v>3763000</v>
+        <v>4725300</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B81" t="n">
-        <v>335.4179027837736</v>
+        <v>334.2433821573216</v>
       </c>
       <c r="C81" t="n">
-        <v>339.9690879170088</v>
+        <v>343.2283069014873</v>
       </c>
       <c r="D81" t="n">
-        <v>333.9987022113515</v>
+        <v>330.5339084400161</v>
       </c>
       <c r="E81" t="n">
-        <v>336.7783508300781</v>
+        <v>341.8678588867188</v>
       </c>
       <c r="F81" t="n">
-        <v>4725300</v>
+        <v>4680300</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B82" t="n">
-        <v>334.2433821573216</v>
+        <v>345.8318135746193</v>
       </c>
       <c r="C82" t="n">
-        <v>343.2283069014873</v>
+        <v>350.882171425454</v>
       </c>
       <c r="D82" t="n">
-        <v>330.5339084400161</v>
+        <v>341.6133999004275</v>
       </c>
       <c r="E82" t="n">
-        <v>341.8678588867188</v>
+        <v>341.6427612304688</v>
       </c>
       <c r="F82" t="n">
-        <v>4680300</v>
+        <v>4442700</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B83" t="n">
-        <v>345.8318135746193</v>
+        <v>337.9724185347548</v>
       </c>
       <c r="C83" t="n">
-        <v>350.882171425454</v>
+        <v>355.5214122846852</v>
       </c>
       <c r="D83" t="n">
-        <v>341.6133999004275</v>
+        <v>336.7881384925595</v>
       </c>
       <c r="E83" t="n">
-        <v>341.6427612304688</v>
+        <v>351.9196166992188</v>
       </c>
       <c r="F83" t="n">
-        <v>4442700</v>
+        <v>5196500</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B84" t="n">
-        <v>337.9724185347548</v>
+        <v>355.7759014105663</v>
       </c>
       <c r="C84" t="n">
-        <v>355.5214122846852</v>
+        <v>367.5111134698199</v>
       </c>
       <c r="D84" t="n">
-        <v>336.7881384925595</v>
+        <v>353.632434855731</v>
       </c>
       <c r="E84" t="n">
-        <v>351.9196166992188</v>
+        <v>366.67919921875</v>
       </c>
       <c r="F84" t="n">
-        <v>5196500</v>
+        <v>7093500</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B85" t="n">
-        <v>355.7759014105663</v>
+        <v>366.679226053498</v>
       </c>
       <c r="C85" t="n">
-        <v>367.5111134698199</v>
+        <v>368.4214013397691</v>
       </c>
       <c r="D85" t="n">
-        <v>353.632434855731</v>
+        <v>361.4037447316197</v>
       </c>
       <c r="E85" t="n">
-        <v>366.67919921875</v>
+        <v>366.9728393554688</v>
       </c>
       <c r="F85" t="n">
-        <v>7093500</v>
+        <v>5859800</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B86" t="n">
-        <v>366.679226053498</v>
+        <v>367.8830461936743</v>
       </c>
       <c r="C86" t="n">
-        <v>368.4214013397691</v>
+        <v>372.1014596119851</v>
       </c>
       <c r="D86" t="n">
-        <v>361.4037447316197</v>
+        <v>362.9403667655412</v>
       </c>
       <c r="E86" t="n">
-        <v>366.9728393554688</v>
+        <v>371.6708068847656</v>
       </c>
       <c r="F86" t="n">
-        <v>5859800</v>
+        <v>4785800</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B87" t="n">
-        <v>367.8830461936743</v>
+        <v>368.6856307593888</v>
       </c>
       <c r="C87" t="n">
-        <v>372.1014596119851</v>
+        <v>372.0133774109565</v>
       </c>
       <c r="D87" t="n">
-        <v>362.9403667655412</v>
+        <v>366.023427464314</v>
       </c>
       <c r="E87" t="n">
-        <v>371.6708068847656</v>
+        <v>367.9613647460938</v>
       </c>
       <c r="F87" t="n">
-        <v>4785800</v>
+        <v>4959900</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B88" t="n">
-        <v>368.6856307593888</v>
+        <v>368.0298576269892</v>
       </c>
       <c r="C88" t="n">
-        <v>372.0133774109565</v>
+        <v>372.1014644570138</v>
       </c>
       <c r="D88" t="n">
-        <v>366.023427464314</v>
+        <v>366.5030087993679</v>
       </c>
       <c r="E88" t="n">
-        <v>367.9613647460938</v>
+        <v>371.1031494140625</v>
       </c>
       <c r="F88" t="n">
-        <v>4959900</v>
+        <v>2990100</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B89" t="n">
-        <v>368.0298576269892</v>
+        <v>371.1912414425437</v>
       </c>
       <c r="C89" t="n">
-        <v>372.1014644570138</v>
+        <v>374.6364335107019</v>
       </c>
       <c r="D89" t="n">
-        <v>366.5030087993679</v>
+        <v>369.4882246061678</v>
       </c>
       <c r="E89" t="n">
-        <v>371.1031494140625</v>
+        <v>372.0917053222656</v>
       </c>
       <c r="F89" t="n">
-        <v>2990100</v>
+        <v>3709000</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B90" t="n">
-        <v>371.1912414425437</v>
+        <v>364.330180714857</v>
       </c>
       <c r="C90" t="n">
-        <v>374.6364335107019</v>
+        <v>369.3218156656606</v>
       </c>
       <c r="D90" t="n">
-        <v>369.4882246061678</v>
+        <v>363.4101525923161</v>
       </c>
       <c r="E90" t="n">
-        <v>372.0917053222656</v>
+        <v>367.1391906738281</v>
       </c>
       <c r="F90" t="n">
-        <v>3709000</v>
+        <v>5353700</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B91" t="n">
-        <v>364.330180714857</v>
+        <v>367.8145223498818</v>
       </c>
       <c r="C91" t="n">
-        <v>369.3218156656606</v>
+        <v>377.7195050958379</v>
       </c>
       <c r="D91" t="n">
-        <v>363.4101525923161</v>
+        <v>366.7183262816438</v>
       </c>
       <c r="E91" t="n">
-        <v>367.1391906738281</v>
+        <v>376.4667053222656</v>
       </c>
       <c r="F91" t="n">
-        <v>5353700</v>
+        <v>5169800</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B92" t="n">
-        <v>367.8145223498818</v>
+        <v>378.2382530449191</v>
       </c>
       <c r="C92" t="n">
-        <v>377.7195050958379</v>
+        <v>382.3000628313615</v>
       </c>
       <c r="D92" t="n">
-        <v>366.7183262816438</v>
+        <v>372.4440352517285</v>
       </c>
       <c r="E92" t="n">
-        <v>376.4667053222656</v>
+        <v>372.9334106445312</v>
       </c>
       <c r="F92" t="n">
-        <v>5169800</v>
+        <v>4828100</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B93" t="n">
-        <v>378.2382530449191</v>
+        <v>373.3934198383746</v>
       </c>
       <c r="C93" t="n">
-        <v>382.3000628313615</v>
+        <v>376.2024297773683</v>
       </c>
       <c r="D93" t="n">
-        <v>372.4440352517285</v>
+        <v>371.1520722052226</v>
       </c>
       <c r="E93" t="n">
-        <v>372.9334106445312</v>
+        <v>375.6151733398438</v>
       </c>
       <c r="F93" t="n">
-        <v>4828100</v>
+        <v>3138300</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B94" t="n">
-        <v>373.3934198383746</v>
+        <v>376.8190408591946</v>
       </c>
       <c r="C94" t="n">
-        <v>376.2024297773683</v>
+        <v>379.1876308298576</v>
       </c>
       <c r="D94" t="n">
-        <v>371.1520722052226</v>
+        <v>373.8338630026265</v>
       </c>
       <c r="E94" t="n">
-        <v>375.6151733398438</v>
+        <v>378.3165283203125</v>
       </c>
       <c r="F94" t="n">
-        <v>3138300</v>
+        <v>3984800</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B95" t="n">
-        <v>376.8190408591946</v>
+        <v>376.7701106050471</v>
       </c>
       <c r="C95" t="n">
-        <v>379.1876308298576</v>
+        <v>378.2871623096181</v>
       </c>
       <c r="D95" t="n">
-        <v>373.8338630026265</v>
+        <v>370.2320329388677</v>
       </c>
       <c r="E95" t="n">
-        <v>378.3165283203125</v>
+        <v>372.2776184082031</v>
       </c>
       <c r="F95" t="n">
-        <v>3984800</v>
+        <v>3466100</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B96" t="n">
-        <v>376.7701106050471</v>
+        <v>372.1308039100364</v>
       </c>
       <c r="C96" t="n">
-        <v>378.2871623096181</v>
+        <v>372.9040253443087</v>
       </c>
       <c r="D96" t="n">
-        <v>370.2320329388677</v>
+        <v>365.7102015587281</v>
       </c>
       <c r="E96" t="n">
-        <v>372.2776184082031</v>
+        <v>367.3251342773438</v>
       </c>
       <c r="F96" t="n">
-        <v>3466100</v>
+        <v>3371500</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B97" t="n">
-        <v>372.1308039100364</v>
+        <v>366.9336686607455</v>
       </c>
       <c r="C97" t="n">
-        <v>372.9040253443087</v>
+        <v>369.0771353006065</v>
       </c>
       <c r="D97" t="n">
-        <v>365.7102015587281</v>
+        <v>362.284602364362</v>
       </c>
       <c r="E97" t="n">
-        <v>367.3251342773438</v>
+        <v>363.9093322753906</v>
       </c>
       <c r="F97" t="n">
-        <v>3371500</v>
+        <v>4744500</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B98" t="n">
-        <v>366.9336686607455</v>
+        <v>364.4965491637078</v>
       </c>
       <c r="C98" t="n">
-        <v>369.0771353006065</v>
+        <v>367.1489551783843</v>
       </c>
       <c r="D98" t="n">
-        <v>362.284602364362</v>
+        <v>360.7185559568027</v>
       </c>
       <c r="E98" t="n">
-        <v>363.9093322753906</v>
+        <v>366.6302185058594</v>
       </c>
       <c r="F98" t="n">
-        <v>4744500</v>
+        <v>3755600</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B99" t="n">
-        <v>364.4965491637078</v>
+        <v>366.2876778370263</v>
       </c>
       <c r="C99" t="n">
-        <v>367.1489551783843</v>
+        <v>371.5827230758924</v>
       </c>
       <c r="D99" t="n">
-        <v>360.7185559568027</v>
+        <v>360.4151732293658</v>
       </c>
       <c r="E99" t="n">
-        <v>366.6302185058594</v>
+        <v>370.0852355957031</v>
       </c>
       <c r="F99" t="n">
-        <v>3755600</v>
+        <v>4757200</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B100" t="n">
-        <v>366.2876778370263</v>
+        <v>369.2728845813793</v>
       </c>
       <c r="C100" t="n">
-        <v>371.5827230758924</v>
+        <v>383.4549736116182</v>
       </c>
       <c r="D100" t="n">
-        <v>360.4151732293658</v>
+        <v>368.9890384961104</v>
       </c>
       <c r="E100" t="n">
-        <v>370.0852355957031</v>
+        <v>373.0019226074219</v>
       </c>
       <c r="F100" t="n">
-        <v>4757200</v>
+        <v>5684400</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B101" t="n">
-        <v>369.2728845813793</v>
+        <v>376.4177654444651</v>
       </c>
       <c r="C101" t="n">
-        <v>383.4549736116182</v>
+        <v>382.2315475683361</v>
       </c>
       <c r="D101" t="n">
-        <v>368.9890384961104</v>
+        <v>376.1926420082714</v>
       </c>
       <c r="E101" t="n">
-        <v>373.0019226074219</v>
+        <v>378.9723205566406</v>
       </c>
       <c r="F101" t="n">
-        <v>5684400</v>
+        <v>5574700</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B102" t="n">
-        <v>376.4177654444651</v>
+        <v>378.4633475893863</v>
       </c>
       <c r="C102" t="n">
-        <v>382.2315475683361</v>
+        <v>378.776555010176</v>
       </c>
       <c r="D102" t="n">
-        <v>376.1926420082714</v>
+        <v>372.7376495049467</v>
       </c>
       <c r="E102" t="n">
-        <v>378.9723205566406</v>
+        <v>374.2449340820312</v>
       </c>
       <c r="F102" t="n">
-        <v>5574700</v>
+        <v>3759700</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B103" t="n">
-        <v>378.4633475893863</v>
+        <v>373.2368128082787</v>
       </c>
       <c r="C103" t="n">
-        <v>378.776555010176</v>
+        <v>378.1599279570784</v>
       </c>
       <c r="D103" t="n">
-        <v>372.7376495049467</v>
+        <v>371.0444206547449</v>
       </c>
       <c r="E103" t="n">
-        <v>374.2449340820312</v>
+        <v>376.9658508300781</v>
       </c>
       <c r="F103" t="n">
-        <v>3759700</v>
+        <v>4685400</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B104" t="n">
-        <v>373.2368128082787</v>
+        <v>376.1926410669886</v>
       </c>
       <c r="C104" t="n">
-        <v>378.1599279570784</v>
+        <v>377.5824803376956</v>
       </c>
       <c r="D104" t="n">
-        <v>371.0444206547449</v>
+        <v>370.163562457197</v>
       </c>
       <c r="E104" t="n">
-        <v>376.9658508300781</v>
+        <v>372.904052734375</v>
       </c>
       <c r="F104" t="n">
-        <v>4685400</v>
+        <v>3639300</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B105" t="n">
-        <v>376.1926410669886</v>
+        <v>375.6543348626084</v>
       </c>
       <c r="C105" t="n">
-        <v>377.5824803376956</v>
+        <v>383.4158213872818</v>
       </c>
       <c r="D105" t="n">
-        <v>370.163562457197</v>
+        <v>373.8240756812119</v>
       </c>
       <c r="E105" t="n">
-        <v>372.904052734375</v>
+        <v>381.3995971679688</v>
       </c>
       <c r="F105" t="n">
-        <v>3639300</v>
+        <v>3160800</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B106" t="n">
-        <v>375.6543348626084</v>
+        <v>376.8190595355247</v>
       </c>
       <c r="C106" t="n">
-        <v>383.4158213872818</v>
+        <v>383.1026528395359</v>
       </c>
       <c r="D106" t="n">
-        <v>373.8240756812119</v>
+        <v>373.9610940454729</v>
       </c>
       <c r="E106" t="n">
-        <v>381.3995971679688</v>
+        <v>382.3783569335938</v>
       </c>
       <c r="F106" t="n">
-        <v>3160800</v>
+        <v>3229900</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B107" t="n">
-        <v>376.8190595355247</v>
+        <v>385.187358063094</v>
       </c>
       <c r="C107" t="n">
-        <v>383.1026528395359</v>
+        <v>389.1806779778082</v>
       </c>
       <c r="D107" t="n">
-        <v>373.9610940454729</v>
+        <v>380.7340539554721</v>
       </c>
       <c r="E107" t="n">
-        <v>382.3783569335938</v>
+        <v>381.9281311035156</v>
       </c>
       <c r="F107" t="n">
-        <v>3229900</v>
+        <v>3702200</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B108" t="n">
-        <v>385.187358063094</v>
+        <v>381.908594703622</v>
       </c>
       <c r="C108" t="n">
-        <v>389.1806779778082</v>
+        <v>385.6278359965556</v>
       </c>
       <c r="D108" t="n">
-        <v>380.7340539554721</v>
+        <v>378.8744610861731</v>
       </c>
       <c r="E108" t="n">
-        <v>381.9281311035156</v>
+        <v>382.7405090332031</v>
       </c>
       <c r="F108" t="n">
-        <v>3702200</v>
+        <v>2875900</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B109" t="n">
-        <v>381.908594703622</v>
+        <v>383.895448836351</v>
       </c>
       <c r="C109" t="n">
-        <v>385.6278359965556</v>
+        <v>385.6278270527202</v>
       </c>
       <c r="D109" t="n">
-        <v>378.8744610861731</v>
+        <v>372.4146908465991</v>
       </c>
       <c r="E109" t="n">
-        <v>382.7405090332031</v>
+        <v>374.9007263183594</v>
       </c>
       <c r="F109" t="n">
-        <v>2875900</v>
+        <v>3485300</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B110" t="n">
-        <v>383.895448836351</v>
+        <v>374.6168560607417</v>
       </c>
       <c r="C110" t="n">
-        <v>385.6278270527202</v>
+        <v>376.9364905994225</v>
       </c>
       <c r="D110" t="n">
-        <v>372.4146908465991</v>
+        <v>371.4750744620919</v>
       </c>
       <c r="E110" t="n">
-        <v>374.9007263183594</v>
+        <v>375.3704833984375</v>
       </c>
       <c r="F110" t="n">
-        <v>3485300</v>
+        <v>2982600</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B111" t="n">
-        <v>374.6168560607417</v>
+        <v>375.5857881596228</v>
       </c>
       <c r="C111" t="n">
-        <v>376.9364905994225</v>
+        <v>375.5857881596228</v>
       </c>
       <c r="D111" t="n">
-        <v>371.4750744620919</v>
+        <v>369.3707450420628</v>
       </c>
       <c r="E111" t="n">
-        <v>375.3704833984375</v>
+        <v>370.5354309082031</v>
       </c>
       <c r="F111" t="n">
-        <v>2982600</v>
+        <v>2930900</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B112" t="n">
-        <v>375.5857881596228</v>
+        <v>369.4295104342575</v>
       </c>
       <c r="C112" t="n">
-        <v>375.5857881596228</v>
+        <v>376.6428992274523</v>
       </c>
       <c r="D112" t="n">
-        <v>369.3707450420628</v>
+        <v>367.9613841983854</v>
       </c>
       <c r="E112" t="n">
-        <v>370.5354309082031</v>
+        <v>374.1275024414062</v>
       </c>
       <c r="F112" t="n">
-        <v>2930900</v>
+        <v>3984100</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B113" t="n">
-        <v>369.4295104342575</v>
+        <v>372.8942511780455</v>
       </c>
       <c r="C113" t="n">
-        <v>376.6428992274523</v>
+        <v>375.977340039125</v>
       </c>
       <c r="D113" t="n">
-        <v>367.9613841983854</v>
+        <v>361.7267011620893</v>
       </c>
       <c r="E113" t="n">
-        <v>374.1275024414062</v>
+        <v>368.979248046875</v>
       </c>
       <c r="F113" t="n">
-        <v>3984100</v>
+        <v>5495700</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B114" t="n">
-        <v>372.8942511780455</v>
+        <v>380.8417107584177</v>
       </c>
       <c r="C114" t="n">
-        <v>375.977340039125</v>
+        <v>385.9703852790173</v>
       </c>
       <c r="D114" t="n">
-        <v>361.7267011620893</v>
+        <v>374.0883361890514</v>
       </c>
       <c r="E114" t="n">
-        <v>368.979248046875</v>
+        <v>376.3101196289062</v>
       </c>
       <c r="F114" t="n">
-        <v>5495700</v>
+        <v>5675800</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B115" t="n">
-        <v>380.8417107584177</v>
+        <v>372.9725764492633</v>
       </c>
       <c r="C115" t="n">
-        <v>385.9703852790173</v>
+        <v>373.3347094680754</v>
       </c>
       <c r="D115" t="n">
-        <v>374.0883361890514</v>
+        <v>363.4786816926297</v>
       </c>
       <c r="E115" t="n">
-        <v>376.3101196289062</v>
+        <v>367.5894470214844</v>
       </c>
       <c r="F115" t="n">
-        <v>5675800</v>
+        <v>5036900</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B116" t="n">
-        <v>372.9725764492633</v>
+        <v>370.3592916198801</v>
       </c>
       <c r="C116" t="n">
-        <v>373.3347094680754</v>
+        <v>373.3738607688525</v>
       </c>
       <c r="D116" t="n">
-        <v>363.4786816926297</v>
+        <v>366.9728222621029</v>
       </c>
       <c r="E116" t="n">
-        <v>367.5894470214844</v>
+        <v>367.11962890625</v>
       </c>
       <c r="F116" t="n">
-        <v>5036900</v>
+        <v>2889400</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B117" t="n">
-        <v>370.3592916198801</v>
+        <v>365.915758878878</v>
       </c>
       <c r="C117" t="n">
-        <v>373.3738607688525</v>
+        <v>374.0687697501482</v>
       </c>
       <c r="D117" t="n">
-        <v>366.9728222621029</v>
+        <v>364.4280684193005</v>
       </c>
       <c r="E117" t="n">
-        <v>367.11962890625</v>
+        <v>372.6300048828125</v>
       </c>
       <c r="F117" t="n">
-        <v>2889400</v>
+        <v>4819500</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B118" t="n">
-        <v>365.915758878878</v>
+        <v>367.0315715092017</v>
       </c>
       <c r="C118" t="n">
-        <v>374.0687697501482</v>
+        <v>367.1392197663403</v>
       </c>
       <c r="D118" t="n">
-        <v>364.4280684193005</v>
+        <v>361.1590663650545</v>
       </c>
       <c r="E118" t="n">
-        <v>372.6300048828125</v>
+        <v>362.9306030273438</v>
       </c>
       <c r="F118" t="n">
-        <v>4819500</v>
+        <v>4537600</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B119" t="n">
-        <v>367.0315715092017</v>
+        <v>356.0010127710523</v>
       </c>
       <c r="C119" t="n">
-        <v>367.1392197663403</v>
+        <v>360.9436919959621</v>
       </c>
       <c r="D119" t="n">
-        <v>361.1590663650545</v>
+        <v>352.4677071137912</v>
       </c>
       <c r="E119" t="n">
-        <v>362.9306030273438</v>
+        <v>359.1232299804688</v>
       </c>
       <c r="F119" t="n">
-        <v>4537600</v>
+        <v>3964700</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B120" t="n">
-        <v>356.0010127710523</v>
+        <v>358.4185545746917</v>
       </c>
       <c r="C120" t="n">
-        <v>360.9436919959621</v>
+        <v>361.716939988571</v>
       </c>
       <c r="D120" t="n">
-        <v>352.4677071137912</v>
+        <v>353.8282109374275</v>
       </c>
       <c r="E120" t="n">
-        <v>359.1232299804688</v>
+        <v>361.2666931152344</v>
       </c>
       <c r="F120" t="n">
-        <v>3964700</v>
+        <v>4324400</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B121" t="n">
-        <v>358.4185545746917</v>
+        <v>358.3402236370215</v>
       </c>
       <c r="C121" t="n">
-        <v>361.716939988571</v>
+        <v>359.1819648229422</v>
       </c>
       <c r="D121" t="n">
-        <v>353.8282109374275</v>
+        <v>351.5672851014027</v>
       </c>
       <c r="E121" t="n">
-        <v>361.2666931152344</v>
+        <v>353.9945678710938</v>
       </c>
       <c r="F121" t="n">
-        <v>4324400</v>
+        <v>4752200</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B122" t="n">
-        <v>358.3402236370215</v>
+        <v>349.9425535763344</v>
       </c>
       <c r="C122" t="n">
-        <v>359.1819648229422</v>
+        <v>351.8119711041206</v>
       </c>
       <c r="D122" t="n">
-        <v>351.5672851014027</v>
+        <v>345.714343142884</v>
       </c>
       <c r="E122" t="n">
-        <v>353.9945678710938</v>
+        <v>350.3144836425781</v>
       </c>
       <c r="F122" t="n">
-        <v>4752200</v>
+        <v>4167400</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B123" t="n">
-        <v>349.9425535763344</v>
+        <v>348.0437483770095</v>
       </c>
       <c r="C123" t="n">
-        <v>351.8119711041206</v>
+        <v>348.9148209517669</v>
       </c>
       <c r="D123" t="n">
-        <v>345.714343142884</v>
+        <v>338.2953999508869</v>
       </c>
       <c r="E123" t="n">
-        <v>350.3144836425781</v>
+        <v>346.0470886230469</v>
       </c>
       <c r="F123" t="n">
-        <v>4167400</v>
+        <v>4224500</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B124" t="n">
-        <v>348.0437483770095</v>
+        <v>345.5382004871225</v>
       </c>
       <c r="C124" t="n">
-        <v>348.9148209517669</v>
+        <v>353.9554635770335</v>
       </c>
       <c r="D124" t="n">
-        <v>338.2953999508869</v>
+        <v>343.5611046994417</v>
       </c>
       <c r="E124" t="n">
-        <v>346.0470886230469</v>
+        <v>349.5608520507812</v>
       </c>
       <c r="F124" t="n">
-        <v>4224500</v>
+        <v>3986000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B125" t="n">
-        <v>345.5382004871225</v>
+        <v>347.9067729324123</v>
       </c>
       <c r="C125" t="n">
-        <v>353.9554635770335</v>
+        <v>348.7485142053993</v>
       </c>
       <c r="D125" t="n">
-        <v>343.5611046994417</v>
+        <v>341.6916989868697</v>
       </c>
       <c r="E125" t="n">
-        <v>349.5608520507812</v>
+        <v>343.3849487304688</v>
       </c>
       <c r="F125" t="n">
-        <v>3986000</v>
+        <v>3197100</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,25 +3693,25 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B126" t="n">
-        <v>347.9067729324123</v>
+        <v>340.9512279608855</v>
       </c>
       <c r="C126" t="n">
-        <v>348.7485142053993</v>
+        <v>343.5425566286561</v>
       </c>
       <c r="D126" t="n">
-        <v>341.6916989868697</v>
+        <v>333.7191718320135</v>
       </c>
       <c r="E126" t="n">
-        <v>343.3849487304688</v>
+        <v>333.9457702636719</v>
       </c>
       <c r="F126" t="n">
-        <v>3197100</v>
+        <v>3893600</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -3719,25 +3719,25 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B127" t="n">
-        <v>340.9512279608855</v>
+        <v>336.6651978613972</v>
       </c>
       <c r="C127" t="n">
-        <v>343.5425566286561</v>
+        <v>338.3697677547303</v>
       </c>
       <c r="D127" t="n">
-        <v>333.7191718320135</v>
+        <v>333.0590172641502</v>
       </c>
       <c r="E127" t="n">
-        <v>333.9457702636719</v>
+        <v>334.0443115234375</v>
       </c>
       <c r="F127" t="n">
-        <v>3893600</v>
+        <v>2531900</v>
       </c>
       <c r="G127" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B128" t="n">
-        <v>336.6651978613972</v>
+        <v>337.4041886890553</v>
       </c>
       <c r="C128" t="n">
-        <v>338.3697677547303</v>
+        <v>340.1630007521627</v>
       </c>
       <c r="D128" t="n">
-        <v>333.0590172641502</v>
+        <v>335.6405034404279</v>
       </c>
       <c r="E128" t="n">
-        <v>334.0443115234375</v>
+        <v>337.5421142578125</v>
       </c>
       <c r="F128" t="n">
-        <v>2531900</v>
+        <v>3194400</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B129" t="n">
-        <v>337.4041886890553</v>
+        <v>339.81816704201</v>
       </c>
       <c r="C129" t="n">
-        <v>340.1630007521627</v>
+        <v>341.6803576413574</v>
       </c>
       <c r="D129" t="n">
-        <v>335.6405034404279</v>
+        <v>335.9262425125186</v>
       </c>
       <c r="E129" t="n">
-        <v>337.5421142578125</v>
+        <v>336.4090270996094</v>
       </c>
       <c r="F129" t="n">
-        <v>3194400</v>
+        <v>3075900</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B130" t="n">
-        <v>339.81816704201</v>
+        <v>333.6206668009991</v>
       </c>
       <c r="C130" t="n">
-        <v>341.6803576413574</v>
+        <v>334.8030019580219</v>
       </c>
       <c r="D130" t="n">
-        <v>335.9262425125186</v>
+        <v>325.2850851722408</v>
       </c>
       <c r="E130" t="n">
-        <v>336.4090270996094</v>
+        <v>326.0634460449219</v>
       </c>
       <c r="F130" t="n">
-        <v>3075900</v>
+        <v>3592200</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B131" t="n">
-        <v>333.6206668009991</v>
+        <v>324.1224241388957</v>
       </c>
       <c r="C131" t="n">
-        <v>334.8030019580219</v>
+        <v>325.3737672197113</v>
       </c>
       <c r="D131" t="n">
-        <v>325.2850851722408</v>
+        <v>319.8561127917808</v>
       </c>
       <c r="E131" t="n">
-        <v>326.0634460449219</v>
+        <v>323.3834533691406</v>
       </c>
       <c r="F131" t="n">
-        <v>3592200</v>
+        <v>3845400</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B132" t="n">
-        <v>324.1224241388957</v>
+        <v>322.9302020886868</v>
       </c>
       <c r="C132" t="n">
-        <v>325.3737672197113</v>
+        <v>325.3737427416146</v>
       </c>
       <c r="D132" t="n">
-        <v>319.8561127917808</v>
+        <v>315.5503575119392</v>
       </c>
       <c r="E132" t="n">
-        <v>323.3834533691406</v>
+        <v>316.0331420898438</v>
       </c>
       <c r="F132" t="n">
-        <v>3845400</v>
+        <v>9672200</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B133" t="n">
-        <v>322.9302020886868</v>
+        <v>327.1078416794463</v>
       </c>
       <c r="C133" t="n">
-        <v>325.3737427416146</v>
+        <v>329.7977059156196</v>
       </c>
       <c r="D133" t="n">
-        <v>315.5503575119392</v>
+        <v>323.3834304664039</v>
       </c>
       <c r="E133" t="n">
-        <v>316.0331420898438</v>
+        <v>326.0338745117188</v>
       </c>
       <c r="F133" t="n">
-        <v>9672200</v>
+        <v>5806300</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B134" t="n">
-        <v>327.1078416794463</v>
+        <v>321.1074278121778</v>
       </c>
       <c r="C134" t="n">
-        <v>329.7977059156196</v>
+        <v>327.6300717030042</v>
       </c>
       <c r="D134" t="n">
-        <v>323.3834304664039</v>
+        <v>318.2697752275627</v>
       </c>
       <c r="E134" t="n">
-        <v>326.0338745117188</v>
+        <v>326.0437622070312</v>
       </c>
       <c r="F134" t="n">
-        <v>5806300</v>
+        <v>4566400</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B135" t="n">
-        <v>321.1074278121778</v>
+        <v>330.0735818610078</v>
       </c>
       <c r="C135" t="n">
-        <v>327.6300717030042</v>
+        <v>332.2313787270356</v>
       </c>
       <c r="D135" t="n">
-        <v>318.2697752275627</v>
+        <v>322.1813651025556</v>
       </c>
       <c r="E135" t="n">
-        <v>326.0437622070312</v>
+        <v>327.6202087402344</v>
       </c>
       <c r="F135" t="n">
-        <v>4566400</v>
+        <v>4397800</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B136" t="n">
-        <v>330.0735818610078</v>
+        <v>326.5659345775528</v>
       </c>
       <c r="C136" t="n">
-        <v>332.2313787270356</v>
+        <v>329.2065159991698</v>
       </c>
       <c r="D136" t="n">
-        <v>322.1813651025556</v>
+        <v>321.7872513641968</v>
       </c>
       <c r="E136" t="n">
-        <v>327.6202087402344</v>
+        <v>323.6001892089844</v>
       </c>
       <c r="F136" t="n">
-        <v>4397800</v>
+        <v>3448400</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B137" t="n">
-        <v>326.5659345775528</v>
+        <v>322.6838998401017</v>
       </c>
       <c r="C137" t="n">
-        <v>329.2065159991698</v>
+        <v>322.7233200333912</v>
       </c>
       <c r="D137" t="n">
-        <v>321.7872513641968</v>
+        <v>316.0233004076466</v>
       </c>
       <c r="E137" t="n">
-        <v>323.6001892089844</v>
+        <v>316.919921875</v>
       </c>
       <c r="F137" t="n">
-        <v>3448400</v>
+        <v>3977400</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B138" t="n">
-        <v>322.6838998401017</v>
+        <v>320.9300608492875</v>
       </c>
       <c r="C138" t="n">
-        <v>322.7233200333912</v>
+        <v>323.1666680872671</v>
       </c>
       <c r="D138" t="n">
-        <v>316.0233004076466</v>
+        <v>317.8362223118503</v>
       </c>
       <c r="E138" t="n">
-        <v>316.919921875</v>
+        <v>318.7427062988281</v>
       </c>
       <c r="F138" t="n">
-        <v>3977400</v>
+        <v>4066000</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B139" t="n">
-        <v>320.9300608492875</v>
+        <v>323.6593250096307</v>
       </c>
       <c r="C139" t="n">
-        <v>323.1666680872671</v>
+        <v>326.5659553121756</v>
       </c>
       <c r="D139" t="n">
-        <v>317.8362223118503</v>
+        <v>318.6540430408731</v>
       </c>
       <c r="E139" t="n">
-        <v>318.7427062988281</v>
+        <v>324.053466796875</v>
       </c>
       <c r="F139" t="n">
-        <v>4066000</v>
+        <v>5749100</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B140" t="n">
-        <v>323.6593250096307</v>
+        <v>324.5264147036482</v>
       </c>
       <c r="C140" t="n">
-        <v>326.5659553121756</v>
+        <v>328.1917111081323</v>
       </c>
       <c r="D140" t="n">
-        <v>318.6540430408731</v>
+        <v>322.9893578310064</v>
       </c>
       <c r="E140" t="n">
-        <v>324.053466796875</v>
+        <v>324.713623046875</v>
       </c>
       <c r="F140" t="n">
-        <v>5749100</v>
+        <v>3386200</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B141" t="n">
-        <v>324.5264147036482</v>
+        <v>318.841238474905</v>
       </c>
       <c r="C141" t="n">
-        <v>328.1917111081323</v>
+        <v>321.5015150184395</v>
       </c>
       <c r="D141" t="n">
-        <v>322.9893578310064</v>
+        <v>313.9738822734865</v>
       </c>
       <c r="E141" t="n">
-        <v>324.713623046875</v>
+        <v>316.9002075195312</v>
       </c>
       <c r="F141" t="n">
-        <v>3386200</v>
+        <v>3732300</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B142" t="n">
-        <v>318.841238474905</v>
+        <v>314.9985972226668</v>
       </c>
       <c r="C142" t="n">
-        <v>321.5015150184395</v>
+        <v>321.875932137731</v>
       </c>
       <c r="D142" t="n">
-        <v>313.9738822734865</v>
+        <v>314.2300688775543</v>
       </c>
       <c r="E142" t="n">
-        <v>316.9002075195312</v>
+        <v>321.8463745117188</v>
       </c>
       <c r="F142" t="n">
-        <v>3732300</v>
+        <v>2448300</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B143" t="n">
-        <v>314.9985972226668</v>
+        <v>318.2500813990391</v>
       </c>
       <c r="C143" t="n">
-        <v>321.875932137731</v>
+        <v>319.6097924401727</v>
       </c>
       <c r="D143" t="n">
-        <v>314.2300688775543</v>
+        <v>310.673165290877</v>
       </c>
       <c r="E143" t="n">
-        <v>321.8463745117188</v>
+        <v>314.082275390625</v>
       </c>
       <c r="F143" t="n">
-        <v>2448300</v>
+        <v>4661600</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B144" t="n">
-        <v>318.2500813990391</v>
+        <v>328.3591748751156</v>
       </c>
       <c r="C144" t="n">
-        <v>319.6097924401727</v>
+        <v>333.7979883682909</v>
       </c>
       <c r="D144" t="n">
-        <v>310.673165290877</v>
+        <v>327.3640180499997</v>
       </c>
       <c r="E144" t="n">
-        <v>314.082275390625</v>
+        <v>331.2165222167969</v>
       </c>
       <c r="F144" t="n">
-        <v>4661600</v>
+        <v>4610600</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B145" t="n">
-        <v>328.3591748751156</v>
+        <v>326.388616523007</v>
       </c>
       <c r="C145" t="n">
-        <v>333.7979883682909</v>
+        <v>335.5617045306175</v>
       </c>
       <c r="D145" t="n">
-        <v>327.3640180499997</v>
+        <v>323.6199418005998</v>
       </c>
       <c r="E145" t="n">
-        <v>331.2165222167969</v>
+        <v>334.5862426757812</v>
       </c>
       <c r="F145" t="n">
-        <v>4610600</v>
+        <v>3002000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B146" t="n">
-        <v>326.388616523007</v>
+        <v>336.0248127567512</v>
       </c>
       <c r="C146" t="n">
-        <v>335.5617045306175</v>
+        <v>336.2120210994593</v>
       </c>
       <c r="D146" t="n">
-        <v>323.6199418005998</v>
+        <v>330.8717121868362</v>
       </c>
       <c r="E146" t="n">
-        <v>334.5862426757812</v>
+        <v>332.3792114257812</v>
       </c>
       <c r="F146" t="n">
-        <v>3002000</v>
+        <v>3208300</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B147" t="n">
-        <v>336.0248127567512</v>
+        <v>330.6056562428727</v>
       </c>
       <c r="C147" t="n">
-        <v>336.2120210994593</v>
+        <v>336.4188865710081</v>
       </c>
       <c r="D147" t="n">
-        <v>330.8717121868362</v>
+        <v>327.0487282012957</v>
       </c>
       <c r="E147" t="n">
-        <v>332.3792114257812</v>
+        <v>336.1430053710938</v>
       </c>
       <c r="F147" t="n">
-        <v>3208300</v>
+        <v>3741200</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B148" t="n">
-        <v>330.6056562428727</v>
+        <v>335.9853517224209</v>
       </c>
       <c r="C148" t="n">
-        <v>336.4188865710081</v>
+        <v>337.7194792888092</v>
       </c>
       <c r="D148" t="n">
-        <v>327.0487282012957</v>
+        <v>333.3644653118732</v>
       </c>
       <c r="E148" t="n">
-        <v>336.1430053710938</v>
+        <v>337.6701965332031</v>
       </c>
       <c r="F148" t="n">
-        <v>3741200</v>
+        <v>2882500</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B149" t="n">
-        <v>335.9853517224209</v>
+        <v>336.8228540004552</v>
       </c>
       <c r="C149" t="n">
-        <v>337.7194792888092</v>
+        <v>337.2366607575258</v>
       </c>
       <c r="D149" t="n">
-        <v>333.3644653118732</v>
+        <v>331.6697541162465</v>
       </c>
       <c r="E149" t="n">
-        <v>337.6701965332031</v>
+        <v>333.9260864257812</v>
       </c>
       <c r="F149" t="n">
-        <v>2882500</v>
+        <v>3365200</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B150" t="n">
-        <v>336.8228540004552</v>
+        <v>334.9902184465357</v>
       </c>
       <c r="C150" t="n">
-        <v>337.2366607575258</v>
+        <v>336.9509746615948</v>
       </c>
       <c r="D150" t="n">
-        <v>331.6697541162465</v>
+        <v>331.7387590995254</v>
       </c>
       <c r="E150" t="n">
-        <v>333.9260864257812</v>
+        <v>332.1919860839844</v>
       </c>
       <c r="F150" t="n">
-        <v>3365200</v>
+        <v>2856700</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B151" t="n">
-        <v>334.9902184465357</v>
+        <v>337.7983122720913</v>
       </c>
       <c r="C151" t="n">
-        <v>336.9509746615948</v>
+        <v>346.8433072133841</v>
       </c>
       <c r="D151" t="n">
-        <v>331.7387590995254</v>
+        <v>337.7983122720913</v>
       </c>
       <c r="E151" t="n">
-        <v>332.1919860839844</v>
+        <v>344.2618408203125</v>
       </c>
       <c r="F151" t="n">
-        <v>2856700</v>
+        <v>4930400</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B152" t="n">
-        <v>337.7983122720913</v>
+        <v>343.2174366312315</v>
       </c>
       <c r="C152" t="n">
-        <v>346.8433072133841</v>
+        <v>346.0058365319325</v>
       </c>
       <c r="D152" t="n">
-        <v>337.7983122720913</v>
+        <v>338.5668460102951</v>
       </c>
       <c r="E152" t="n">
-        <v>344.2618408203125</v>
+        <v>345.8284606933594</v>
       </c>
       <c r="F152" t="n">
-        <v>4930400</v>
+        <v>3260900</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B153" t="n">
-        <v>343.2174366312315</v>
+        <v>347.7399078982703</v>
       </c>
       <c r="C153" t="n">
-        <v>346.0058365319325</v>
+        <v>348.350785549426</v>
       </c>
       <c r="D153" t="n">
-        <v>338.5668460102951</v>
+        <v>337.9263851511736</v>
       </c>
       <c r="E153" t="n">
-        <v>345.8284606933594</v>
+        <v>338.8624267578125</v>
       </c>
       <c r="F153" t="n">
-        <v>3260900</v>
+        <v>3081000</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B154" t="n">
-        <v>347.7399078982703</v>
+        <v>338.8919874460811</v>
       </c>
       <c r="C154" t="n">
-        <v>348.350785549426</v>
+        <v>340.1629954470494</v>
       </c>
       <c r="D154" t="n">
-        <v>337.9263851511736</v>
+        <v>332.950664003466</v>
       </c>
       <c r="E154" t="n">
-        <v>338.8624267578125</v>
+        <v>334.5074157714844</v>
       </c>
       <c r="F154" t="n">
-        <v>3081000</v>
+        <v>2855800</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B155" t="n">
-        <v>338.8919874460811</v>
+        <v>334.5074474516935</v>
       </c>
       <c r="C155" t="n">
-        <v>340.1629954470494</v>
+        <v>335.81787576814</v>
       </c>
       <c r="D155" t="n">
-        <v>332.950664003466</v>
+        <v>331.9259809451064</v>
       </c>
       <c r="E155" t="n">
-        <v>334.5074157714844</v>
+        <v>335.1577453613281</v>
       </c>
       <c r="F155" t="n">
-        <v>2855800</v>
+        <v>2712400</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B156" t="n">
-        <v>334.5074474516935</v>
+        <v>332.9112571246521</v>
       </c>
       <c r="C156" t="n">
-        <v>335.81787576814</v>
+        <v>335.2660949665313</v>
       </c>
       <c r="D156" t="n">
-        <v>331.9259809451064</v>
+        <v>329.758303202367</v>
       </c>
       <c r="E156" t="n">
-        <v>335.1577453613281</v>
+        <v>330.9505310058594</v>
       </c>
       <c r="F156" t="n">
-        <v>2712400</v>
+        <v>3255900</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B157" t="n">
-        <v>332.9112571246521</v>
+        <v>329.5612640898174</v>
       </c>
       <c r="C157" t="n">
-        <v>335.2660949665313</v>
+        <v>332.4186116830558</v>
       </c>
       <c r="D157" t="n">
-        <v>329.758303202367</v>
+        <v>327.2556789255299</v>
       </c>
       <c r="E157" t="n">
-        <v>330.9505310058594</v>
+        <v>327.4132995605469</v>
       </c>
       <c r="F157" t="n">
-        <v>3255900</v>
+        <v>3282900</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B158" t="n">
-        <v>329.5612640898174</v>
+        <v>329.5316980954363</v>
       </c>
       <c r="C158" t="n">
-        <v>332.4186116830558</v>
+        <v>330.9899144482985</v>
       </c>
       <c r="D158" t="n">
-        <v>327.2556789255299</v>
+        <v>322.5459348903251</v>
       </c>
       <c r="E158" t="n">
-        <v>327.4132995605469</v>
+        <v>324.220947265625</v>
       </c>
       <c r="F158" t="n">
-        <v>3282900</v>
+        <v>4279300</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B159" t="n">
-        <v>329.5316980954363</v>
+        <v>320.8709611177203</v>
       </c>
       <c r="C159" t="n">
-        <v>330.9899144482985</v>
+        <v>321.0483068839262</v>
       </c>
       <c r="D159" t="n">
-        <v>322.5459348903251</v>
+        <v>314.3581498388285</v>
       </c>
       <c r="E159" t="n">
-        <v>324.220947265625</v>
+        <v>318.0628662109375</v>
       </c>
       <c r="F159" t="n">
-        <v>4279300</v>
+        <v>4150000</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B160" t="n">
-        <v>320.8709611177203</v>
+        <v>317.5012539357068</v>
       </c>
       <c r="C160" t="n">
-        <v>321.0483068839262</v>
+        <v>325.2653785233867</v>
       </c>
       <c r="D160" t="n">
-        <v>314.3581498388285</v>
+        <v>317.5012539357068</v>
       </c>
       <c r="E160" t="n">
-        <v>318.0628662109375</v>
+        <v>323.9647827148438</v>
       </c>
       <c r="F160" t="n">
-        <v>4150000</v>
+        <v>4317900</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B161" t="n">
-        <v>317.5012539357068</v>
+        <v>325.245658285994</v>
       </c>
       <c r="C161" t="n">
-        <v>325.2653785233867</v>
+        <v>325.6594650583568</v>
       </c>
       <c r="D161" t="n">
-        <v>317.5012539357068</v>
+        <v>318.6047541787617</v>
       </c>
       <c r="E161" t="n">
-        <v>323.9647827148438</v>
+        <v>319.1171264648438</v>
       </c>
       <c r="F161" t="n">
-        <v>4317900</v>
+        <v>3865300</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B162" t="n">
-        <v>325.245658285994</v>
+        <v>317.3435693878982</v>
       </c>
       <c r="C162" t="n">
-        <v>325.6594650583568</v>
+        <v>317.3435693878982</v>
       </c>
       <c r="D162" t="n">
-        <v>318.6047541787617</v>
+        <v>307.6680023826615</v>
       </c>
       <c r="E162" t="n">
-        <v>319.1171264648438</v>
+        <v>307.8256530761719</v>
       </c>
       <c r="F162" t="n">
-        <v>3865300</v>
+        <v>6396100</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B163" t="n">
-        <v>317.3435693878982</v>
+        <v>308.8011039225745</v>
       </c>
       <c r="C163" t="n">
-        <v>317.3435693878982</v>
+        <v>312.959047256485</v>
       </c>
       <c r="D163" t="n">
-        <v>307.6680023826615</v>
+        <v>305.8353583254913</v>
       </c>
       <c r="E163" t="n">
-        <v>307.8256530761719</v>
+        <v>310.7815551757812</v>
       </c>
       <c r="F163" t="n">
-        <v>6396100</v>
+        <v>6391400</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B164" t="n">
-        <v>308.8011039225745</v>
+        <v>317.2253492112466</v>
       </c>
       <c r="C164" t="n">
-        <v>312.959047256485</v>
+        <v>320.4571133614208</v>
       </c>
       <c r="D164" t="n">
-        <v>305.8353583254913</v>
+        <v>314.6537454823368</v>
       </c>
       <c r="E164" t="n">
-        <v>310.7815551757812</v>
+        <v>318.29931640625</v>
       </c>
       <c r="F164" t="n">
-        <v>6391400</v>
+        <v>5455900</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B165" t="n">
-        <v>317.2253492112466</v>
+        <v>320.2304978152761</v>
       </c>
       <c r="C165" t="n">
-        <v>320.4571133614208</v>
+        <v>322.6740083417755</v>
       </c>
       <c r="D165" t="n">
-        <v>314.6537454823368</v>
+        <v>317.6884217799922</v>
       </c>
       <c r="E165" t="n">
-        <v>318.29931640625</v>
+        <v>317.8953552246094</v>
       </c>
       <c r="F165" t="n">
-        <v>5455900</v>
+        <v>4411700</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B166" t="n">
-        <v>320.2304978152761</v>
+        <v>317.9347470211017</v>
       </c>
       <c r="C166" t="n">
-        <v>322.6740083417755</v>
+        <v>319.2353426707153</v>
       </c>
       <c r="D166" t="n">
-        <v>317.6884217799922</v>
+        <v>312.1412119171815</v>
       </c>
       <c r="E166" t="n">
-        <v>317.8953552246094</v>
+        <v>312.7816772460938</v>
       </c>
       <c r="F166" t="n">
-        <v>4411700</v>
+        <v>4995500</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B167" t="n">
-        <v>317.9347470211017</v>
+        <v>311.8456552875821</v>
       </c>
       <c r="C167" t="n">
-        <v>319.2353426707153</v>
+        <v>312.4565329608662</v>
       </c>
       <c r="D167" t="n">
-        <v>312.1412119171815</v>
+        <v>305.1554983709962</v>
       </c>
       <c r="E167" t="n">
-        <v>312.7816772460938</v>
+        <v>306.8206481933594</v>
       </c>
       <c r="F167" t="n">
-        <v>4995500</v>
+        <v>4335700</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B168" t="n">
-        <v>311.8456552875821</v>
+        <v>308.6237547613812</v>
       </c>
       <c r="C168" t="n">
-        <v>312.4565329608662</v>
+        <v>310.150948950067</v>
       </c>
       <c r="D168" t="n">
-        <v>305.1554983709962</v>
+        <v>304.5643168514869</v>
       </c>
       <c r="E168" t="n">
-        <v>306.8206481933594</v>
+        <v>305.8944702148438</v>
       </c>
       <c r="F168" t="n">
-        <v>4335700</v>
+        <v>4225700</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B169" t="n">
-        <v>308.6237547613812</v>
+        <v>303.0863866663159</v>
       </c>
       <c r="C169" t="n">
-        <v>310.150948950067</v>
+        <v>303.1652270544281</v>
       </c>
       <c r="D169" t="n">
-        <v>304.5643168514869</v>
+        <v>294.8690352302997</v>
       </c>
       <c r="E169" t="n">
-        <v>305.8944702148438</v>
+        <v>298.1007995605469</v>
       </c>
       <c r="F169" t="n">
-        <v>4225700</v>
+        <v>6307800</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B170" t="n">
-        <v>303.0863866663159</v>
+        <v>300.5739097413743</v>
       </c>
       <c r="C170" t="n">
-        <v>303.1652270544281</v>
+        <v>301.4803938271338</v>
       </c>
       <c r="D170" t="n">
-        <v>294.8690352302997</v>
+        <v>296.9874537315239</v>
       </c>
       <c r="E170" t="n">
-        <v>298.1007995605469</v>
+        <v>299.8743591308594</v>
       </c>
       <c r="F170" t="n">
-        <v>6307800</v>
+        <v>5072600</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B171" t="n">
-        <v>300.5739097413743</v>
+        <v>295.8937302385283</v>
       </c>
       <c r="C171" t="n">
-        <v>301.4803938271338</v>
+        <v>298.4751965058313</v>
       </c>
       <c r="D171" t="n">
-        <v>296.9874537315239</v>
+        <v>292.5141779899232</v>
       </c>
       <c r="E171" t="n">
-        <v>299.8743591308594</v>
+        <v>293.1349182128906</v>
       </c>
       <c r="F171" t="n">
-        <v>5072600</v>
+        <v>6121500</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B172" t="n">
-        <v>295.8937302385283</v>
+        <v>294.8493301065311</v>
       </c>
       <c r="C172" t="n">
-        <v>298.4751965058313</v>
+        <v>299.3127122467453</v>
       </c>
       <c r="D172" t="n">
-        <v>292.5141779899232</v>
+        <v>292.9279941234309</v>
       </c>
       <c r="E172" t="n">
-        <v>293.1349182128906</v>
+        <v>295.4010925292969</v>
       </c>
       <c r="F172" t="n">
-        <v>6121500</v>
+        <v>6366100</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B173" t="n">
-        <v>294.8493301065311</v>
+        <v>287.5778334831647</v>
       </c>
       <c r="C173" t="n">
-        <v>299.3127122467453</v>
+        <v>298.7313718247998</v>
       </c>
       <c r="D173" t="n">
-        <v>292.9279941234309</v>
+        <v>284.84857918279</v>
       </c>
       <c r="E173" t="n">
-        <v>295.4010925292969</v>
+        <v>297.9924011230469</v>
       </c>
       <c r="F173" t="n">
-        <v>6366100</v>
+        <v>8692500</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B174" t="n">
-        <v>287.5778334831647</v>
+        <v>296.6327042526405</v>
       </c>
       <c r="C174" t="n">
-        <v>298.7313718247998</v>
+        <v>306.4363947204983</v>
       </c>
       <c r="D174" t="n">
-        <v>284.84857918279</v>
+        <v>292.307277842878</v>
       </c>
       <c r="E174" t="n">
-        <v>297.9924011230469</v>
+        <v>306.0126953125</v>
       </c>
       <c r="F174" t="n">
-        <v>8692500</v>
+        <v>5810900</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B175" t="n">
-        <v>296.6327042526405</v>
+        <v>301.8547523557064</v>
       </c>
       <c r="C175" t="n">
-        <v>306.4363947204983</v>
+        <v>309.3725528012548</v>
       </c>
       <c r="D175" t="n">
-        <v>292.307277842878</v>
+        <v>299.9038888531578</v>
       </c>
       <c r="E175" t="n">
-        <v>306.0126953125</v>
+        <v>309.1656494140625</v>
       </c>
       <c r="F175" t="n">
-        <v>5810900</v>
+        <v>4516600</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B176" t="n">
-        <v>301.8547523557064</v>
+        <v>309.8750586089163</v>
       </c>
       <c r="C176" t="n">
-        <v>309.3725528012548</v>
+        <v>310.3282855694948</v>
       </c>
       <c r="D176" t="n">
-        <v>299.9038888531578</v>
+        <v>306.8797555054846</v>
       </c>
       <c r="E176" t="n">
-        <v>309.1656494140625</v>
+        <v>308.4660949707031</v>
       </c>
       <c r="F176" t="n">
-        <v>4516600</v>
+        <v>2963800</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B177" t="n">
-        <v>309.8750586089163</v>
+        <v>310.4268474452446</v>
       </c>
       <c r="C177" t="n">
-        <v>310.3282855694948</v>
+        <v>312.1314175610734</v>
       </c>
       <c r="D177" t="n">
-        <v>306.8797555054846</v>
+        <v>304.4165456653147</v>
       </c>
       <c r="E177" t="n">
-        <v>308.4660949707031</v>
+        <v>305.9733276367188</v>
       </c>
       <c r="F177" t="n">
-        <v>2963800</v>
+        <v>6978200</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B178" t="n">
-        <v>310.4268474452446</v>
+        <v>310.1213630819786</v>
       </c>
       <c r="C178" t="n">
-        <v>312.1314175610734</v>
+        <v>316.2794521026693</v>
       </c>
       <c r="D178" t="n">
-        <v>304.4165456653147</v>
+        <v>309.8849020855982</v>
       </c>
       <c r="E178" t="n">
-        <v>305.9733276367188</v>
+        <v>313.17578125</v>
       </c>
       <c r="F178" t="n">
-        <v>6978200</v>
+        <v>5990100</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B179" t="n">
-        <v>310.1213630819786</v>
+        <v>312.7817028577755</v>
       </c>
       <c r="C179" t="n">
-        <v>316.2794521026693</v>
+        <v>317.1465496037087</v>
       </c>
       <c r="D179" t="n">
-        <v>309.8849020855982</v>
+        <v>310.5253703811763</v>
       </c>
       <c r="E179" t="n">
-        <v>313.17578125</v>
+        <v>316.4863891601562</v>
       </c>
       <c r="F179" t="n">
-        <v>5990100</v>
+        <v>6818900</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B180" t="n">
-        <v>312.7817028577755</v>
+        <v>315.7671367684214</v>
       </c>
       <c r="C180" t="n">
-        <v>317.1465496037087</v>
+        <v>317.3633087672889</v>
       </c>
       <c r="D180" t="n">
-        <v>310.5253703811763</v>
+        <v>312.3383016854047</v>
       </c>
       <c r="E180" t="n">
-        <v>316.4863891601562</v>
+        <v>312.4762573242188</v>
       </c>
       <c r="F180" t="n">
-        <v>6818900</v>
+        <v>6963300</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B181" t="n">
-        <v>315.7671367684214</v>
+        <v>310.4958029229232</v>
       </c>
       <c r="C181" t="n">
-        <v>317.3633087672889</v>
+        <v>311.2446362258477</v>
       </c>
       <c r="D181" t="n">
-        <v>312.3383016854047</v>
+        <v>303.1652107990409</v>
       </c>
       <c r="E181" t="n">
-        <v>312.4762573242188</v>
+        <v>306.12109375</v>
       </c>
       <c r="F181" t="n">
-        <v>6963300</v>
+        <v>4544200</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B182" t="n">
-        <v>310.4958029229232</v>
+        <v>305.4215416998635</v>
       </c>
       <c r="C182" t="n">
-        <v>311.2446362258477</v>
+        <v>307.6088962755514</v>
       </c>
       <c r="D182" t="n">
-        <v>303.1652107990409</v>
+        <v>304.0322731114999</v>
       </c>
       <c r="E182" t="n">
-        <v>306.12109375</v>
+        <v>306.9388732910156</v>
       </c>
       <c r="F182" t="n">
-        <v>4544200</v>
+        <v>4310000</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B183" t="n">
-        <v>305.4215416998635</v>
+        <v>303.4115246580221</v>
       </c>
       <c r="C183" t="n">
-        <v>307.6088962755514</v>
+        <v>308.9094535404009</v>
       </c>
       <c r="D183" t="n">
-        <v>304.0322731114999</v>
+        <v>302.6035761274661</v>
       </c>
       <c r="E183" t="n">
-        <v>306.9388732910156</v>
+        <v>308.3675537109375</v>
       </c>
       <c r="F183" t="n">
-        <v>4310000</v>
+        <v>4328300</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,25 +5201,25 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B184" t="n">
-        <v>303.4115246580221</v>
+        <v>315.5049467263879</v>
       </c>
       <c r="C184" t="n">
-        <v>308.9094535404009</v>
+        <v>318.403599213189</v>
       </c>
       <c r="D184" t="n">
-        <v>302.6035761274661</v>
+        <v>305.8560507855353</v>
       </c>
       <c r="E184" t="n">
-        <v>308.3675537109375</v>
+        <v>307.6826171875</v>
       </c>
       <c r="F184" t="n">
-        <v>4328300</v>
+        <v>4558600</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5227,25 +5227,25 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B185" t="n">
-        <v>315.5049467263879</v>
+        <v>308.5561528759146</v>
       </c>
       <c r="C185" t="n">
-        <v>318.403599213189</v>
+        <v>311.7525986238699</v>
       </c>
       <c r="D185" t="n">
-        <v>305.8560507855353</v>
+        <v>306.3722648476684</v>
       </c>
       <c r="E185" t="n">
-        <v>307.6826171875</v>
+        <v>308.5065307617188</v>
       </c>
       <c r="F185" t="n">
-        <v>4558600</v>
+        <v>3946300</v>
       </c>
       <c r="G185" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B186" t="n">
-        <v>308.5561528759146</v>
+        <v>306.6204514929628</v>
       </c>
       <c r="C186" t="n">
-        <v>311.7525986238699</v>
+        <v>311.4746638676563</v>
       </c>
       <c r="D186" t="n">
-        <v>306.3722648476684</v>
+        <v>304.8236946299612</v>
       </c>
       <c r="E186" t="n">
-        <v>308.5065307617188</v>
+        <v>307.4443664550781</v>
       </c>
       <c r="F186" t="n">
-        <v>3946300</v>
+        <v>4381800</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B187" t="n">
-        <v>306.6204514929628</v>
+        <v>309.0723663566284</v>
       </c>
       <c r="C187" t="n">
-        <v>311.4746638676563</v>
+        <v>320.5279554969379</v>
       </c>
       <c r="D187" t="n">
-        <v>304.8236946299612</v>
+        <v>308.000249988811</v>
       </c>
       <c r="E187" t="n">
-        <v>307.4443664550781</v>
+        <v>318.9793395996094</v>
       </c>
       <c r="F187" t="n">
-        <v>4381800</v>
+        <v>4875300</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B188" t="n">
-        <v>309.0723663566284</v>
+        <v>320.9051596578416</v>
       </c>
       <c r="C188" t="n">
-        <v>320.5279554969379</v>
+        <v>321.6298303667879</v>
       </c>
       <c r="D188" t="n">
-        <v>308.000249988811</v>
+        <v>316.4678580086006</v>
       </c>
       <c r="E188" t="n">
-        <v>318.9793395996094</v>
+        <v>316.5870056152344</v>
       </c>
       <c r="F188" t="n">
-        <v>4875300</v>
+        <v>4823800</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B189" t="n">
-        <v>320.9051596578416</v>
+        <v>319.9323340788724</v>
       </c>
       <c r="C189" t="n">
-        <v>321.6298303667879</v>
+        <v>324.6376494749074</v>
       </c>
       <c r="D189" t="n">
-        <v>316.4678580086006</v>
+        <v>316.2196730066971</v>
       </c>
       <c r="E189" t="n">
-        <v>316.5870056152344</v>
+        <v>323.6251220703125</v>
       </c>
       <c r="F189" t="n">
-        <v>4823800</v>
+        <v>4656600</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B190" t="n">
-        <v>319.9323340788724</v>
+        <v>326.0969127055492</v>
       </c>
       <c r="C190" t="n">
-        <v>324.6376494749074</v>
+        <v>328.598467157331</v>
       </c>
       <c r="D190" t="n">
-        <v>316.2196730066971</v>
+        <v>322.9104034108394</v>
       </c>
       <c r="E190" t="n">
-        <v>323.6251220703125</v>
+        <v>325.9877319335938</v>
       </c>
       <c r="F190" t="n">
-        <v>4656600</v>
+        <v>3649000</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B191" t="n">
-        <v>326.0969127055492</v>
+        <v>331.3184370072605</v>
       </c>
       <c r="C191" t="n">
-        <v>328.598467157331</v>
+        <v>335.5274102103883</v>
       </c>
       <c r="D191" t="n">
-        <v>322.9104034108394</v>
+        <v>327.1293065910854</v>
       </c>
       <c r="E191" t="n">
-        <v>325.9877319335938</v>
+        <v>327.4072570800781</v>
       </c>
       <c r="F191" t="n">
-        <v>3649000</v>
+        <v>4695000</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B192" t="n">
-        <v>331.3184370072605</v>
+        <v>329.4819549089526</v>
       </c>
       <c r="C192" t="n">
-        <v>335.5274102103883</v>
+        <v>335.7954145326594</v>
       </c>
       <c r="D192" t="n">
-        <v>327.1293065910854</v>
+        <v>327.337752500619</v>
       </c>
       <c r="E192" t="n">
-        <v>327.4072570800781</v>
+        <v>334.6240539550781</v>
       </c>
       <c r="F192" t="n">
-        <v>4695000</v>
+        <v>5131500</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B193" t="n">
-        <v>329.4819549089526</v>
+        <v>333.5519799826949</v>
       </c>
       <c r="C193" t="n">
-        <v>335.7954145326594</v>
+        <v>338.6543633465824</v>
       </c>
       <c r="D193" t="n">
-        <v>327.337752500619</v>
+        <v>323.7839666314997</v>
       </c>
       <c r="E193" t="n">
-        <v>334.6240539550781</v>
+        <v>325.0843811035156</v>
       </c>
       <c r="F193" t="n">
-        <v>5131500</v>
+        <v>6085400</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B194" t="n">
-        <v>333.5519799826949</v>
+        <v>329.2735121638814</v>
       </c>
       <c r="C194" t="n">
-        <v>338.6543633465824</v>
+        <v>335.5472561594589</v>
       </c>
       <c r="D194" t="n">
-        <v>323.7839666314997</v>
+        <v>328.4793462633244</v>
       </c>
       <c r="E194" t="n">
-        <v>325.0843811035156</v>
+        <v>331.8346252441406</v>
       </c>
       <c r="F194" t="n">
-        <v>6085400</v>
+        <v>10604400</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B195" t="n">
-        <v>329.2735121638814</v>
+        <v>327.585930781475</v>
       </c>
       <c r="C195" t="n">
-        <v>335.5472561594589</v>
+        <v>329.30328611244</v>
       </c>
       <c r="D195" t="n">
-        <v>328.4793462633244</v>
+        <v>323.9527013683971</v>
       </c>
       <c r="E195" t="n">
-        <v>331.8346252441406</v>
+        <v>324.2306518554688</v>
       </c>
       <c r="F195" t="n">
-        <v>10604400</v>
+        <v>4713600</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B196" t="n">
-        <v>327.585930781475</v>
+        <v>321.5007640397083</v>
       </c>
       <c r="C196" t="n">
-        <v>329.30328611244</v>
+        <v>326.6130837898613</v>
       </c>
       <c r="D196" t="n">
-        <v>323.9527013683971</v>
+        <v>319.3466553723836</v>
       </c>
       <c r="E196" t="n">
-        <v>324.2306518554688</v>
+        <v>322.0765380859375</v>
       </c>
       <c r="F196" t="n">
-        <v>4713600</v>
+        <v>4788000</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B197" t="n">
-        <v>321.5007640397083</v>
+        <v>326.7123600579221</v>
       </c>
       <c r="C197" t="n">
-        <v>326.6130837898613</v>
+        <v>340.4511116799111</v>
       </c>
       <c r="D197" t="n">
-        <v>319.3466553723836</v>
+        <v>325.3126710965327</v>
       </c>
       <c r="E197" t="n">
-        <v>322.0765380859375</v>
+        <v>340.3518371582031</v>
       </c>
       <c r="F197" t="n">
-        <v>4788000</v>
+        <v>6385000</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B198" t="n">
-        <v>326.7123600579221</v>
+        <v>339.7463135650192</v>
       </c>
       <c r="C198" t="n">
-        <v>340.4511116799111</v>
+        <v>346.0895828723475</v>
       </c>
       <c r="D198" t="n">
-        <v>325.3126710965327</v>
+        <v>339.3194664460809</v>
       </c>
       <c r="E198" t="n">
-        <v>340.3518371582031</v>
+        <v>342.4761962890625</v>
       </c>
       <c r="F198" t="n">
-        <v>6385000</v>
+        <v>6974100</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B199" t="n">
-        <v>339.7463135650192</v>
+        <v>345.3549840981078</v>
       </c>
       <c r="C199" t="n">
-        <v>346.0895828723475</v>
+        <v>347.9359702501276</v>
       </c>
       <c r="D199" t="n">
-        <v>339.3194664460809</v>
+        <v>343.3199926808538</v>
       </c>
       <c r="E199" t="n">
-        <v>342.4761962890625</v>
+        <v>346.3079528808594</v>
       </c>
       <c r="F199" t="n">
-        <v>6974100</v>
+        <v>7771700</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B200" t="n">
-        <v>345.3549840981078</v>
+        <v>346.307966117321</v>
       </c>
       <c r="C200" t="n">
-        <v>347.9359702501276</v>
+        <v>348.779771593463</v>
       </c>
       <c r="D200" t="n">
-        <v>343.3199926808538</v>
+        <v>343.0122759730193</v>
       </c>
       <c r="E200" t="n">
-        <v>346.3079528808594</v>
+        <v>348.2437133789062</v>
       </c>
       <c r="F200" t="n">
-        <v>7771700</v>
+        <v>5786500</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B201" t="n">
-        <v>346.307966117321</v>
+        <v>348.1245733949154</v>
       </c>
       <c r="C201" t="n">
-        <v>348.779771593463</v>
+        <v>350.9140147662578</v>
       </c>
       <c r="D201" t="n">
-        <v>343.0122759730193</v>
+        <v>344.7593579765289</v>
       </c>
       <c r="E201" t="n">
-        <v>348.2437133789062</v>
+        <v>350.1000061035156</v>
       </c>
       <c r="F201" t="n">
-        <v>5786500</v>
+        <v>4579000</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B202" t="n">
-        <v>348.1245733949154</v>
+        <v>351.3905430525372</v>
       </c>
       <c r="C202" t="n">
-        <v>350.9140147662578</v>
+        <v>354.507557275585</v>
       </c>
       <c r="D202" t="n">
-        <v>344.7593579765289</v>
+        <v>348.2734985351562</v>
       </c>
       <c r="E202" t="n">
-        <v>350.1000061035156</v>
+        <v>348.2734985351562</v>
       </c>
       <c r="F202" t="n">
-        <v>4579000</v>
+        <v>4041300</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B203" t="n">
-        <v>351.3905430525372</v>
+        <v>350.2588479333682</v>
       </c>
       <c r="C203" t="n">
-        <v>354.507557275585</v>
+        <v>355.5697168646199</v>
       </c>
       <c r="D203" t="n">
-        <v>348.2734985351562</v>
+        <v>345.1068121812833</v>
       </c>
       <c r="E203" t="n">
-        <v>348.2734985351562</v>
+        <v>355.2818298339844</v>
       </c>
       <c r="F203" t="n">
-        <v>4041300</v>
+        <v>3110500</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B204" t="n">
-        <v>350.2588479333682</v>
+        <v>355.2024317145021</v>
       </c>
       <c r="C204" t="n">
-        <v>355.5697168646199</v>
+        <v>356.2248957008094</v>
       </c>
       <c r="D204" t="n">
-        <v>345.1068121812833</v>
+        <v>343.2703427329958</v>
       </c>
       <c r="E204" t="n">
-        <v>355.2818298339844</v>
+        <v>348.0848693847656</v>
       </c>
       <c r="F204" t="n">
-        <v>3110500</v>
+        <v>4460800</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B205" t="n">
-        <v>355.2024317145021</v>
+        <v>352.4626117928308</v>
       </c>
       <c r="C205" t="n">
-        <v>356.2248957008094</v>
+        <v>352.8199940223038</v>
       </c>
       <c r="D205" t="n">
-        <v>343.2703427329958</v>
+        <v>341.9600214541982</v>
       </c>
       <c r="E205" t="n">
-        <v>348.0848693847656</v>
+        <v>342.6846618652344</v>
       </c>
       <c r="F205" t="n">
-        <v>4460800</v>
+        <v>3592800</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B206" t="n">
-        <v>352.4626117928308</v>
+        <v>335.5174656966423</v>
       </c>
       <c r="C206" t="n">
-        <v>352.8199940223038</v>
+        <v>335.5174656966423</v>
       </c>
       <c r="D206" t="n">
-        <v>341.9600214541982</v>
+        <v>328.241100746865</v>
       </c>
       <c r="E206" t="n">
-        <v>342.6846618652344</v>
+        <v>333.75048828125</v>
       </c>
       <c r="F206" t="n">
-        <v>3592800</v>
+        <v>4192300</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B207" t="n">
-        <v>335.5174656966423</v>
+        <v>335.2891698936722</v>
       </c>
       <c r="C207" t="n">
-        <v>335.5174656966423</v>
+        <v>338.2374444527704</v>
       </c>
       <c r="D207" t="n">
-        <v>328.241100746865</v>
+        <v>333.1548737064404</v>
       </c>
       <c r="E207" t="n">
-        <v>333.75048828125</v>
+        <v>336.2520751953125</v>
       </c>
       <c r="F207" t="n">
-        <v>4192300</v>
+        <v>2780800</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B208" t="n">
-        <v>335.2891698936722</v>
+        <v>337.0660677396515</v>
       </c>
       <c r="C208" t="n">
-        <v>338.2374444527704</v>
+        <v>341.8805944502874</v>
       </c>
       <c r="D208" t="n">
-        <v>333.1548737064404</v>
+        <v>335.4281440922459</v>
       </c>
       <c r="E208" t="n">
-        <v>336.2520751953125</v>
+        <v>340.7886352539062</v>
       </c>
       <c r="F208" t="n">
-        <v>2780800</v>
+        <v>2748000</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B209" t="n">
-        <v>337.0660677396515</v>
+        <v>341.4835329455154</v>
       </c>
       <c r="C209" t="n">
-        <v>341.8805944502874</v>
+        <v>342.5853984087983</v>
       </c>
       <c r="D209" t="n">
-        <v>335.4281440922459</v>
+        <v>332.9762178919015</v>
       </c>
       <c r="E209" t="n">
-        <v>340.7886352539062</v>
+        <v>334.6439208984375</v>
       </c>
       <c r="F209" t="n">
-        <v>2748000</v>
+        <v>3650400</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B210" t="n">
-        <v>341.4835329455154</v>
+        <v>337.0362951640151</v>
       </c>
       <c r="C210" t="n">
-        <v>342.5853984087983</v>
+        <v>339.2499929294707</v>
       </c>
       <c r="D210" t="n">
-        <v>332.9762178919015</v>
+        <v>334.1078935040618</v>
       </c>
       <c r="E210" t="n">
-        <v>334.6439208984375</v>
+        <v>335.2693176269531</v>
       </c>
       <c r="F210" t="n">
-        <v>3650400</v>
+        <v>2807300</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B211" t="n">
-        <v>337.0362951640151</v>
+        <v>336.5101711499915</v>
       </c>
       <c r="C211" t="n">
-        <v>339.2499929294707</v>
+        <v>343.7170716460562</v>
       </c>
       <c r="D211" t="n">
-        <v>334.1078935040618</v>
+        <v>334.7928460359882</v>
       </c>
       <c r="E211" t="n">
-        <v>335.2693176269531</v>
+        <v>338.9422607421875</v>
       </c>
       <c r="F211" t="n">
-        <v>2807300</v>
+        <v>3953100</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B212" t="n">
-        <v>336.5101711499915</v>
+        <v>339.0514198724459</v>
       </c>
       <c r="C212" t="n">
-        <v>343.7170716460562</v>
+        <v>348.2436891486228</v>
       </c>
       <c r="D212" t="n">
-        <v>334.7928460359882</v>
+        <v>338.148103527179</v>
       </c>
       <c r="E212" t="n">
-        <v>338.9422607421875</v>
+        <v>345.4740905761719</v>
       </c>
       <c r="F212" t="n">
-        <v>3953100</v>
+        <v>3810300</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B213" t="n">
-        <v>339.0514198724459</v>
+        <v>346.3774576909258</v>
       </c>
       <c r="C213" t="n">
-        <v>348.2436891486228</v>
+        <v>351.3905334952897</v>
       </c>
       <c r="D213" t="n">
-        <v>338.148103527179</v>
+        <v>335.6167594084301</v>
       </c>
       <c r="E213" t="n">
-        <v>345.4740905761719</v>
+        <v>336.3910522460938</v>
       </c>
       <c r="F213" t="n">
-        <v>3810300</v>
+        <v>4434000</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B214" t="n">
-        <v>346.3774576909258</v>
+        <v>337.4829959680537</v>
       </c>
       <c r="C214" t="n">
-        <v>351.3905334952897</v>
+        <v>337.7113243396537</v>
       </c>
       <c r="D214" t="n">
-        <v>335.6167594084301</v>
+        <v>328.985617931225</v>
       </c>
       <c r="E214" t="n">
-        <v>336.3910522460938</v>
+        <v>330.6036987304688</v>
       </c>
       <c r="F214" t="n">
-        <v>4434000</v>
+        <v>4125300</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B215" t="n">
-        <v>337.4829959680537</v>
+        <v>328.8764012920007</v>
       </c>
       <c r="C215" t="n">
-        <v>337.7113243396537</v>
+        <v>330.5639772575944</v>
       </c>
       <c r="D215" t="n">
-        <v>328.985617931225</v>
+        <v>324.6078695592594</v>
       </c>
       <c r="E215" t="n">
-        <v>330.6036987304688</v>
+        <v>329.1742248535156</v>
       </c>
       <c r="F215" t="n">
-        <v>4125300</v>
+        <v>3112600</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B216" t="n">
-        <v>328.8764012920007</v>
+        <v>331.0901002710247</v>
       </c>
       <c r="C216" t="n">
-        <v>330.5639772575944</v>
+        <v>334.097933459434</v>
       </c>
       <c r="D216" t="n">
-        <v>324.6078695592594</v>
+        <v>328.2907223705125</v>
       </c>
       <c r="E216" t="n">
-        <v>329.1742248535156</v>
+        <v>329.0253295898438</v>
       </c>
       <c r="F216" t="n">
-        <v>3112600</v>
+        <v>2907700</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B217" t="n">
-        <v>331.0901002710247</v>
+        <v>322.9203055541834</v>
       </c>
       <c r="C217" t="n">
-        <v>334.097933459434</v>
+        <v>325.8288946116248</v>
       </c>
       <c r="D217" t="n">
-        <v>328.2907223705125</v>
+        <v>320.6867650845805</v>
       </c>
       <c r="E217" t="n">
-        <v>329.0253295898438</v>
+        <v>322.3346252441406</v>
       </c>
       <c r="F217" t="n">
-        <v>2907700</v>
+        <v>4523100</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B218" t="n">
-        <v>322.9203055541834</v>
+        <v>322.6920194034342</v>
       </c>
       <c r="C218" t="n">
-        <v>325.8288946116248</v>
+        <v>331.0206281983068</v>
       </c>
       <c r="D218" t="n">
-        <v>320.6867650845805</v>
+        <v>320.8654832094117</v>
       </c>
       <c r="E218" t="n">
-        <v>322.3346252441406</v>
+        <v>330.5441589355469</v>
       </c>
       <c r="F218" t="n">
-        <v>4523100</v>
+        <v>3874500</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B219" t="n">
-        <v>322.6920194034342</v>
+        <v>336.9072556737336</v>
       </c>
       <c r="C219" t="n">
-        <v>331.0206281983068</v>
+        <v>339.3889672822994</v>
       </c>
       <c r="D219" t="n">
-        <v>320.8654832094117</v>
+        <v>332.8968012318786</v>
       </c>
       <c r="E219" t="n">
-        <v>330.5441589355469</v>
+        <v>333.6313781738281</v>
       </c>
       <c r="F219" t="n">
-        <v>3874500</v>
+        <v>3622400</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B220" t="n">
-        <v>336.9072556737336</v>
+        <v>340.133473711892</v>
       </c>
       <c r="C220" t="n">
-        <v>339.3889672822994</v>
+        <v>346.8737804890717</v>
       </c>
       <c r="D220" t="n">
-        <v>332.8968012318786</v>
+        <v>340.0937578445657</v>
       </c>
       <c r="E220" t="n">
-        <v>333.6313781738281</v>
+        <v>341.9500732421875</v>
       </c>
       <c r="F220" t="n">
-        <v>3622400</v>
+        <v>4308000</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B221" t="n">
-        <v>340.133473711892</v>
+        <v>337.8900211320969</v>
       </c>
       <c r="C221" t="n">
-        <v>346.8737804890717</v>
+        <v>342.7442335347337</v>
       </c>
       <c r="D221" t="n">
-        <v>340.0937578445657</v>
+        <v>334.495026147691</v>
       </c>
       <c r="E221" t="n">
-        <v>341.9500732421875</v>
+        <v>335.7954406738281</v>
       </c>
       <c r="F221" t="n">
-        <v>4308000</v>
+        <v>4028500</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B222" t="n">
-        <v>337.8900211320969</v>
+        <v>332.5394250801792</v>
       </c>
       <c r="C222" t="n">
-        <v>342.7442335347337</v>
+        <v>333.2343164610006</v>
       </c>
       <c r="D222" t="n">
-        <v>334.495026147691</v>
+        <v>327.8341094785939</v>
       </c>
       <c r="E222" t="n">
-        <v>335.7954406738281</v>
+        <v>330.9114379882812</v>
       </c>
       <c r="F222" t="n">
-        <v>4028500</v>
+        <v>6275400</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B223" t="n">
-        <v>332.5394250801792</v>
+        <v>330.0080852280822</v>
       </c>
       <c r="C223" t="n">
-        <v>333.2343164610006</v>
+        <v>331.5566708480175</v>
       </c>
       <c r="D223" t="n">
-        <v>327.8341094785939</v>
+        <v>326.3946985853459</v>
       </c>
       <c r="E223" t="n">
-        <v>330.9114379882812</v>
+        <v>329.5315856933594</v>
       </c>
       <c r="F223" t="n">
-        <v>6275400</v>
+        <v>4961900</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B224" t="n">
-        <v>330.0080852280822</v>
+        <v>337.3142314565633</v>
       </c>
       <c r="C224" t="n">
-        <v>331.5566708480175</v>
+        <v>341.126167165973</v>
       </c>
       <c r="D224" t="n">
-        <v>326.3946985853459</v>
+        <v>331.2787221229386</v>
       </c>
       <c r="E224" t="n">
-        <v>329.5315856933594</v>
+        <v>337.5326232910156</v>
       </c>
       <c r="F224" t="n">
-        <v>4961900</v>
+        <v>2908100</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B225" t="n">
-        <v>337.3142314565633</v>
+        <v>337.741121159039</v>
       </c>
       <c r="C225" t="n">
-        <v>341.126167165973</v>
+        <v>348.2933339094608</v>
       </c>
       <c r="D225" t="n">
-        <v>331.2787221229386</v>
+        <v>336.8675537894677</v>
       </c>
       <c r="E225" t="n">
-        <v>337.5326232910156</v>
+        <v>345.6925048828125</v>
       </c>
       <c r="F225" t="n">
-        <v>2908100</v>
+        <v>4275000</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B226" t="n">
-        <v>337.741121159039</v>
+        <v>347.5984599855233</v>
       </c>
       <c r="C226" t="n">
-        <v>348.2933339094608</v>
+        <v>351.9563298372728</v>
       </c>
       <c r="D226" t="n">
-        <v>336.8675537894677</v>
+        <v>345.6031541488199</v>
       </c>
       <c r="E226" t="n">
-        <v>345.6925048828125</v>
+        <v>350.5566711425781</v>
       </c>
       <c r="F226" t="n">
-        <v>4275000</v>
+        <v>3140400</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B227" t="n">
-        <v>347.5984599855233</v>
+        <v>350.9140306560572</v>
       </c>
       <c r="C227" t="n">
-        <v>351.9563298372728</v>
+        <v>350.9636527717977</v>
       </c>
       <c r="D227" t="n">
-        <v>345.6031541488199</v>
+        <v>344.967859180145</v>
       </c>
       <c r="E227" t="n">
-        <v>350.5566711425781</v>
+        <v>346.963134765625</v>
       </c>
       <c r="F227" t="n">
-        <v>3140400</v>
+        <v>2622400</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B228" t="n">
-        <v>350.9140306560572</v>
+        <v>348.9386046403958</v>
       </c>
       <c r="C228" t="n">
-        <v>350.9636527717977</v>
+        <v>354.219664160909</v>
       </c>
       <c r="D228" t="n">
-        <v>344.967859180145</v>
+        <v>346.1888486641563</v>
       </c>
       <c r="E228" t="n">
-        <v>346.963134765625</v>
+        <v>353.0185241699219</v>
       </c>
       <c r="F228" t="n">
-        <v>2622400</v>
+        <v>3584800</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B229" t="n">
-        <v>348.9386046403958</v>
+        <v>349.524279261052</v>
       </c>
       <c r="C229" t="n">
-        <v>354.219664160909</v>
+        <v>351.4103740800161</v>
       </c>
       <c r="D229" t="n">
-        <v>346.1888486641563</v>
+        <v>344.5211400290252</v>
       </c>
       <c r="E229" t="n">
-        <v>353.0185241699219</v>
+        <v>348.2139282226562</v>
       </c>
       <c r="F229" t="n">
-        <v>3584800</v>
+        <v>3124800</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B230" t="n">
-        <v>349.524279261052</v>
+        <v>349.7128894956296</v>
       </c>
       <c r="C230" t="n">
-        <v>351.4103740800161</v>
+        <v>355.7384623950411</v>
       </c>
       <c r="D230" t="n">
-        <v>344.5211400290252</v>
+        <v>348.0352499864083</v>
       </c>
       <c r="E230" t="n">
-        <v>348.2139282226562</v>
+        <v>351.8868713378906</v>
       </c>
       <c r="F230" t="n">
-        <v>3124800</v>
+        <v>2549700</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B231" t="n">
-        <v>349.7128894956296</v>
+        <v>349.4250091127092</v>
       </c>
       <c r="C231" t="n">
-        <v>355.7384623950411</v>
+        <v>351.2813246265272</v>
       </c>
       <c r="D231" t="n">
-        <v>348.0352499864083</v>
+        <v>340.5206262766717</v>
       </c>
       <c r="E231" t="n">
-        <v>351.8868713378906</v>
+        <v>340.9176940917969</v>
       </c>
       <c r="F231" t="n">
-        <v>2549700</v>
+        <v>3965800</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B232" t="n">
-        <v>349.4250091127092</v>
+        <v>344.4615642861647</v>
       </c>
       <c r="C232" t="n">
-        <v>351.2813246265272</v>
+        <v>345.206077753642</v>
       </c>
       <c r="D232" t="n">
-        <v>340.5206262766717</v>
+        <v>338.0190507751135</v>
       </c>
       <c r="E232" t="n">
-        <v>340.9176940917969</v>
+        <v>339.2003479003906</v>
       </c>
       <c r="F232" t="n">
-        <v>3965800</v>
+        <v>2439900</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B233" t="n">
-        <v>344.4615642861647</v>
+        <v>338.3168506868042</v>
       </c>
       <c r="C233" t="n">
-        <v>345.206077753642</v>
+        <v>338.3168506868042</v>
       </c>
       <c r="D233" t="n">
-        <v>338.0190507751135</v>
+        <v>333.5519765191293</v>
       </c>
       <c r="E233" t="n">
-        <v>339.2003479003906</v>
+        <v>336.381103515625</v>
       </c>
       <c r="F233" t="n">
-        <v>2439900</v>
+        <v>3073100</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B234" t="n">
-        <v>338.3168506868042</v>
+        <v>332.2614710050206</v>
       </c>
       <c r="C234" t="n">
-        <v>338.3168506868042</v>
+        <v>336.9568803095206</v>
       </c>
       <c r="D234" t="n">
-        <v>333.5519765191293</v>
+        <v>330.4548079641576</v>
       </c>
       <c r="E234" t="n">
-        <v>336.381103515625</v>
+        <v>335.4082946777344</v>
       </c>
       <c r="F234" t="n">
-        <v>3073100</v>
+        <v>5580000</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B235" t="n">
-        <v>332.2614710050206</v>
+        <v>334.3163510292147</v>
       </c>
       <c r="C235" t="n">
-        <v>336.9568803095206</v>
+        <v>342.0195939717831</v>
       </c>
       <c r="D235" t="n">
-        <v>330.4548079641576</v>
+        <v>328.2709048600699</v>
       </c>
       <c r="E235" t="n">
-        <v>335.4082946777344</v>
+        <v>335.0211486816406</v>
       </c>
       <c r="F235" t="n">
-        <v>5580000</v>
+        <v>6603400</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B236" t="n">
-        <v>334.3163510292147</v>
+        <v>338.9224047058033</v>
       </c>
       <c r="C236" t="n">
-        <v>342.0195939717831</v>
+        <v>347.8366934263856</v>
       </c>
       <c r="D236" t="n">
-        <v>328.2709048600699</v>
+        <v>338.9224047058033</v>
       </c>
       <c r="E236" t="n">
-        <v>335.0211486816406</v>
+        <v>341.7813110351562</v>
       </c>
       <c r="F236" t="n">
-        <v>6603400</v>
+        <v>4971000</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B237" t="n">
-        <v>338.9224047058033</v>
+        <v>333.542054389882</v>
       </c>
       <c r="C237" t="n">
-        <v>347.8366934263856</v>
+        <v>336.4009911317456</v>
       </c>
       <c r="D237" t="n">
-        <v>338.9224047058033</v>
+        <v>329.1643112906949</v>
       </c>
       <c r="E237" t="n">
-        <v>341.7813110351562</v>
+        <v>332.0430908203125</v>
       </c>
       <c r="F237" t="n">
-        <v>4971000</v>
+        <v>4027700</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B238" t="n">
-        <v>333.542054389882</v>
+        <v>334.0582233645888</v>
       </c>
       <c r="C238" t="n">
-        <v>336.4009911317456</v>
+        <v>336.1031512946537</v>
       </c>
       <c r="D238" t="n">
-        <v>329.1643112906949</v>
+        <v>330.5639843459303</v>
       </c>
       <c r="E238" t="n">
-        <v>332.0430908203125</v>
+        <v>333.1548767089844</v>
       </c>
       <c r="F238" t="n">
-        <v>4027700</v>
+        <v>3422800</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B239" t="n">
-        <v>334.0582233645888</v>
+        <v>333.4229292601251</v>
       </c>
       <c r="C239" t="n">
-        <v>336.1031512946537</v>
+        <v>339.7165463845368</v>
       </c>
       <c r="D239" t="n">
-        <v>330.5639843459303</v>
+        <v>332.7081950914107</v>
       </c>
       <c r="E239" t="n">
-        <v>333.1548767089844</v>
+        <v>334.9615783691406</v>
       </c>
       <c r="F239" t="n">
-        <v>3422800</v>
+        <v>3298600</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B240" t="n">
-        <v>333.4229292601251</v>
+        <v>336.8873851133212</v>
       </c>
       <c r="C240" t="n">
-        <v>339.7165463845368</v>
+        <v>337.0065024243307</v>
       </c>
       <c r="D240" t="n">
-        <v>332.7081950914107</v>
+        <v>331.2588801078031</v>
       </c>
       <c r="E240" t="n">
-        <v>334.9615783691406</v>
+        <v>335.4082946777344</v>
       </c>
       <c r="F240" t="n">
-        <v>3298600</v>
+        <v>2528100</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B241" t="n">
-        <v>336.8873851133212</v>
+        <v>336.9469338983794</v>
       </c>
       <c r="C241" t="n">
-        <v>337.0065024243307</v>
+        <v>336.9568704387829</v>
       </c>
       <c r="D241" t="n">
-        <v>331.2588801078031</v>
+        <v>332.0629425240725</v>
       </c>
       <c r="E241" t="n">
-        <v>335.4082946777344</v>
+        <v>332.4004516601562</v>
       </c>
       <c r="F241" t="n">
-        <v>2528100</v>
+        <v>4258100</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B242" t="n">
-        <v>336.9469338983794</v>
+        <v>328.1517689125653</v>
       </c>
       <c r="C242" t="n">
-        <v>336.9568704387829</v>
+        <v>329.5812372185705</v>
       </c>
       <c r="D242" t="n">
-        <v>332.0629425240725</v>
+        <v>325.4814448058147</v>
       </c>
       <c r="E242" t="n">
-        <v>332.4004516601562</v>
+        <v>326.2060852050781</v>
       </c>
       <c r="F242" t="n">
-        <v>4258100</v>
+        <v>3618000</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B243" t="n">
-        <v>328.1517689125653</v>
+        <v>328.0822659405567</v>
       </c>
       <c r="C243" t="n">
-        <v>329.5812372185705</v>
+        <v>329.1841313242223</v>
       </c>
       <c r="D243" t="n">
-        <v>325.4814448058147</v>
+        <v>325.1042120893565</v>
       </c>
       <c r="E243" t="n">
-        <v>326.2060852050781</v>
+        <v>327.7745361328125</v>
       </c>
       <c r="F243" t="n">
-        <v>3618000</v>
+        <v>3136100</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B244" t="n">
-        <v>328.0822659405567</v>
+        <v>325.838797551875</v>
       </c>
       <c r="C244" t="n">
-        <v>329.1841313242223</v>
+        <v>326.8414187355763</v>
       </c>
       <c r="D244" t="n">
-        <v>325.1042120893565</v>
+        <v>323.3670224847805</v>
       </c>
       <c r="E244" t="n">
-        <v>327.7745361328125</v>
+        <v>325.4317932128906</v>
       </c>
       <c r="F244" t="n">
-        <v>3136100</v>
+        <v>3858700</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B245" t="n">
-        <v>325.838797551875</v>
+        <v>323.6251283531417</v>
       </c>
       <c r="C245" t="n">
-        <v>326.8414187355763</v>
+        <v>324.439106732169</v>
       </c>
       <c r="D245" t="n">
-        <v>323.3670224847805</v>
+        <v>316.4678503051231</v>
       </c>
       <c r="E245" t="n">
-        <v>325.4317932128906</v>
+        <v>317.4307556152344</v>
       </c>
       <c r="F245" t="n">
-        <v>3858700</v>
+        <v>3291000</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B246" t="n">
-        <v>323.6251283531417</v>
+        <v>319.1481100391916</v>
       </c>
       <c r="C246" t="n">
-        <v>324.439106732169</v>
+        <v>319.813222073911</v>
       </c>
       <c r="D246" t="n">
-        <v>316.4678503051231</v>
+        <v>315.3858267914646</v>
       </c>
       <c r="E246" t="n">
-        <v>317.4307556152344</v>
+        <v>316.1799926757812</v>
       </c>
       <c r="F246" t="n">
-        <v>3291000</v>
+        <v>3499300</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,25 +6839,25 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B247" t="n">
-        <v>319.1481100391916</v>
+        <v>318.2099914550781</v>
       </c>
       <c r="C247" t="n">
-        <v>319.813222073911</v>
+        <v>320.4400024414062</v>
       </c>
       <c r="D247" t="n">
-        <v>315.3858267914646</v>
+        <v>315.2099914550781</v>
       </c>
       <c r="E247" t="n">
-        <v>316.1799926757812</v>
+        <v>318.0700073242188</v>
       </c>
       <c r="F247" t="n">
-        <v>3499300</v>
+        <v>3377700</v>
       </c>
       <c r="G247" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -6865,25 +6865,25 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B248" t="n">
-        <v>318.2099914550781</v>
+        <v>316.7000122070312</v>
       </c>
       <c r="C248" t="n">
-        <v>320.4400024414062</v>
+        <v>321.7999877929688</v>
       </c>
       <c r="D248" t="n">
-        <v>315.2099914550781</v>
+        <v>316.1000061035156</v>
       </c>
       <c r="E248" t="n">
-        <v>318.0700073242188</v>
+        <v>321.0499877929688</v>
       </c>
       <c r="F248" t="n">
-        <v>3377700</v>
+        <v>2261000</v>
       </c>
       <c r="G248" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B249" t="n">
-        <v>316.7000122070312</v>
+        <v>320.7300109863281</v>
       </c>
       <c r="C249" t="n">
-        <v>321.7999877929688</v>
+        <v>321.5</v>
       </c>
       <c r="D249" t="n">
-        <v>316.1000061035156</v>
+        <v>313.239990234375</v>
       </c>
       <c r="E249" t="n">
-        <v>321.0499877929688</v>
+        <v>313.7000122070312</v>
       </c>
       <c r="F249" t="n">
-        <v>2261000</v>
+        <v>5655700</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B250" t="n">
-        <v>320.7300109863281</v>
+        <v>310.4700012207031</v>
       </c>
       <c r="C250" t="n">
-        <v>321.5</v>
+        <v>313.3900146484375</v>
       </c>
       <c r="D250" t="n">
-        <v>313.239990234375</v>
+        <v>309.8399963378906</v>
       </c>
       <c r="E250" t="n">
-        <v>313.7000122070312</v>
+        <v>310.4500122070312</v>
       </c>
       <c r="F250" t="n">
-        <v>5655700</v>
+        <v>3611700</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B251" t="n">
-        <v>310.4700012207031</v>
+        <v>308.1300048828125</v>
       </c>
       <c r="C251" t="n">
-        <v>313.3900146484375</v>
+        <v>308.2799987792969</v>
       </c>
       <c r="D251" t="n">
-        <v>309.8399963378906</v>
+        <v>304.2999877929688</v>
       </c>
       <c r="E251" t="n">
-        <v>310.4500122070312</v>
+        <v>305.6900024414062</v>
       </c>
       <c r="F251" t="n">
-        <v>3611700</v>
+        <v>4493800</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B252" t="n">
-        <v>308.1300048828125</v>
+        <v>309.0899963378906</v>
       </c>
       <c r="C252" t="n">
-        <v>308.2799987792969</v>
+        <v>311.2099914550781</v>
       </c>
       <c r="D252" t="n">
-        <v>304.2999877929688</v>
+        <v>307.8999938964844</v>
       </c>
       <c r="E252" t="n">
-        <v>305.6900024414062</v>
+        <v>308.739990234375</v>
       </c>
       <c r="F252" t="n">
-        <v>4482300</v>
+        <v>3488800</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10594,37 +10594,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>308.74</v>
+      </c>
+      <c r="D2" t="n">
         <v>305.69</v>
       </c>
-      <c r="D2" t="n">
-        <v>310.45</v>
-      </c>
       <c r="E2" t="n">
-        <v>308.13</v>
+        <v>309.09</v>
       </c>
       <c r="F2" t="n">
-        <v>308.28</v>
+        <v>311.21</v>
       </c>
       <c r="G2" t="n">
-        <v>304.3</v>
+        <v>307.9</v>
       </c>
       <c r="H2" t="n">
-        <v>4307096</v>
+        <v>3214823</v>
       </c>
       <c r="I2" t="n">
-        <v>4190704</v>
+        <v>4185495</v>
       </c>
       <c r="J2" t="n">
-        <v>304983736320</v>
+        <v>308026671104</v>
       </c>
       <c r="K2" t="n">
-        <v>21.74182</v>
+        <v>21.605318</v>
       </c>
       <c r="L2" t="n">
-        <v>19.076057</v>
+        <v>19.266388</v>
       </c>
       <c r="M2" t="n">
-        <v>14.06</v>
+        <v>14.28</v>
       </c>
       <c r="N2" t="n">
         <v>426.75</v>
@@ -10636,7 +10636,7 @@
         <v>0.955</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="R2" t="n">
         <v>0.08409999999999999</v>
@@ -10660,7 +10660,7 @@
         <v>16.65</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.35976</v>
+        <v>18.542942</v>
       </c>
       <c r="Z2" t="n">
         <v>0.046</v>
@@ -10672,7 +10672,7 @@
         <v>169176006656</v>
       </c>
       <c r="AC2" t="n">
-        <v>366086750208</v>
+        <v>369129684992</v>
       </c>
       <c r="AD2" t="n">
         <v>24647999488</v>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-11 19:03:26</t>
+          <t>2026-09-12 21:47:28</t>
         </is>
       </c>
     </row>
